--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -1815,13 +1815,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46169.502150949076</v>
+        <v>46169.66881761574</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.70470055555</v>
+        <v>46175.87136722222</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.704711956016</v>
+        <v>46175.87137862269</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1868,13 +1868,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46169.502275844905</v>
+        <v>46169.66894251158</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.7046774537</v>
+        <v>46175.87134412037</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.70470079861</v>
+        <v>46175.87136746528</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1931,13 +1931,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46169.50227936343</v>
+        <v>46169.66894603009</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.70467826389</v>
+        <v>46175.87134493055</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.70470105324</v>
+        <v>46175.87136771991</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1994,13 +1994,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="9">
-        <v>46169.50228355324</v>
+        <v>46169.66895021991</v>
       </c>
       <c r="C7" s="9">
-        <v>46175.70467869213</v>
+        <v>46175.8713453588</v>
       </c>
       <c r="D7" s="9">
-        <v>46175.70470082176</v>
+        <v>46175.87136748843</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>37</v>
@@ -2057,13 +2057,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46169.502286620365</v>
+        <v>46169.66895328704</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.704679131944</v>
+        <v>46175.871345798616</v>
       </c>
       <c r="D8" s="5">
-        <v>46175.70470079861</v>
+        <v>46175.87136746528</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -2120,13 +2120,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="9">
-        <v>46169.50229052083</v>
+        <v>46169.6689571875</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.704679745366</v>
+        <v>46175.87134641204</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.70470199074</v>
+        <v>46175.871368657405</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>44</v>
@@ -2183,11 +2183,11 @@
         <v>46</v>
       </c>
       <c r="B10" s="5">
-        <v>46169.50215484954</v>
+        <v>46169.6688215162</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46169.50239</v>
+        <v>46169.669056666666</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -2230,11 +2230,11 @@
         <v>49</v>
       </c>
       <c r="B11" s="9">
-        <v>46169.50229400463</v>
+        <v>46169.6689606713</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="9">
-        <v>46175.70470412037</v>
+        <v>46175.871370787034</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>50</v>
@@ -2293,11 +2293,11 @@
         <v>55</v>
       </c>
       <c r="B12" s="5">
-        <v>46169.50229908565</v>
+        <v>46169.66896575232</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46174.65451085648</v>
+        <v>46174.82117752315</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -2356,11 +2356,11 @@
         <v>62</v>
       </c>
       <c r="B13" s="9">
-        <v>46169.502305</v>
+        <v>46169.668971666666</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="9">
-        <v>46174.65497377315</v>
+        <v>46174.82164043981</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>63</v>
@@ -2407,11 +2407,11 @@
         <v>64</v>
       </c>
       <c r="B14" s="5">
-        <v>46169.50215916667</v>
+        <v>46169.66882583333</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46181.47012082176</v>
+        <v>46181.63678748843</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>65</v>
@@ -2454,13 +2454,13 @@
         <v>67</v>
       </c>
       <c r="B15" s="9">
-        <v>46169.502324189816</v>
+        <v>46169.66899085648</v>
       </c>
       <c r="C15" s="9">
-        <v>46181.470113981486</v>
+        <v>46181.63678064814</v>
       </c>
       <c r="D15" s="9">
-        <v>46181.47013244213</v>
+        <v>46181.6367991088</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>68</v>
@@ -2519,13 +2519,13 @@
         <v>73</v>
       </c>
       <c r="B16" s="5">
-        <v>46169.50232951389</v>
+        <v>46169.66899618055</v>
       </c>
       <c r="C16" s="5">
-        <v>46181.47007760417</v>
+        <v>46181.63674427083</v>
       </c>
       <c r="D16" s="5">
-        <v>46181.47009415509</v>
+        <v>46181.636760821755</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>74</v>
@@ -2584,13 +2584,13 @@
         <v>77</v>
       </c>
       <c r="B17" s="9">
-        <v>46169.502335439814</v>
+        <v>46169.669002106486</v>
       </c>
       <c r="C17" s="9">
-        <v>46181.47008326389</v>
+        <v>46181.636749930556</v>
       </c>
       <c r="D17" s="9">
-        <v>46181.47009837963</v>
+        <v>46181.63676504629</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>78</v>
@@ -2649,11 +2649,11 @@
         <v>80</v>
       </c>
       <c r="B18" s="5">
-        <v>46169.50234162037</v>
+        <v>46169.669008287034</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46181.4701337963</v>
+        <v>46181.63680046296</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>81</v>
@@ -2712,11 +2712,11 @@
         <v>84</v>
       </c>
       <c r="B19" s="9">
-        <v>46169.50216334491</v>
+        <v>46169.66883001158</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46181.47017875</v>
+        <v>46181.636845416666</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>85</v>
@@ -2759,13 +2759,13 @@
         <v>87</v>
       </c>
       <c r="B20" s="5">
-        <v>46169.502349386574</v>
+        <v>46169.669016053245</v>
       </c>
       <c r="C20" s="5">
-        <v>46181.4701584838</v>
+        <v>46181.63682515046</v>
       </c>
       <c r="D20" s="5">
-        <v>46181.47017395833</v>
+        <v>46181.636840625</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>88</v>
@@ -2824,13 +2824,13 @@
         <v>90</v>
       </c>
       <c r="B21" s="9">
-        <v>46169.50235475694</v>
+        <v>46169.669021423615</v>
       </c>
       <c r="C21" s="9">
-        <v>46181.470163645834</v>
+        <v>46181.6368303125</v>
       </c>
       <c r="D21" s="9">
-        <v>46181.47018055555</v>
+        <v>46181.636847222224</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>91</v>
@@ -2889,13 +2889,13 @@
         <v>93</v>
       </c>
       <c r="B22" s="5">
-        <v>46169.50236013889</v>
+        <v>46169.66902680555</v>
       </c>
       <c r="C22" s="5">
-        <v>46181.470173194444</v>
+        <v>46181.63683986111</v>
       </c>
       <c r="D22" s="5">
-        <v>46181.47018822917</v>
+        <v>46181.636854895834</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>94</v>
@@ -2954,11 +2954,11 @@
         <v>97</v>
       </c>
       <c r="B23" s="9">
-        <v>46169.502365671295</v>
+        <v>46169.66903233796</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46174.65856804398</v>
+        <v>46174.825234710646</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>98</v>
@@ -3017,11 +3017,11 @@
         <v>103</v>
       </c>
       <c r="B24" s="5">
-        <v>46169.502370625</v>
+        <v>46169.669037291664</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46174.65856519676</v>
+        <v>46174.825231863426</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>104</v>
@@ -3080,11 +3080,11 @@
         <v>106</v>
       </c>
       <c r="B25" s="9">
-        <v>46169.50237457176</v>
+        <v>46169.66904123843</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46174.65856241898</v>
+        <v>46174.82522908565</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>107</v>
@@ -3143,11 +3143,11 @@
         <v>109</v>
       </c>
       <c r="B26" s="5">
-        <v>46169.50237844908</v>
+        <v>46169.66904511574</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46174.65855821759</v>
+        <v>46174.82522488426</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>110</v>
@@ -3206,11 +3206,11 @@
         <v>112</v>
       </c>
       <c r="B27" s="9">
-        <v>46169.50238211805</v>
+        <v>46169.66904878472</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46174.65838040509</v>
+        <v>46174.82504707176</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>113</v>
@@ -3269,11 +3269,11 @@
         <v>115</v>
       </c>
       <c r="B28" s="5">
-        <v>46169.50216752315</v>
+        <v>46169.66883418981</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46182.46799320602</v>
+        <v>46182.63465987268</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>116</v>
@@ -3316,13 +3316,13 @@
         <v>118</v>
       </c>
       <c r="B29" s="9">
-        <v>46169.50242258102</v>
+        <v>46169.66908924768</v>
       </c>
       <c r="C29" s="9">
-        <v>46182.46798378472</v>
+        <v>46182.63465045139</v>
       </c>
       <c r="D29" s="9">
-        <v>46182.46799741898</v>
+        <v>46182.63466408565</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>119</v>
@@ -3381,13 +3381,13 @@
         <v>123</v>
       </c>
       <c r="B30" s="5">
-        <v>46169.502428541666</v>
+        <v>46169.66909520833</v>
       </c>
       <c r="C30" s="5">
-        <v>46182.465695266204</v>
+        <v>46182.63236193287</v>
       </c>
       <c r="D30" s="5">
-        <v>46182.4656965625</v>
+        <v>46182.63236322917</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>124</v>
@@ -3442,13 +3442,13 @@
         <v>126</v>
       </c>
       <c r="B31" s="9">
-        <v>46169.50243414352</v>
+        <v>46169.669100810184</v>
       </c>
       <c r="C31" s="9">
-        <v>46182.467969143516</v>
+        <v>46182.63463581019</v>
       </c>
       <c r="D31" s="9">
-        <v>46182.46797055556</v>
+        <v>46182.63463722222</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>127</v>
@@ -3503,13 +3503,13 @@
         <v>129</v>
       </c>
       <c r="B32" s="5">
-        <v>46169.50243961805</v>
+        <v>46169.669106284724</v>
       </c>
       <c r="C32" s="5">
-        <v>46182.46792015046</v>
+        <v>46182.634586817134</v>
       </c>
       <c r="D32" s="5">
-        <v>46182.467933761574</v>
+        <v>46182.63460042824</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>130</v>
@@ -3568,13 +3568,13 @@
         <v>133</v>
       </c>
       <c r="B33" s="9">
-        <v>46169.502444618054</v>
+        <v>46169.66911128472</v>
       </c>
       <c r="C33" s="9">
-        <v>46182.46514231482</v>
+        <v>46182.63180898148</v>
       </c>
       <c r="D33" s="9">
-        <v>46182.465144270835</v>
+        <v>46182.6318109375</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>134</v>
@@ -3629,13 +3629,13 @@
         <v>136</v>
       </c>
       <c r="B34" s="5">
-        <v>46169.50245013888</v>
+        <v>46169.669116805555</v>
       </c>
       <c r="C34" s="5">
-        <v>46182.46790510417</v>
+        <v>46182.63457177083</v>
       </c>
       <c r="D34" s="5">
-        <v>46182.4679066088</v>
+        <v>46182.63457327546</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>137</v>
@@ -3690,13 +3690,13 @@
         <v>139</v>
       </c>
       <c r="B35" s="9">
-        <v>46169.502455381946</v>
+        <v>46169.66912204861</v>
       </c>
       <c r="C35" s="9">
-        <v>46182.467756805556</v>
+        <v>46182.63442347222</v>
       </c>
       <c r="D35" s="9">
-        <v>46182.467768912036</v>
+        <v>46182.6344355787</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>140</v>
@@ -3755,13 +3755,13 @@
         <v>142</v>
       </c>
       <c r="B36" s="5">
-        <v>46169.50246045139</v>
+        <v>46169.66912711806</v>
       </c>
       <c r="C36" s="5">
-        <v>46182.46537144676</v>
+        <v>46182.63203811343</v>
       </c>
       <c r="D36" s="5">
-        <v>46182.46537292824</v>
+        <v>46182.63203959491</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>143</v>
@@ -3816,13 +3816,13 @@
         <v>145</v>
       </c>
       <c r="B37" s="9">
-        <v>46169.50246604167</v>
+        <v>46169.66913270833</v>
       </c>
       <c r="C37" s="9">
-        <v>46182.46774303241</v>
+        <v>46182.63440969907</v>
       </c>
       <c r="D37" s="9">
-        <v>46182.46774453703</v>
+        <v>46182.634411203704</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>146</v>
@@ -3877,13 +3877,13 @@
         <v>148</v>
       </c>
       <c r="B38" s="5">
-        <v>46169.502471423606</v>
+        <v>46169.66913809028</v>
       </c>
       <c r="C38" s="5">
-        <v>46182.46768396991</v>
+        <v>46182.634350636574</v>
       </c>
       <c r="D38" s="5">
-        <v>46182.46768619213</v>
+        <v>46182.6343528588</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>149</v>
@@ -3938,11 +3938,11 @@
         <v>151</v>
       </c>
       <c r="B39" s="9">
-        <v>46169.502478090275</v>
+        <v>46169.66914475695</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46174.67585670139</v>
+        <v>46174.84252336806</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>152</v>
@@ -4001,11 +4001,11 @@
         <v>154</v>
       </c>
       <c r="B40" s="5">
-        <v>46169.50248260416</v>
+        <v>46169.669149270834</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46174.67582052083</v>
+        <v>46174.8424871875</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>114</v>
@@ -4054,11 +4054,11 @@
         <v>156</v>
       </c>
       <c r="B41" s="9">
-        <v>46169.502487418984</v>
+        <v>46169.66915408565</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46174.675817650466</v>
+        <v>46174.84248431713</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>157</v>
@@ -4107,11 +4107,11 @@
         <v>159</v>
       </c>
       <c r="B42" s="5">
-        <v>46169.502491990745</v>
+        <v>46169.66915865741</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46174.6759772338</v>
+        <v>46174.84264390046</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>160</v>
@@ -4170,11 +4170,11 @@
         <v>164</v>
       </c>
       <c r="B43" s="9">
-        <v>46169.502497106485</v>
+        <v>46169.66916377315</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46174.67593440972</v>
+        <v>46174.842601076394</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>165</v>
@@ -4229,11 +4229,11 @@
         <v>167</v>
       </c>
       <c r="B44" s="5">
-        <v>46169.50250293982</v>
+        <v>46169.66916960648</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46174.67593158565</v>
+        <v>46174.84259825232</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>168</v>
@@ -4288,11 +4288,11 @@
         <v>170</v>
       </c>
       <c r="B45" s="9">
-        <v>46169.50250836805</v>
+        <v>46169.66917503472</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46174.676139664356</v>
+        <v>46174.84280633102</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>171</v>
@@ -4351,11 +4351,11 @@
         <v>173</v>
       </c>
       <c r="B46" s="5">
-        <v>46169.50251222222</v>
+        <v>46169.669178888886</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46174.67610978009</v>
+        <v>46174.84277644676</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>105</v>
@@ -4404,11 +4404,11 @@
         <v>175</v>
       </c>
       <c r="B47" s="9">
-        <v>46169.50251701389</v>
+        <v>46169.669183680555</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46174.67610671296</v>
+        <v>46174.84277337963</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>176</v>
@@ -4457,11 +4457,11 @@
         <v>178</v>
       </c>
       <c r="B48" s="5">
-        <v>46169.502521828705</v>
+        <v>46169.66918849537</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46174.67640329861</v>
+        <v>46174.84306996528</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>179</v>
@@ -4520,11 +4520,11 @@
         <v>183</v>
       </c>
       <c r="B49" s="9">
-        <v>46169.502525856486</v>
+        <v>46169.66919252315</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46174.676313194446</v>
+        <v>46174.84297986111</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>111</v>
@@ -4573,11 +4573,11 @@
         <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46169.502530682876</v>
+        <v>46169.66919734953</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46174.67631048612</v>
+        <v>46174.84297715277</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>186</v>
@@ -4626,11 +4626,11 @@
         <v>188</v>
       </c>
       <c r="B51" s="9">
-        <v>46169.502535625</v>
+        <v>46169.66920229167</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46174.67634989583</v>
+        <v>46174.8430165625</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>189</v>
@@ -4679,11 +4679,11 @@
         <v>192</v>
       </c>
       <c r="B52" s="5">
-        <v>46169.5025753588</v>
+        <v>46169.66924202546</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46174.676543379624</v>
+        <v>46174.843210046296</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>193</v>
@@ -4742,11 +4742,11 @@
         <v>195</v>
       </c>
       <c r="B53" s="9">
-        <v>46169.5025796875</v>
+        <v>46169.66924635417</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46174.67649615741</v>
+        <v>46174.84316282407</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>108</v>
@@ -4795,11 +4795,11 @@
         <v>197</v>
       </c>
       <c r="B54" s="5">
-        <v>46169.50258424769</v>
+        <v>46169.66925091435</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46174.67649322917</v>
+        <v>46174.843159895834</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>198</v>
@@ -4848,11 +4848,11 @@
         <v>200</v>
       </c>
       <c r="B55" s="9">
-        <v>46169.502588993055</v>
+        <v>46169.669255659726</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46169.63901155093</v>
+        <v>46169.80567821759</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>201</v>
@@ -4895,11 +4895,11 @@
         <v>203</v>
       </c>
       <c r="B56" s="5">
-        <v>46169.50259230324</v>
+        <v>46169.66925896991</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46185.00557653935</v>
+        <v>46185.17224320602</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>204</v>
@@ -4958,11 +4958,11 @@
         <v>208</v>
       </c>
       <c r="B57" s="9">
-        <v>46169.50259741898</v>
+        <v>46169.66926408565</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46181.47009364583</v>
+        <v>46181.636760312496</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>209</v>
@@ -5011,11 +5011,11 @@
         <v>211</v>
       </c>
       <c r="B58" s="5">
-        <v>46169.502602858796</v>
+        <v>46169.66926952546</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46181.4700921412</v>
+        <v>46181.63675880787</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>212</v>
@@ -5064,11 +5064,11 @@
         <v>214</v>
       </c>
       <c r="B59" s="9">
-        <v>46169.50262597222</v>
+        <v>46169.66929263889</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46174.67989615741</v>
+        <v>46174.846562824074</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>215</v>
@@ -5127,11 +5127,11 @@
         <v>217</v>
       </c>
       <c r="B60" s="5">
-        <v>46169.50263108796</v>
+        <v>46169.66929775463</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46185.0048759375</v>
+        <v>46185.17154260416</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>209</v>
@@ -5180,11 +5180,11 @@
         <v>220</v>
       </c>
       <c r="B61" s="9">
-        <v>46169.5026369213</v>
+        <v>46169.66930358796</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46185.00487226852</v>
+        <v>46185.17153893519</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>212</v>
@@ -5233,11 +5233,11 @@
         <v>223</v>
       </c>
       <c r="B62" s="5">
-        <v>46169.50266038194</v>
+        <v>46169.669327048614</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46174.67989291667</v>
+        <v>46174.84655958333</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>101</v>
@@ -5296,11 +5296,11 @@
         <v>225</v>
       </c>
       <c r="B63" s="9">
-        <v>46169.50267328703</v>
+        <v>46169.6693399537</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46174.68018414352</v>
+        <v>46174.84685081019</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>209</v>
@@ -5349,11 +5349,11 @@
         <v>226</v>
       </c>
       <c r="B64" s="5">
-        <v>46169.5026777662</v>
+        <v>46169.66934443287</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46174.68018079861</v>
+        <v>46174.84684746528</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>212</v>
@@ -5402,11 +5402,11 @@
         <v>227</v>
       </c>
       <c r="B65" s="9">
-        <v>46169.502694537034</v>
+        <v>46169.669361203705</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46174.67994138889</v>
+        <v>46174.84660805555</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>228</v>
@@ -5465,11 +5465,11 @@
         <v>231</v>
       </c>
       <c r="B66" s="5">
-        <v>46169.502698344906</v>
+        <v>46169.66936501158</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46174.680252754624</v>
+        <v>46174.846919421296</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>209</v>
@@ -5518,11 +5518,11 @@
         <v>233</v>
       </c>
       <c r="B67" s="9">
-        <v>46169.5027514699</v>
+        <v>46169.669418136575</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46170.42657998843</v>
+        <v>46170.59324665509</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>234</v>
@@ -5565,11 +5565,11 @@
         <v>236</v>
       </c>
       <c r="B68" s="5">
-        <v>46169.50276018518</v>
+        <v>46169.66942685185</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46174.68034853009</v>
+        <v>46174.84701519676</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>237</v>
@@ -5628,11 +5628,11 @@
         <v>241</v>
       </c>
       <c r="B69" s="9">
-        <v>46169.502765694444</v>
+        <v>46169.669432361115</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46174.68049690972</v>
+        <v>46174.847163576385</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>242</v>
@@ -5691,11 +5691,11 @@
         <v>245</v>
       </c>
       <c r="B70" s="5">
-        <v>46169.50277170139</v>
+        <v>46169.66943836806</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46174.68034577546</v>
+        <v>46174.84701244213</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>246</v>
@@ -5754,11 +5754,11 @@
         <v>248</v>
       </c>
       <c r="B71" s="9">
-        <v>46169.50277702547</v>
+        <v>46169.669443692124</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46174.6804941088</v>
+        <v>46174.84716077546</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>249</v>
@@ -5817,11 +5817,11 @@
         <v>251</v>
       </c>
       <c r="B72" s="5">
-        <v>46169.50278170139</v>
+        <v>46169.669448368055</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46174.680341493055</v>
+        <v>46174.84700815972</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>252</v>
@@ -5880,11 +5880,11 @@
         <v>254</v>
       </c>
       <c r="B73" s="9">
-        <v>46169.50278631944</v>
+        <v>46169.66945298611</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46174.68049027778</v>
+        <v>46174.847156944445</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>253</v>
@@ -5943,11 +5943,11 @@
         <v>255</v>
       </c>
       <c r="B74" s="5">
-        <v>46169.502791122686</v>
+        <v>46169.66945778935</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46170.46087596065</v>
+        <v>46170.62754262731</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>256</v>
@@ -5990,11 +5990,11 @@
         <v>258</v>
       </c>
       <c r="B75" s="9">
-        <v>46169.502794375</v>
+        <v>46169.66946104167</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46174.680633703705</v>
+        <v>46174.84730037037</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>259</v>
@@ -6053,11 +6053,11 @@
         <v>263</v>
       </c>
       <c r="B76" s="5">
-        <v>46169.50280061342</v>
+        <v>46169.669467280095</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46174.68059793982</v>
+        <v>46174.84726460648</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>209</v>
@@ -6106,11 +6106,11 @@
         <v>266</v>
       </c>
       <c r="B77" s="9">
-        <v>46169.50280682871</v>
+        <v>46169.66947349537</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46174.68059503472</v>
+        <v>46174.84726170139</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>267</v>
@@ -6159,11 +6159,11 @@
         <v>269</v>
       </c>
       <c r="B78" s="5">
-        <v>46169.50283622685</v>
+        <v>46169.66950289352</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46174.68077684028</v>
+        <v>46174.847443506944</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>270</v>
@@ -6222,11 +6222,11 @@
         <v>271</v>
       </c>
       <c r="B79" s="9">
-        <v>46169.502840914356</v>
+        <v>46169.66950758102</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46174.68074872685</v>
+        <v>46174.84741539352</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>209</v>
@@ -6275,11 +6275,11 @@
         <v>274</v>
       </c>
       <c r="B80" s="5">
-        <v>46169.502846979165</v>
+        <v>46169.66951364583</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46174.68074489583</v>
+        <v>46174.8474115625</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>212</v>
@@ -6328,11 +6328,11 @@
         <v>277</v>
       </c>
       <c r="B81" s="9">
-        <v>46169.5028671412</v>
+        <v>46169.66953380787</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46174.680936944445</v>
+        <v>46174.84760361111</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>278</v>
@@ -6391,11 +6391,11 @@
         <v>279</v>
       </c>
       <c r="B82" s="5">
-        <v>46169.502871874996</v>
+        <v>46169.66953854167</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46174.68085709491</v>
+        <v>46174.84752376158</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>209</v>
@@ -6442,11 +6442,11 @@
         <v>281</v>
       </c>
       <c r="B83" s="9">
-        <v>46169.5028775463</v>
+        <v>46169.669544212964</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46174.680854398146</v>
+        <v>46174.84752106482</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>212</v>
@@ -6493,11 +6493,11 @@
         <v>284</v>
       </c>
       <c r="B84" s="5">
-        <v>46169.502934421296</v>
+        <v>46169.66960108797</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46171.51944895834</v>
+        <v>46171.686115625</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>234</v>
@@ -6540,11 +6540,11 @@
         <v>286</v>
       </c>
       <c r="B85" s="9">
-        <v>46169.50294289352</v>
+        <v>46169.66960956018</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46182.46792298611</v>
+        <v>46182.63458965278</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>287</v>
@@ -6603,11 +6603,11 @@
         <v>289</v>
       </c>
       <c r="B86" s="5">
-        <v>46169.50294984954</v>
+        <v>46169.6696165162</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46182.46798901621</v>
+        <v>46182.63465568287</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>290</v>
@@ -6666,11 +6666,11 @@
         <v>292</v>
       </c>
       <c r="B87" s="9">
-        <v>46169.50295627315</v>
+        <v>46169.669622939815</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46182.46776100695</v>
+        <v>46182.63442767361</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>293</v>
@@ -6729,11 +6729,11 @@
         <v>294</v>
       </c>
       <c r="B88" s="5">
-        <v>46169.502963136576</v>
+        <v>46169.66962980324</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46174.681127800926</v>
+        <v>46174.8477944676</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>295</v>
@@ -6792,11 +6792,11 @@
         <v>297</v>
       </c>
       <c r="B89" s="9">
-        <v>46169.502968518515</v>
+        <v>46169.669635185186</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46174.68112206018</v>
+        <v>46174.84778872685</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>59</v>
@@ -6855,11 +6855,11 @@
         <v>299</v>
       </c>
       <c r="B90" s="5">
-        <v>46169.50298123843</v>
+        <v>46169.66964790509</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46171.54782046296</v>
+        <v>46171.71448712963</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>300</v>
@@ -6902,11 +6902,11 @@
         <v>302</v>
       </c>
       <c r="B91" s="9">
-        <v>46169.50298443287</v>
+        <v>46169.66965109954</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46174.68123428241</v>
+        <v>46174.84790094907</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>303</v>
@@ -6965,11 +6965,11 @@
         <v>305</v>
       </c>
       <c r="B92" s="5">
-        <v>46169.50299016204</v>
+        <v>46169.6696568287</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46174.681321724536</v>
+        <v>46174.84798839121</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>209</v>
@@ -7018,11 +7018,11 @@
         <v>307</v>
       </c>
       <c r="B93" s="9">
-        <v>46169.503021956014</v>
+        <v>46169.669688622685</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46174.681230891205</v>
+        <v>46174.84789755787</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>308</v>
@@ -7081,11 +7081,11 @@
         <v>309</v>
       </c>
       <c r="B94" s="5">
-        <v>46169.503026805556</v>
+        <v>46169.66969347223</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46174.68137046296</v>
+        <v>46174.84803712963</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>209</v>
@@ -7132,11 +7132,11 @@
         <v>312</v>
       </c>
       <c r="B95" s="9">
-        <v>46169.50306015046</v>
+        <v>46169.66972681713</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46174.68122747685</v>
+        <v>46174.84789414352</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>313</v>
@@ -7195,11 +7195,11 @@
         <v>314</v>
       </c>
       <c r="B96" s="5">
-        <v>46169.50306513889</v>
+        <v>46169.66973180555</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46174.68141462963</v>
+        <v>46174.848081296295</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>209</v>
@@ -7248,11 +7248,11 @@
         <v>317</v>
       </c>
       <c r="B97" s="9">
-        <v>46169.503143877315</v>
+        <v>46169.66981054399</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46174.68122427083</v>
+        <v>46174.8478909375</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>318</v>
@@ -7311,11 +7311,11 @@
         <v>319</v>
       </c>
       <c r="B98" s="5">
-        <v>46169.503150578705</v>
+        <v>46169.66981724537</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46174.681461851855</v>
+        <v>46174.84812851852</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>209</v>
@@ -7364,11 +7364,11 @@
         <v>322</v>
       </c>
       <c r="B99" s="9">
-        <v>46169.503194375</v>
+        <v>46169.669861041664</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46174.68121953704</v>
+        <v>46174.8478862037</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>323</v>
@@ -7427,11 +7427,11 @@
         <v>324</v>
       </c>
       <c r="B100" s="5">
-        <v>46169.50320057871</v>
+        <v>46169.66986724537</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46174.68150009259</v>
+        <v>46174.84816675926</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>209</v>
@@ -7480,11 +7480,11 @@
         <v>326</v>
       </c>
       <c r="B101" s="9">
-        <v>46169.503236296296</v>
+        <v>46169.66990296297</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46174.681218784724</v>
+        <v>46174.84788545139</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>327</v>
@@ -7543,11 +7543,11 @@
         <v>329</v>
       </c>
       <c r="B102" s="5">
-        <v>46169.50327888889</v>
+        <v>46169.66994555556</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46174.68160265047</v>
+        <v>46174.848269317125</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>209</v>
@@ -7594,11 +7594,11 @@
         <v>331</v>
       </c>
       <c r="B103" s="9">
-        <v>46169.50331197916</v>
+        <v>46169.669978645834</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46174.65735081019</v>
+        <v>46174.82401747685</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>332</v>
@@ -7641,11 +7641,11 @@
         <v>334</v>
       </c>
       <c r="B104" s="5">
-        <v>46169.503315775466</v>
+        <v>46169.66998244213</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46174.68176847222</v>
+        <v>46174.84843513889</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>335</v>
@@ -7704,11 +7704,11 @@
         <v>339</v>
       </c>
       <c r="B105" s="9">
-        <v>46169.503323275465</v>
+        <v>46169.66998994213</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46174.681721712965</v>
+        <v>46174.84838837963</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>209</v>
@@ -7755,11 +7755,11 @@
         <v>341</v>
       </c>
       <c r="B106" s="5">
-        <v>46170.46452224537</v>
+        <v>46170.63118891204</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46174.68171880787</v>
+        <v>46174.848385474535</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>212</v>
@@ -7806,11 +7806,11 @@
         <v>342</v>
       </c>
       <c r="B107" s="9">
-        <v>46174.654289224534</v>
+        <v>46174.820955891206</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46174.681714618055</v>
+        <v>46174.848381284726</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>63</v>
@@ -7859,11 +7859,11 @@
         <v>344</v>
       </c>
       <c r="B108" s="5">
-        <v>46169.50337755787</v>
+        <v>46169.670044224535</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46174.68189216436</v>
+        <v>46174.848558831014</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>345</v>
@@ -7920,11 +7920,11 @@
         <v>346</v>
       </c>
       <c r="B109" s="9">
-        <v>46169.50338238426</v>
+        <v>46169.670049050925</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46174.68186048611</v>
+        <v>46174.848527152775</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>209</v>
@@ -7971,11 +7971,11 @@
         <v>348</v>
       </c>
       <c r="B110" s="5">
-        <v>46170.46547012731</v>
+        <v>46170.63213679398</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46174.68185760417</v>
+        <v>46174.848524270834</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>212</v>
@@ -8022,11 +8022,11 @@
         <v>349</v>
       </c>
       <c r="B111" s="9">
-        <v>46174.65432623842</v>
+        <v>46174.82099290509</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46174.681853622686</v>
+        <v>46174.84852028935</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>343</v>
@@ -8075,11 +8075,11 @@
         <v>350</v>
       </c>
       <c r="B112" s="5">
-        <v>46169.50347310185</v>
+        <v>46169.67013976852</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46174.682036412036</v>
+        <v>46174.84870307871</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>351</v>
@@ -8136,11 +8136,11 @@
         <v>352</v>
       </c>
       <c r="B113" s="9">
-        <v>46169.50348471064</v>
+        <v>46169.670151377315</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46174.68200320602</v>
+        <v>46174.848669872685</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>209</v>
@@ -8189,11 +8189,11 @@
         <v>354</v>
       </c>
       <c r="B114" s="5">
-        <v>46170.46619331019</v>
+        <v>46170.63285997685</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46174.68200064814</v>
+        <v>46174.848667314815</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>212</v>
@@ -8242,11 +8242,11 @@
         <v>355</v>
       </c>
       <c r="B115" s="9">
-        <v>46174.65435747685</v>
+        <v>46174.821024143515</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46174.68199670139</v>
+        <v>46174.84866336806</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>63</v>
@@ -8295,11 +8295,11 @@
         <v>356</v>
       </c>
       <c r="B116" s="5">
-        <v>46169.50355298611</v>
+        <v>46169.67021965278</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46174.682143136575</v>
+        <v>46174.84880980324</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>357</v>
@@ -8358,11 +8358,11 @@
         <v>359</v>
       </c>
       <c r="B117" s="9">
-        <v>46169.50356010417</v>
+        <v>46169.67022677083</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46174.68211905092</v>
+        <v>46174.84878571759</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>209</v>
@@ -8409,11 +8409,11 @@
         <v>360</v>
       </c>
       <c r="B118" s="5">
-        <v>46170.46691516203</v>
+        <v>46170.633581828704</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46174.68211648148</v>
+        <v>46174.84878314815</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>212</v>
@@ -8460,11 +8460,11 @@
         <v>361</v>
       </c>
       <c r="B119" s="9">
-        <v>46174.65439037037</v>
+        <v>46174.821057037036</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46174.68211247685</v>
+        <v>46174.84877914352</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>63</v>
@@ -8511,11 +8511,11 @@
         <v>362</v>
       </c>
       <c r="B120" s="5">
-        <v>46169.503649502316</v>
+        <v>46169.67031616898</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46174.65735084491</v>
+        <v>46174.82401751158</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>363</v>
@@ -8558,11 +8558,11 @@
         <v>365</v>
       </c>
       <c r="B121" s="9">
-        <v>46169.503653101856</v>
+        <v>46169.67031976852</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46174.6821881713</v>
+        <v>46174.84885483797</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>366</v>
@@ -8621,11 +8621,11 @@
         <v>369</v>
       </c>
       <c r="B122" s="5">
-        <v>46169.50365864583</v>
+        <v>46169.6703253125</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46174.682227418976</v>
+        <v>46174.84889408565</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>370</v>
@@ -8684,11 +8684,11 @@
         <v>372</v>
       </c>
       <c r="B123" s="9">
-        <v>46169.503665763885</v>
+        <v>46169.670332430556</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46174.65735060185</v>
+        <v>46174.82401726852</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>373</v>
@@ -8737,11 +8737,11 @@
         <v>375</v>
       </c>
       <c r="B124" s="5">
-        <v>46169.503669247686</v>
+        <v>46169.67033591435</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46174.68229203703</v>
+        <v>46174.848958703704</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>376</v>
@@ -8800,11 +8800,11 @@
         <v>378</v>
       </c>
       <c r="B125" s="9">
-        <v>46169.503680821756</v>
+        <v>46169.67034748843</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46174.68228920139</v>
+        <v>46174.84895586806</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>379</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -5300,7 +5300,7 @@
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46174.84685081019</v>
+        <v>46188.17164222222</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>209</v>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46174.84684746528</v>
+        <v>46188.171644201386</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>212</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="50001558 -  GESVIAL ot 4342 -43" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="50001558 -  GESVIAL" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1490" uniqueCount="380">
   <si>
-    <t xml:space="preserve">50001558 -  GESVIAL ot 4342 -4344 -4342  </t>
+    <t>50001558 -  GESVIAL</t>
   </si>
   <si>
     <t xml:space="preserve">Powered by </t>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46185.17224320602</v>
+        <v>46190.68404121528</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>204</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1490" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1491" uniqueCount="380">
   <si>
     <t>50001558 -  GESVIAL</t>
   </si>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="9">
-        <v>46174.82164043981</v>
+        <v>46191.686801284726</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>63</v>
@@ -2369,9 +2369,11 @@
         <v>26</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H13" s="10"/>
+        <v>57</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>58</v>
+      </c>
       <c r="I13" s="9">
         <v>46223</v>
       </c>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -4901,7 +4901,7 @@
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46190.68404121528</v>
+        <v>46191.69432710648</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>204</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1491" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1479" uniqueCount="375">
   <si>
     <t>50001558 -  GESVIAL</t>
   </si>
@@ -243,7 +243,7 @@
     <t>Ingenieria Jefe de proyecto:</t>
   </si>
   <si>
-    <t>Ingenieria basica Rodete,Ingenieria Detalle,Ingenieria Basica Motor,Analisis de costeo</t>
+    <t>Ingenieria basica Rodete,Ingenieria Detalle,Ingenieria Basica Motor</t>
   </si>
   <si>
     <t>1215174266168927</t>
@@ -261,7 +261,7 @@
     <t>MOTOR DE STOCK WEG - 02 POLOS - IE3 FRAME 280</t>
   </si>
   <si>
-    <t>Ingenieria Jefe de proyecto:,Analisis de costeo,propuesta motor</t>
+    <t>Ingenieria Jefe de proyecto:,propuesta motor</t>
   </si>
   <si>
     <t>1215174266168950</t>
@@ -279,7 +279,7 @@
 </t>
   </si>
   <si>
-    <t>Ingenieria Jefe de proyecto:,propuesta alabes,propuesta nucleo rodete,Analisis de costeo</t>
+    <t>Ingenieria Jefe de proyecto:,propuesta alabes,propuesta nucleo rodete</t>
   </si>
   <si>
     <t>1215174166392287</t>
@@ -288,19 +288,7 @@
     <t>Ingenieria Detalle</t>
   </si>
   <si>
-    <t>Ingenieria Jefe de proyecto:,OT 4344 - MANGA DE VENTILACION Ø1600MM,Analisis de costeo,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A</t>
-  </si>
-  <si>
-    <t>1215174266170339</t>
-  </si>
-  <si>
-    <t>Analisis de costeo</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle,Ingenieria Basica Motor,Ingenieria basica Rodete</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,Costos</t>
+    <t>Ingenieria Jefe de proyecto:,OT 4344 - MANGA DE VENTILACION Ø1600MM,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A</t>
   </si>
   <si>
     <t>1215137857526710</t>
@@ -1162,9 +1150,6 @@
   </si>
   <si>
     <t>Costos</t>
-  </si>
-  <si>
-    <t>Despacho,Analisis de costeo</t>
   </si>
   <si>
     <t>1215174267257524</t>
@@ -1712,7 +1697,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U125"/>
+  <dimension ref="A1:U124"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -2413,7 +2398,7 @@
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46181.63678748843</v>
+        <v>46192.97341535879</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>65</v>
@@ -2449,7 +2434,9 @@
       <c r="R14" s="6"/>
       <c r="S14" s="6"/>
       <c r="T14" s="6"/>
-      <c r="U14" s="6"/>
+      <c r="U14" s="11" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
@@ -2462,7 +2449,7 @@
         <v>46181.63678064814</v>
       </c>
       <c r="D15" s="9">
-        <v>46181.6367991088</v>
+        <v>46192.97339646991</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>68</v>
@@ -2527,7 +2514,7 @@
         <v>46181.63674427083</v>
       </c>
       <c r="D16" s="5">
-        <v>46181.636760821755</v>
+        <v>46192.97339646991</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>74</v>
@@ -2592,7 +2579,7 @@
         <v>46181.636749930556</v>
       </c>
       <c r="D17" s="9">
-        <v>46181.63676504629</v>
+        <v>46192.97339675926</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>78</v>
@@ -2651,30 +2638,24 @@
         <v>80</v>
       </c>
       <c r="B18" s="5">
-        <v>46169.669008287034</v>
+        <v>46169.66883001158</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46181.63680046296</v>
+        <v>46181.636845416666</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>81</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="I18" s="5">
-        <v>46155</v>
-      </c>
-      <c r="J18" s="5">
-        <v>46164</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
       <c r="K18" s="6" t="s">
         <v>26</v>
       </c>
@@ -2682,95 +2663,103 @@
         <v>26</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>82</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q18" s="5">
-        <v>46155</v>
-      </c>
-      <c r="R18" s="5">
-        <v>46164</v>
-      </c>
-      <c r="S18" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T18" s="6">
-        <v>0</v>
-      </c>
-      <c r="U18" s="11" t="s">
-        <v>54</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q18" s="6"/>
+      <c r="R18" s="6"/>
+      <c r="S18" s="6"/>
+      <c r="T18" s="6"/>
+      <c r="U18" s="6"/>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" s="9">
+        <v>46169.669016053245</v>
+      </c>
+      <c r="C19" s="9">
+        <v>46181.63682515046</v>
+      </c>
+      <c r="D19" s="9">
+        <v>46181.636840625</v>
+      </c>
+      <c r="E19" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="B19" s="9">
-        <v>46169.66883001158</v>
-      </c>
-      <c r="C19" s="10"/>
-      <c r="D19" s="9">
-        <v>46181.636845416666</v>
-      </c>
-      <c r="E19" s="10" t="s">
+      <c r="F19" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="I19" s="9">
+        <v>46157</v>
+      </c>
+      <c r="J19" s="9">
+        <v>46160</v>
+      </c>
+      <c r="K19" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L19" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M19" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N19" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="O19" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="P19" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="F19" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L19" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M19" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="N19" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O19" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="P19" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q19" s="10"/>
-      <c r="R19" s="10"/>
-      <c r="S19" s="10"/>
-      <c r="T19" s="10"/>
-      <c r="U19" s="10"/>
+      <c r="Q19" s="9">
+        <v>46157</v>
+      </c>
+      <c r="R19" s="9">
+        <v>46160</v>
+      </c>
+      <c r="S19" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T19" s="10">
+        <v>1</v>
+      </c>
+      <c r="U19" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20" s="5">
+        <v>46169.669021423615</v>
+      </c>
+      <c r="C20" s="5">
+        <v>46181.6368303125</v>
+      </c>
+      <c r="D20" s="5">
+        <v>46181.636847222224</v>
+      </c>
+      <c r="E20" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="B20" s="5">
-        <v>46169.669016053245</v>
-      </c>
-      <c r="C20" s="5">
-        <v>46181.63682515046</v>
-      </c>
-      <c r="D20" s="5">
-        <v>46181.636840625</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>88</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2782,10 +2771,10 @@
         <v>70</v>
       </c>
       <c r="I20" s="5">
-        <v>46157</v>
+        <v>46167</v>
       </c>
       <c r="J20" s="5">
-        <v>46160</v>
+        <v>46168</v>
       </c>
       <c r="K20" s="6" t="s">
         <v>26</v>
@@ -2797,19 +2786,19 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Q20" s="5">
-        <v>46157</v>
+        <v>46167</v>
       </c>
       <c r="R20" s="5">
-        <v>46160</v>
+        <v>46168</v>
       </c>
       <c r="S20" s="7" t="s">
         <v>33</v>
@@ -2823,28 +2812,28 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B21" s="9">
+        <v>46169.66902680555</v>
+      </c>
+      <c r="C21" s="9">
+        <v>46181.63683986111</v>
+      </c>
+      <c r="D21" s="9">
+        <v>46181.636854895834</v>
+      </c>
+      <c r="E21" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="B21" s="9">
-        <v>46169.669021423615</v>
-      </c>
-      <c r="C21" s="9">
-        <v>46181.6368303125</v>
-      </c>
-      <c r="D21" s="9">
-        <v>46181.636847222224</v>
-      </c>
-      <c r="E21" s="10" t="s">
+      <c r="F21" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="F21" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>69</v>
-      </c>
       <c r="H21" s="10" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="I21" s="9">
         <v>46167</v>
@@ -2862,7 +2851,7 @@
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O21" s="10" t="s">
         <v>74</v>
@@ -2891,13 +2880,11 @@
         <v>93</v>
       </c>
       <c r="B22" s="5">
-        <v>46169.66902680555</v>
-      </c>
-      <c r="C22" s="5">
-        <v>46181.63683986111</v>
-      </c>
+        <v>46169.66903233796</v>
+      </c>
+      <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46181.636854895834</v>
+        <v>46174.825234710646</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>94</v>
@@ -2909,13 +2896,13 @@
         <v>95</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I22" s="5">
-        <v>46167</v>
+        <v>46241</v>
       </c>
       <c r="J22" s="5">
-        <v>46168</v>
+        <v>46244</v>
       </c>
       <c r="K22" s="6" t="s">
         <v>26</v>
@@ -2927,52 +2914,52 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q22" s="5">
-        <v>46167</v>
+        <v>46241</v>
       </c>
       <c r="R22" s="5">
-        <v>46168</v>
+        <v>46244</v>
       </c>
       <c r="S22" s="7" t="s">
         <v>33</v>
       </c>
       <c r="T22" s="6">
-        <v>1</v>
-      </c>
-      <c r="U22" s="7" t="s">
-        <v>27</v>
+        <v>0</v>
+      </c>
+      <c r="U22" s="12" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B23" s="9">
-        <v>46169.66903233796</v>
+        <v>46169.669037291664</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46174.825234710646</v>
+        <v>46174.825231863426</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I23" s="9">
         <v>46241</v>
@@ -2990,13 +2977,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O23" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="P23" s="10" t="s">
         <v>101</v>
-      </c>
-      <c r="P23" s="10" t="s">
-        <v>102</v>
       </c>
       <c r="Q23" s="9">
         <v>46241</v>
@@ -3016,26 +3003,26 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B24" s="5">
-        <v>46169.669037291664</v>
+        <v>46169.66904123843</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46174.825231863426</v>
+        <v>46174.82522908565</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I24" s="5">
         <v>46241</v>
@@ -3053,13 +3040,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q24" s="5">
         <v>46241</v>
@@ -3079,26 +3066,26 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B25" s="9">
-        <v>46169.66904123843</v>
+        <v>46169.66904511574</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46174.82522908565</v>
+        <v>46174.82522488426</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I25" s="9">
         <v>46241</v>
@@ -3116,13 +3103,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Q25" s="9">
         <v>46241</v>
@@ -3142,56 +3129,56 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B26" s="5">
-        <v>46169.66904511574</v>
+        <v>46169.66904878472</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46174.82522488426</v>
+        <v>46174.82504707176</v>
       </c>
       <c r="E26" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I26" s="5">
+        <v>46157</v>
+      </c>
+      <c r="J26" s="5">
+        <v>46160</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N26" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="O26" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="P26" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="F26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="I26" s="5">
-        <v>46241</v>
-      </c>
-      <c r="J26" s="5">
-        <v>46244</v>
-      </c>
-      <c r="K26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N26" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="O26" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="P26" s="6" t="s">
-        <v>111</v>
-      </c>
       <c r="Q26" s="5">
-        <v>46241</v>
+        <v>46157</v>
       </c>
       <c r="R26" s="5">
-        <v>46244</v>
+        <v>46160</v>
       </c>
       <c r="S26" s="7" t="s">
         <v>33</v>
@@ -3205,90 +3192,82 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B27" s="9">
-        <v>46169.66904878472</v>
+        <v>46169.66883418981</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46174.82504707176</v>
+        <v>46182.63465987268</v>
       </c>
       <c r="E27" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L27" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M27" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="N27" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="O27" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="F27" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G27" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="I27" s="9">
-        <v>46157</v>
-      </c>
-      <c r="J27" s="9">
-        <v>46160</v>
-      </c>
-      <c r="K27" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L27" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M27" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N27" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="O27" s="10" t="s">
-        <v>50</v>
-      </c>
       <c r="P27" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q27" s="9">
-        <v>46157</v>
-      </c>
-      <c r="R27" s="9">
-        <v>46160</v>
-      </c>
-      <c r="S27" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T27" s="10">
-        <v>0</v>
-      </c>
-      <c r="U27" s="12" t="s">
-        <v>61</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q27" s="10"/>
+      <c r="R27" s="10"/>
+      <c r="S27" s="10"/>
+      <c r="T27" s="10"/>
+      <c r="U27" s="10"/>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B28" s="5">
+        <v>46169.66908924768</v>
+      </c>
+      <c r="C28" s="5">
+        <v>46182.63465045139</v>
+      </c>
+      <c r="D28" s="5">
+        <v>46182.63466408565</v>
+      </c>
+      <c r="E28" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="B28" s="5">
-        <v>46169.66883418981</v>
-      </c>
-      <c r="C28" s="6"/>
-      <c r="D28" s="5">
-        <v>46182.63465987268</v>
-      </c>
-      <c r="E28" s="6" t="s">
+      <c r="F28" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G28" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="F28" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
+      <c r="H28" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="I28" s="5">
+        <v>46171</v>
+      </c>
+      <c r="J28" s="5">
+        <v>46287</v>
+      </c>
       <c r="K28" s="6" t="s">
         <v>26</v>
       </c>
@@ -3296,136 +3275,142 @@
         <v>26</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>26</v>
+        <v>112</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="6"/>
-      <c r="S28" s="6"/>
-      <c r="T28" s="6"/>
-      <c r="U28" s="6"/>
+        <v>112</v>
+      </c>
+      <c r="Q28" s="5">
+        <v>46168</v>
+      </c>
+      <c r="R28" s="5">
+        <v>46287</v>
+      </c>
+      <c r="S28" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T28" s="6">
+        <v>1</v>
+      </c>
+      <c r="U28" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B29" s="9">
-        <v>46169.66908924768</v>
+        <v>46169.66909520833</v>
       </c>
       <c r="C29" s="9">
-        <v>46182.63465045139</v>
+        <v>46182.63236193287</v>
       </c>
       <c r="D29" s="9">
-        <v>46182.63466408565</v>
+        <v>46182.63236322917</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H29" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="I29" s="9">
+        <v>46169</v>
+      </c>
+      <c r="J29" s="9">
+        <v>46170</v>
+      </c>
+      <c r="K29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N29" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="O29" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="P29" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="I29" s="9">
-        <v>46171</v>
-      </c>
-      <c r="J29" s="9">
-        <v>46287</v>
-      </c>
-      <c r="K29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N29" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="O29" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="P29" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q29" s="9">
-        <v>46168</v>
-      </c>
-      <c r="R29" s="9">
-        <v>46287</v>
-      </c>
+      <c r="Q29" s="10"/>
+      <c r="R29" s="10"/>
       <c r="S29" s="7" t="s">
         <v>33</v>
       </c>
       <c r="T29" s="10">
-        <v>1</v>
-      </c>
-      <c r="U29" s="7" t="s">
-        <v>27</v>
+        <v>0</v>
+      </c>
+      <c r="U29" s="12" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B30" s="5">
+        <v>46169.669100810184</v>
+      </c>
+      <c r="C30" s="5">
+        <v>46182.63463581019</v>
+      </c>
+      <c r="D30" s="5">
+        <v>46182.63463722222</v>
+      </c>
+      <c r="E30" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="B30" s="5">
-        <v>46169.66909520833</v>
-      </c>
-      <c r="C30" s="5">
-        <v>46182.63236193287</v>
-      </c>
-      <c r="D30" s="5">
-        <v>46182.63236322917</v>
-      </c>
-      <c r="E30" s="6" t="s">
+      <c r="F30" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="I30" s="5">
+        <v>46171</v>
+      </c>
+      <c r="J30" s="5">
+        <v>46282</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M30" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N30" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="O30" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="P30" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="I30" s="5">
-        <v>46169</v>
-      </c>
-      <c r="J30" s="5">
-        <v>46170</v>
-      </c>
-      <c r="K30" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L30" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M30" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N30" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="O30" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="P30" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3441,63 +3426,67 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="B31" s="9">
+        <v>46169.669106284724</v>
+      </c>
+      <c r="C31" s="9">
+        <v>46182.634586817134</v>
+      </c>
+      <c r="D31" s="9">
+        <v>46182.63460042824</v>
+      </c>
+      <c r="E31" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="B31" s="9">
-        <v>46169.669100810184</v>
-      </c>
-      <c r="C31" s="9">
-        <v>46182.63463581019</v>
-      </c>
-      <c r="D31" s="9">
-        <v>46182.63463722222</v>
-      </c>
-      <c r="E31" s="10" t="s">
+      <c r="F31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="I31" s="9">
+        <v>46168</v>
+      </c>
+      <c r="J31" s="9">
+        <v>46171</v>
+      </c>
+      <c r="K31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N31" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="O31" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="F31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G31" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="I31" s="9">
+      <c r="P31" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q31" s="9">
+        <v>46168</v>
+      </c>
+      <c r="R31" s="9">
         <v>46171</v>
       </c>
-      <c r="J31" s="9">
-        <v>46282</v>
-      </c>
-      <c r="K31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N31" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="O31" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="P31" s="10" t="s">
+      <c r="S31" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="Q31" s="10"/>
-      <c r="R31" s="10"/>
-      <c r="S31" s="7" t="s">
-        <v>33</v>
-      </c>
       <c r="T31" s="10">
-        <v>0</v>
-      </c>
-      <c r="U31" s="12" t="s">
-        <v>61</v>
+        <v>1</v>
+      </c>
+      <c r="U31" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
@@ -3505,13 +3494,13 @@
         <v>129</v>
       </c>
       <c r="B32" s="5">
-        <v>46169.669106284724</v>
+        <v>46169.66911128472</v>
       </c>
       <c r="C32" s="5">
-        <v>46182.634586817134</v>
+        <v>46182.63180898148</v>
       </c>
       <c r="D32" s="5">
-        <v>46182.63460042824</v>
+        <v>46182.6318109375</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>130</v>
@@ -3520,16 +3509,16 @@
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="I32" s="5">
         <v>46168</v>
       </c>
       <c r="J32" s="5">
-        <v>46171</v>
+        <v>46169</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>26</v>
@@ -3541,78 +3530,74 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="O32" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="P32" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="P32" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q32" s="5">
-        <v>46168</v>
-      </c>
-      <c r="R32" s="5">
-        <v>46171</v>
-      </c>
-      <c r="S32" s="12" t="s">
-        <v>132</v>
+      <c r="Q32" s="6"/>
+      <c r="R32" s="6"/>
+      <c r="S32" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="T32" s="6">
-        <v>1</v>
-      </c>
-      <c r="U32" s="7" t="s">
-        <v>27</v>
+        <v>0</v>
+      </c>
+      <c r="U32" s="12" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="B33" s="9">
+        <v>46169.669116805555</v>
+      </c>
+      <c r="C33" s="9">
+        <v>46182.63457177083</v>
+      </c>
+      <c r="D33" s="9">
+        <v>46182.63457327546</v>
+      </c>
+      <c r="E33" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="B33" s="9">
-        <v>46169.66911128472</v>
-      </c>
-      <c r="C33" s="9">
-        <v>46182.63180898148</v>
-      </c>
-      <c r="D33" s="9">
-        <v>46182.6318109375</v>
-      </c>
-      <c r="E33" s="10" t="s">
+      <c r="F33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="I33" s="9">
+        <v>46170</v>
+      </c>
+      <c r="J33" s="9">
+        <v>46171</v>
+      </c>
+      <c r="K33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N33" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="O33" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="P33" s="10" t="s">
         <v>134</v>
-      </c>
-      <c r="F33" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="I33" s="9">
-        <v>46168</v>
-      </c>
-      <c r="J33" s="9">
-        <v>46169</v>
-      </c>
-      <c r="K33" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L33" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M33" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N33" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="O33" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="P33" s="10" t="s">
-        <v>135</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3628,95 +3613,99 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B34" s="5">
+        <v>46169.66912204861</v>
+      </c>
+      <c r="C34" s="5">
+        <v>46182.63442347222</v>
+      </c>
+      <c r="D34" s="5">
+        <v>46182.6344355787</v>
+      </c>
+      <c r="E34" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="B34" s="5">
-        <v>46169.669116805555</v>
-      </c>
-      <c r="C34" s="5">
-        <v>46182.63457177083</v>
-      </c>
-      <c r="D34" s="5">
-        <v>46182.63457327546</v>
-      </c>
-      <c r="E34" s="6" t="s">
+      <c r="F34" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="I34" s="5">
+        <v>46161</v>
+      </c>
+      <c r="J34" s="5">
+        <v>46307</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L34" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M34" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N34" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="O34" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="F34" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="I34" s="5">
-        <v>46170</v>
-      </c>
-      <c r="J34" s="5">
-        <v>46171</v>
-      </c>
-      <c r="K34" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L34" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M34" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N34" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="O34" s="6" t="s">
-        <v>134</v>
-      </c>
       <c r="P34" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q34" s="6"/>
-      <c r="R34" s="6"/>
+        <v>112</v>
+      </c>
+      <c r="Q34" s="5">
+        <v>46161</v>
+      </c>
+      <c r="R34" s="5">
+        <v>46307</v>
+      </c>
       <c r="S34" s="7" t="s">
         <v>33</v>
       </c>
       <c r="T34" s="6">
-        <v>0</v>
-      </c>
-      <c r="U34" s="12" t="s">
-        <v>61</v>
+        <v>1</v>
+      </c>
+      <c r="U34" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="B35" s="9">
+        <v>46169.66912711806</v>
+      </c>
+      <c r="C35" s="9">
+        <v>46182.63203811343</v>
+      </c>
+      <c r="D35" s="9">
+        <v>46182.63203959491</v>
+      </c>
+      <c r="E35" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="B35" s="9">
-        <v>46169.66912204861</v>
-      </c>
-      <c r="C35" s="9">
-        <v>46182.63442347222</v>
-      </c>
-      <c r="D35" s="9">
-        <v>46182.6344355787</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>140</v>
-      </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="I35" s="9">
         <v>46161</v>
       </c>
       <c r="J35" s="9">
-        <v>46307</v>
+        <v>46181</v>
       </c>
       <c r="K35" s="10" t="s">
         <v>26</v>
@@ -3728,78 +3717,74 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>141</v>
+        <v>84</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q35" s="9">
-        <v>46161</v>
-      </c>
-      <c r="R35" s="9">
-        <v>46307</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="Q35" s="10"/>
+      <c r="R35" s="10"/>
       <c r="S35" s="7" t="s">
         <v>33</v>
       </c>
       <c r="T35" s="10">
-        <v>1</v>
-      </c>
-      <c r="U35" s="7" t="s">
-        <v>27</v>
+        <v>0</v>
+      </c>
+      <c r="U35" s="12" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B36" s="5">
+        <v>46169.66913270833</v>
+      </c>
+      <c r="C36" s="5">
+        <v>46182.63440969907</v>
+      </c>
+      <c r="D36" s="5">
+        <v>46182.634411203704</v>
+      </c>
+      <c r="E36" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="B36" s="5">
-        <v>46169.66912711806</v>
-      </c>
-      <c r="C36" s="5">
-        <v>46182.63203811343</v>
-      </c>
-      <c r="D36" s="5">
-        <v>46182.63203959491</v>
-      </c>
-      <c r="E36" s="6" t="s">
+      <c r="F36" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="I36" s="5">
+        <v>46182</v>
+      </c>
+      <c r="J36" s="5">
+        <v>46307</v>
+      </c>
+      <c r="K36" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L36" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M36" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N36" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="O36" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="P36" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="I36" s="5">
-        <v>46161</v>
-      </c>
-      <c r="J36" s="5">
-        <v>46181</v>
-      </c>
-      <c r="K36" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L36" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M36" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N36" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="O36" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="P36" s="6" t="s">
-        <v>144</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3815,34 +3800,34 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="B37" s="9">
+        <v>46169.66913809028</v>
+      </c>
+      <c r="C37" s="9">
+        <v>46182.634350636574</v>
+      </c>
+      <c r="D37" s="9">
+        <v>46182.6343528588</v>
+      </c>
+      <c r="E37" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="B37" s="9">
-        <v>46169.66913270833</v>
-      </c>
-      <c r="C37" s="9">
-        <v>46182.63440969907</v>
-      </c>
-      <c r="D37" s="9">
-        <v>46182.634411203704</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>146</v>
-      </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="I37" s="9">
         <v>46182</v>
       </c>
       <c r="J37" s="9">
-        <v>46307</v>
+        <v>46219</v>
       </c>
       <c r="K37" s="10" t="s">
         <v>26</v>
@@ -3854,13 +3839,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3876,31 +3861,29 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B38" s="5">
+        <v>46169.66914475695</v>
+      </c>
+      <c r="C38" s="6"/>
+      <c r="D38" s="5">
+        <v>46174.84252336806</v>
+      </c>
+      <c r="E38" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="B38" s="5">
-        <v>46169.66913809028</v>
-      </c>
-      <c r="C38" s="5">
-        <v>46182.634350636574</v>
-      </c>
-      <c r="D38" s="5">
-        <v>46182.6343528588</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>149</v>
-      </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="I38" s="5">
-        <v>46182</v>
+        <v>46161</v>
       </c>
       <c r="J38" s="5">
         <v>46219</v>
@@ -3915,16 +3898,20 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q38" s="6"/>
-      <c r="R38" s="6"/>
+        <v>26</v>
+      </c>
+      <c r="Q38" s="5">
+        <v>46161</v>
+      </c>
+      <c r="R38" s="5">
+        <v>46219</v>
+      </c>
       <c r="S38" s="7" t="s">
         <v>33</v>
       </c>
@@ -3937,32 +3924,32 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B39" s="9">
-        <v>46169.66914475695</v>
+        <v>46169.669149270834</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46174.84252336806</v>
+        <v>46174.8424871875</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>152</v>
+        <v>110</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="I39" s="9">
         <v>46161</v>
       </c>
       <c r="J39" s="9">
-        <v>46219</v>
+        <v>46170</v>
       </c>
       <c r="K39" s="10" t="s">
         <v>26</v>
@@ -3974,58 +3961,48 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>153</v>
+        <v>109</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q39" s="9">
-        <v>46161</v>
-      </c>
-      <c r="R39" s="9">
-        <v>46219</v>
-      </c>
-      <c r="S39" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T39" s="10">
-        <v>0</v>
-      </c>
-      <c r="U39" s="12" t="s">
-        <v>61</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="Q39" s="10"/>
+      <c r="R39" s="10"/>
+      <c r="S39" s="10"/>
+      <c r="T39" s="10"/>
+      <c r="U39" s="10"/>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B40" s="5">
-        <v>46169.669149270834</v>
+        <v>46169.66915408565</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46174.8424871875</v>
+        <v>46174.84248431713</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="I40" s="5">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="J40" s="5">
-        <v>46170</v>
+        <v>46219</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>26</v>
@@ -4037,13 +4014,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4053,32 +4030,32 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B41" s="9">
-        <v>46169.66915408565</v>
+        <v>46169.66915865741</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46174.84248431713</v>
+        <v>46174.84264390046</v>
       </c>
       <c r="E41" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="F41" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G41" s="10" t="s">
-        <v>120</v>
-      </c>
       <c r="H41" s="10" t="s">
-        <v>121</v>
+        <v>158</v>
       </c>
       <c r="I41" s="9">
-        <v>46171</v>
+        <v>46245</v>
       </c>
       <c r="J41" s="9">
-        <v>46219</v>
+        <v>46255</v>
       </c>
       <c r="K41" s="10" t="s">
         <v>26</v>
@@ -4090,48 +4067,58 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>152</v>
+        <v>112</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>114</v>
+        <v>159</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q41" s="10"/>
-      <c r="R41" s="10"/>
-      <c r="S41" s="10"/>
-      <c r="T41" s="10"/>
-      <c r="U41" s="10"/>
+        <v>112</v>
+      </c>
+      <c r="Q41" s="9">
+        <v>46245</v>
+      </c>
+      <c r="R41" s="9">
+        <v>46255</v>
+      </c>
+      <c r="S41" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T41" s="10">
+        <v>0</v>
+      </c>
+      <c r="U41" s="12" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B42" s="5">
-        <v>46169.66915865741</v>
+        <v>46169.66916377315</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46174.84264390046</v>
+        <v>46174.842601076394</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I42" s="5">
         <v>46245</v>
       </c>
       <c r="J42" s="5">
-        <v>46255</v>
+        <v>46246</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>26</v>
@@ -4143,20 +4130,16 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>116</v>
+        <v>156</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>163</v>
+        <v>94</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q42" s="5">
-        <v>46245</v>
-      </c>
-      <c r="R42" s="5">
-        <v>46255</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="Q42" s="6"/>
+      <c r="R42" s="6"/>
       <c r="S42" s="7" t="s">
         <v>33</v>
       </c>
@@ -4169,50 +4152,50 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B43" s="9">
-        <v>46169.66916377315</v>
+        <v>46169.66916960648</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46174.842601076394</v>
+        <v>46174.84259825232</v>
       </c>
       <c r="E43" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="I43" s="9">
+        <v>46247</v>
+      </c>
+      <c r="J43" s="9">
+        <v>46255</v>
+      </c>
+      <c r="K43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N43" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="O43" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="P43" s="10" t="s">
         <v>165</v>
-      </c>
-      <c r="F43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="I43" s="9">
-        <v>46245</v>
-      </c>
-      <c r="J43" s="9">
-        <v>46246</v>
-      </c>
-      <c r="K43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N43" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="O43" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="P43" s="10" t="s">
-        <v>166</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4228,29 +4211,29 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B44" s="5">
-        <v>46169.66916960648</v>
+        <v>46169.66917503472</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46174.84259825232</v>
+        <v>46174.84280633102</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I44" s="5">
-        <v>46247</v>
+        <v>46245</v>
       </c>
       <c r="J44" s="5">
         <v>46255</v>
@@ -4265,16 +4248,20 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>160</v>
+        <v>112</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q44" s="6"/>
-      <c r="R44" s="6"/>
+        <v>26</v>
+      </c>
+      <c r="Q44" s="5">
+        <v>46245</v>
+      </c>
+      <c r="R44" s="5">
+        <v>46255</v>
+      </c>
       <c r="S44" s="7" t="s">
         <v>33</v>
       </c>
@@ -4287,32 +4274,32 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B45" s="9">
-        <v>46169.66917503472</v>
+        <v>46169.669178888886</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46174.84280633102</v>
+        <v>46174.84277644676</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>171</v>
+        <v>101</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I45" s="9">
         <v>46245</v>
       </c>
       <c r="J45" s="9">
-        <v>46255</v>
+        <v>46246</v>
       </c>
       <c r="K45" s="10" t="s">
         <v>26</v>
@@ -4324,58 +4311,48 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>116</v>
+        <v>167</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>172</v>
+        <v>100</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q45" s="9">
-        <v>46245</v>
-      </c>
-      <c r="R45" s="9">
-        <v>46255</v>
-      </c>
-      <c r="S45" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T45" s="10">
-        <v>0</v>
-      </c>
-      <c r="U45" s="12" t="s">
-        <v>61</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="Q45" s="10"/>
+      <c r="R45" s="10"/>
+      <c r="S45" s="10"/>
+      <c r="T45" s="10"/>
+      <c r="U45" s="10"/>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B46" s="5">
-        <v>46169.669178888886</v>
+        <v>46169.669183680555</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46174.84277644676</v>
+        <v>46174.84277337963</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I46" s="5">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="J46" s="5">
-        <v>46246</v>
+        <v>46255</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>26</v>
@@ -4387,13 +4364,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4403,32 +4380,32 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B47" s="9">
-        <v>46169.669183680555</v>
+        <v>46169.66918849537</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46174.84277337963</v>
+        <v>46174.84306996528</v>
       </c>
       <c r="E47" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="F47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="10" t="s">
-        <v>161</v>
-      </c>
       <c r="H47" s="10" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="I47" s="9">
-        <v>46247</v>
+        <v>46245</v>
       </c>
       <c r="J47" s="9">
-        <v>46255</v>
+        <v>46286</v>
       </c>
       <c r="K47" s="10" t="s">
         <v>26</v>
@@ -4440,48 +4417,58 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>171</v>
+        <v>112</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>105</v>
+        <v>178</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="Q47" s="10"/>
-      <c r="R47" s="10"/>
-      <c r="S47" s="10"/>
-      <c r="T47" s="10"/>
-      <c r="U47" s="10"/>
+        <v>26</v>
+      </c>
+      <c r="Q47" s="9">
+        <v>46245</v>
+      </c>
+      <c r="R47" s="9">
+        <v>46286</v>
+      </c>
+      <c r="S47" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T47" s="10">
+        <v>0</v>
+      </c>
+      <c r="U47" s="12" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B48" s="5">
-        <v>46169.66918849537</v>
+        <v>46169.66919252315</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46174.84306996528</v>
+        <v>46174.84297986111</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>179</v>
+        <v>107</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="I48" s="5">
         <v>46245</v>
       </c>
       <c r="J48" s="5">
-        <v>46286</v>
+        <v>46253</v>
       </c>
       <c r="K48" s="6" t="s">
         <v>26</v>
@@ -4493,58 +4480,48 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>116</v>
+        <v>175</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>182</v>
+        <v>106</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q48" s="5">
-        <v>46245</v>
-      </c>
-      <c r="R48" s="5">
-        <v>46286</v>
-      </c>
-      <c r="S48" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T48" s="6">
-        <v>0</v>
-      </c>
-      <c r="U48" s="12" t="s">
-        <v>61</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="Q48" s="6"/>
+      <c r="R48" s="6"/>
+      <c r="S48" s="6"/>
+      <c r="T48" s="6"/>
+      <c r="U48" s="6"/>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B49" s="9">
-        <v>46169.66919252315</v>
+        <v>46169.66919734953</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46174.84297986111</v>
+        <v>46174.84297715277</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>111</v>
+        <v>182</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="I49" s="9">
-        <v>46245</v>
+        <v>46254</v>
       </c>
       <c r="J49" s="9">
-        <v>46253</v>
+        <v>46282</v>
       </c>
       <c r="K49" s="10" t="s">
         <v>26</v>
@@ -4556,13 +4533,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4572,32 +4549,32 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
-        <v>46169.66919734953</v>
+        <v>46169.66920229167</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46174.84297715277</v>
+        <v>46174.8430165625</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="6" t="s">
-        <v>180</v>
-      </c>
       <c r="H50" s="6" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="I50" s="5">
-        <v>46254</v>
+        <v>46286</v>
       </c>
       <c r="J50" s="5">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="K50" s="6" t="s">
         <v>26</v>
@@ -4609,13 +4586,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>111</v>
+        <v>182</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>187</v>
+        <v>26</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4628,11 +4605,11 @@
         <v>188</v>
       </c>
       <c r="B51" s="9">
-        <v>46169.66920229167</v>
+        <v>46169.66924202546</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46174.8430165625</v>
+        <v>46174.843210046296</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>189</v>
@@ -4641,69 +4618,79 @@
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H51" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="I51" s="9">
+        <v>46245</v>
+      </c>
+      <c r="J51" s="9">
+        <v>46255</v>
+      </c>
+      <c r="K51" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L51" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M51" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N51" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="O51" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="H51" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="I51" s="9">
-        <v>46286</v>
-      </c>
-      <c r="J51" s="9">
-        <v>46286</v>
-      </c>
-      <c r="K51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N51" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="O51" s="10" t="s">
-        <v>186</v>
-      </c>
       <c r="P51" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="Q51" s="10"/>
-      <c r="R51" s="10"/>
-      <c r="S51" s="10"/>
-      <c r="T51" s="10"/>
-      <c r="U51" s="10"/>
+      <c r="Q51" s="9">
+        <v>46245</v>
+      </c>
+      <c r="R51" s="9">
+        <v>46255</v>
+      </c>
+      <c r="S51" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T51" s="10">
+        <v>0</v>
+      </c>
+      <c r="U51" s="12" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B52" s="5">
-        <v>46169.66924202546</v>
+        <v>46169.66924635417</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46174.843210046296</v>
+        <v>46174.84316282407</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>193</v>
+        <v>104</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I52" s="5">
         <v>46245</v>
       </c>
       <c r="J52" s="5">
-        <v>46255</v>
+        <v>46246</v>
       </c>
       <c r="K52" s="6" t="s">
         <v>26</v>
@@ -4715,58 +4702,48 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>116</v>
+        <v>189</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>194</v>
+        <v>103</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q52" s="5">
-        <v>46245</v>
-      </c>
-      <c r="R52" s="5">
-        <v>46255</v>
-      </c>
-      <c r="S52" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T52" s="6">
-        <v>0</v>
-      </c>
-      <c r="U52" s="12" t="s">
-        <v>61</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="Q52" s="6"/>
+      <c r="R52" s="6"/>
+      <c r="S52" s="6"/>
+      <c r="T52" s="6"/>
+      <c r="U52" s="6"/>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B53" s="9">
-        <v>46169.66924635417</v>
+        <v>46169.66925091435</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46174.84316282407</v>
+        <v>46174.843159895834</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>108</v>
+        <v>194</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I53" s="9">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="J53" s="9">
-        <v>46246</v>
+        <v>46255</v>
       </c>
       <c r="K53" s="10" t="s">
         <v>26</v>
@@ -4778,13 +4755,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4794,50 +4771,44 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B54" s="5">
-        <v>46169.66925091435</v>
+        <v>46169.669255659726</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46174.843159895834</v>
+        <v>46169.80567821759</v>
       </c>
       <c r="E54" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H54" s="6"/>
+      <c r="I54" s="6"/>
+      <c r="J54" s="6"/>
+      <c r="K54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M54" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O54" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="F54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="I54" s="5">
-        <v>46247</v>
-      </c>
-      <c r="J54" s="5">
-        <v>46255</v>
-      </c>
-      <c r="K54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N54" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="O54" s="6" t="s">
-        <v>108</v>
-      </c>
       <c r="P54" s="6" t="s">
-        <v>199</v>
+        <v>26</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4847,27 +4818,33 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B55" s="9">
-        <v>46169.669255659726</v>
+        <v>46169.66925896991</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46169.80567821759</v>
+        <v>46191.69432710648</v>
       </c>
       <c r="E55" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G55" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F55" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H55" s="10"/>
-      <c r="I55" s="10"/>
-      <c r="J55" s="10"/>
+      <c r="H55" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="I55" s="9">
+        <v>46167</v>
+      </c>
+      <c r="J55" s="9">
+        <v>46184</v>
+      </c>
       <c r="K55" s="10" t="s">
         <v>26</v>
       </c>
@@ -4875,51 +4852,61 @@
         <v>26</v>
       </c>
       <c r="M55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N55" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="O55" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="P55" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="Q55" s="9">
+        <v>46167</v>
+      </c>
+      <c r="R55" s="9">
+        <v>46184</v>
+      </c>
+      <c r="S55" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="T55" s="10">
         <v>0</v>
       </c>
-      <c r="N55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O55" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="P55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q55" s="10"/>
-      <c r="R55" s="10"/>
-      <c r="S55" s="10"/>
-      <c r="T55" s="10"/>
-      <c r="U55" s="10"/>
+      <c r="U55" s="12" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B56" s="5">
-        <v>46169.66925896991</v>
+        <v>46169.66926408565</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46191.69432710648</v>
+        <v>46181.636760312496</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I56" s="5">
         <v>46167</v>
       </c>
       <c r="J56" s="5">
-        <v>46184</v>
+        <v>46171</v>
       </c>
       <c r="K56" s="6" t="s">
         <v>26</v>
@@ -4931,52 +4918,42 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q56" s="5">
-        <v>46167</v>
-      </c>
-      <c r="R56" s="5">
-        <v>46184</v>
-      </c>
-      <c r="S56" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="T56" s="6">
-        <v>0</v>
-      </c>
-      <c r="U56" s="12" t="s">
-        <v>61</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="Q56" s="6"/>
+      <c r="R56" s="6"/>
+      <c r="S56" s="6"/>
+      <c r="T56" s="6"/>
+      <c r="U56" s="6"/>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B57" s="9">
-        <v>46169.66926408565</v>
+        <v>46169.66926952546</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46181.636760312496</v>
+        <v>46181.63675880787</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I57" s="9">
         <v>46167</v>
@@ -4994,13 +4971,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="O57" s="10" t="s">
         <v>78</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -5010,142 +4987,142 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B58" s="5">
-        <v>46169.66926952546</v>
+        <v>46169.66929263889</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46181.63675880787</v>
+        <v>46174.846562824074</v>
       </c>
       <c r="E58" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="I58" s="5">
+        <v>46220</v>
+      </c>
+      <c r="J58" s="5">
+        <v>46239</v>
+      </c>
+      <c r="K58" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L58" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M58" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N58" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="O58" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="F58" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G58" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="I58" s="5">
-        <v>46167</v>
-      </c>
-      <c r="J58" s="5">
-        <v>46171</v>
-      </c>
-      <c r="K58" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L58" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M58" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N58" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="O58" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="P58" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q58" s="6"/>
-      <c r="R58" s="6"/>
-      <c r="S58" s="6"/>
-      <c r="T58" s="6"/>
-      <c r="U58" s="6"/>
+        <v>197</v>
+      </c>
+      <c r="Q58" s="5">
+        <v>46220</v>
+      </c>
+      <c r="R58" s="5">
+        <v>46239</v>
+      </c>
+      <c r="S58" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T58" s="6">
+        <v>0</v>
+      </c>
+      <c r="U58" s="12" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B59" s="9">
-        <v>46169.66929263889</v>
+        <v>46169.66929775463</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46174.846562824074</v>
+        <v>46185.17154260416</v>
       </c>
       <c r="E59" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G59" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="H59" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="I59" s="9">
+        <v>46181</v>
+      </c>
+      <c r="J59" s="9">
+        <v>46185</v>
+      </c>
+      <c r="K59" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L59" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M59" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N59" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="O59" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="P59" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="F59" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G59" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="I59" s="9">
-        <v>46220</v>
-      </c>
-      <c r="J59" s="9">
-        <v>46239</v>
-      </c>
-      <c r="K59" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L59" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M59" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N59" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="O59" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="P59" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q59" s="9">
-        <v>46220</v>
-      </c>
-      <c r="R59" s="9">
-        <v>46239</v>
-      </c>
-      <c r="S59" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T59" s="10">
-        <v>0</v>
-      </c>
-      <c r="U59" s="12" t="s">
-        <v>61</v>
-      </c>
+      <c r="Q59" s="10"/>
+      <c r="R59" s="10"/>
+      <c r="S59" s="10"/>
+      <c r="T59" s="10"/>
+      <c r="U59" s="10"/>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B60" s="5">
-        <v>46169.66929775463</v>
+        <v>46169.66930358796</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46185.17154260416</v>
+        <v>46185.17153893519</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I60" s="5">
         <v>46181</v>
@@ -5163,13 +5140,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="O60" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="P60" s="6" t="s">
         <v>218</v>
-      </c>
-      <c r="P60" s="6" t="s">
-        <v>219</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5179,142 +5156,142 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B61" s="9">
-        <v>46169.66930358796</v>
+        <v>46169.669327048614</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46185.17153893519</v>
+        <v>46174.84655958333</v>
       </c>
       <c r="E61" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="F61" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G61" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="H61" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="I61" s="9">
+        <v>46240</v>
+      </c>
+      <c r="J61" s="9">
+        <v>46240</v>
+      </c>
+      <c r="K61" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L61" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M61" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N61" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="O61" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="F61" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G61" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="I61" s="9">
-        <v>46181</v>
-      </c>
-      <c r="J61" s="9">
-        <v>46185</v>
-      </c>
-      <c r="K61" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L61" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M61" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N61" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="O61" s="10" t="s">
-        <v>221</v>
-      </c>
       <c r="P61" s="10" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q61" s="10"/>
-      <c r="R61" s="10"/>
-      <c r="S61" s="10"/>
-      <c r="T61" s="10"/>
-      <c r="U61" s="10"/>
+        <v>220</v>
+      </c>
+      <c r="Q61" s="9">
+        <v>46240</v>
+      </c>
+      <c r="R61" s="9">
+        <v>46240</v>
+      </c>
+      <c r="S61" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T61" s="10">
+        <v>0</v>
+      </c>
+      <c r="U61" s="12" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B62" s="5">
-        <v>46169.669327048614</v>
+        <v>46169.6693399537</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46174.84655958333</v>
+        <v>46188.17164222222</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>101</v>
+        <v>205</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="I62" s="5">
+        <v>46188</v>
+      </c>
+      <c r="J62" s="5">
+        <v>46188</v>
+      </c>
+      <c r="K62" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L62" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M62" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N62" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="O62" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="H62" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="I62" s="5">
-        <v>46240</v>
-      </c>
-      <c r="J62" s="5">
-        <v>46240</v>
-      </c>
-      <c r="K62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N62" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="O62" s="6" t="s">
-        <v>216</v>
-      </c>
       <c r="P62" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="Q62" s="5">
-        <v>46240</v>
-      </c>
-      <c r="R62" s="5">
-        <v>46240</v>
-      </c>
-      <c r="S62" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T62" s="6">
-        <v>0</v>
-      </c>
-      <c r="U62" s="12" t="s">
-        <v>61</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="Q62" s="6"/>
+      <c r="R62" s="6"/>
+      <c r="S62" s="6"/>
+      <c r="T62" s="6"/>
+      <c r="U62" s="6"/>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B63" s="9">
-        <v>46169.6693399537</v>
+        <v>46169.66934443287</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46188.17164222222</v>
+        <v>46188.171644201386</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I63" s="9">
         <v>46188</v>
@@ -5332,13 +5309,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5348,149 +5325,143 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B64" s="5">
-        <v>46169.66934443287</v>
+        <v>46169.669361203705</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46188.171644201386</v>
+        <v>46174.84660805555</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="I64" s="5">
+        <v>46322</v>
+      </c>
+      <c r="J64" s="5">
+        <v>46322</v>
+      </c>
+      <c r="K64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N64" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="O64" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="H64" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="I64" s="5">
-        <v>46188</v>
-      </c>
-      <c r="J64" s="5">
-        <v>46188</v>
-      </c>
-      <c r="K64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N64" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="O64" s="6" t="s">
-        <v>212</v>
-      </c>
       <c r="P64" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q64" s="6"/>
-      <c r="R64" s="6"/>
-      <c r="S64" s="6"/>
-      <c r="T64" s="6"/>
-      <c r="U64" s="6"/>
+        <v>26</v>
+      </c>
+      <c r="Q64" s="5">
+        <v>46322</v>
+      </c>
+      <c r="R64" s="5">
+        <v>46322</v>
+      </c>
+      <c r="S64" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T64" s="6">
+        <v>0</v>
+      </c>
+      <c r="U64" s="12" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
         <v>227</v>
       </c>
       <c r="B65" s="9">
-        <v>46169.669361203705</v>
+        <v>46169.66936501158</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46174.84660805555</v>
+        <v>46174.846919421296</v>
       </c>
       <c r="E65" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="F65" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G65" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="H65" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="I65" s="9">
+        <v>46290</v>
+      </c>
+      <c r="J65" s="9">
+        <v>46290</v>
+      </c>
+      <c r="K65" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L65" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M65" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N65" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="O65" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="P65" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="F65" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G65" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="I65" s="9">
-        <v>46322</v>
-      </c>
-      <c r="J65" s="9">
-        <v>46322</v>
-      </c>
-      <c r="K65" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L65" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M65" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N65" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="O65" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="P65" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q65" s="9">
-        <v>46322</v>
-      </c>
-      <c r="R65" s="9">
-        <v>46322</v>
-      </c>
-      <c r="S65" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T65" s="10">
-        <v>0</v>
-      </c>
-      <c r="U65" s="12" t="s">
-        <v>61</v>
-      </c>
+      <c r="Q65" s="10"/>
+      <c r="R65" s="10"/>
+      <c r="S65" s="10"/>
+      <c r="T65" s="10"/>
+      <c r="U65" s="10"/>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B66" s="5">
-        <v>46169.66936501158</v>
+        <v>46169.669418136575</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46174.846919421296</v>
+        <v>46170.59324665509</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="I66" s="5">
-        <v>46290</v>
-      </c>
-      <c r="J66" s="5">
-        <v>46290</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H66" s="6"/>
+      <c r="I66" s="6"/>
+      <c r="J66" s="6"/>
       <c r="K66" s="6" t="s">
         <v>26</v>
       </c>
@@ -5498,16 +5469,16 @@
         <v>26</v>
       </c>
       <c r="M66" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>228</v>
+        <v>26</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>232</v>
+        <v>26</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5517,27 +5488,33 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B67" s="9">
-        <v>46169.669418136575</v>
+        <v>46169.66942685185</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46170.59324665509</v>
+        <v>46174.84701519676</v>
       </c>
       <c r="E67" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="F67" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G67" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="F67" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G67" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H67" s="10"/>
-      <c r="I67" s="10"/>
-      <c r="J67" s="10"/>
+      <c r="H67" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="I67" s="9">
+        <v>46258</v>
+      </c>
+      <c r="J67" s="9">
+        <v>46259</v>
+      </c>
       <c r="K67" s="10" t="s">
         <v>26</v>
       </c>
@@ -5545,75 +5522,85 @@
         <v>26</v>
       </c>
       <c r="M67" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N67" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="O67" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="P67" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q67" s="9">
+        <v>46258</v>
+      </c>
+      <c r="R67" s="9">
+        <v>46259</v>
+      </c>
+      <c r="S67" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T67" s="10">
         <v>0</v>
       </c>
-      <c r="N67" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O67" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="P67" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q67" s="10"/>
-      <c r="R67" s="10"/>
-      <c r="S67" s="10"/>
-      <c r="T67" s="10"/>
-      <c r="U67" s="10"/>
+      <c r="U67" s="12" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B68" s="5">
-        <v>46169.66942685185</v>
+        <v>46169.669432361115</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46174.84701519676</v>
+        <v>46174.847163576385</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>238</v>
+        <v>186</v>
       </c>
       <c r="H68" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="I68" s="5">
+        <v>46260</v>
+      </c>
+      <c r="J68" s="5">
+        <v>46261</v>
+      </c>
+      <c r="K68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N68" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="O68" s="6" t="s">
         <v>239</v>
-      </c>
-      <c r="I68" s="5">
-        <v>46258</v>
-      </c>
-      <c r="J68" s="5">
-        <v>46259</v>
-      </c>
-      <c r="K68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N68" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="O68" s="6" t="s">
-        <v>168</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>240</v>
       </c>
       <c r="Q68" s="5">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="R68" s="5">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="S68" s="7" t="s">
         <v>33</v>
@@ -5630,11 +5617,11 @@
         <v>241</v>
       </c>
       <c r="B69" s="9">
-        <v>46169.669432361115</v>
+        <v>46169.66943836806</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46174.847163576385</v>
+        <v>46174.84701244213</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>242</v>
@@ -5643,16 +5630,16 @@
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>191</v>
+        <v>235</v>
       </c>
       <c r="I69" s="9">
-        <v>46260</v>
+        <v>46258</v>
       </c>
       <c r="J69" s="9">
-        <v>46261</v>
+        <v>46259</v>
       </c>
       <c r="K69" s="10" t="s">
         <v>26</v>
@@ -5664,19 +5651,19 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="O69" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="P69" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="P69" s="10" t="s">
-        <v>244</v>
-      </c>
       <c r="Q69" s="9">
-        <v>46260</v>
+        <v>46258</v>
       </c>
       <c r="R69" s="9">
-        <v>46261</v>
+        <v>46259</v>
       </c>
       <c r="S69" s="7" t="s">
         <v>33</v>
@@ -5690,56 +5677,56 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B70" s="5">
-        <v>46169.66943836806</v>
+        <v>46169.669443692124</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46174.84701244213</v>
+        <v>46174.84716077546</v>
       </c>
       <c r="E70" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="F70" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G70" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="I70" s="5">
+        <v>46260</v>
+      </c>
+      <c r="J70" s="5">
+        <v>46261</v>
+      </c>
+      <c r="K70" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L70" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M70" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N70" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="O70" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="P70" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="F70" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G70" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="I70" s="5">
-        <v>46258</v>
-      </c>
-      <c r="J70" s="5">
-        <v>46259</v>
-      </c>
-      <c r="K70" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L70" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M70" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N70" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="O70" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="P70" s="6" t="s">
-        <v>247</v>
-      </c>
       <c r="Q70" s="5">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="R70" s="5">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="S70" s="7" t="s">
         <v>33</v>
@@ -5753,56 +5740,56 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B71" s="9">
-        <v>46169.669443692124</v>
+        <v>46169.669448368055</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46174.84716077546</v>
+        <v>46174.84700815972</v>
       </c>
       <c r="E71" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="F71" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G71" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H71" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="I71" s="9">
+        <v>46258</v>
+      </c>
+      <c r="J71" s="9">
+        <v>46259</v>
+      </c>
+      <c r="K71" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L71" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M71" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N71" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="O71" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="P71" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="F71" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G71" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="I71" s="9">
-        <v>46260</v>
-      </c>
-      <c r="J71" s="9">
-        <v>46261</v>
-      </c>
-      <c r="K71" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L71" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M71" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N71" s="10" t="s">
-        <v>234</v>
-      </c>
-      <c r="O71" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="P71" s="10" t="s">
-        <v>250</v>
-      </c>
       <c r="Q71" s="9">
-        <v>46260</v>
+        <v>46258</v>
       </c>
       <c r="R71" s="9">
-        <v>46261</v>
+        <v>46259</v>
       </c>
       <c r="S71" s="7" t="s">
         <v>33</v>
@@ -5816,32 +5803,32 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B72" s="5">
-        <v>46169.669448368055</v>
+        <v>46169.66945298611</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46174.84700815972</v>
+        <v>46174.847156944445</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>238</v>
+        <v>186</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>239</v>
+        <v>187</v>
       </c>
       <c r="I72" s="5">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="J72" s="5">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="K72" s="6" t="s">
         <v>26</v>
@@ -5853,19 +5840,19 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>198</v>
+        <v>248</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="Q72" s="5">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="R72" s="5">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="S72" s="7" t="s">
         <v>33</v>
@@ -5879,90 +5866,80 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B73" s="9">
-        <v>46169.66945298611</v>
+        <v>46169.66945778935</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46174.847156944445</v>
+        <v>46170.62754262731</v>
       </c>
       <c r="E73" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="F73" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G73" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H73" s="10"/>
+      <c r="I73" s="10"/>
+      <c r="J73" s="10"/>
+      <c r="K73" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L73" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M73" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="N73" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="O73" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="F73" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G73" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="I73" s="9">
-        <v>46260</v>
-      </c>
-      <c r="J73" s="9">
-        <v>46261</v>
-      </c>
-      <c r="K73" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L73" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M73" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N73" s="10" t="s">
-        <v>234</v>
-      </c>
-      <c r="O73" s="10" t="s">
-        <v>252</v>
-      </c>
       <c r="P73" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="Q73" s="9">
-        <v>46260</v>
-      </c>
-      <c r="R73" s="9">
-        <v>46261</v>
-      </c>
-      <c r="S73" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T73" s="10">
-        <v>0</v>
-      </c>
-      <c r="U73" s="12" t="s">
-        <v>61</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q73" s="10"/>
+      <c r="R73" s="10"/>
+      <c r="S73" s="10"/>
+      <c r="T73" s="10"/>
+      <c r="U73" s="10"/>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B74" s="5">
-        <v>46169.66945778935</v>
+        <v>46169.66946104167</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46170.62754262731</v>
+        <v>46174.84730037037</v>
       </c>
       <c r="E74" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G74" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="F74" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H74" s="6"/>
-      <c r="I74" s="6"/>
-      <c r="J74" s="6"/>
+      <c r="H74" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="I74" s="5">
+        <v>46262</v>
+      </c>
+      <c r="J74" s="5">
+        <v>46272</v>
+      </c>
       <c r="K74" s="6" t="s">
         <v>26</v>
       </c>
@@ -5970,45 +5947,55 @@
         <v>26</v>
       </c>
       <c r="M74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N74" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="O74" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="P74" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q74" s="5">
+        <v>46262</v>
+      </c>
+      <c r="R74" s="5">
+        <v>46272</v>
+      </c>
+      <c r="S74" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T74" s="6">
         <v>0</v>
       </c>
-      <c r="N74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O74" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="P74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q74" s="6"/>
-      <c r="R74" s="6"/>
-      <c r="S74" s="6"/>
-      <c r="T74" s="6"/>
-      <c r="U74" s="6"/>
+      <c r="U74" s="12" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B75" s="9">
-        <v>46169.66946104167</v>
+        <v>46169.669467280095</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46174.84730037037</v>
+        <v>46174.84726460648</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>259</v>
+        <v>205</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="I75" s="9">
         <v>46262</v>
@@ -6026,52 +6013,42 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>256</v>
-      </c>
-      <c r="Q75" s="9">
-        <v>46262</v>
-      </c>
-      <c r="R75" s="9">
-        <v>46272</v>
-      </c>
-      <c r="S75" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T75" s="10">
-        <v>0</v>
-      </c>
-      <c r="U75" s="12" t="s">
-        <v>61</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="Q75" s="10"/>
+      <c r="R75" s="10"/>
+      <c r="S75" s="10"/>
+      <c r="T75" s="10"/>
+      <c r="U75" s="10"/>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B76" s="5">
-        <v>46169.669467280095</v>
+        <v>46169.66947349537</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46174.84726460648</v>
+        <v>46174.84726170139</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>209</v>
+        <v>263</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="I76" s="5">
         <v>46262</v>
@@ -6089,13 +6066,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>264</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>265</v>
+        <v>208</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6105,32 +6082,32 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B77" s="9">
-        <v>46169.66947349537</v>
+        <v>46169.66950289352</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46174.84726170139</v>
+        <v>46174.847443506944</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="I77" s="9">
-        <v>46262</v>
+        <v>46273</v>
       </c>
       <c r="J77" s="9">
-        <v>46272</v>
+        <v>46293</v>
       </c>
       <c r="K77" s="10" t="s">
         <v>26</v>
@@ -6142,42 +6119,52 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="Q77" s="10"/>
-      <c r="R77" s="10"/>
-      <c r="S77" s="10"/>
-      <c r="T77" s="10"/>
-      <c r="U77" s="10"/>
+        <v>252</v>
+      </c>
+      <c r="Q77" s="9">
+        <v>46273</v>
+      </c>
+      <c r="R77" s="9">
+        <v>46293</v>
+      </c>
+      <c r="S77" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T77" s="10">
+        <v>0</v>
+      </c>
+      <c r="U77" s="12" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B78" s="5">
-        <v>46169.66950289352</v>
+        <v>46169.66950758102</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46174.847443506944</v>
+        <v>46174.84741539352</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>270</v>
+        <v>205</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="I78" s="5">
         <v>46273</v>
@@ -6195,52 +6182,42 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>207</v>
+        <v>268</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="Q78" s="5">
-        <v>46273</v>
-      </c>
-      <c r="R78" s="5">
-        <v>46293</v>
-      </c>
-      <c r="S78" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T78" s="6">
-        <v>0</v>
-      </c>
-      <c r="U78" s="12" t="s">
-        <v>61</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="Q78" s="6"/>
+      <c r="R78" s="6"/>
+      <c r="S78" s="6"/>
+      <c r="T78" s="6"/>
+      <c r="U78" s="6"/>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B79" s="9">
-        <v>46169.66950758102</v>
+        <v>46169.66951364583</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46174.84741539352</v>
+        <v>46174.8474115625</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="I79" s="9">
         <v>46273</v>
@@ -6258,13 +6235,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="O79" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="P79" s="10" t="s">
         <v>272</v>
-      </c>
-      <c r="P79" s="10" t="s">
-        <v>273</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6274,32 +6251,32 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B80" s="5">
-        <v>46169.66951364583</v>
+        <v>46169.66953380787</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46174.8474115625</v>
+        <v>46174.84760361111</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>212</v>
+        <v>274</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="I80" s="5">
-        <v>46273</v>
+        <v>46294</v>
       </c>
       <c r="J80" s="5">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="K80" s="6" t="s">
         <v>26</v>
@@ -6311,46 +6288,54 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>275</v>
+        <v>203</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="Q80" s="6"/>
-      <c r="R80" s="6"/>
-      <c r="S80" s="6"/>
-      <c r="T80" s="6"/>
-      <c r="U80" s="6"/>
+        <v>252</v>
+      </c>
+      <c r="Q80" s="5">
+        <v>46294</v>
+      </c>
+      <c r="R80" s="5">
+        <v>46294</v>
+      </c>
+      <c r="S80" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T80" s="6">
+        <v>0</v>
+      </c>
+      <c r="U80" s="12" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B81" s="9">
-        <v>46169.66953380787</v>
+        <v>46169.66953854167</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46174.84760361111</v>
+        <v>46174.84752376158</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>278</v>
+        <v>205</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="I81" s="9">
-        <v>46294</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="I81" s="10"/>
       <c r="J81" s="9">
         <v>46294</v>
       </c>
@@ -6364,52 +6349,42 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>207</v>
+        <v>268</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>256</v>
-      </c>
-      <c r="Q81" s="9">
-        <v>46294</v>
-      </c>
-      <c r="R81" s="9">
-        <v>46294</v>
-      </c>
-      <c r="S81" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T81" s="10">
-        <v>0</v>
-      </c>
-      <c r="U81" s="12" t="s">
-        <v>61</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="Q81" s="10"/>
+      <c r="R81" s="10"/>
+      <c r="S81" s="10"/>
+      <c r="T81" s="10"/>
+      <c r="U81" s="10"/>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B82" s="5">
-        <v>46169.66953854167</v>
+        <v>46169.669544212964</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46174.84752376158</v>
+        <v>46174.84752106482</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="I82" s="6"/>
       <c r="J82" s="5">
@@ -6425,13 +6400,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="O82" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="O82" s="6" t="s">
-        <v>272</v>
-      </c>
       <c r="P82" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6441,31 +6416,27 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B83" s="9">
-        <v>46169.669544212964</v>
+        <v>46169.66960108797</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46174.84752106482</v>
+        <v>46171.686115625</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="F83" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>261</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H83" s="10"/>
       <c r="I83" s="10"/>
-      <c r="J83" s="9">
-        <v>46294</v>
-      </c>
+      <c r="J83" s="10"/>
       <c r="K83" s="10" t="s">
         <v>26</v>
       </c>
@@ -6473,16 +6444,16 @@
         <v>26</v>
       </c>
       <c r="M83" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>278</v>
+        <v>26</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>283</v>
+        <v>26</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6492,27 +6463,33 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B84" s="5">
-        <v>46169.66960108797</v>
+        <v>46169.66960956018</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46171.686115625</v>
+        <v>46182.63458965278</v>
       </c>
       <c r="E84" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="F84" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G84" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="F84" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H84" s="6"/>
-      <c r="I84" s="6"/>
-      <c r="J84" s="6"/>
+      <c r="H84" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="I84" s="5">
+        <v>46174</v>
+      </c>
+      <c r="J84" s="5">
+        <v>46174</v>
+      </c>
       <c r="K84" s="6" t="s">
         <v>26</v>
       </c>
@@ -6520,78 +6497,88 @@
         <v>26</v>
       </c>
       <c r="M84" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N84" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="O84" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="P84" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="Q84" s="5">
+        <v>46174</v>
+      </c>
+      <c r="R84" s="5">
+        <v>46174</v>
+      </c>
+      <c r="S84" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="T84" s="6">
         <v>0</v>
       </c>
-      <c r="N84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O84" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="P84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q84" s="6"/>
-      <c r="R84" s="6"/>
-      <c r="S84" s="6"/>
-      <c r="T84" s="6"/>
-      <c r="U84" s="6"/>
+      <c r="U84" s="11" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B85" s="9">
-        <v>46169.66960956018</v>
+        <v>46169.6696165162</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46182.63458965278</v>
+        <v>46182.63465568287</v>
       </c>
       <c r="E85" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="F85" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G85" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H85" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="I85" s="9">
+        <v>46288</v>
+      </c>
+      <c r="J85" s="9">
+        <v>46288</v>
+      </c>
+      <c r="K85" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L85" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M85" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N85" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="O85" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="P85" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="F85" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G85" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="I85" s="9">
-        <v>46174</v>
-      </c>
-      <c r="J85" s="9">
-        <v>46174</v>
-      </c>
-      <c r="K85" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L85" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M85" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N85" s="10" t="s">
-        <v>234</v>
-      </c>
-      <c r="O85" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="P85" s="10" t="s">
-        <v>288</v>
-      </c>
       <c r="Q85" s="9">
-        <v>46174</v>
+        <v>46288</v>
       </c>
       <c r="R85" s="9">
-        <v>46174</v>
-      </c>
-      <c r="S85" s="12" t="s">
-        <v>132</v>
+        <v>46288</v>
+      </c>
+      <c r="S85" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="T85" s="10">
         <v>0</v>
@@ -6602,32 +6589,32 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B86" s="5">
-        <v>46169.6696165162</v>
+        <v>46169.669622939815</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46182.63465568287</v>
+        <v>46182.63442767361</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="I86" s="5">
-        <v>46288</v>
+        <v>46308</v>
       </c>
       <c r="J86" s="5">
-        <v>46288</v>
+        <v>46308</v>
       </c>
       <c r="K86" s="6" t="s">
         <v>26</v>
@@ -6639,19 +6626,19 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="Q86" s="5">
-        <v>46288</v>
+        <v>46308</v>
       </c>
       <c r="R86" s="5">
-        <v>46288</v>
+        <v>46308</v>
       </c>
       <c r="S86" s="7" t="s">
         <v>33</v>
@@ -6665,32 +6652,32 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B87" s="9">
-        <v>46169.669622939815</v>
+        <v>46169.66962980324</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46182.63442767361</v>
+        <v>46174.8477944676</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="I87" s="9">
-        <v>46308</v>
+        <v>46287</v>
       </c>
       <c r="J87" s="9">
-        <v>46308</v>
+        <v>46287</v>
       </c>
       <c r="K87" s="10" t="s">
         <v>26</v>
@@ -6702,19 +6689,19 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>146</v>
+        <v>182</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q87" s="9">
-        <v>46308</v>
+        <v>46287</v>
       </c>
       <c r="R87" s="9">
-        <v>46308</v>
+        <v>46287</v>
       </c>
       <c r="S87" s="7" t="s">
         <v>33</v>
@@ -6722,38 +6709,38 @@
       <c r="T87" s="10">
         <v>0</v>
       </c>
-      <c r="U87" s="11" t="s">
-        <v>54</v>
+      <c r="U87" s="12" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B88" s="5">
-        <v>46169.66962980324</v>
+        <v>46169.669635185186</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46174.8477944676</v>
+        <v>46174.84778872685</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>295</v>
+        <v>59</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="I88" s="5">
-        <v>46287</v>
+        <v>46220</v>
       </c>
       <c r="J88" s="5">
-        <v>46287</v>
+        <v>46220</v>
       </c>
       <c r="K88" s="6" t="s">
         <v>26</v>
@@ -6765,19 +6752,19 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>186</v>
+        <v>153</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="Q88" s="5">
-        <v>46287</v>
+        <v>46220</v>
       </c>
       <c r="R88" s="5">
-        <v>46287</v>
+        <v>46220</v>
       </c>
       <c r="S88" s="7" t="s">
         <v>33</v>
@@ -6791,33 +6778,27 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B89" s="9">
-        <v>46169.669635185186</v>
+        <v>46169.66964790509</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46174.84778872685</v>
+        <v>46171.71448712963</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>59</v>
+        <v>296</v>
       </c>
       <c r="F89" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="I89" s="9">
-        <v>46220</v>
-      </c>
-      <c r="J89" s="9">
-        <v>46220</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H89" s="10"/>
+      <c r="I89" s="10"/>
+      <c r="J89" s="10"/>
       <c r="K89" s="10" t="s">
         <v>26</v>
       </c>
@@ -6825,102 +6806,108 @@
         <v>26</v>
       </c>
       <c r="M89" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>234</v>
+        <v>26</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>157</v>
+        <v>297</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="Q89" s="9">
-        <v>46220</v>
-      </c>
-      <c r="R89" s="9">
-        <v>46220</v>
-      </c>
-      <c r="S89" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T89" s="10">
-        <v>0</v>
-      </c>
-      <c r="U89" s="12" t="s">
-        <v>61</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q89" s="10"/>
+      <c r="R89" s="10"/>
+      <c r="S89" s="10"/>
+      <c r="T89" s="10"/>
+      <c r="U89" s="10"/>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B90" s="5">
-        <v>46169.66964790509</v>
+        <v>46169.66965109954</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46171.71448712963</v>
+        <v>46174.84790094907</v>
       </c>
       <c r="E90" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="F90" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G90" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="I90" s="5">
+        <v>46294</v>
+      </c>
+      <c r="J90" s="5">
+        <v>46315</v>
+      </c>
+      <c r="K90" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L90" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M90" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N90" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="O90" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="F90" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G90" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H90" s="6"/>
-      <c r="I90" s="6"/>
-      <c r="J90" s="6"/>
-      <c r="K90" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L90" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M90" s="6" t="s">
+      <c r="P90" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="Q90" s="5">
+        <v>46294</v>
+      </c>
+      <c r="R90" s="5">
+        <v>46315</v>
+      </c>
+      <c r="S90" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T90" s="6">
         <v>0</v>
       </c>
-      <c r="N90" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O90" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="P90" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q90" s="6"/>
-      <c r="R90" s="6"/>
-      <c r="S90" s="6"/>
-      <c r="T90" s="6"/>
-      <c r="U90" s="6"/>
+      <c r="U90" s="12" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B91" s="9">
-        <v>46169.66965109954</v>
+        <v>46169.6696568287</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46174.84790094907</v>
+        <v>46174.84798839121</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>303</v>
+        <v>205</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I91" s="9">
         <v>46294</v>
@@ -6938,58 +6925,48 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q91" s="9">
-        <v>46294</v>
-      </c>
-      <c r="R91" s="9">
-        <v>46315</v>
-      </c>
-      <c r="S91" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T91" s="10">
-        <v>0</v>
-      </c>
-      <c r="U91" s="12" t="s">
-        <v>61</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="Q91" s="10"/>
+      <c r="R91" s="10"/>
+      <c r="S91" s="10"/>
+      <c r="T91" s="10"/>
+      <c r="U91" s="10"/>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B92" s="5">
-        <v>46169.6696568287</v>
+        <v>46169.669688622685</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46174.84798839121</v>
+        <v>46174.84789755787</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>209</v>
+        <v>304</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I92" s="5">
-        <v>46294</v>
+        <v>46316</v>
       </c>
       <c r="J92" s="5">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="K92" s="6" t="s">
         <v>26</v>
@@ -7001,46 +6978,54 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>306</v>
+        <v>205</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="Q92" s="6"/>
-      <c r="R92" s="6"/>
-      <c r="S92" s="6"/>
-      <c r="T92" s="6"/>
-      <c r="U92" s="6"/>
+        <v>296</v>
+      </c>
+      <c r="Q92" s="5">
+        <v>46316</v>
+      </c>
+      <c r="R92" s="5">
+        <v>46316</v>
+      </c>
+      <c r="S92" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T92" s="6">
+        <v>0</v>
+      </c>
+      <c r="U92" s="12" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B93" s="9">
-        <v>46169.669688622685</v>
+        <v>46169.66969347223</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46174.84789755787</v>
+        <v>46174.84803712963</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>308</v>
+        <v>205</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="I93" s="9">
-        <v>46316</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="I93" s="10"/>
       <c r="J93" s="9">
         <v>46316</v>
       </c>
@@ -7054,56 +7039,48 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>209</v>
+        <v>306</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q93" s="9">
-        <v>46316</v>
-      </c>
-      <c r="R93" s="9">
-        <v>46316</v>
-      </c>
-      <c r="S93" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T93" s="10">
-        <v>0</v>
-      </c>
-      <c r="U93" s="12" t="s">
-        <v>61</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="Q93" s="10"/>
+      <c r="R93" s="10"/>
+      <c r="S93" s="10"/>
+      <c r="T93" s="10"/>
+      <c r="U93" s="10"/>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B94" s="5">
-        <v>46169.66969347223</v>
+        <v>46169.66972681713</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46174.84803712963</v>
+        <v>46174.84789414352</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>209</v>
+        <v>309</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="I94" s="6"/>
+        <v>91</v>
+      </c>
+      <c r="I94" s="5">
+        <v>46317</v>
+      </c>
       <c r="J94" s="5">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="K94" s="6" t="s">
         <v>26</v>
@@ -7115,42 +7092,52 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>310</v>
+        <v>205</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q94" s="6"/>
-      <c r="R94" s="6"/>
-      <c r="S94" s="6"/>
-      <c r="T94" s="6"/>
-      <c r="U94" s="6"/>
+        <v>296</v>
+      </c>
+      <c r="Q94" s="5">
+        <v>46317</v>
+      </c>
+      <c r="R94" s="5">
+        <v>46317</v>
+      </c>
+      <c r="S94" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T94" s="6">
+        <v>0</v>
+      </c>
+      <c r="U94" s="12" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B95" s="9">
-        <v>46169.66972681713</v>
+        <v>46169.66973180555</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46174.84789414352</v>
+        <v>46174.848081296295</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>313</v>
+        <v>205</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I95" s="9">
         <v>46317</v>
@@ -7168,58 +7155,48 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>209</v>
+        <v>311</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q95" s="9">
-        <v>46317</v>
-      </c>
-      <c r="R95" s="9">
-        <v>46317</v>
-      </c>
-      <c r="S95" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T95" s="10">
-        <v>0</v>
-      </c>
-      <c r="U95" s="12" t="s">
-        <v>61</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="Q95" s="10"/>
+      <c r="R95" s="10"/>
+      <c r="S95" s="10"/>
+      <c r="T95" s="10"/>
+      <c r="U95" s="10"/>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B96" s="5">
-        <v>46169.66973180555</v>
+        <v>46169.66981054399</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46174.848081296295</v>
+        <v>46174.8478909375</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>209</v>
+        <v>314</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I96" s="5">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="J96" s="5">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="K96" s="6" t="s">
         <v>26</v>
@@ -7231,42 +7208,52 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>313</v>
+        <v>296</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>315</v>
+        <v>205</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="Q96" s="6"/>
-      <c r="R96" s="6"/>
-      <c r="S96" s="6"/>
-      <c r="T96" s="6"/>
-      <c r="U96" s="6"/>
+        <v>296</v>
+      </c>
+      <c r="Q96" s="5">
+        <v>46318</v>
+      </c>
+      <c r="R96" s="5">
+        <v>46318</v>
+      </c>
+      <c r="S96" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T96" s="6">
+        <v>0</v>
+      </c>
+      <c r="U96" s="12" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B97" s="9">
-        <v>46169.66981054399</v>
+        <v>46169.66981724537</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46174.8478909375</v>
+        <v>46174.84812851852</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>318</v>
+        <v>205</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I97" s="9">
         <v>46318</v>
@@ -7284,58 +7271,48 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>209</v>
+        <v>316</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q97" s="9">
-        <v>46318</v>
-      </c>
-      <c r="R97" s="9">
-        <v>46318</v>
-      </c>
-      <c r="S97" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T97" s="10">
-        <v>0</v>
-      </c>
-      <c r="U97" s="12" t="s">
-        <v>61</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="Q97" s="10"/>
+      <c r="R97" s="10"/>
+      <c r="S97" s="10"/>
+      <c r="T97" s="10"/>
+      <c r="U97" s="10"/>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B98" s="5">
-        <v>46169.66981724537</v>
+        <v>46169.669861041664</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46174.84812851852</v>
+        <v>46174.8478862037</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>209</v>
+        <v>319</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I98" s="5">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="J98" s="5">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="K98" s="6" t="s">
         <v>26</v>
@@ -7347,42 +7324,52 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>318</v>
+        <v>296</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>320</v>
+        <v>205</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="Q98" s="6"/>
-      <c r="R98" s="6"/>
-      <c r="S98" s="6"/>
-      <c r="T98" s="6"/>
-      <c r="U98" s="6"/>
+        <v>296</v>
+      </c>
+      <c r="Q98" s="5">
+        <v>46321</v>
+      </c>
+      <c r="R98" s="5">
+        <v>46321</v>
+      </c>
+      <c r="S98" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T98" s="6">
+        <v>0</v>
+      </c>
+      <c r="U98" s="12" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B99" s="9">
-        <v>46169.669861041664</v>
+        <v>46169.66986724537</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46174.8478862037</v>
+        <v>46174.84816675926</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>323</v>
+        <v>205</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I99" s="9">
         <v>46321</v>
@@ -7400,58 +7387,48 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>300</v>
+        <v>319</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q99" s="9">
-        <v>46321</v>
-      </c>
-      <c r="R99" s="9">
-        <v>46321</v>
-      </c>
-      <c r="S99" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T99" s="10">
-        <v>0</v>
-      </c>
-      <c r="U99" s="12" t="s">
-        <v>61</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="Q99" s="10"/>
+      <c r="R99" s="10"/>
+      <c r="S99" s="10"/>
+      <c r="T99" s="10"/>
+      <c r="U99" s="10"/>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B100" s="5">
-        <v>46169.66986724537</v>
+        <v>46169.66990296297</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46174.84816675926</v>
+        <v>46174.84788545139</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>209</v>
+        <v>323</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I100" s="5">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="J100" s="5">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="K100" s="6" t="s">
         <v>26</v>
@@ -7463,46 +7440,54 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>323</v>
+        <v>296</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q100" s="6"/>
-      <c r="R100" s="6"/>
-      <c r="S100" s="6"/>
-      <c r="T100" s="6"/>
-      <c r="U100" s="6"/>
+        <v>324</v>
+      </c>
+      <c r="Q100" s="5">
+        <v>46323</v>
+      </c>
+      <c r="R100" s="5">
+        <v>46323</v>
+      </c>
+      <c r="S100" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T100" s="6">
+        <v>0</v>
+      </c>
+      <c r="U100" s="12" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B101" s="9">
-        <v>46169.66990296297</v>
+        <v>46169.66994555556</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46174.84788545139</v>
+        <v>46174.848269317125</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>327</v>
+        <v>205</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="I101" s="9">
-        <v>46323</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="I101" s="10"/>
       <c r="J101" s="9">
         <v>46323</v>
       </c>
@@ -7516,57 +7501,43 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>300</v>
+        <v>323</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>328</v>
-      </c>
-      <c r="Q101" s="9">
-        <v>46323</v>
-      </c>
-      <c r="R101" s="9">
-        <v>46323</v>
-      </c>
-      <c r="S101" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T101" s="10">
-        <v>0</v>
-      </c>
-      <c r="U101" s="12" t="s">
-        <v>61</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="Q101" s="10"/>
+      <c r="R101" s="10"/>
+      <c r="S101" s="10"/>
+      <c r="T101" s="10"/>
+      <c r="U101" s="10"/>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B102" s="5">
-        <v>46169.66994555556</v>
+        <v>46169.669978645834</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46174.848269317125</v>
+        <v>46174.82401747685</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>209</v>
+        <v>328</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>95</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H102" s="6"/>
       <c r="I102" s="6"/>
-      <c r="J102" s="5">
-        <v>46323</v>
-      </c>
+      <c r="J102" s="6"/>
       <c r="K102" s="6" t="s">
         <v>26</v>
       </c>
@@ -7574,16 +7545,16 @@
         <v>26</v>
       </c>
       <c r="M102" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>327</v>
+        <v>26</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>209</v>
+        <v>329</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>330</v>
+        <v>26</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7593,27 +7564,33 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B103" s="9">
-        <v>46169.669978645834</v>
+        <v>46169.66998244213</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46174.82401747685</v>
+        <v>46174.84843513889</v>
       </c>
       <c r="E103" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="F103" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G103" s="10" t="s">
         <v>332</v>
       </c>
-      <c r="F103" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G103" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H103" s="10"/>
-      <c r="I103" s="10"/>
-      <c r="J103" s="10"/>
+      <c r="H103" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="I103" s="9">
+        <v>46324</v>
+      </c>
+      <c r="J103" s="9">
+        <v>46324</v>
+      </c>
       <c r="K103" s="10" t="s">
         <v>26</v>
       </c>
@@ -7621,49 +7598,57 @@
         <v>26</v>
       </c>
       <c r="M103" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N103" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="O103" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="P103" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q103" s="9">
+        <v>46324</v>
+      </c>
+      <c r="R103" s="9">
+        <v>46324</v>
+      </c>
+      <c r="S103" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T103" s="10">
         <v>0</v>
       </c>
-      <c r="N103" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O103" s="10" t="s">
-        <v>333</v>
-      </c>
-      <c r="P103" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q103" s="10"/>
-      <c r="R103" s="10"/>
-      <c r="S103" s="10"/>
-      <c r="T103" s="10"/>
-      <c r="U103" s="10"/>
+      <c r="U103" s="12" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B104" s="5">
-        <v>46169.66998244213</v>
+        <v>46169.66998994213</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46174.84843513889</v>
+        <v>46174.84838837963</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>335</v>
+        <v>205</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="I104" s="5">
-        <v>46324</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="I104" s="6"/>
       <c r="J104" s="5">
         <v>46324</v>
       </c>
@@ -7677,52 +7662,42 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>338</v>
+        <v>205</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>332</v>
-      </c>
-      <c r="Q104" s="5">
-        <v>46324</v>
-      </c>
-      <c r="R104" s="5">
-        <v>46324</v>
-      </c>
-      <c r="S104" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T104" s="6">
-        <v>0</v>
-      </c>
-      <c r="U104" s="12" t="s">
-        <v>61</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="Q104" s="6"/>
+      <c r="R104" s="6"/>
+      <c r="S104" s="6"/>
+      <c r="T104" s="6"/>
+      <c r="U104" s="6"/>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B105" s="9">
-        <v>46169.66998994213</v>
+        <v>46170.63118891204</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46174.84838837963</v>
+        <v>46174.848385474535</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="I105" s="10"/>
       <c r="J105" s="9">
@@ -7738,13 +7713,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>340</v>
+        <v>208</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7754,28 +7729,30 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B106" s="5">
-        <v>46170.63118891204</v>
+        <v>46174.820955891206</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46174.848385474535</v>
+        <v>46174.848381284726</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>212</v>
+        <v>63</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="I106" s="6"/>
+        <v>333</v>
+      </c>
+      <c r="I106" s="5">
+        <v>46324</v>
+      </c>
       <c r="J106" s="5">
         <v>46324</v>
       </c>
@@ -7789,13 +7766,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>212</v>
+        <v>63</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>212</v>
+        <v>339</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7805,32 +7782,30 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B107" s="9">
-        <v>46174.820955891206</v>
+        <v>46169.670044224535</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46174.848381284726</v>
+        <v>46174.848558831014</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>63</v>
+        <v>341</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>336</v>
+        <v>91</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>337</v>
-      </c>
-      <c r="I107" s="9">
-        <v>46324</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="I107" s="10"/>
       <c r="J107" s="9">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="K107" s="10" t="s">
         <v>26</v>
@@ -7842,42 +7817,52 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>63</v>
+        <v>205</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>343</v>
-      </c>
-      <c r="Q107" s="10"/>
-      <c r="R107" s="10"/>
-      <c r="S107" s="10"/>
-      <c r="T107" s="10"/>
-      <c r="U107" s="10"/>
+        <v>328</v>
+      </c>
+      <c r="Q107" s="9">
+        <v>46325</v>
+      </c>
+      <c r="R107" s="9">
+        <v>46325</v>
+      </c>
+      <c r="S107" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T107" s="10">
+        <v>0</v>
+      </c>
+      <c r="U107" s="12" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B108" s="5">
-        <v>46169.670044224535</v>
+        <v>46169.670049050925</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46174.848558831014</v>
+        <v>46174.848527152775</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>345</v>
+        <v>205</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I108" s="6"/>
       <c r="J108" s="5">
@@ -7893,52 +7878,42 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>332</v>
-      </c>
-      <c r="Q108" s="5">
-        <v>46325</v>
-      </c>
-      <c r="R108" s="5">
-        <v>46325</v>
-      </c>
-      <c r="S108" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T108" s="6">
-        <v>0</v>
-      </c>
-      <c r="U108" s="12" t="s">
-        <v>61</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="Q108" s="6"/>
+      <c r="R108" s="6"/>
+      <c r="S108" s="6"/>
+      <c r="T108" s="6"/>
+      <c r="U108" s="6"/>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B109" s="9">
-        <v>46169.670049050925</v>
+        <v>46170.63213679398</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46174.848527152775</v>
+        <v>46174.848524270834</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I109" s="10"/>
       <c r="J109" s="9">
@@ -7954,13 +7929,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>347</v>
+        <v>208</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -7970,28 +7945,30 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B110" s="5">
-        <v>46170.63213679398</v>
+        <v>46174.82099290509</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46174.848524270834</v>
+        <v>46174.84852028935</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>212</v>
+        <v>339</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="I110" s="6"/>
+        <v>91</v>
+      </c>
+      <c r="I110" s="5">
+        <v>46325</v>
+      </c>
       <c r="J110" s="5">
         <v>46325</v>
       </c>
@@ -8005,13 +7982,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>212</v>
+        <v>63</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>212</v>
+        <v>63</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8021,32 +7998,30 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B111" s="9">
-        <v>46174.82099290509</v>
+        <v>46169.67013976852</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46174.84852028935</v>
+        <v>46174.84870307871</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>95</v>
+        <v>256</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="I111" s="9">
-        <v>46325</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="I111" s="10"/>
       <c r="J111" s="9">
-        <v>46325</v>
+        <v>46328</v>
       </c>
       <c r="K111" s="10" t="s">
         <v>26</v>
@@ -8058,44 +8033,56 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>345</v>
+        <v>328</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>63</v>
+        <v>205</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q111" s="10"/>
-      <c r="R111" s="10"/>
-      <c r="S111" s="10"/>
-      <c r="T111" s="10"/>
-      <c r="U111" s="10"/>
+        <v>328</v>
+      </c>
+      <c r="Q111" s="9">
+        <v>46328</v>
+      </c>
+      <c r="R111" s="9">
+        <v>46328</v>
+      </c>
+      <c r="S111" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T111" s="10">
+        <v>0</v>
+      </c>
+      <c r="U111" s="12" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B112" s="5">
-        <v>46169.67013976852</v>
+        <v>46169.670151377315</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46174.84870307871</v>
+        <v>46174.848669872685</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>351</v>
+        <v>205</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="I112" s="6"/>
+        <v>257</v>
+      </c>
+      <c r="I112" s="5">
+        <v>46328</v>
+      </c>
       <c r="J112" s="5">
         <v>46328</v>
       </c>
@@ -8109,52 +8096,42 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>332</v>
-      </c>
-      <c r="Q112" s="5">
-        <v>46328</v>
-      </c>
-      <c r="R112" s="5">
-        <v>46328</v>
-      </c>
-      <c r="S112" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T112" s="6">
-        <v>0</v>
-      </c>
-      <c r="U112" s="12" t="s">
-        <v>61</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="Q112" s="6"/>
+      <c r="R112" s="6"/>
+      <c r="S112" s="6"/>
+      <c r="T112" s="6"/>
+      <c r="U112" s="6"/>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B113" s="9">
-        <v>46169.670151377315</v>
+        <v>46170.63285997685</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46174.848669872685</v>
+        <v>46174.848667314815</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="I113" s="9">
         <v>46328</v>
@@ -8172,13 +8149,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>353</v>
+        <v>208</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -8188,26 +8165,26 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B114" s="5">
-        <v>46170.63285997685</v>
+        <v>46174.821024143515</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46174.848667314815</v>
+        <v>46174.84866336806</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>212</v>
+        <v>63</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="I114" s="5">
         <v>46328</v>
@@ -8225,13 +8202,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>212</v>
+        <v>339</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>212</v>
+        <v>63</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8241,32 +8218,32 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B115" s="9">
-        <v>46174.821024143515</v>
+        <v>46169.67021965278</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46174.84866336806</v>
+        <v>46174.84880980324</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>63</v>
+        <v>353</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="I115" s="9">
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="J115" s="9">
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="K115" s="10" t="s">
         <v>26</v>
@@ -8278,46 +8255,54 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>351</v>
+        <v>328</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>343</v>
+        <v>205</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q115" s="10"/>
-      <c r="R115" s="10"/>
-      <c r="S115" s="10"/>
-      <c r="T115" s="10"/>
-      <c r="U115" s="10"/>
+        <v>354</v>
+      </c>
+      <c r="Q115" s="9">
+        <v>46329</v>
+      </c>
+      <c r="R115" s="9">
+        <v>46329</v>
+      </c>
+      <c r="S115" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T115" s="10">
+        <v>0</v>
+      </c>
+      <c r="U115" s="12" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B116" s="5">
-        <v>46169.67021965278</v>
+        <v>46169.67022677083</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46174.84880980324</v>
+        <v>46174.84878571759</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>357</v>
+        <v>205</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="I116" s="5">
-        <v>46329</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="I116" s="6"/>
       <c r="J116" s="5">
         <v>46329</v>
       </c>
@@ -8331,52 +8316,42 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>332</v>
+        <v>353</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="Q116" s="5">
-        <v>46329</v>
-      </c>
-      <c r="R116" s="5">
-        <v>46329</v>
-      </c>
-      <c r="S116" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T116" s="6">
-        <v>0</v>
-      </c>
-      <c r="U116" s="12" t="s">
-        <v>61</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="Q116" s="6"/>
+      <c r="R116" s="6"/>
+      <c r="S116" s="6"/>
+      <c r="T116" s="6"/>
+      <c r="U116" s="6"/>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B117" s="9">
-        <v>46169.67022677083</v>
+        <v>46170.633581828704</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46174.84878571759</v>
+        <v>46174.84878314815</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="I117" s="10"/>
       <c r="J117" s="9">
@@ -8392,13 +8367,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>357</v>
+        <v>26</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8408,26 +8383,26 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B118" s="5">
-        <v>46170.633581828704</v>
+        <v>46174.821057037036</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46174.84878314815</v>
+        <v>46174.84877914352</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>212</v>
+        <v>63</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="I118" s="6"/>
       <c r="J118" s="5">
@@ -8443,10 +8418,10 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>212</v>
+        <v>63</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>26</v>
@@ -8459,31 +8434,27 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B119" s="9">
-        <v>46174.821057037036</v>
+        <v>46169.67031616898</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46174.84877914352</v>
+        <v>46174.82401751158</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>63</v>
+        <v>359</v>
       </c>
       <c r="F119" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="H119" s="10" t="s">
-        <v>261</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H119" s="10"/>
       <c r="I119" s="10"/>
-      <c r="J119" s="9">
-        <v>46329</v>
-      </c>
+      <c r="J119" s="10"/>
       <c r="K119" s="10" t="s">
         <v>26</v>
       </c>
@@ -8491,13 +8462,13 @@
         <v>26</v>
       </c>
       <c r="M119" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>357</v>
+        <v>26</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>63</v>
+        <v>360</v>
       </c>
       <c r="P119" s="10" t="s">
         <v>26</v>
@@ -8510,27 +8481,33 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B120" s="5">
-        <v>46169.67031616898</v>
+        <v>46169.67031976852</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46174.82401751158</v>
+        <v>46174.84885483797</v>
       </c>
       <c r="E120" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="F120" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G120" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="F120" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G120" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H120" s="6"/>
-      <c r="I120" s="6"/>
-      <c r="J120" s="6"/>
+      <c r="H120" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="I120" s="5">
+        <v>46330</v>
+      </c>
+      <c r="J120" s="5">
+        <v>46338</v>
+      </c>
       <c r="K120" s="6" t="s">
         <v>26</v>
       </c>
@@ -8538,33 +8515,43 @@
         <v>26</v>
       </c>
       <c r="M120" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N120" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="O120" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="P120" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="Q120" s="5">
+        <v>46330</v>
+      </c>
+      <c r="R120" s="5">
+        <v>46338</v>
+      </c>
+      <c r="S120" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T120" s="6">
         <v>0</v>
       </c>
-      <c r="N120" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O120" s="6" t="s">
-        <v>364</v>
-      </c>
-      <c r="P120" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q120" s="6"/>
-      <c r="R120" s="6"/>
-      <c r="S120" s="6"/>
-      <c r="T120" s="6"/>
-      <c r="U120" s="6"/>
+      <c r="U120" s="12" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
         <v>365</v>
       </c>
       <c r="B121" s="9">
-        <v>46169.67031976852</v>
+        <v>46169.6703253125</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46174.84885483797</v>
+        <v>46192.97339644676</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>366</v>
@@ -8573,10 +8560,10 @@
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>367</v>
+        <v>69</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>368</v>
+        <v>70</v>
       </c>
       <c r="I121" s="9">
         <v>46330</v>
@@ -8594,13 +8581,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="Q121" s="9">
         <v>46330</v>
@@ -8620,33 +8607,27 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B122" s="5">
-        <v>46169.6703253125</v>
+        <v>46169.670332430556</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46174.84889408565</v>
+        <v>46174.82401726852</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F122" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="H122" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="I122" s="5">
-        <v>46330</v>
-      </c>
-      <c r="J122" s="5">
-        <v>46338</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H122" s="6"/>
+      <c r="I122" s="6"/>
+      <c r="J122" s="6"/>
       <c r="K122" s="6" t="s">
         <v>26</v>
       </c>
@@ -8654,23 +8635,19 @@
         <v>26</v>
       </c>
       <c r="M122" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>363</v>
+        <v>26</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>363</v>
-      </c>
-      <c r="Q122" s="5">
-        <v>46330</v>
-      </c>
-      <c r="R122" s="5">
-        <v>46338</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q122" s="6"/>
+      <c r="R122" s="6"/>
       <c r="S122" s="7" t="s">
         <v>33</v>
       </c>
@@ -8683,27 +8660,33 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B123" s="9">
-        <v>46169.670332430556</v>
+        <v>46169.67033591435</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46174.82401726852</v>
+        <v>46174.848958703704</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="F123" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H123" s="10"/>
-      <c r="I123" s="10"/>
-      <c r="J123" s="10"/>
+        <v>51</v>
+      </c>
+      <c r="H123" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I123" s="9">
+        <v>46330</v>
+      </c>
+      <c r="J123" s="9">
+        <v>46338</v>
+      </c>
       <c r="K123" s="10" t="s">
         <v>26</v>
       </c>
@@ -8711,19 +8694,23 @@
         <v>26</v>
       </c>
       <c r="M123" s="10" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>26</v>
+        <v>368</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>374</v>
+        <v>353</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q123" s="10"/>
-      <c r="R123" s="10"/>
+        <v>372</v>
+      </c>
+      <c r="Q123" s="9">
+        <v>46330</v>
+      </c>
+      <c r="R123" s="9">
+        <v>46338</v>
+      </c>
       <c r="S123" s="7" t="s">
         <v>33</v>
       </c>
@@ -8736,17 +8723,17 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B124" s="5">
-        <v>46169.67033591435</v>
+        <v>46169.67034748843</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46174.848958703704</v>
+        <v>46174.84895586806</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8758,10 +8745,10 @@
         <v>52</v>
       </c>
       <c r="I124" s="5">
-        <v>46330</v>
+        <v>46339</v>
       </c>
       <c r="J124" s="5">
-        <v>46338</v>
+        <v>46349</v>
       </c>
       <c r="K124" s="6" t="s">
         <v>26</v>
@@ -8773,19 +8760,19 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="Q124" s="5">
-        <v>46330</v>
+        <v>46339</v>
       </c>
       <c r="R124" s="5">
-        <v>46338</v>
+        <v>46349</v>
       </c>
       <c r="S124" s="7" t="s">
         <v>33</v>
@@ -8794,69 +8781,6 @@
         <v>0</v>
       </c>
       <c r="U124" s="12" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="125" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A125" s="8" t="s">
-        <v>378</v>
-      </c>
-      <c r="B125" s="9">
-        <v>46169.67034748843</v>
-      </c>
-      <c r="C125" s="10"/>
-      <c r="D125" s="9">
-        <v>46174.84895586806</v>
-      </c>
-      <c r="E125" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="F125" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G125" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="H125" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="I125" s="9">
-        <v>46339</v>
-      </c>
-      <c r="J125" s="9">
-        <v>46349</v>
-      </c>
-      <c r="K125" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L125" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M125" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N125" s="10" t="s">
-        <v>373</v>
-      </c>
-      <c r="O125" s="10" t="s">
-        <v>376</v>
-      </c>
-      <c r="P125" s="10" t="s">
-        <v>373</v>
-      </c>
-      <c r="Q125" s="9">
-        <v>46339</v>
-      </c>
-      <c r="R125" s="9">
-        <v>46349</v>
-      </c>
-      <c r="S125" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T125" s="10">
-        <v>0</v>
-      </c>
-      <c r="U125" s="12" t="s">
         <v>61</v>
       </c>
     </row>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1479" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1479" uniqueCount="376">
   <si>
     <t>50001558 -  GESVIAL</t>
   </si>
@@ -207,43 +207,43 @@
     <t xml:space="preserve">Ingenieria Servicios ,Propuesta Tableros </t>
   </si>
   <si>
+    <t>1215174266151861</t>
+  </si>
+  <si>
+    <t>Revision Tableros</t>
+  </si>
+  <si>
+    <t>sergio saavedra fernandez</t>
+  </si>
+  <si>
+    <t>sergio.saavedra@zitron.com</t>
+  </si>
+  <si>
+    <t>Recepcion Tableros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coordinacion Entrega con Cliente,Ingenieria Servicios </t>
+  </si>
+  <si>
+    <t>Tarea sin iniciar</t>
+  </si>
+  <si>
+    <t>1215174266151878</t>
+  </si>
+  <si>
+    <t>OT 4343 -VDF DANFOSS FC102 160KW</t>
+  </si>
+  <si>
+    <t>1215137857526708</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:</t>
+  </si>
+  <si>
+    <t>Ingenieria basica Rodete,Ingenieria Detalle,Ingenieria Basica Motor</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1215174266151861</t>
-  </si>
-  <si>
-    <t>Revision Tableros</t>
-  </si>
-  <si>
-    <t>sergio saavedra fernandez</t>
-  </si>
-  <si>
-    <t>sergio.saavedra@zitron.com</t>
-  </si>
-  <si>
-    <t>Recepcion Tableros</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coordinacion Entrega con Cliente,Ingenieria Servicios </t>
-  </si>
-  <si>
-    <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1215174266151878</t>
-  </si>
-  <si>
-    <t>OT 4343 -VDF DANFOSS FC102 160KW</t>
-  </si>
-  <si>
-    <t>1215137857526708</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:</t>
-  </si>
-  <si>
-    <t>Ingenieria basica Rodete,Ingenieria Detalle,Ingenieria Basica Motor</t>
   </si>
   <si>
     <t>1215174266168927</t>
@@ -658,6 +658,11 @@
   </si>
   <si>
     <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O/4342 - ZVN 1-16-160/4: CH1490
+Calaje: +9°
+Consumo estimado en fabrica: 140kW</t>
   </si>
   <si>
     <t>OT 4344 - MANGA DE VENTILACION Ø1600MM,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A</t>
@@ -1242,12 +1247,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFeec300"/>
+        <fgColor rgb="FFe8384f"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFe8384f"/>
+        <fgColor rgb="FFeec300"/>
       </patternFill>
     </fill>
   </fills>
@@ -2172,7 +2177,7 @@
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46169.669056666666</v>
+        <v>46195.60097974537</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -2217,9 +2222,11 @@
       <c r="B11" s="9">
         <v>46169.6689606713</v>
       </c>
-      <c r="C11" s="10"/>
+      <c r="C11" s="9">
+        <v>46195.600972824075</v>
+      </c>
       <c r="D11" s="9">
-        <v>46175.871370787034</v>
+        <v>46195.60099197917</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>50</v>
@@ -2267,15 +2274,15 @@
         <v>33</v>
       </c>
       <c r="T11" s="10">
-        <v>0</v>
-      </c>
-      <c r="U11" s="11" t="s">
-        <v>54</v>
+        <v>1</v>
+      </c>
+      <c r="U11" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B12" s="5">
         <v>46169.66896575232</v>
@@ -2285,16 +2292,16 @@
         <v>46174.82117752315</v>
       </c>
       <c r="E12" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G12" s="6" t="s">
+      <c r="H12" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="I12" s="5">
         <v>46223</v>
@@ -2315,10 +2322,10 @@
         <v>47</v>
       </c>
       <c r="O12" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="P12" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="P12" s="6" t="s">
-        <v>60</v>
       </c>
       <c r="Q12" s="5">
         <v>46223</v>
@@ -2332,13 +2339,13 @@
       <c r="T12" s="6">
         <v>0</v>
       </c>
-      <c r="U12" s="12" t="s">
-        <v>61</v>
+      <c r="U12" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B13" s="9">
         <v>46169.668971666666</v>
@@ -2348,16 +2355,16 @@
         <v>46191.686801284726</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G13" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H13" s="10" t="s">
         <v>57</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>58</v>
       </c>
       <c r="I13" s="9">
         <v>46223</v>
@@ -2375,13 +2382,13 @@
         <v>26</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q13" s="10"/>
       <c r="R13" s="10"/>
@@ -2391,7 +2398,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B14" s="5">
         <v>46169.66882583333</v>
@@ -2401,7 +2408,7 @@
         <v>46192.97341535879</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>25</v>
@@ -2425,7 +2432,7 @@
         <v>26</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P14" s="6" t="s">
         <v>26</v>
@@ -2434,8 +2441,8 @@
       <c r="R14" s="6"/>
       <c r="S14" s="6"/>
       <c r="T14" s="6"/>
-      <c r="U14" s="11" t="s">
-        <v>54</v>
+      <c r="U14" s="12" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
@@ -2479,7 +2486,7 @@
         <v>26</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O15" s="10" t="s">
         <v>40</v>
@@ -2544,7 +2551,7 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>40</v>
@@ -2609,7 +2616,7 @@
         <v>26</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O17" s="10" t="s">
         <v>40</v>
@@ -2934,8 +2941,8 @@
       <c r="T22" s="6">
         <v>0</v>
       </c>
-      <c r="U22" s="12" t="s">
-        <v>61</v>
+      <c r="U22" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
@@ -2997,8 +3004,8 @@
       <c r="T23" s="10">
         <v>0</v>
       </c>
-      <c r="U23" s="12" t="s">
-        <v>61</v>
+      <c r="U23" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
@@ -3060,8 +3067,8 @@
       <c r="T24" s="6">
         <v>0</v>
       </c>
-      <c r="U24" s="12" t="s">
-        <v>61</v>
+      <c r="U24" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -3123,8 +3130,8 @@
       <c r="T25" s="10">
         <v>0</v>
       </c>
-      <c r="U25" s="12" t="s">
-        <v>61</v>
+      <c r="U25" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
@@ -3134,9 +3141,11 @@
       <c r="B26" s="5">
         <v>46169.66904878472</v>
       </c>
-      <c r="C26" s="6"/>
+      <c r="C26" s="5">
+        <v>46195.601674432866</v>
+      </c>
       <c r="D26" s="5">
-        <v>46174.82504707176</v>
+        <v>46195.60168921296</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>109</v>
@@ -3184,10 +3193,10 @@
         <v>33</v>
       </c>
       <c r="T26" s="6">
-        <v>0</v>
-      </c>
-      <c r="U26" s="12" t="s">
-        <v>61</v>
+        <v>1</v>
+      </c>
+      <c r="U26" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
@@ -3359,8 +3368,8 @@
       <c r="T29" s="10">
         <v>0</v>
       </c>
-      <c r="U29" s="12" t="s">
-        <v>61</v>
+      <c r="U29" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -3420,8 +3429,8 @@
       <c r="T30" s="6">
         <v>0</v>
       </c>
-      <c r="U30" s="12" t="s">
-        <v>61</v>
+      <c r="U30" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -3479,7 +3488,7 @@
       <c r="R31" s="9">
         <v>46171</v>
       </c>
-      <c r="S31" s="12" t="s">
+      <c r="S31" s="11" t="s">
         <v>128</v>
       </c>
       <c r="T31" s="10">
@@ -3546,8 +3555,8 @@
       <c r="T32" s="6">
         <v>0</v>
       </c>
-      <c r="U32" s="12" t="s">
-        <v>61</v>
+      <c r="U32" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
@@ -3607,8 +3616,8 @@
       <c r="T33" s="10">
         <v>0</v>
       </c>
-      <c r="U33" s="12" t="s">
-        <v>61</v>
+      <c r="U33" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -3733,8 +3742,8 @@
       <c r="T35" s="10">
         <v>0</v>
       </c>
-      <c r="U35" s="12" t="s">
-        <v>61</v>
+      <c r="U35" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
@@ -3794,8 +3803,8 @@
       <c r="T36" s="6">
         <v>0</v>
       </c>
-      <c r="U36" s="12" t="s">
-        <v>61</v>
+      <c r="U36" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -3855,8 +3864,8 @@
       <c r="T37" s="10">
         <v>0</v>
       </c>
-      <c r="U37" s="12" t="s">
-        <v>61</v>
+      <c r="U37" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
@@ -3918,8 +3927,8 @@
       <c r="T38" s="6">
         <v>0</v>
       </c>
-      <c r="U38" s="12" t="s">
-        <v>61</v>
+      <c r="U38" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
@@ -3931,7 +3940,7 @@
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46174.8424871875</v>
+        <v>46195.601680694446</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>110</v>
@@ -4087,8 +4096,8 @@
       <c r="T41" s="10">
         <v>0</v>
       </c>
-      <c r="U41" s="12" t="s">
-        <v>61</v>
+      <c r="U41" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
@@ -4146,8 +4155,8 @@
       <c r="T42" s="6">
         <v>0</v>
       </c>
-      <c r="U42" s="12" t="s">
-        <v>61</v>
+      <c r="U42" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
@@ -4205,8 +4214,8 @@
       <c r="T43" s="10">
         <v>0</v>
       </c>
-      <c r="U43" s="12" t="s">
-        <v>61</v>
+      <c r="U43" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -4268,8 +4277,8 @@
       <c r="T44" s="6">
         <v>0</v>
       </c>
-      <c r="U44" s="12" t="s">
-        <v>61</v>
+      <c r="U44" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
@@ -4437,8 +4446,8 @@
       <c r="T47" s="10">
         <v>0</v>
       </c>
-      <c r="U47" s="12" t="s">
-        <v>61</v>
+      <c r="U47" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
@@ -4659,8 +4668,8 @@
       <c r="T51" s="10">
         <v>0</v>
       </c>
-      <c r="U51" s="12" t="s">
-        <v>61</v>
+      <c r="U51" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -4825,7 +4834,7 @@
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46191.69432710648</v>
+        <v>46195.60120340278</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>200</v>
@@ -4849,7 +4858,7 @@
         <v>26</v>
       </c>
       <c r="L55" s="10" t="s">
-        <v>26</v>
+        <v>203</v>
       </c>
       <c r="M55" s="10" t="s">
         <v>26</v>
@@ -4858,7 +4867,7 @@
         <v>197</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P55" s="10" t="s">
         <v>197</v>
@@ -4869,19 +4878,19 @@
       <c r="R55" s="9">
         <v>46184</v>
       </c>
-      <c r="S55" s="12" t="s">
+      <c r="S55" s="11" t="s">
         <v>128</v>
       </c>
       <c r="T55" s="10">
         <v>0</v>
       </c>
-      <c r="U55" s="12" t="s">
-        <v>61</v>
+      <c r="U55" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B56" s="5">
         <v>46169.66926408565</v>
@@ -4891,7 +4900,7 @@
         <v>46181.636760312496</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -4924,7 +4933,7 @@
         <v>78</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4934,7 +4943,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B57" s="9">
         <v>46169.66926952546</v>
@@ -4944,7 +4953,7 @@
         <v>46181.63675880787</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
@@ -4977,7 +4986,7 @@
         <v>78</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -4987,7 +4996,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B58" s="5">
         <v>46169.66929263889</v>
@@ -4997,7 +5006,7 @@
         <v>46174.846562824074</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -5027,7 +5036,7 @@
         <v>197</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>197</v>
@@ -5044,13 +5053,13 @@
       <c r="T58" s="6">
         <v>0</v>
       </c>
-      <c r="U58" s="12" t="s">
-        <v>61</v>
+      <c r="U58" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B59" s="9">
         <v>46169.66929775463</v>
@@ -5060,7 +5069,7 @@
         <v>46185.17154260416</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
@@ -5087,13 +5096,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5103,7 +5112,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B60" s="5">
         <v>46169.66930358796</v>
@@ -5113,7 +5122,7 @@
         <v>46185.17153893519</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
@@ -5140,13 +5149,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5156,7 +5165,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B61" s="9">
         <v>46169.669327048614</v>
@@ -5196,10 +5205,10 @@
         <v>197</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q61" s="9">
         <v>46240</v>
@@ -5213,13 +5222,13 @@
       <c r="T61" s="10">
         <v>0</v>
       </c>
-      <c r="U61" s="12" t="s">
-        <v>61</v>
+      <c r="U61" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B62" s="5">
         <v>46169.6693399537</v>
@@ -5229,7 +5238,7 @@
         <v>46188.17164222222</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5259,7 +5268,7 @@
         <v>97</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>97</v>
@@ -5272,7 +5281,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B63" s="9">
         <v>46169.66934443287</v>
@@ -5282,7 +5291,7 @@
         <v>46188.171644201386</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
@@ -5312,7 +5321,7 @@
         <v>97</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P63" s="10" t="s">
         <v>97</v>
@@ -5325,7 +5334,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B64" s="5">
         <v>46169.669361203705</v>
@@ -5335,16 +5344,16 @@
         <v>46174.84660805555</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I64" s="5">
         <v>46322</v>
@@ -5365,7 +5374,7 @@
         <v>197</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>26</v>
@@ -5382,13 +5391,13 @@
       <c r="T64" s="6">
         <v>0</v>
       </c>
-      <c r="U64" s="12" t="s">
-        <v>61</v>
+      <c r="U64" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B65" s="9">
         <v>46169.66936501158</v>
@@ -5398,16 +5407,16 @@
         <v>46174.846919421296</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I65" s="9">
         <v>46290</v>
@@ -5425,13 +5434,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5441,7 +5450,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B66" s="5">
         <v>46169.669418136575</v>
@@ -5451,7 +5460,7 @@
         <v>46170.59324665509</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>25</v>
@@ -5475,7 +5484,7 @@
         <v>26</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5488,7 +5497,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B67" s="9">
         <v>46169.66942685185</v>
@@ -5498,16 +5507,16 @@
         <v>46174.84701519676</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I67" s="9">
         <v>46258</v>
@@ -5525,13 +5534,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>164</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q67" s="9">
         <v>46258</v>
@@ -5545,13 +5554,13 @@
       <c r="T67" s="10">
         <v>0</v>
       </c>
-      <c r="U67" s="12" t="s">
-        <v>61</v>
+      <c r="U67" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B68" s="5">
         <v>46169.669432361115</v>
@@ -5561,7 +5570,7 @@
         <v>46174.847163576385</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5588,13 +5597,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q68" s="5">
         <v>46260</v>
@@ -5608,13 +5617,13 @@
       <c r="T68" s="6">
         <v>0</v>
       </c>
-      <c r="U68" s="12" t="s">
-        <v>61</v>
+      <c r="U68" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B69" s="9">
         <v>46169.66943836806</v>
@@ -5624,16 +5633,16 @@
         <v>46174.84701244213</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I69" s="9">
         <v>46258</v>
@@ -5651,13 +5660,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O69" s="10" t="s">
         <v>172</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q69" s="9">
         <v>46258</v>
@@ -5671,13 +5680,13 @@
       <c r="T69" s="10">
         <v>0</v>
       </c>
-      <c r="U69" s="12" t="s">
-        <v>61</v>
+      <c r="U69" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B70" s="5">
         <v>46169.669443692124</v>
@@ -5687,7 +5696,7 @@
         <v>46174.84716077546</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5714,13 +5723,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q70" s="5">
         <v>46260</v>
@@ -5734,13 +5743,13 @@
       <c r="T70" s="6">
         <v>0</v>
       </c>
-      <c r="U70" s="12" t="s">
-        <v>61</v>
+      <c r="U70" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B71" s="9">
         <v>46169.669448368055</v>
@@ -5750,16 +5759,16 @@
         <v>46174.84700815972</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I71" s="9">
         <v>46258</v>
@@ -5777,13 +5786,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O71" s="10" t="s">
         <v>194</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q71" s="9">
         <v>46258</v>
@@ -5797,13 +5806,13 @@
       <c r="T71" s="10">
         <v>0</v>
       </c>
-      <c r="U71" s="12" t="s">
-        <v>61</v>
+      <c r="U71" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B72" s="5">
         <v>46169.66945298611</v>
@@ -5813,7 +5822,7 @@
         <v>46174.847156944445</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5840,13 +5849,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q72" s="5">
         <v>46260</v>
@@ -5860,13 +5869,13 @@
       <c r="T72" s="6">
         <v>0</v>
       </c>
-      <c r="U72" s="12" t="s">
-        <v>61</v>
+      <c r="U72" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B73" s="9">
         <v>46169.66945778935</v>
@@ -5876,7 +5885,7 @@
         <v>46170.62754262731</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>25</v>
@@ -5900,7 +5909,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>26</v>
@@ -5913,7 +5922,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B74" s="5">
         <v>46169.66946104167</v>
@@ -5923,16 +5932,16 @@
         <v>46174.84730037037</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I74" s="5">
         <v>46262</v>
@@ -5950,13 +5959,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q74" s="5">
         <v>46262</v>
@@ -5970,13 +5979,13 @@
       <c r="T74" s="6">
         <v>0</v>
       </c>
-      <c r="U74" s="12" t="s">
-        <v>61</v>
+      <c r="U74" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B75" s="9">
         <v>46169.669467280095</v>
@@ -5986,16 +5995,16 @@
         <v>46174.84726460648</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I75" s="9">
         <v>46262</v>
@@ -6013,13 +6022,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6029,7 +6038,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B76" s="5">
         <v>46169.66947349537</v>
@@ -6039,16 +6048,16 @@
         <v>46174.84726170139</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I76" s="5">
         <v>46262</v>
@@ -6066,13 +6075,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6082,7 +6091,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B77" s="9">
         <v>46169.66950289352</v>
@@ -6092,16 +6101,16 @@
         <v>46174.847443506944</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I77" s="9">
         <v>46273</v>
@@ -6119,13 +6128,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q77" s="9">
         <v>46273</v>
@@ -6139,13 +6148,13 @@
       <c r="T77" s="10">
         <v>0</v>
       </c>
-      <c r="U77" s="12" t="s">
-        <v>61</v>
+      <c r="U77" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B78" s="5">
         <v>46169.66950758102</v>
@@ -6155,16 +6164,16 @@
         <v>46174.84741539352</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I78" s="5">
         <v>46273</v>
@@ -6182,13 +6191,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6198,7 +6207,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B79" s="9">
         <v>46169.66951364583</v>
@@ -6208,16 +6217,16 @@
         <v>46174.8474115625</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I79" s="9">
         <v>46273</v>
@@ -6235,13 +6244,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6251,7 +6260,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B80" s="5">
         <v>46169.66953380787</v>
@@ -6261,16 +6270,16 @@
         <v>46174.84760361111</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I80" s="5">
         <v>46294</v>
@@ -6288,13 +6297,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q80" s="5">
         <v>46294</v>
@@ -6308,13 +6317,13 @@
       <c r="T80" s="6">
         <v>0</v>
       </c>
-      <c r="U80" s="12" t="s">
-        <v>61</v>
+      <c r="U80" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B81" s="9">
         <v>46169.66953854167</v>
@@ -6324,16 +6333,16 @@
         <v>46174.84752376158</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I81" s="10"/>
       <c r="J81" s="9">
@@ -6349,13 +6358,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6365,7 +6374,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B82" s="5">
         <v>46169.669544212964</v>
@@ -6375,16 +6384,16 @@
         <v>46174.84752106482</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I82" s="6"/>
       <c r="J82" s="5">
@@ -6400,13 +6409,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6416,7 +6425,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B83" s="9">
         <v>46169.66960108797</v>
@@ -6426,7 +6435,7 @@
         <v>46171.686115625</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>25</v>
@@ -6450,7 +6459,7 @@
         <v>26</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P83" s="10" t="s">
         <v>26</v>
@@ -6463,7 +6472,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B84" s="5">
         <v>46169.66960956018</v>
@@ -6473,16 +6482,16 @@
         <v>46182.63458965278</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I84" s="5">
         <v>46174</v>
@@ -6500,13 +6509,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>133</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q84" s="5">
         <v>46174</v>
@@ -6514,19 +6523,19 @@
       <c r="R84" s="5">
         <v>46174</v>
       </c>
-      <c r="S84" s="12" t="s">
+      <c r="S84" s="11" t="s">
         <v>128</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
       </c>
-      <c r="U84" s="11" t="s">
-        <v>54</v>
+      <c r="U84" s="12" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B85" s="9">
         <v>46169.6696165162</v>
@@ -6536,16 +6545,16 @@
         <v>46182.63465568287</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I85" s="9">
         <v>46288</v>
@@ -6563,13 +6572,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O85" s="10" t="s">
         <v>123</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q85" s="9">
         <v>46288</v>
@@ -6583,13 +6592,13 @@
       <c r="T85" s="10">
         <v>0</v>
       </c>
-      <c r="U85" s="11" t="s">
-        <v>54</v>
+      <c r="U85" s="12" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B86" s="5">
         <v>46169.669622939815</v>
@@ -6599,16 +6608,16 @@
         <v>46182.63442767361</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I86" s="5">
         <v>46308</v>
@@ -6626,13 +6635,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>142</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q86" s="5">
         <v>46308</v>
@@ -6646,13 +6655,13 @@
       <c r="T86" s="6">
         <v>0</v>
       </c>
-      <c r="U86" s="11" t="s">
-        <v>54</v>
+      <c r="U86" s="12" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B87" s="9">
         <v>46169.66962980324</v>
@@ -6662,16 +6671,16 @@
         <v>46174.8477944676</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I87" s="9">
         <v>46287</v>
@@ -6689,13 +6698,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O87" s="10" t="s">
         <v>182</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q87" s="9">
         <v>46287</v>
@@ -6709,13 +6718,13 @@
       <c r="T87" s="10">
         <v>0</v>
       </c>
-      <c r="U87" s="12" t="s">
-        <v>61</v>
+      <c r="U87" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B88" s="5">
         <v>46169.669635185186</v>
@@ -6725,16 +6734,16 @@
         <v>46174.84778872685</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I88" s="5">
         <v>46220</v>
@@ -6752,13 +6761,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>153</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q88" s="5">
         <v>46220</v>
@@ -6772,13 +6781,13 @@
       <c r="T88" s="6">
         <v>0</v>
       </c>
-      <c r="U88" s="12" t="s">
-        <v>61</v>
+      <c r="U88" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B89" s="9">
         <v>46169.66964790509</v>
@@ -6788,7 +6797,7 @@
         <v>46171.71448712963</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>25</v>
@@ -6812,7 +6821,7 @@
         <v>26</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P89" s="10" t="s">
         <v>26</v>
@@ -6825,7 +6834,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B90" s="5">
         <v>46169.66965109954</v>
@@ -6835,7 +6844,7 @@
         <v>46174.84790094907</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6862,13 +6871,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q90" s="5">
         <v>46294</v>
@@ -6882,13 +6891,13 @@
       <c r="T90" s="6">
         <v>0</v>
       </c>
-      <c r="U90" s="12" t="s">
-        <v>61</v>
+      <c r="U90" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B91" s="9">
         <v>46169.6696568287</v>
@@ -6898,7 +6907,7 @@
         <v>46174.84798839121</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6925,13 +6934,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6941,7 +6950,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B92" s="5">
         <v>46169.669688622685</v>
@@ -6951,7 +6960,7 @@
         <v>46174.84789755787</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6978,13 +6987,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q92" s="5">
         <v>46316</v>
@@ -6998,13 +7007,13 @@
       <c r="T92" s="6">
         <v>0</v>
       </c>
-      <c r="U92" s="12" t="s">
-        <v>61</v>
+      <c r="U92" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B93" s="9">
         <v>46169.66969347223</v>
@@ -7014,7 +7023,7 @@
         <v>46174.84803712963</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7039,13 +7048,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7055,7 +7064,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B94" s="5">
         <v>46169.66972681713</v>
@@ -7065,7 +7074,7 @@
         <v>46174.84789414352</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7092,13 +7101,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q94" s="5">
         <v>46317</v>
@@ -7112,13 +7121,13 @@
       <c r="T94" s="6">
         <v>0</v>
       </c>
-      <c r="U94" s="12" t="s">
-        <v>61</v>
+      <c r="U94" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B95" s="9">
         <v>46169.66973180555</v>
@@ -7128,7 +7137,7 @@
         <v>46174.848081296295</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7155,13 +7164,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7171,7 +7180,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B96" s="5">
         <v>46169.66981054399</v>
@@ -7181,7 +7190,7 @@
         <v>46174.8478909375</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7208,13 +7217,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q96" s="5">
         <v>46318</v>
@@ -7228,13 +7237,13 @@
       <c r="T96" s="6">
         <v>0</v>
       </c>
-      <c r="U96" s="12" t="s">
-        <v>61</v>
+      <c r="U96" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B97" s="9">
         <v>46169.66981724537</v>
@@ -7244,7 +7253,7 @@
         <v>46174.84812851852</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7271,13 +7280,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7287,7 +7296,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B98" s="5">
         <v>46169.669861041664</v>
@@ -7297,7 +7306,7 @@
         <v>46174.8478862037</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7324,13 +7333,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q98" s="5">
         <v>46321</v>
@@ -7344,13 +7353,13 @@
       <c r="T98" s="6">
         <v>0</v>
       </c>
-      <c r="U98" s="12" t="s">
-        <v>61</v>
+      <c r="U98" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B99" s="9">
         <v>46169.66986724537</v>
@@ -7360,7 +7369,7 @@
         <v>46174.84816675926</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7387,13 +7396,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7403,7 +7412,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B100" s="5">
         <v>46169.66990296297</v>
@@ -7413,7 +7422,7 @@
         <v>46174.84788545139</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7440,13 +7449,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q100" s="5">
         <v>46323</v>
@@ -7460,13 +7469,13 @@
       <c r="T100" s="6">
         <v>0</v>
       </c>
-      <c r="U100" s="12" t="s">
-        <v>61</v>
+      <c r="U100" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B101" s="9">
         <v>46169.66994555556</v>
@@ -7476,7 +7485,7 @@
         <v>46174.848269317125</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7501,13 +7510,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7517,7 +7526,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B102" s="5">
         <v>46169.669978645834</v>
@@ -7527,7 +7536,7 @@
         <v>46174.82401747685</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>25</v>
@@ -7551,7 +7560,7 @@
         <v>26</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>26</v>
@@ -7564,7 +7573,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B103" s="9">
         <v>46169.66998244213</v>
@@ -7574,16 +7583,16 @@
         <v>46174.84843513889</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="I103" s="9">
         <v>46324</v>
@@ -7601,13 +7610,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q103" s="9">
         <v>46324</v>
@@ -7621,13 +7630,13 @@
       <c r="T103" s="10">
         <v>0</v>
       </c>
-      <c r="U103" s="12" t="s">
-        <v>61</v>
+      <c r="U103" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B104" s="5">
         <v>46169.66998994213</v>
@@ -7637,16 +7646,16 @@
         <v>46174.84838837963</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="I104" s="6"/>
       <c r="J104" s="5">
@@ -7662,13 +7671,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7678,7 +7687,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B105" s="9">
         <v>46170.63118891204</v>
@@ -7688,16 +7697,16 @@
         <v>46174.848385474535</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="I105" s="10"/>
       <c r="J105" s="9">
@@ -7713,13 +7722,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7729,7 +7738,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B106" s="5">
         <v>46174.820955891206</v>
@@ -7739,16 +7748,16 @@
         <v>46174.848381284726</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="I106" s="5">
         <v>46324</v>
@@ -7766,13 +7775,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7782,7 +7791,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B107" s="9">
         <v>46169.670044224535</v>
@@ -7792,7 +7801,7 @@
         <v>46174.848558831014</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7817,13 +7826,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q107" s="9">
         <v>46325</v>
@@ -7837,13 +7846,13 @@
       <c r="T107" s="10">
         <v>0</v>
       </c>
-      <c r="U107" s="12" t="s">
-        <v>61</v>
+      <c r="U107" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B108" s="5">
         <v>46169.670049050925</v>
@@ -7853,7 +7862,7 @@
         <v>46174.848527152775</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7878,13 +7887,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7894,7 +7903,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B109" s="9">
         <v>46170.63213679398</v>
@@ -7904,7 +7913,7 @@
         <v>46174.848524270834</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -7929,13 +7938,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -7945,7 +7954,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B110" s="5">
         <v>46174.82099290509</v>
@@ -7955,7 +7964,7 @@
         <v>46174.84852028935</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -7982,13 +7991,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -7998,7 +8007,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B111" s="9">
         <v>46169.67013976852</v>
@@ -8008,16 +8017,16 @@
         <v>46174.84870307871</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I111" s="10"/>
       <c r="J111" s="9">
@@ -8033,13 +8042,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q111" s="9">
         <v>46328</v>
@@ -8053,13 +8062,13 @@
       <c r="T111" s="10">
         <v>0</v>
       </c>
-      <c r="U111" s="12" t="s">
-        <v>61</v>
+      <c r="U111" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B112" s="5">
         <v>46169.670151377315</v>
@@ -8069,16 +8078,16 @@
         <v>46174.848669872685</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I112" s="5">
         <v>46328</v>
@@ -8096,13 +8105,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8112,7 +8121,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B113" s="9">
         <v>46170.63285997685</v>
@@ -8122,16 +8131,16 @@
         <v>46174.848667314815</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I113" s="9">
         <v>46328</v>
@@ -8149,13 +8158,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -8165,7 +8174,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B114" s="5">
         <v>46174.821024143515</v>
@@ -8175,16 +8184,16 @@
         <v>46174.84866336806</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I114" s="5">
         <v>46328</v>
@@ -8202,13 +8211,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8218,7 +8227,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B115" s="9">
         <v>46169.67021965278</v>
@@ -8228,16 +8237,16 @@
         <v>46174.84880980324</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I115" s="9">
         <v>46329</v>
@@ -8255,13 +8264,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q115" s="9">
         <v>46329</v>
@@ -8275,13 +8284,13 @@
       <c r="T115" s="10">
         <v>0</v>
       </c>
-      <c r="U115" s="12" t="s">
-        <v>61</v>
+      <c r="U115" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B116" s="5">
         <v>46169.67022677083</v>
@@ -8291,16 +8300,16 @@
         <v>46174.84878571759</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I116" s="6"/>
       <c r="J116" s="5">
@@ -8316,13 +8325,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8332,7 +8341,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B117" s="9">
         <v>46170.633581828704</v>
@@ -8342,16 +8351,16 @@
         <v>46174.84878314815</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I117" s="10"/>
       <c r="J117" s="9">
@@ -8367,10 +8376,10 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P117" s="10" t="s">
         <v>26</v>
@@ -8383,7 +8392,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B118" s="5">
         <v>46174.821057037036</v>
@@ -8393,16 +8402,16 @@
         <v>46174.84877914352</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I118" s="6"/>
       <c r="J118" s="5">
@@ -8418,10 +8427,10 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>26</v>
@@ -8434,7 +8443,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B119" s="9">
         <v>46169.67031616898</v>
@@ -8444,7 +8453,7 @@
         <v>46174.82401751158</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>25</v>
@@ -8468,7 +8477,7 @@
         <v>26</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="P119" s="10" t="s">
         <v>26</v>
@@ -8481,7 +8490,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B120" s="5">
         <v>46169.67031976852</v>
@@ -8491,16 +8500,16 @@
         <v>46174.84885483797</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I120" s="5">
         <v>46330</v>
@@ -8518,13 +8527,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q120" s="5">
         <v>46330</v>
@@ -8538,13 +8547,13 @@
       <c r="T120" s="6">
         <v>0</v>
       </c>
-      <c r="U120" s="12" t="s">
-        <v>61</v>
+      <c r="U120" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B121" s="9">
         <v>46169.6703253125</v>
@@ -8554,7 +8563,7 @@
         <v>46192.97339644676</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8581,13 +8590,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q121" s="9">
         <v>46330</v>
@@ -8601,13 +8610,13 @@
       <c r="T121" s="10">
         <v>0</v>
       </c>
-      <c r="U121" s="12" t="s">
-        <v>61</v>
+      <c r="U121" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B122" s="5">
         <v>46169.670332430556</v>
@@ -8617,7 +8626,7 @@
         <v>46174.82401726852</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>25</v>
@@ -8641,7 +8650,7 @@
         <v>26</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>26</v>
@@ -8654,13 +8663,13 @@
       <c r="T122" s="6">
         <v>0</v>
       </c>
-      <c r="U122" s="12" t="s">
-        <v>61</v>
+      <c r="U122" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B123" s="9">
         <v>46169.67033591435</v>
@@ -8670,7 +8679,7 @@
         <v>46174.848958703704</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8697,13 +8706,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q123" s="9">
         <v>46330</v>
@@ -8717,13 +8726,13 @@
       <c r="T123" s="10">
         <v>0</v>
       </c>
-      <c r="U123" s="12" t="s">
-        <v>61</v>
+      <c r="U123" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B124" s="5">
         <v>46169.67034748843</v>
@@ -8733,7 +8742,7 @@
         <v>46174.84895586806</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8760,13 +8769,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q124" s="5">
         <v>46339</v>
@@ -8780,8 +8789,8 @@
       <c r="T124" s="6">
         <v>0</v>
       </c>
-      <c r="U124" s="12" t="s">
-        <v>61</v>
+      <c r="U124" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -3877,7 +3877,7 @@
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46174.84252336806</v>
+        <v>46195.68641738426</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>148</v>
@@ -3938,9 +3938,11 @@
       <c r="B39" s="9">
         <v>46169.669149270834</v>
       </c>
-      <c r="C39" s="10"/>
+      <c r="C39" s="9">
+        <v>46195.686411111106</v>
+      </c>
       <c r="D39" s="9">
-        <v>46195.601680694446</v>
+        <v>46195.68641299769</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>110</v>
@@ -3993,7 +3995,7 @@
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46174.84248431713</v>
+        <v>46195.686418576384</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>153</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1479" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1480" uniqueCount="376">
   <si>
     <t>50001558 -  GESVIAL</t>
   </si>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46169.80567821759</v>
+        <v>46195.950137974534</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>197</v>
@@ -4825,7 +4825,9 @@
       <c r="R54" s="6"/>
       <c r="S54" s="6"/>
       <c r="T54" s="6"/>
-      <c r="U54" s="6"/>
+      <c r="U54" s="12" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
@@ -4834,9 +4836,11 @@
       <c r="B55" s="9">
         <v>46169.66925896991</v>
       </c>
-      <c r="C55" s="10"/>
+      <c r="C55" s="9">
+        <v>46195.950004328704</v>
+      </c>
       <c r="D55" s="9">
-        <v>46195.60120340278</v>
+        <v>46195.95001555556</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>200</v>
@@ -4884,10 +4888,10 @@
         <v>128</v>
       </c>
       <c r="T55" s="10">
-        <v>0</v>
-      </c>
-      <c r="U55" s="11" t="s">
-        <v>60</v>
+        <v>1</v>
+      </c>
+      <c r="U55" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
@@ -4897,9 +4901,11 @@
       <c r="B56" s="5">
         <v>46169.66926408565</v>
       </c>
-      <c r="C56" s="6"/>
+      <c r="C56" s="5">
+        <v>46195.94997732639</v>
+      </c>
       <c r="D56" s="5">
-        <v>46181.636760312496</v>
+        <v>46195.94997940972</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>206</v>
@@ -4950,9 +4956,11 @@
       <c r="B57" s="9">
         <v>46169.66926952546</v>
       </c>
-      <c r="C57" s="10"/>
+      <c r="C57" s="9">
+        <v>46195.9499871875</v>
+      </c>
       <c r="D57" s="9">
-        <v>46181.63675880787</v>
+        <v>46195.94998958333</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>209</v>
@@ -5003,9 +5011,11 @@
       <c r="B58" s="5">
         <v>46169.66929263889</v>
       </c>
-      <c r="C58" s="6"/>
+      <c r="C58" s="5">
+        <v>46195.95012040509</v>
+      </c>
       <c r="D58" s="5">
-        <v>46174.846562824074</v>
+        <v>46195.95013246528</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>212</v>
@@ -5053,10 +5063,10 @@
         <v>33</v>
       </c>
       <c r="T58" s="6">
-        <v>0</v>
-      </c>
-      <c r="U58" s="11" t="s">
-        <v>60</v>
+        <v>1</v>
+      </c>
+      <c r="U58" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -5066,9 +5076,11 @@
       <c r="B59" s="9">
         <v>46169.66929775463</v>
       </c>
-      <c r="C59" s="10"/>
+      <c r="C59" s="9">
+        <v>46195.950094699074</v>
+      </c>
       <c r="D59" s="9">
-        <v>46185.17154260416</v>
+        <v>46195.950096458335</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>206</v>
@@ -5119,9 +5131,11 @@
       <c r="B60" s="5">
         <v>46169.66930358796</v>
       </c>
-      <c r="C60" s="6"/>
+      <c r="C60" s="5">
+        <v>46195.950105219905</v>
+      </c>
       <c r="D60" s="5">
-        <v>46185.17153893519</v>
+        <v>46195.950106874996</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>209</v>
@@ -5174,7 +5188,7 @@
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46174.84655958333</v>
+        <v>46195.95042853009</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>97</v>
@@ -5235,9 +5249,11 @@
       <c r="B62" s="5">
         <v>46169.6693399537</v>
       </c>
-      <c r="C62" s="6"/>
+      <c r="C62" s="5">
+        <v>46195.950422222224</v>
+      </c>
       <c r="D62" s="5">
-        <v>46188.17164222222</v>
+        <v>46195.95042396991</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>206</v>
@@ -5290,7 +5306,7 @@
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46188.171644201386</v>
+        <v>46196.55961763889</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>209</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46196.55961763889</v>
+        <v>46196.570888738424</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>209</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1480" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1469" uniqueCount="374">
   <si>
     <t>50001558 -  GESVIAL</t>
   </si>
@@ -710,9 +710,6 @@
     <t>OT 4344 - MANGA DE VENTILACION Ø1600MM,Planos motor proveedor ot 4342</t>
   </si>
   <si>
-    <t>OT 4344 - MANGA DE VENTILACION Ø1600MM,Planos definitivos</t>
-  </si>
-  <si>
     <t>1215174260169824</t>
   </si>
   <si>
@@ -720,9 +717,6 @@
   </si>
   <si>
     <t>1215174141207989</t>
-  </si>
-  <si>
-    <t>1215174141208006</t>
   </si>
   <si>
     <t>1215174141212263</t>
@@ -1702,7 +1696,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U124"/>
+  <dimension ref="A1:U123"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -2891,7 +2885,7 @@
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46174.825234710646</v>
+        <v>46196.879980694444</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>94</v>
@@ -2941,8 +2935,8 @@
       <c r="T22" s="6">
         <v>0</v>
       </c>
-      <c r="U22" s="11" t="s">
-        <v>60</v>
+      <c r="U22" s="12" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
@@ -2954,7 +2948,7 @@
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46174.825231863426</v>
+        <v>46196.87998158565</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>100</v>
@@ -3004,8 +2998,8 @@
       <c r="T23" s="10">
         <v>0</v>
       </c>
-      <c r="U23" s="11" t="s">
-        <v>60</v>
+      <c r="U23" s="12" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
@@ -3017,7 +3011,7 @@
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46174.82522908565</v>
+        <v>46196.87998078704</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>103</v>
@@ -3067,8 +3061,8 @@
       <c r="T24" s="6">
         <v>0</v>
       </c>
-      <c r="U24" s="11" t="s">
-        <v>60</v>
+      <c r="U24" s="12" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -3080,7 +3074,7 @@
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46174.82522488426</v>
+        <v>46196.87998084491</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>106</v>
@@ -3130,8 +3124,8 @@
       <c r="T25" s="10">
         <v>0</v>
       </c>
-      <c r="U25" s="11" t="s">
-        <v>60</v>
+      <c r="U25" s="12" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
@@ -5135,7 +5129,7 @@
         <v>46195.950105219905</v>
       </c>
       <c r="D60" s="5">
-        <v>46195.950106874996</v>
+        <v>46196.87985491898</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>209</v>
@@ -5171,7 +5165,7 @@
         <v>218</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5181,14 +5175,16 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B61" s="9">
         <v>46169.669327048614</v>
       </c>
-      <c r="C61" s="10"/>
+      <c r="C61" s="9">
+        <v>46196.87995266204</v>
+      </c>
       <c r="D61" s="9">
-        <v>46195.95042853009</v>
+        <v>46196.879968090274</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>97</v>
@@ -5221,10 +5217,10 @@
         <v>197</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q61" s="9">
         <v>46240</v>
@@ -5236,15 +5232,15 @@
         <v>33</v>
       </c>
       <c r="T61" s="10">
-        <v>0</v>
-      </c>
-      <c r="U61" s="11" t="s">
-        <v>60</v>
+        <v>1</v>
+      </c>
+      <c r="U61" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B62" s="5">
         <v>46169.6693399537</v>
@@ -5299,32 +5295,32 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B63" s="9">
-        <v>46169.66934443287</v>
+        <v>46169.669361203705</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46196.570888738424</v>
+        <v>46174.84660805555</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="I63" s="9">
-        <v>46188</v>
+        <v>46322</v>
       </c>
       <c r="J63" s="9">
-        <v>46188</v>
+        <v>46322</v>
       </c>
       <c r="K63" s="10" t="s">
         <v>26</v>
@@ -5336,48 +5332,58 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>97</v>
+        <v>197</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q63" s="10"/>
-      <c r="R63" s="10"/>
-      <c r="S63" s="10"/>
-      <c r="T63" s="10"/>
-      <c r="U63" s="10"/>
+        <v>26</v>
+      </c>
+      <c r="Q63" s="9">
+        <v>46322</v>
+      </c>
+      <c r="R63" s="9">
+        <v>46322</v>
+      </c>
+      <c r="S63" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T63" s="10">
+        <v>0</v>
+      </c>
+      <c r="U63" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B64" s="5">
-        <v>46169.669361203705</v>
+        <v>46169.66936501158</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46174.84660805555</v>
+        <v>46174.846919421296</v>
       </c>
       <c r="E64" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="F64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G64" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>227</v>
-      </c>
       <c r="I64" s="5">
-        <v>46322</v>
+        <v>46290</v>
       </c>
       <c r="J64" s="5">
-        <v>46322</v>
+        <v>46290</v>
       </c>
       <c r="K64" s="6" t="s">
         <v>26</v>
@@ -5389,59 +5395,43 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>197</v>
+        <v>223</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q64" s="5">
-        <v>46322</v>
-      </c>
-      <c r="R64" s="5">
-        <v>46322</v>
-      </c>
-      <c r="S64" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T64" s="6">
-        <v>0</v>
-      </c>
-      <c r="U64" s="11" t="s">
-        <v>60</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="Q64" s="6"/>
+      <c r="R64" s="6"/>
+      <c r="S64" s="6"/>
+      <c r="T64" s="6"/>
+      <c r="U64" s="6"/>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
         <v>228</v>
       </c>
       <c r="B65" s="9">
-        <v>46169.66936501158</v>
+        <v>46169.669418136575</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46174.846919421296</v>
+        <v>46170.59324665509</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
       <c r="F65" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>227</v>
-      </c>
-      <c r="I65" s="9">
-        <v>46290</v>
-      </c>
-      <c r="J65" s="9">
-        <v>46290</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H65" s="10"/>
+      <c r="I65" s="10"/>
+      <c r="J65" s="10"/>
       <c r="K65" s="10" t="s">
         <v>26</v>
       </c>
@@ -5449,16 +5439,16 @@
         <v>26</v>
       </c>
       <c r="M65" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>225</v>
+        <v>26</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>206</v>
+        <v>230</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>229</v>
+        <v>26</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5468,27 +5458,33 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B66" s="5">
-        <v>46169.669418136575</v>
+        <v>46169.66942685185</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46170.59324665509</v>
+        <v>46174.84701519676</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H66" s="6"/>
-      <c r="I66" s="6"/>
-      <c r="J66" s="6"/>
+        <v>233</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="I66" s="5">
+        <v>46258</v>
+      </c>
+      <c r="J66" s="5">
+        <v>46259</v>
+      </c>
       <c r="K66" s="6" t="s">
         <v>26</v>
       </c>
@@ -5496,51 +5492,61 @@
         <v>26</v>
       </c>
       <c r="M66" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N66" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="O66" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="P66" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q66" s="5">
+        <v>46258</v>
+      </c>
+      <c r="R66" s="5">
+        <v>46259</v>
+      </c>
+      <c r="S66" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T66" s="6">
         <v>0</v>
       </c>
-      <c r="N66" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O66" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="P66" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q66" s="6"/>
-      <c r="R66" s="6"/>
-      <c r="S66" s="6"/>
-      <c r="T66" s="6"/>
-      <c r="U66" s="6"/>
+      <c r="U66" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B67" s="9">
-        <v>46169.66942685185</v>
+        <v>46169.669432361115</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46174.84701519676</v>
+        <v>46174.847163576385</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>235</v>
+        <v>186</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>236</v>
+        <v>187</v>
       </c>
       <c r="I67" s="9">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="J67" s="9">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="K67" s="10" t="s">
         <v>26</v>
@@ -5552,19 +5558,19 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>164</v>
+        <v>238</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q67" s="9">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="R67" s="9">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="S67" s="7" t="s">
         <v>33</v>
@@ -5578,32 +5584,32 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B68" s="5">
-        <v>46169.669432361115</v>
+        <v>46169.66943836806</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46174.847163576385</v>
+        <v>46174.84701244213</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>186</v>
+        <v>233</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>187</v>
+        <v>234</v>
       </c>
       <c r="I68" s="5">
-        <v>46260</v>
+        <v>46258</v>
       </c>
       <c r="J68" s="5">
-        <v>46261</v>
+        <v>46259</v>
       </c>
       <c r="K68" s="6" t="s">
         <v>26</v>
@@ -5615,19 +5621,19 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>240</v>
+        <v>172</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q68" s="5">
-        <v>46260</v>
+        <v>46258</v>
       </c>
       <c r="R68" s="5">
-        <v>46261</v>
+        <v>46259</v>
       </c>
       <c r="S68" s="7" t="s">
         <v>33</v>
@@ -5641,32 +5647,32 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B69" s="9">
-        <v>46169.66943836806</v>
+        <v>46169.669443692124</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46174.84701244213</v>
+        <v>46174.84716077546</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>235</v>
+        <v>186</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>236</v>
+        <v>187</v>
       </c>
       <c r="I69" s="9">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="J69" s="9">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="K69" s="10" t="s">
         <v>26</v>
@@ -5678,19 +5684,19 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>172</v>
+        <v>241</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q69" s="9">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="R69" s="9">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="S69" s="7" t="s">
         <v>33</v>
@@ -5704,32 +5710,32 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B70" s="5">
-        <v>46169.669443692124</v>
+        <v>46169.669448368055</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46174.84716077546</v>
+        <v>46174.84700815972</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>186</v>
+        <v>233</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>187</v>
+        <v>234</v>
       </c>
       <c r="I70" s="5">
-        <v>46260</v>
+        <v>46258</v>
       </c>
       <c r="J70" s="5">
-        <v>46261</v>
+        <v>46259</v>
       </c>
       <c r="K70" s="6" t="s">
         <v>26</v>
@@ -5741,19 +5747,19 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>243</v>
+        <v>194</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q70" s="5">
-        <v>46260</v>
+        <v>46258</v>
       </c>
       <c r="R70" s="5">
-        <v>46261</v>
+        <v>46259</v>
       </c>
       <c r="S70" s="7" t="s">
         <v>33</v>
@@ -5767,32 +5773,32 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B71" s="9">
-        <v>46169.669448368055</v>
+        <v>46169.66945298611</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46174.84700815972</v>
+        <v>46174.847156944445</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>235</v>
+        <v>186</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>236</v>
+        <v>187</v>
       </c>
       <c r="I71" s="9">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="J71" s="9">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="K71" s="10" t="s">
         <v>26</v>
@@ -5804,19 +5810,19 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>194</v>
+        <v>247</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="Q71" s="9">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="R71" s="9">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="S71" s="7" t="s">
         <v>33</v>
@@ -5830,33 +5836,27 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B72" s="5">
-        <v>46169.66945298611</v>
+        <v>46169.66945778935</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46174.847156944445</v>
+        <v>46170.62754262731</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="I72" s="5">
-        <v>46260</v>
-      </c>
-      <c r="J72" s="5">
-        <v>46261</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H72" s="6"/>
+      <c r="I72" s="6"/>
+      <c r="J72" s="6"/>
       <c r="K72" s="6" t="s">
         <v>26</v>
       </c>
@@ -5864,56 +5864,52 @@
         <v>26</v>
       </c>
       <c r="M72" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>231</v>
+        <v>26</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="Q72" s="5">
-        <v>46260</v>
-      </c>
-      <c r="R72" s="5">
-        <v>46261</v>
-      </c>
-      <c r="S72" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T72" s="6">
-        <v>0</v>
-      </c>
-      <c r="U72" s="11" t="s">
-        <v>60</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q72" s="6"/>
+      <c r="R72" s="6"/>
+      <c r="S72" s="6"/>
+      <c r="T72" s="6"/>
+      <c r="U72" s="6"/>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B73" s="9">
-        <v>46169.66945778935</v>
+        <v>46169.66946104167</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46170.62754262731</v>
+        <v>46174.84730037037</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F73" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H73" s="10"/>
-      <c r="I73" s="10"/>
-      <c r="J73" s="10"/>
+        <v>255</v>
+      </c>
+      <c r="H73" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="I73" s="9">
+        <v>46262</v>
+      </c>
+      <c r="J73" s="9">
+        <v>46272</v>
+      </c>
       <c r="K73" s="10" t="s">
         <v>26</v>
       </c>
@@ -5921,45 +5917,55 @@
         <v>26</v>
       </c>
       <c r="M73" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N73" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="O73" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="P73" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q73" s="9">
+        <v>46262</v>
+      </c>
+      <c r="R73" s="9">
+        <v>46272</v>
+      </c>
+      <c r="S73" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T73" s="10">
         <v>0</v>
       </c>
-      <c r="N73" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O73" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="P73" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q73" s="10"/>
-      <c r="R73" s="10"/>
-      <c r="S73" s="10"/>
-      <c r="T73" s="10"/>
-      <c r="U73" s="10"/>
+      <c r="U73" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B74" s="5">
-        <v>46169.66946104167</v>
+        <v>46169.669467280095</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46174.84730037037</v>
+        <v>46174.84726460648</v>
       </c>
       <c r="E74" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G74" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>256</v>
-      </c>
-      <c r="F74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G74" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="I74" s="5">
         <v>46262</v>
@@ -5977,52 +5983,42 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>259</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q74" s="5">
-        <v>46262</v>
-      </c>
-      <c r="R74" s="5">
-        <v>46272</v>
-      </c>
-      <c r="S74" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T74" s="6">
-        <v>0</v>
-      </c>
-      <c r="U74" s="11" t="s">
-        <v>60</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="Q74" s="6"/>
+      <c r="R74" s="6"/>
+      <c r="S74" s="6"/>
+      <c r="T74" s="6"/>
+      <c r="U74" s="6"/>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B75" s="9">
-        <v>46169.669467280095</v>
+        <v>46169.66947349537</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46174.84726460648</v>
+        <v>46174.84726170139</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>206</v>
+        <v>262</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="I75" s="9">
         <v>46262</v>
@@ -6040,13 +6036,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>262</v>
+        <v>209</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6056,32 +6052,32 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B76" s="5">
-        <v>46169.66947349537</v>
+        <v>46169.66950289352</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46174.84726170139</v>
+        <v>46174.847443506944</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="I76" s="5">
-        <v>46262</v>
+        <v>46273</v>
       </c>
       <c r="J76" s="5">
-        <v>46272</v>
+        <v>46293</v>
       </c>
       <c r="K76" s="6" t="s">
         <v>26</v>
@@ -6093,42 +6089,52 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>265</v>
+        <v>204</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q76" s="6"/>
-      <c r="R76" s="6"/>
-      <c r="S76" s="6"/>
-      <c r="T76" s="6"/>
-      <c r="U76" s="6"/>
+        <v>251</v>
+      </c>
+      <c r="Q76" s="5">
+        <v>46273</v>
+      </c>
+      <c r="R76" s="5">
+        <v>46293</v>
+      </c>
+      <c r="S76" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T76" s="6">
+        <v>0</v>
+      </c>
+      <c r="U76" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
         <v>266</v>
       </c>
       <c r="B77" s="9">
-        <v>46169.66950289352</v>
+        <v>46169.66950758102</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46174.847443506944</v>
+        <v>46196.87995929398</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>267</v>
+        <v>206</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="I77" s="9">
         <v>46273</v>
@@ -6146,52 +6152,42 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>204</v>
+        <v>267</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q77" s="9">
-        <v>46273</v>
-      </c>
-      <c r="R77" s="9">
-        <v>46293</v>
-      </c>
-      <c r="S77" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T77" s="10">
-        <v>0</v>
-      </c>
-      <c r="U77" s="11" t="s">
-        <v>60</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="Q77" s="10"/>
+      <c r="R77" s="10"/>
+      <c r="S77" s="10"/>
+      <c r="T77" s="10"/>
+      <c r="U77" s="10"/>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B78" s="5">
-        <v>46169.66950758102</v>
+        <v>46169.66951364583</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46174.84741539352</v>
+        <v>46196.87995984954</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="I78" s="5">
         <v>46273</v>
@@ -6209,13 +6205,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6225,32 +6221,32 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B79" s="9">
-        <v>46169.66951364583</v>
+        <v>46169.66953380787</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46174.8474115625</v>
+        <v>46174.84760361111</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>209</v>
+        <v>273</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="I79" s="9">
-        <v>46273</v>
+        <v>46294</v>
       </c>
       <c r="J79" s="9">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="K79" s="10" t="s">
         <v>26</v>
@@ -6262,46 +6258,54 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>267</v>
+        <v>251</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>272</v>
+        <v>204</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="Q79" s="10"/>
-      <c r="R79" s="10"/>
-      <c r="S79" s="10"/>
-      <c r="T79" s="10"/>
-      <c r="U79" s="10"/>
+        <v>251</v>
+      </c>
+      <c r="Q79" s="9">
+        <v>46294</v>
+      </c>
+      <c r="R79" s="9">
+        <v>46294</v>
+      </c>
+      <c r="S79" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T79" s="10">
+        <v>0</v>
+      </c>
+      <c r="U79" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
         <v>274</v>
       </c>
       <c r="B80" s="5">
-        <v>46169.66953380787</v>
+        <v>46169.66953854167</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46174.84760361111</v>
+        <v>46196.87996049768</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>275</v>
+        <v>206</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="I80" s="5">
-        <v>46294</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="I80" s="6"/>
       <c r="J80" s="5">
         <v>46294</v>
       </c>
@@ -6315,52 +6319,42 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>204</v>
+        <v>267</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q80" s="5">
-        <v>46294</v>
-      </c>
-      <c r="R80" s="5">
-        <v>46294</v>
-      </c>
-      <c r="S80" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T80" s="6">
-        <v>0</v>
-      </c>
-      <c r="U80" s="11" t="s">
-        <v>60</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="Q80" s="6"/>
+      <c r="R80" s="6"/>
+      <c r="S80" s="6"/>
+      <c r="T80" s="6"/>
+      <c r="U80" s="6"/>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
         <v>276</v>
       </c>
       <c r="B81" s="9">
-        <v>46169.66953854167</v>
+        <v>46169.669544212964</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46174.84752376158</v>
+        <v>46196.8799586574</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="I81" s="10"/>
       <c r="J81" s="9">
@@ -6376,13 +6370,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6392,31 +6386,27 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B82" s="5">
-        <v>46169.669544212964</v>
+        <v>46169.66960108797</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46174.84752106482</v>
+        <v>46171.686115625</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>209</v>
+        <v>229</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>258</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H82" s="6"/>
       <c r="I82" s="6"/>
-      <c r="J82" s="5">
-        <v>46294</v>
-      </c>
+      <c r="J82" s="6"/>
       <c r="K82" s="6" t="s">
         <v>26</v>
       </c>
@@ -6424,16 +6414,16 @@
         <v>26</v>
       </c>
       <c r="M82" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>275</v>
+        <v>26</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>280</v>
+        <v>26</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6446,24 +6436,30 @@
         <v>281</v>
       </c>
       <c r="B83" s="9">
-        <v>46169.66960108797</v>
+        <v>46169.66960956018</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46171.686115625</v>
+        <v>46182.63458965278</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>231</v>
+        <v>282</v>
       </c>
       <c r="F83" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H83" s="10"/>
-      <c r="I83" s="10"/>
-      <c r="J83" s="10"/>
+        <v>233</v>
+      </c>
+      <c r="H83" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="I83" s="9">
+        <v>46174</v>
+      </c>
+      <c r="J83" s="9">
+        <v>46174</v>
+      </c>
       <c r="K83" s="10" t="s">
         <v>26</v>
       </c>
@@ -6471,51 +6467,61 @@
         <v>26</v>
       </c>
       <c r="M83" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N83" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="O83" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="P83" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q83" s="9">
+        <v>46174</v>
+      </c>
+      <c r="R83" s="9">
+        <v>46174</v>
+      </c>
+      <c r="S83" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T83" s="10">
         <v>0</v>
       </c>
-      <c r="N83" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O83" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="P83" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q83" s="10"/>
-      <c r="R83" s="10"/>
-      <c r="S83" s="10"/>
-      <c r="T83" s="10"/>
-      <c r="U83" s="10"/>
+      <c r="U83" s="12" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B84" s="5">
-        <v>46169.66960956018</v>
+        <v>46169.6696165162</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46182.63458965278</v>
+        <v>46182.63465568287</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I84" s="5">
-        <v>46174</v>
+        <v>46288</v>
       </c>
       <c r="J84" s="5">
-        <v>46174</v>
+        <v>46288</v>
       </c>
       <c r="K84" s="6" t="s">
         <v>26</v>
@@ -6527,22 +6533,22 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q84" s="5">
-        <v>46174</v>
+        <v>46288</v>
       </c>
       <c r="R84" s="5">
-        <v>46174</v>
-      </c>
-      <c r="S84" s="11" t="s">
-        <v>128</v>
+        <v>46288</v>
+      </c>
+      <c r="S84" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
@@ -6553,32 +6559,32 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B85" s="9">
-        <v>46169.6696165162</v>
+        <v>46169.669622939815</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46182.63465568287</v>
+        <v>46182.63442767361</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I85" s="9">
-        <v>46288</v>
+        <v>46308</v>
       </c>
       <c r="J85" s="9">
-        <v>46288</v>
+        <v>46308</v>
       </c>
       <c r="K85" s="10" t="s">
         <v>26</v>
@@ -6590,19 +6596,19 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="Q85" s="9">
-        <v>46288</v>
+        <v>46308</v>
       </c>
       <c r="R85" s="9">
-        <v>46288</v>
+        <v>46308</v>
       </c>
       <c r="S85" s="7" t="s">
         <v>33</v>
@@ -6619,11 +6625,11 @@
         <v>289</v>
       </c>
       <c r="B86" s="5">
-        <v>46169.669622939815</v>
+        <v>46169.66962980324</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46182.63442767361</v>
+        <v>46174.8477944676</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>290</v>
@@ -6632,16 +6638,16 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I86" s="5">
-        <v>46308</v>
+        <v>46287</v>
       </c>
       <c r="J86" s="5">
-        <v>46308</v>
+        <v>46287</v>
       </c>
       <c r="K86" s="6" t="s">
         <v>26</v>
@@ -6653,19 +6659,19 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>142</v>
+        <v>182</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q86" s="5">
-        <v>46308</v>
+        <v>46287</v>
       </c>
       <c r="R86" s="5">
-        <v>46308</v>
+        <v>46287</v>
       </c>
       <c r="S86" s="7" t="s">
         <v>33</v>
@@ -6673,38 +6679,38 @@
       <c r="T86" s="6">
         <v>0</v>
       </c>
-      <c r="U86" s="12" t="s">
-        <v>66</v>
+      <c r="U86" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B87" s="9">
-        <v>46169.66962980324</v>
+        <v>46169.669635185186</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46174.8477944676</v>
+        <v>46174.84778872685</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>292</v>
+        <v>58</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I87" s="9">
-        <v>46287</v>
+        <v>46220</v>
       </c>
       <c r="J87" s="9">
-        <v>46287</v>
+        <v>46220</v>
       </c>
       <c r="K87" s="10" t="s">
         <v>26</v>
@@ -6716,19 +6722,19 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="P87" s="10" t="s">
         <v>293</v>
       </c>
       <c r="Q87" s="9">
-        <v>46287</v>
+        <v>46220</v>
       </c>
       <c r="R87" s="9">
-        <v>46287</v>
+        <v>46220</v>
       </c>
       <c r="S87" s="7" t="s">
         <v>33</v>
@@ -6745,30 +6751,24 @@
         <v>294</v>
       </c>
       <c r="B88" s="5">
-        <v>46169.669635185186</v>
+        <v>46169.66964790509</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46174.84778872685</v>
+        <v>46171.71448712963</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>58</v>
+        <v>295</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="I88" s="5">
-        <v>46220</v>
-      </c>
-      <c r="J88" s="5">
-        <v>46220</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H88" s="6"/>
+      <c r="I88" s="6"/>
+      <c r="J88" s="6"/>
       <c r="K88" s="6" t="s">
         <v>26</v>
       </c>
@@ -6776,56 +6776,52 @@
         <v>26</v>
       </c>
       <c r="M88" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>231</v>
+        <v>26</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>153</v>
+        <v>296</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="Q88" s="5">
-        <v>46220</v>
-      </c>
-      <c r="R88" s="5">
-        <v>46220</v>
-      </c>
-      <c r="S88" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T88" s="6">
-        <v>0</v>
-      </c>
-      <c r="U88" s="11" t="s">
-        <v>60</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q88" s="6"/>
+      <c r="R88" s="6"/>
+      <c r="S88" s="6"/>
+      <c r="T88" s="6"/>
+      <c r="U88" s="6"/>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B89" s="9">
-        <v>46169.66964790509</v>
+        <v>46169.66965109954</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46171.71448712963</v>
+        <v>46174.84790094907</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F89" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H89" s="10"/>
-      <c r="I89" s="10"/>
-      <c r="J89" s="10"/>
+        <v>91</v>
+      </c>
+      <c r="H89" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="I89" s="9">
+        <v>46294</v>
+      </c>
+      <c r="J89" s="9">
+        <v>46315</v>
+      </c>
       <c r="K89" s="10" t="s">
         <v>26</v>
       </c>
@@ -6833,36 +6829,46 @@
         <v>26</v>
       </c>
       <c r="M89" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N89" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="O89" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="P89" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q89" s="9">
+        <v>46294</v>
+      </c>
+      <c r="R89" s="9">
+        <v>46315</v>
+      </c>
+      <c r="S89" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T89" s="10">
         <v>0</v>
       </c>
-      <c r="N89" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O89" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="P89" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q89" s="10"/>
-      <c r="R89" s="10"/>
-      <c r="S89" s="10"/>
-      <c r="T89" s="10"/>
-      <c r="U89" s="10"/>
+      <c r="U89" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B90" s="5">
-        <v>46169.66965109954</v>
+        <v>46169.6696568287</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46174.84790094907</v>
+        <v>46174.84798839121</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>300</v>
+        <v>206</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6889,43 +6895,33 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>301</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q90" s="5">
-        <v>46294</v>
-      </c>
-      <c r="R90" s="5">
-        <v>46315</v>
-      </c>
-      <c r="S90" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T90" s="6">
-        <v>0</v>
-      </c>
-      <c r="U90" s="11" t="s">
-        <v>60</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="Q90" s="6"/>
+      <c r="R90" s="6"/>
+      <c r="S90" s="6"/>
+      <c r="T90" s="6"/>
+      <c r="U90" s="6"/>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
         <v>302</v>
       </c>
       <c r="B91" s="9">
-        <v>46169.6696568287</v>
+        <v>46169.669688622685</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46174.84798839121</v>
+        <v>46174.84789755787</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>206</v>
+        <v>303</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6937,10 +6933,10 @@
         <v>91</v>
       </c>
       <c r="I91" s="9">
-        <v>46294</v>
+        <v>46316</v>
       </c>
       <c r="J91" s="9">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="K91" s="10" t="s">
         <v>26</v>
@@ -6952,33 +6948,43 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>303</v>
+        <v>206</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q91" s="10"/>
-      <c r="R91" s="10"/>
-      <c r="S91" s="10"/>
-      <c r="T91" s="10"/>
-      <c r="U91" s="10"/>
+        <v>295</v>
+      </c>
+      <c r="Q91" s="9">
+        <v>46316</v>
+      </c>
+      <c r="R91" s="9">
+        <v>46316</v>
+      </c>
+      <c r="S91" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T91" s="10">
+        <v>0</v>
+      </c>
+      <c r="U91" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
         <v>304</v>
       </c>
       <c r="B92" s="5">
-        <v>46169.669688622685</v>
+        <v>46169.66969347223</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46174.84789755787</v>
+        <v>46196.87997025463</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>305</v>
+        <v>206</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6989,9 +6995,7 @@
       <c r="H92" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="I92" s="5">
-        <v>46316</v>
-      </c>
+      <c r="I92" s="6"/>
       <c r="J92" s="5">
         <v>46316</v>
       </c>
@@ -7005,43 +7009,33 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>206</v>
+        <v>305</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q92" s="5">
-        <v>46316</v>
-      </c>
-      <c r="R92" s="5">
-        <v>46316</v>
-      </c>
-      <c r="S92" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T92" s="6">
-        <v>0</v>
-      </c>
-      <c r="U92" s="11" t="s">
-        <v>60</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="Q92" s="6"/>
+      <c r="R92" s="6"/>
+      <c r="S92" s="6"/>
+      <c r="T92" s="6"/>
+      <c r="U92" s="6"/>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B93" s="9">
-        <v>46169.66969347223</v>
+        <v>46169.66972681713</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46174.84803712963</v>
+        <v>46174.84789414352</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>206</v>
+        <v>308</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7052,9 +7046,11 @@
       <c r="H93" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="I93" s="10"/>
+      <c r="I93" s="9">
+        <v>46317</v>
+      </c>
       <c r="J93" s="9">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="K93" s="10" t="s">
         <v>26</v>
@@ -7066,33 +7062,43 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>307</v>
+        <v>206</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="Q93" s="10"/>
-      <c r="R93" s="10"/>
-      <c r="S93" s="10"/>
-      <c r="T93" s="10"/>
-      <c r="U93" s="10"/>
+        <v>295</v>
+      </c>
+      <c r="Q93" s="9">
+        <v>46317</v>
+      </c>
+      <c r="R93" s="9">
+        <v>46317</v>
+      </c>
+      <c r="S93" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T93" s="10">
+        <v>0</v>
+      </c>
+      <c r="U93" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
         <v>309</v>
       </c>
       <c r="B94" s="5">
-        <v>46169.66972681713</v>
+        <v>46169.66973180555</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46174.84789414352</v>
+        <v>46196.87996092593</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>310</v>
+        <v>206</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7119,43 +7125,33 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>206</v>
+        <v>310</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q94" s="5">
-        <v>46317</v>
-      </c>
-      <c r="R94" s="5">
-        <v>46317</v>
-      </c>
-      <c r="S94" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T94" s="6">
-        <v>0</v>
-      </c>
-      <c r="U94" s="11" t="s">
-        <v>60</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="Q94" s="6"/>
+      <c r="R94" s="6"/>
+      <c r="S94" s="6"/>
+      <c r="T94" s="6"/>
+      <c r="U94" s="6"/>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B95" s="9">
-        <v>46169.66973180555</v>
+        <v>46169.66981054399</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46174.848081296295</v>
+        <v>46174.8478909375</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>206</v>
+        <v>313</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7167,10 +7163,10 @@
         <v>91</v>
       </c>
       <c r="I95" s="9">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="J95" s="9">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="K95" s="10" t="s">
         <v>26</v>
@@ -7182,33 +7178,43 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>312</v>
+        <v>206</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>313</v>
-      </c>
-      <c r="Q95" s="10"/>
-      <c r="R95" s="10"/>
-      <c r="S95" s="10"/>
-      <c r="T95" s="10"/>
-      <c r="U95" s="10"/>
+        <v>295</v>
+      </c>
+      <c r="Q95" s="9">
+        <v>46318</v>
+      </c>
+      <c r="R95" s="9">
+        <v>46318</v>
+      </c>
+      <c r="S95" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T95" s="10">
+        <v>0</v>
+      </c>
+      <c r="U95" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
         <v>314</v>
       </c>
       <c r="B96" s="5">
-        <v>46169.66981054399</v>
+        <v>46169.66981724537</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46174.8478909375</v>
+        <v>46196.87997091435</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>315</v>
+        <v>206</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7235,43 +7241,33 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>206</v>
+        <v>315</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q96" s="5">
-        <v>46318</v>
-      </c>
-      <c r="R96" s="5">
-        <v>46318</v>
-      </c>
-      <c r="S96" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T96" s="6">
-        <v>0</v>
-      </c>
-      <c r="U96" s="11" t="s">
-        <v>60</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="Q96" s="6"/>
+      <c r="R96" s="6"/>
+      <c r="S96" s="6"/>
+      <c r="T96" s="6"/>
+      <c r="U96" s="6"/>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B97" s="9">
-        <v>46169.66981724537</v>
+        <v>46169.669861041664</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46174.84812851852</v>
+        <v>46174.8478862037</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>206</v>
+        <v>318</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7283,10 +7279,10 @@
         <v>91</v>
       </c>
       <c r="I97" s="9">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="J97" s="9">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="K97" s="10" t="s">
         <v>26</v>
@@ -7298,33 +7294,43 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>315</v>
+        <v>295</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>317</v>
+        <v>206</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="Q97" s="10"/>
-      <c r="R97" s="10"/>
-      <c r="S97" s="10"/>
-      <c r="T97" s="10"/>
-      <c r="U97" s="10"/>
+        <v>295</v>
+      </c>
+      <c r="Q97" s="9">
+        <v>46321</v>
+      </c>
+      <c r="R97" s="9">
+        <v>46321</v>
+      </c>
+      <c r="S97" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T97" s="10">
+        <v>0</v>
+      </c>
+      <c r="U97" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
         <v>319</v>
       </c>
       <c r="B98" s="5">
-        <v>46169.669861041664</v>
+        <v>46169.66986724537</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46174.8478862037</v>
+        <v>46174.84816675926</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>320</v>
+        <v>206</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7351,43 +7357,33 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="O98" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q98" s="5">
-        <v>46321</v>
-      </c>
-      <c r="R98" s="5">
-        <v>46321</v>
-      </c>
-      <c r="S98" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T98" s="6">
-        <v>0</v>
-      </c>
-      <c r="U98" s="11" t="s">
-        <v>60</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="Q98" s="6"/>
+      <c r="R98" s="6"/>
+      <c r="S98" s="6"/>
+      <c r="T98" s="6"/>
+      <c r="U98" s="6"/>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
         <v>321</v>
       </c>
       <c r="B99" s="9">
-        <v>46169.66986724537</v>
+        <v>46169.66990296297</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46174.84816675926</v>
+        <v>46174.84788545139</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>206</v>
+        <v>322</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7399,10 +7395,10 @@
         <v>91</v>
       </c>
       <c r="I99" s="9">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="J99" s="9">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="K99" s="10" t="s">
         <v>26</v>
@@ -7414,33 +7410,43 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>320</v>
+        <v>295</v>
       </c>
       <c r="O99" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>322</v>
-      </c>
-      <c r="Q99" s="10"/>
-      <c r="R99" s="10"/>
-      <c r="S99" s="10"/>
-      <c r="T99" s="10"/>
-      <c r="U99" s="10"/>
+        <v>323</v>
+      </c>
+      <c r="Q99" s="9">
+        <v>46323</v>
+      </c>
+      <c r="R99" s="9">
+        <v>46323</v>
+      </c>
+      <c r="S99" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T99" s="10">
+        <v>0</v>
+      </c>
+      <c r="U99" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B100" s="5">
-        <v>46169.66990296297</v>
+        <v>46169.66994555556</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46174.84788545139</v>
+        <v>46174.848269317125</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>324</v>
+        <v>206</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7451,9 +7457,7 @@
       <c r="H100" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="I100" s="5">
-        <v>46323</v>
-      </c>
+      <c r="I100" s="6"/>
       <c r="J100" s="5">
         <v>46323</v>
       </c>
@@ -7467,7 +7471,7 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>297</v>
+        <v>322</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>206</v>
@@ -7475,49 +7479,35 @@
       <c r="P100" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="Q100" s="5">
-        <v>46323</v>
-      </c>
-      <c r="R100" s="5">
-        <v>46323</v>
-      </c>
-      <c r="S100" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T100" s="6">
-        <v>0</v>
-      </c>
-      <c r="U100" s="11" t="s">
-        <v>60</v>
-      </c>
+      <c r="Q100" s="6"/>
+      <c r="R100" s="6"/>
+      <c r="S100" s="6"/>
+      <c r="T100" s="6"/>
+      <c r="U100" s="6"/>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
         <v>326</v>
       </c>
       <c r="B101" s="9">
-        <v>46169.66994555556</v>
+        <v>46169.669978645834</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46174.848269317125</v>
+        <v>46174.82401747685</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>206</v>
+        <v>327</v>
       </c>
       <c r="F101" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H101" s="10"/>
       <c r="I101" s="10"/>
-      <c r="J101" s="9">
-        <v>46323</v>
-      </c>
+      <c r="J101" s="10"/>
       <c r="K101" s="10" t="s">
         <v>26</v>
       </c>
@@ -7525,16 +7515,16 @@
         <v>26</v>
       </c>
       <c r="M101" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>324</v>
+        <v>26</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>206</v>
+        <v>328</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>327</v>
+        <v>26</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7544,27 +7534,33 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B102" s="5">
-        <v>46169.669978645834</v>
+        <v>46169.66998244213</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46174.82401747685</v>
+        <v>46174.84843513889</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H102" s="6"/>
-      <c r="I102" s="6"/>
-      <c r="J102" s="6"/>
+        <v>331</v>
+      </c>
+      <c r="H102" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="I102" s="5">
+        <v>46324</v>
+      </c>
+      <c r="J102" s="5">
+        <v>46324</v>
+      </c>
       <c r="K102" s="6" t="s">
         <v>26</v>
       </c>
@@ -7572,49 +7568,57 @@
         <v>26</v>
       </c>
       <c r="M102" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N102" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="O102" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="P102" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="Q102" s="5">
+        <v>46324</v>
+      </c>
+      <c r="R102" s="5">
+        <v>46324</v>
+      </c>
+      <c r="S102" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T102" s="6">
         <v>0</v>
       </c>
-      <c r="N102" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O102" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="P102" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q102" s="6"/>
-      <c r="R102" s="6"/>
-      <c r="S102" s="6"/>
-      <c r="T102" s="6"/>
-      <c r="U102" s="6"/>
+      <c r="U102" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B103" s="9">
-        <v>46169.66998244213</v>
+        <v>46169.66998994213</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46174.84843513889</v>
+        <v>46174.84838837963</v>
       </c>
       <c r="E103" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="F103" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G103" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="H103" s="10" t="s">
         <v>332</v>
       </c>
-      <c r="F103" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G103" s="10" t="s">
-        <v>333</v>
-      </c>
-      <c r="H103" s="10" t="s">
-        <v>334</v>
-      </c>
-      <c r="I103" s="9">
-        <v>46324</v>
-      </c>
+      <c r="I103" s="10"/>
       <c r="J103" s="9">
         <v>46324</v>
       </c>
@@ -7628,52 +7632,42 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O103" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="P103" s="10" t="s">
         <v>335</v>
       </c>
-      <c r="P103" s="10" t="s">
-        <v>329</v>
-      </c>
-      <c r="Q103" s="9">
-        <v>46324</v>
-      </c>
-      <c r="R103" s="9">
-        <v>46324</v>
-      </c>
-      <c r="S103" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T103" s="10">
-        <v>0</v>
-      </c>
-      <c r="U103" s="11" t="s">
-        <v>60</v>
-      </c>
+      <c r="Q103" s="10"/>
+      <c r="R103" s="10"/>
+      <c r="S103" s="10"/>
+      <c r="T103" s="10"/>
+      <c r="U103" s="10"/>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
         <v>336</v>
       </c>
       <c r="B104" s="5">
-        <v>46169.66998994213</v>
+        <v>46170.63118891204</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46174.84838837963</v>
+        <v>46174.848385474535</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="I104" s="6"/>
       <c r="J104" s="5">
@@ -7689,13 +7683,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>337</v>
+        <v>209</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7705,28 +7699,30 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B105" s="9">
-        <v>46170.63118891204</v>
+        <v>46174.820955891206</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46174.848385474535</v>
+        <v>46174.848381284726</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>209</v>
+        <v>62</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>334</v>
-      </c>
-      <c r="I105" s="10"/>
+        <v>332</v>
+      </c>
+      <c r="I105" s="9">
+        <v>46324</v>
+      </c>
       <c r="J105" s="9">
         <v>46324</v>
       </c>
@@ -7740,13 +7736,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>209</v>
+        <v>62</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>209</v>
+        <v>338</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7759,29 +7755,27 @@
         <v>339</v>
       </c>
       <c r="B106" s="5">
-        <v>46174.820955891206</v>
+        <v>46169.670044224535</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46174.848381284726</v>
+        <v>46174.848558831014</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>62</v>
+        <v>340</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>333</v>
+        <v>91</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="I106" s="5">
-        <v>46324</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="I106" s="6"/>
       <c r="J106" s="5">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="K106" s="6" t="s">
         <v>26</v>
@@ -7793,33 +7787,43 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>62</v>
+        <v>206</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="Q106" s="6"/>
-      <c r="R106" s="6"/>
-      <c r="S106" s="6"/>
-      <c r="T106" s="6"/>
-      <c r="U106" s="6"/>
+        <v>327</v>
+      </c>
+      <c r="Q106" s="5">
+        <v>46325</v>
+      </c>
+      <c r="R106" s="5">
+        <v>46325</v>
+      </c>
+      <c r="S106" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T106" s="6">
+        <v>0</v>
+      </c>
+      <c r="U106" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
         <v>341</v>
       </c>
       <c r="B107" s="9">
-        <v>46169.670044224535</v>
+        <v>46169.670049050925</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46174.848558831014</v>
+        <v>46174.848527152775</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>342</v>
+        <v>206</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7844,43 +7848,33 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="O107" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>329</v>
-      </c>
-      <c r="Q107" s="9">
-        <v>46325</v>
-      </c>
-      <c r="R107" s="9">
-        <v>46325</v>
-      </c>
-      <c r="S107" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T107" s="10">
-        <v>0</v>
-      </c>
-      <c r="U107" s="11" t="s">
-        <v>60</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="Q107" s="10"/>
+      <c r="R107" s="10"/>
+      <c r="S107" s="10"/>
+      <c r="T107" s="10"/>
+      <c r="U107" s="10"/>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
         <v>343</v>
       </c>
       <c r="B108" s="5">
-        <v>46169.670049050925</v>
+        <v>46170.63213679398</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46174.848527152775</v>
+        <v>46174.848524270834</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7905,13 +7899,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>344</v>
+        <v>209</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7921,17 +7915,17 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B109" s="9">
-        <v>46170.63213679398</v>
+        <v>46174.82099290509</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46174.848524270834</v>
+        <v>46174.84852028935</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>209</v>
+        <v>338</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -7942,7 +7936,9 @@
       <c r="H109" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="I109" s="10"/>
+      <c r="I109" s="9">
+        <v>46325</v>
+      </c>
       <c r="J109" s="9">
         <v>46325</v>
       </c>
@@ -7956,13 +7952,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>209</v>
+        <v>62</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>209</v>
+        <v>62</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -7972,32 +7968,30 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B110" s="5">
-        <v>46174.82099290509</v>
+        <v>46169.67013976852</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46174.84852028935</v>
+        <v>46174.84870307871</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>91</v>
+        <v>255</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="I110" s="5">
-        <v>46325</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="I110" s="6"/>
       <c r="J110" s="5">
-        <v>46325</v>
+        <v>46328</v>
       </c>
       <c r="K110" s="6" t="s">
         <v>26</v>
@@ -8009,44 +8003,56 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>62</v>
+        <v>206</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q110" s="6"/>
-      <c r="R110" s="6"/>
-      <c r="S110" s="6"/>
-      <c r="T110" s="6"/>
-      <c r="U110" s="6"/>
+        <v>327</v>
+      </c>
+      <c r="Q110" s="5">
+        <v>46328</v>
+      </c>
+      <c r="R110" s="5">
+        <v>46328</v>
+      </c>
+      <c r="S110" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T110" s="6">
+        <v>0</v>
+      </c>
+      <c r="U110" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
         <v>347</v>
       </c>
       <c r="B111" s="9">
-        <v>46169.67013976852</v>
+        <v>46169.670151377315</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46174.84870307871</v>
+        <v>46174.848669872685</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>348</v>
+        <v>206</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="I111" s="10"/>
+        <v>256</v>
+      </c>
+      <c r="I111" s="9">
+        <v>46328</v>
+      </c>
       <c r="J111" s="9">
         <v>46328</v>
       </c>
@@ -8060,52 +8066,42 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>329</v>
+        <v>346</v>
       </c>
       <c r="O111" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>329</v>
-      </c>
-      <c r="Q111" s="9">
-        <v>46328</v>
-      </c>
-      <c r="R111" s="9">
-        <v>46328</v>
-      </c>
-      <c r="S111" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T111" s="10">
-        <v>0</v>
-      </c>
-      <c r="U111" s="11" t="s">
-        <v>60</v>
-      </c>
+        <v>348</v>
+      </c>
+      <c r="Q111" s="10"/>
+      <c r="R111" s="10"/>
+      <c r="S111" s="10"/>
+      <c r="T111" s="10"/>
+      <c r="U111" s="10"/>
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
         <v>349</v>
       </c>
       <c r="B112" s="5">
-        <v>46169.670151377315</v>
+        <v>46170.63285997685</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46174.848669872685</v>
+        <v>46174.848667314815</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="I112" s="5">
         <v>46328</v>
@@ -8123,13 +8119,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>350</v>
+        <v>209</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8139,26 +8135,26 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B113" s="9">
-        <v>46170.63285997685</v>
+        <v>46174.821024143515</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46174.848667314815</v>
+        <v>46174.84866336806</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>209</v>
+        <v>62</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="I113" s="9">
         <v>46328</v>
@@ -8176,13 +8172,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>209</v>
+        <v>338</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>209</v>
+        <v>62</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -8192,32 +8188,32 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B114" s="5">
-        <v>46174.821024143515</v>
+        <v>46169.67021965278</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46174.84866336806</v>
+        <v>46174.84880980324</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>62</v>
+        <v>352</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="I114" s="5">
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="J114" s="5">
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="K114" s="6" t="s">
         <v>26</v>
@@ -8229,46 +8225,54 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>340</v>
+        <v>206</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q114" s="6"/>
-      <c r="R114" s="6"/>
-      <c r="S114" s="6"/>
-      <c r="T114" s="6"/>
-      <c r="U114" s="6"/>
+        <v>353</v>
+      </c>
+      <c r="Q114" s="5">
+        <v>46329</v>
+      </c>
+      <c r="R114" s="5">
+        <v>46329</v>
+      </c>
+      <c r="S114" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T114" s="6">
+        <v>0</v>
+      </c>
+      <c r="U114" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B115" s="9">
-        <v>46169.67021965278</v>
+        <v>46169.67022677083</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46174.84880980324</v>
+        <v>46174.84878571759</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>354</v>
+        <v>206</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="I115" s="9">
-        <v>46329</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="I115" s="10"/>
       <c r="J115" s="9">
         <v>46329</v>
       </c>
@@ -8282,52 +8286,42 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>329</v>
+        <v>352</v>
       </c>
       <c r="O115" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="Q115" s="9">
-        <v>46329</v>
-      </c>
-      <c r="R115" s="9">
-        <v>46329</v>
-      </c>
-      <c r="S115" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T115" s="10">
-        <v>0</v>
-      </c>
-      <c r="U115" s="11" t="s">
-        <v>60</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="Q115" s="10"/>
+      <c r="R115" s="10"/>
+      <c r="S115" s="10"/>
+      <c r="T115" s="10"/>
+      <c r="U115" s="10"/>
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B116" s="5">
-        <v>46169.67022677083</v>
+        <v>46170.633581828704</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46174.84878571759</v>
+        <v>46174.84878314815</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="I116" s="6"/>
       <c r="J116" s="5">
@@ -8343,13 +8337,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>354</v>
+        <v>26</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8359,26 +8353,26 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B117" s="9">
-        <v>46170.633581828704</v>
+        <v>46174.821057037036</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46174.84878314815</v>
+        <v>46174.84877914352</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>209</v>
+        <v>62</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="I117" s="10"/>
       <c r="J117" s="9">
@@ -8394,10 +8388,10 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>209</v>
+        <v>62</v>
       </c>
       <c r="P117" s="10" t="s">
         <v>26</v>
@@ -8410,31 +8404,27 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B118" s="5">
-        <v>46174.821057037036</v>
+        <v>46169.67031616898</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46174.84877914352</v>
+        <v>46174.82401751158</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>62</v>
+        <v>358</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="H118" s="6" t="s">
-        <v>258</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H118" s="6"/>
       <c r="I118" s="6"/>
-      <c r="J118" s="5">
-        <v>46329</v>
-      </c>
+      <c r="J118" s="6"/>
       <c r="K118" s="6" t="s">
         <v>26</v>
       </c>
@@ -8442,13 +8432,13 @@
         <v>26</v>
       </c>
       <c r="M118" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>354</v>
+        <v>26</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>62</v>
+        <v>359</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>26</v>
@@ -8461,27 +8451,33 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B119" s="9">
-        <v>46169.67031616898</v>
+        <v>46169.67031976852</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46174.82401751158</v>
+        <v>46174.84885483797</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F119" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H119" s="10"/>
-      <c r="I119" s="10"/>
-      <c r="J119" s="10"/>
+        <v>362</v>
+      </c>
+      <c r="H119" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="I119" s="9">
+        <v>46330</v>
+      </c>
+      <c r="J119" s="9">
+        <v>46338</v>
+      </c>
       <c r="K119" s="10" t="s">
         <v>26</v>
       </c>
@@ -8489,45 +8485,55 @@
         <v>26</v>
       </c>
       <c r="M119" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N119" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="O119" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="P119" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="Q119" s="9">
+        <v>46330</v>
+      </c>
+      <c r="R119" s="9">
+        <v>46338</v>
+      </c>
+      <c r="S119" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T119" s="10">
         <v>0</v>
       </c>
-      <c r="N119" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O119" s="10" t="s">
-        <v>361</v>
-      </c>
-      <c r="P119" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q119" s="10"/>
-      <c r="R119" s="10"/>
-      <c r="S119" s="10"/>
-      <c r="T119" s="10"/>
-      <c r="U119" s="10"/>
+      <c r="U119" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B120" s="5">
-        <v>46169.67031976852</v>
+        <v>46169.6703253125</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46174.84885483797</v>
+        <v>46192.97339644676</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>364</v>
+        <v>69</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>365</v>
+        <v>70</v>
       </c>
       <c r="I120" s="5">
         <v>46330</v>
@@ -8545,13 +8551,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="Q120" s="5">
         <v>46330</v>
@@ -8574,30 +8580,24 @@
         <v>366</v>
       </c>
       <c r="B121" s="9">
-        <v>46169.6703253125</v>
+        <v>46169.670332430556</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46192.97339644676</v>
+        <v>46174.82401726852</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>367</v>
       </c>
       <c r="F121" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="H121" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="I121" s="9">
-        <v>46330</v>
-      </c>
-      <c r="J121" s="9">
-        <v>46338</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H121" s="10"/>
+      <c r="I121" s="10"/>
+      <c r="J121" s="10"/>
       <c r="K121" s="10" t="s">
         <v>26</v>
       </c>
@@ -8605,23 +8605,19 @@
         <v>26</v>
       </c>
       <c r="M121" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>360</v>
+        <v>26</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>360</v>
-      </c>
-      <c r="Q121" s="9">
-        <v>46330</v>
-      </c>
-      <c r="R121" s="9">
-        <v>46338</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q121" s="10"/>
+      <c r="R121" s="10"/>
       <c r="S121" s="7" t="s">
         <v>33</v>
       </c>
@@ -8634,27 +8630,33 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B122" s="5">
-        <v>46169.670332430556</v>
+        <v>46169.67033591435</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46174.82401726852</v>
+        <v>46174.848958703704</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F122" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H122" s="6"/>
-      <c r="I122" s="6"/>
-      <c r="J122" s="6"/>
+        <v>51</v>
+      </c>
+      <c r="H122" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="I122" s="5">
+        <v>46330</v>
+      </c>
+      <c r="J122" s="5">
+        <v>46338</v>
+      </c>
       <c r="K122" s="6" t="s">
         <v>26</v>
       </c>
@@ -8662,19 +8664,23 @@
         <v>26</v>
       </c>
       <c r="M122" s="6" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>26</v>
+        <v>367</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q122" s="6"/>
-      <c r="R122" s="6"/>
+        <v>371</v>
+      </c>
+      <c r="Q122" s="5">
+        <v>46330</v>
+      </c>
+      <c r="R122" s="5">
+        <v>46338</v>
+      </c>
       <c r="S122" s="7" t="s">
         <v>33</v>
       </c>
@@ -8687,17 +8693,17 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B123" s="9">
-        <v>46169.67033591435</v>
+        <v>46169.67034748843</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46174.848958703704</v>
+        <v>46174.84895586806</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8709,10 +8715,10 @@
         <v>52</v>
       </c>
       <c r="I123" s="9">
-        <v>46330</v>
+        <v>46339</v>
       </c>
       <c r="J123" s="9">
-        <v>46338</v>
+        <v>46349</v>
       </c>
       <c r="K123" s="10" t="s">
         <v>26</v>
@@ -8724,19 +8730,19 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>354</v>
+        <v>370</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="Q123" s="9">
-        <v>46330</v>
+        <v>46339</v>
       </c>
       <c r="R123" s="9">
-        <v>46338</v>
+        <v>46349</v>
       </c>
       <c r="S123" s="7" t="s">
         <v>33</v>
@@ -8745,69 +8751,6 @@
         <v>0</v>
       </c>
       <c r="U123" s="11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="124" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A124" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="B124" s="5">
-        <v>46169.67034748843</v>
-      </c>
-      <c r="C124" s="6"/>
-      <c r="D124" s="5">
-        <v>46174.84895586806</v>
-      </c>
-      <c r="E124" s="6" t="s">
-        <v>375</v>
-      </c>
-      <c r="F124" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G124" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="H124" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="I124" s="5">
-        <v>46339</v>
-      </c>
-      <c r="J124" s="5">
-        <v>46349</v>
-      </c>
-      <c r="K124" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L124" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M124" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N124" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="O124" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="P124" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="Q124" s="5">
-        <v>46339</v>
-      </c>
-      <c r="R124" s="5">
-        <v>46349</v>
-      </c>
-      <c r="S124" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T124" s="6">
-        <v>0</v>
-      </c>
-      <c r="U124" s="11" t="s">
         <v>60</v>
       </c>
     </row>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -824,7 +824,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4232 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A</t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A</t>
   </si>
   <si>
     <t>1215174141301410</t>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1469" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1470" uniqueCount="374">
   <si>
     <t>50001558 -  GESVIAL</t>
   </si>
@@ -2641,9 +2641,11 @@
       <c r="B18" s="5">
         <v>46169.66883001158</v>
       </c>
-      <c r="C18" s="6"/>
+      <c r="C18" s="5">
+        <v>46197.64487326389</v>
+      </c>
       <c r="D18" s="5">
-        <v>46181.636845416666</v>
+        <v>46197.64488530092</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>81</v>
@@ -2678,8 +2680,12 @@
       <c r="Q18" s="6"/>
       <c r="R18" s="6"/>
       <c r="S18" s="6"/>
-      <c r="T18" s="6"/>
-      <c r="U18" s="6"/>
+      <c r="T18" s="6">
+        <v>1</v>
+      </c>
+      <c r="U18" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
@@ -2883,9 +2889,11 @@
       <c r="B22" s="5">
         <v>46169.66903233796</v>
       </c>
-      <c r="C22" s="6"/>
+      <c r="C22" s="5">
+        <v>46197.64318571759</v>
+      </c>
       <c r="D22" s="5">
-        <v>46196.879980694444</v>
+        <v>46197.643735335645</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>94</v>
@@ -2933,10 +2941,10 @@
         <v>33</v>
       </c>
       <c r="T22" s="6">
-        <v>0</v>
-      </c>
-      <c r="U22" s="12" t="s">
-        <v>66</v>
+        <v>1</v>
+      </c>
+      <c r="U22" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
@@ -2946,9 +2954,11 @@
       <c r="B23" s="9">
         <v>46169.669037291664</v>
       </c>
-      <c r="C23" s="10"/>
+      <c r="C23" s="9">
+        <v>46197.64404108796</v>
+      </c>
       <c r="D23" s="9">
-        <v>46196.87998158565</v>
+        <v>46197.644057592595</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>100</v>
@@ -2996,10 +3006,10 @@
         <v>33</v>
       </c>
       <c r="T23" s="10">
-        <v>0</v>
-      </c>
-      <c r="U23" s="12" t="s">
-        <v>66</v>
+        <v>1</v>
+      </c>
+      <c r="U23" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
@@ -3009,9 +3019,11 @@
       <c r="B24" s="5">
         <v>46169.66904123843</v>
       </c>
-      <c r="C24" s="6"/>
+      <c r="C24" s="5">
+        <v>46197.64418927083</v>
+      </c>
       <c r="D24" s="5">
-        <v>46196.87998078704</v>
+        <v>46197.64420756944</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>103</v>
@@ -3059,10 +3071,10 @@
         <v>33</v>
       </c>
       <c r="T24" s="6">
-        <v>0</v>
-      </c>
-      <c r="U24" s="12" t="s">
-        <v>66</v>
+        <v>1</v>
+      </c>
+      <c r="U24" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -3072,9 +3084,11 @@
       <c r="B25" s="9">
         <v>46169.66904511574</v>
       </c>
-      <c r="C25" s="10"/>
+      <c r="C25" s="9">
+        <v>46197.644859120366</v>
+      </c>
       <c r="D25" s="9">
-        <v>46196.87998084491</v>
+        <v>46197.64487474537</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>106</v>
@@ -3122,10 +3136,10 @@
         <v>33</v>
       </c>
       <c r="T25" s="10">
-        <v>0</v>
-      </c>
-      <c r="U25" s="12" t="s">
-        <v>66</v>
+        <v>1</v>
+      </c>
+      <c r="U25" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
@@ -4105,7 +4119,7 @@
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46174.842601076394</v>
+        <v>46197.64319292824</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>161</v>
@@ -4286,7 +4300,7 @@
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46174.84277644676</v>
+        <v>46197.64404900463</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>101</v>
@@ -4455,7 +4469,7 @@
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46174.84297986111</v>
+        <v>46197.64486568287</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>107</v>
@@ -4677,7 +4691,7 @@
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46174.84316282407</v>
+        <v>46197.64419611111</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>104</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1470" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1470" uniqueCount="376">
   <si>
     <t>50001558 -  GESVIAL</t>
   </si>
@@ -654,10 +654,10 @@
     <t>Planos preliminar</t>
   </si>
   <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
   </si>
   <si>
     <t xml:space="preserve">O/4342 - ZVN 1-16-160/4: CH1490
@@ -672,6 +672,12 @@
   </si>
   <si>
     <t>OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
   </si>
   <si>
     <t>Planos preliminar,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A</t>
@@ -4848,7 +4854,7 @@
         <v>46195.950004328704</v>
       </c>
       <c r="D55" s="9">
-        <v>46195.95001555556</v>
+        <v>46197.71564204861</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>200</v>
@@ -4922,10 +4928,10 @@
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="I56" s="5">
         <v>46167</v>
@@ -4949,7 +4955,7 @@
         <v>78</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4959,7 +4965,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B57" s="9">
         <v>46169.66926952546</v>
@@ -4971,16 +4977,16 @@
         <v>46195.94998958333</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="I57" s="9">
         <v>46167</v>
@@ -5004,7 +5010,7 @@
         <v>78</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -5014,7 +5020,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B58" s="5">
         <v>46169.66929263889</v>
@@ -5023,10 +5029,10 @@
         <v>46195.95012040509</v>
       </c>
       <c r="D58" s="5">
-        <v>46195.95013246528</v>
+        <v>46197.71567513889</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -5056,7 +5062,7 @@
         <v>197</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>197</v>
@@ -5079,7 +5085,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B59" s="9">
         <v>46169.66929775463</v>
@@ -5097,10 +5103,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="I59" s="9">
         <v>46181</v>
@@ -5118,13 +5124,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5134,7 +5140,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B60" s="5">
         <v>46169.66930358796</v>
@@ -5146,16 +5152,16 @@
         <v>46196.87985491898</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="I60" s="5">
         <v>46181</v>
@@ -5173,13 +5179,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5189,7 +5195,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B61" s="9">
         <v>46169.669327048614</v>
@@ -5207,10 +5213,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="I61" s="9">
         <v>46240</v>
@@ -5234,7 +5240,7 @@
         <v>206</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q61" s="9">
         <v>46240</v>
@@ -5254,7 +5260,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B62" s="5">
         <v>46169.6693399537</v>
@@ -5272,10 +5278,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="I62" s="5">
         <v>46188</v>
@@ -5309,7 +5315,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B63" s="9">
         <v>46169.669361203705</v>
@@ -5319,16 +5325,16 @@
         <v>46174.84660805555</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I63" s="9">
         <v>46322</v>
@@ -5372,7 +5378,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B64" s="5">
         <v>46169.66936501158</v>
@@ -5388,10 +5394,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I64" s="5">
         <v>46290</v>
@@ -5409,13 +5415,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5425,7 +5431,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B65" s="9">
         <v>46169.669418136575</v>
@@ -5435,7 +5441,7 @@
         <v>46170.59324665509</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>25</v>
@@ -5459,7 +5465,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="P65" s="10" t="s">
         <v>26</v>
@@ -5472,7 +5478,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B66" s="5">
         <v>46169.66942685185</v>
@@ -5482,16 +5488,16 @@
         <v>46174.84701519676</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I66" s="5">
         <v>46258</v>
@@ -5509,13 +5515,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>164</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q66" s="5">
         <v>46258</v>
@@ -5535,7 +5541,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B67" s="9">
         <v>46169.669432361115</v>
@@ -5545,7 +5551,7 @@
         <v>46174.847163576385</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -5572,13 +5578,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q67" s="9">
         <v>46260</v>
@@ -5598,7 +5604,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B68" s="5">
         <v>46169.66943836806</v>
@@ -5608,16 +5614,16 @@
         <v>46174.84701244213</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I68" s="5">
         <v>46258</v>
@@ -5635,13 +5641,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>172</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q68" s="5">
         <v>46258</v>
@@ -5661,7 +5667,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B69" s="9">
         <v>46169.669443692124</v>
@@ -5671,7 +5677,7 @@
         <v>46174.84716077546</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -5698,13 +5704,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q69" s="9">
         <v>46260</v>
@@ -5724,7 +5730,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B70" s="5">
         <v>46169.669448368055</v>
@@ -5734,16 +5740,16 @@
         <v>46174.84700815972</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I70" s="5">
         <v>46258</v>
@@ -5761,13 +5767,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>194</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q70" s="5">
         <v>46258</v>
@@ -5787,7 +5793,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B71" s="9">
         <v>46169.66945298611</v>
@@ -5797,7 +5803,7 @@
         <v>46174.847156944445</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
@@ -5824,13 +5830,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O71" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="P71" s="10" t="s">
         <v>247</v>
-      </c>
-      <c r="P71" s="10" t="s">
-        <v>245</v>
       </c>
       <c r="Q71" s="9">
         <v>46260</v>
@@ -5850,7 +5856,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B72" s="5">
         <v>46169.66945778935</v>
@@ -5860,7 +5866,7 @@
         <v>46170.62754262731</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>25</v>
@@ -5884,7 +5890,7 @@
         <v>26</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>26</v>
@@ -5897,7 +5903,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B73" s="9">
         <v>46169.66946104167</v>
@@ -5907,16 +5913,16 @@
         <v>46174.84730037037</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I73" s="9">
         <v>46262</v>
@@ -5934,13 +5940,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q73" s="9">
         <v>46262</v>
@@ -5960,7 +5966,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B74" s="5">
         <v>46169.669467280095</v>
@@ -5976,10 +5982,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I74" s="5">
         <v>46262</v>
@@ -5997,13 +6003,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6013,7 +6019,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B75" s="9">
         <v>46169.66947349537</v>
@@ -6023,16 +6029,16 @@
         <v>46174.84726170139</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I75" s="9">
         <v>46262</v>
@@ -6050,13 +6056,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6066,7 +6072,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B76" s="5">
         <v>46169.66950289352</v>
@@ -6076,16 +6082,16 @@
         <v>46174.847443506944</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I76" s="5">
         <v>46273</v>
@@ -6103,13 +6109,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>204</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q76" s="5">
         <v>46273</v>
@@ -6129,7 +6135,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B77" s="9">
         <v>46169.66950758102</v>
@@ -6145,10 +6151,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I77" s="9">
         <v>46273</v>
@@ -6166,13 +6172,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6182,7 +6188,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B78" s="5">
         <v>46169.66951364583</v>
@@ -6192,16 +6198,16 @@
         <v>46196.87995984954</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I78" s="5">
         <v>46273</v>
@@ -6219,13 +6225,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6235,7 +6241,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B79" s="9">
         <v>46169.66953380787</v>
@@ -6245,16 +6251,16 @@
         <v>46174.84760361111</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I79" s="9">
         <v>46294</v>
@@ -6272,13 +6278,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O79" s="10" t="s">
         <v>204</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q79" s="9">
         <v>46294</v>
@@ -6298,7 +6304,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B80" s="5">
         <v>46169.66953854167</v>
@@ -6314,10 +6320,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I80" s="6"/>
       <c r="J80" s="5">
@@ -6333,13 +6339,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6349,7 +6355,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B81" s="9">
         <v>46169.669544212964</v>
@@ -6359,16 +6365,16 @@
         <v>46196.8799586574</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I81" s="10"/>
       <c r="J81" s="9">
@@ -6384,13 +6390,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6400,7 +6406,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B82" s="5">
         <v>46169.66960108797</v>
@@ -6410,7 +6416,7 @@
         <v>46171.686115625</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>25</v>
@@ -6434,7 +6440,7 @@
         <v>26</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>26</v>
@@ -6447,7 +6453,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B83" s="9">
         <v>46169.66960956018</v>
@@ -6457,16 +6463,16 @@
         <v>46182.63458965278</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I83" s="9">
         <v>46174</v>
@@ -6484,13 +6490,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O83" s="10" t="s">
         <v>133</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q83" s="9">
         <v>46174</v>
@@ -6510,7 +6516,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B84" s="5">
         <v>46169.6696165162</v>
@@ -6520,16 +6526,16 @@
         <v>46182.63465568287</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I84" s="5">
         <v>46288</v>
@@ -6547,13 +6553,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>123</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q84" s="5">
         <v>46288</v>
@@ -6573,7 +6579,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B85" s="9">
         <v>46169.669622939815</v>
@@ -6583,16 +6589,16 @@
         <v>46182.63442767361</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I85" s="9">
         <v>46308</v>
@@ -6610,13 +6616,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O85" s="10" t="s">
         <v>142</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q85" s="9">
         <v>46308</v>
@@ -6636,7 +6642,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B86" s="5">
         <v>46169.66962980324</v>
@@ -6646,16 +6652,16 @@
         <v>46174.8477944676</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I86" s="5">
         <v>46287</v>
@@ -6673,13 +6679,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>182</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q86" s="5">
         <v>46287</v>
@@ -6699,7 +6705,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B87" s="9">
         <v>46169.669635185186</v>
@@ -6715,10 +6721,10 @@
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I87" s="9">
         <v>46220</v>
@@ -6736,13 +6742,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O87" s="10" t="s">
         <v>153</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q87" s="9">
         <v>46220</v>
@@ -6762,7 +6768,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B88" s="5">
         <v>46169.66964790509</v>
@@ -6772,7 +6778,7 @@
         <v>46171.71448712963</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>25</v>
@@ -6796,7 +6802,7 @@
         <v>26</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>26</v>
@@ -6809,7 +6815,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B89" s="9">
         <v>46169.66965109954</v>
@@ -6819,7 +6825,7 @@
         <v>46174.84790094907</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6846,13 +6852,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q89" s="9">
         <v>46294</v>
@@ -6872,7 +6878,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B90" s="5">
         <v>46169.6696568287</v>
@@ -6909,13 +6915,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6925,7 +6931,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B91" s="9">
         <v>46169.669688622685</v>
@@ -6935,7 +6941,7 @@
         <v>46174.84789755787</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6962,13 +6968,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="O91" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q91" s="9">
         <v>46316</v>
@@ -6988,7 +6994,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B92" s="5">
         <v>46169.66969347223</v>
@@ -7023,13 +7029,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7039,7 +7045,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B93" s="9">
         <v>46169.66972681713</v>
@@ -7049,7 +7055,7 @@
         <v>46174.84789414352</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7076,13 +7082,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="O93" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q93" s="9">
         <v>46317</v>
@@ -7102,7 +7108,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B94" s="5">
         <v>46169.66973180555</v>
@@ -7139,13 +7145,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7155,7 +7161,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B95" s="9">
         <v>46169.66981054399</v>
@@ -7165,7 +7171,7 @@
         <v>46174.8478909375</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7192,13 +7198,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="O95" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q95" s="9">
         <v>46318</v>
@@ -7218,7 +7224,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B96" s="5">
         <v>46169.66981724537</v>
@@ -7255,13 +7261,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7271,7 +7277,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B97" s="9">
         <v>46169.669861041664</v>
@@ -7281,7 +7287,7 @@
         <v>46174.8478862037</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7308,13 +7314,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="O97" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q97" s="9">
         <v>46321</v>
@@ -7334,7 +7340,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B98" s="5">
         <v>46169.66986724537</v>
@@ -7371,13 +7377,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="O98" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7387,7 +7393,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B99" s="9">
         <v>46169.66990296297</v>
@@ -7397,7 +7403,7 @@
         <v>46174.84788545139</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7424,13 +7430,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="O99" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q99" s="9">
         <v>46323</v>
@@ -7450,7 +7456,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B100" s="5">
         <v>46169.66994555556</v>
@@ -7485,13 +7491,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7501,7 +7507,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B101" s="9">
         <v>46169.669978645834</v>
@@ -7511,7 +7517,7 @@
         <v>46174.82401747685</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>25</v>
@@ -7535,7 +7541,7 @@
         <v>26</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="P101" s="10" t="s">
         <v>26</v>
@@ -7548,7 +7554,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B102" s="5">
         <v>46169.66998244213</v>
@@ -7558,16 +7564,16 @@
         <v>46174.84843513889</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="I102" s="5">
         <v>46324</v>
@@ -7585,13 +7591,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q102" s="5">
         <v>46324</v>
@@ -7611,7 +7617,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B103" s="9">
         <v>46169.66998994213</v>
@@ -7627,10 +7633,10 @@
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="I103" s="10"/>
       <c r="J103" s="9">
@@ -7646,13 +7652,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O103" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7662,7 +7668,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B104" s="5">
         <v>46170.63118891204</v>
@@ -7672,16 +7678,16 @@
         <v>46174.848385474535</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="I104" s="6"/>
       <c r="J104" s="5">
@@ -7697,13 +7703,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7713,7 +7719,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B105" s="9">
         <v>46174.820955891206</v>
@@ -7729,10 +7735,10 @@
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="I105" s="9">
         <v>46324</v>
@@ -7750,13 +7756,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O105" s="10" t="s">
         <v>62</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7766,7 +7772,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B106" s="5">
         <v>46169.670044224535</v>
@@ -7776,7 +7782,7 @@
         <v>46174.848558831014</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7801,13 +7807,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q106" s="5">
         <v>46325</v>
@@ -7827,7 +7833,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B107" s="9">
         <v>46169.670049050925</v>
@@ -7862,13 +7868,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="O107" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7878,7 +7884,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B108" s="5">
         <v>46170.63213679398</v>
@@ -7888,7 +7894,7 @@
         <v>46174.848524270834</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7913,13 +7919,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7929,7 +7935,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B109" s="9">
         <v>46174.82099290509</v>
@@ -7939,7 +7945,7 @@
         <v>46174.84852028935</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -7966,7 +7972,7 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="O109" s="10" t="s">
         <v>62</v>
@@ -7982,7 +7988,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B110" s="5">
         <v>46169.67013976852</v>
@@ -7992,16 +7998,16 @@
         <v>46174.84870307871</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I110" s="6"/>
       <c r="J110" s="5">
@@ -8017,13 +8023,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O110" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q110" s="5">
         <v>46328</v>
@@ -8043,7 +8049,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B111" s="9">
         <v>46169.670151377315</v>
@@ -8059,10 +8065,10 @@
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I111" s="9">
         <v>46328</v>
@@ -8080,13 +8086,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O111" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -8096,7 +8102,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B112" s="5">
         <v>46170.63285997685</v>
@@ -8106,16 +8112,16 @@
         <v>46174.848667314815</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I112" s="5">
         <v>46328</v>
@@ -8133,13 +8139,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8149,7 +8155,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B113" s="9">
         <v>46174.821024143515</v>
@@ -8165,10 +8171,10 @@
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I113" s="9">
         <v>46328</v>
@@ -8186,10 +8192,10 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>62</v>
@@ -8202,7 +8208,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B114" s="5">
         <v>46169.67021965278</v>
@@ -8212,16 +8218,16 @@
         <v>46174.84880980324</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I114" s="5">
         <v>46329</v>
@@ -8239,13 +8245,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q114" s="5">
         <v>46329</v>
@@ -8265,7 +8271,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B115" s="9">
         <v>46169.67022677083</v>
@@ -8281,10 +8287,10 @@
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I115" s="10"/>
       <c r="J115" s="9">
@@ -8300,13 +8306,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="O115" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8316,7 +8322,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B116" s="5">
         <v>46170.633581828704</v>
@@ -8326,16 +8332,16 @@
         <v>46174.84878314815</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I116" s="6"/>
       <c r="J116" s="5">
@@ -8351,10 +8357,10 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>26</v>
@@ -8367,7 +8373,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B117" s="9">
         <v>46174.821057037036</v>
@@ -8383,10 +8389,10 @@
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I117" s="10"/>
       <c r="J117" s="9">
@@ -8402,7 +8408,7 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="O117" s="10" t="s">
         <v>62</v>
@@ -8418,7 +8424,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B118" s="5">
         <v>46169.67031616898</v>
@@ -8428,7 +8434,7 @@
         <v>46174.82401751158</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>25</v>
@@ -8452,7 +8458,7 @@
         <v>26</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>26</v>
@@ -8465,7 +8471,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B119" s="9">
         <v>46169.67031976852</v>
@@ -8475,16 +8481,16 @@
         <v>46174.84885483797</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="I119" s="9">
         <v>46330</v>
@@ -8502,13 +8508,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q119" s="9">
         <v>46330</v>
@@ -8528,7 +8534,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B120" s="5">
         <v>46169.6703253125</v>
@@ -8538,7 +8544,7 @@
         <v>46192.97339644676</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8565,13 +8571,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q120" s="5">
         <v>46330</v>
@@ -8591,7 +8597,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B121" s="9">
         <v>46169.670332430556</v>
@@ -8601,7 +8607,7 @@
         <v>46174.82401726852</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>25</v>
@@ -8625,7 +8631,7 @@
         <v>26</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="P121" s="10" t="s">
         <v>26</v>
@@ -8644,7 +8650,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B122" s="5">
         <v>46169.67033591435</v>
@@ -8654,7 +8660,7 @@
         <v>46174.848958703704</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8681,13 +8687,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Q122" s="5">
         <v>46330</v>
@@ -8707,7 +8713,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B123" s="9">
         <v>46169.67034748843</v>
@@ -8717,7 +8723,7 @@
         <v>46174.84895586806</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8744,13 +8750,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q123" s="9">
         <v>46339</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46174.84760361111</v>
+        <v>46197.84261425926</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>275</v>
@@ -6257,10 +6257,10 @@
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>257</v>
+        <v>186</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>258</v>
+        <v>187</v>
       </c>
       <c r="I79" s="9">
         <v>46294</v>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46196.87996049768</v>
+        <v>46197.84256122685</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>206</v>
@@ -6320,10 +6320,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>257</v>
+        <v>186</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>258</v>
+        <v>187</v>
       </c>
       <c r="I80" s="6"/>
       <c r="J80" s="5">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46196.8799586574</v>
+        <v>46197.84251650463</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>211</v>
@@ -6371,10 +6371,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>257</v>
+        <v>186</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>258</v>
+        <v>187</v>
       </c>
       <c r="I81" s="10"/>
       <c r="J81" s="9">

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -4062,7 +4062,7 @@
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46174.84264390046</v>
+        <v>46199.56919171296</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>156</v>
@@ -4123,9 +4123,11 @@
       <c r="B42" s="5">
         <v>46169.66916377315</v>
       </c>
-      <c r="C42" s="6"/>
+      <c r="C42" s="5">
+        <v>46199.56636615741</v>
+      </c>
       <c r="D42" s="5">
-        <v>46197.64319292824</v>
+        <v>46199.56927892361</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>161</v>
@@ -4184,7 +4186,7 @@
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46174.84259825232</v>
+        <v>46199.566634780094</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>164</v>
@@ -4241,9 +4243,11 @@
       <c r="B44" s="5">
         <v>46169.66917503472</v>
       </c>
-      <c r="C44" s="6"/>
+      <c r="C44" s="5">
+        <v>46199.56727092592</v>
+      </c>
       <c r="D44" s="5">
-        <v>46174.84280633102</v>
+        <v>46199.567282199074</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>167</v>
@@ -4291,10 +4295,10 @@
         <v>33</v>
       </c>
       <c r="T44" s="6">
-        <v>0</v>
-      </c>
-      <c r="U44" s="11" t="s">
-        <v>60</v>
+        <v>1</v>
+      </c>
+      <c r="U44" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
@@ -4304,9 +4308,11 @@
       <c r="B45" s="9">
         <v>46169.669178888886</v>
       </c>
-      <c r="C45" s="10"/>
+      <c r="C45" s="9">
+        <v>46199.56705996528</v>
+      </c>
       <c r="D45" s="9">
-        <v>46197.64404900463</v>
+        <v>46199.569896354165</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>101</v>
@@ -4357,9 +4363,11 @@
       <c r="B46" s="5">
         <v>46169.669183680555</v>
       </c>
-      <c r="C46" s="6"/>
+      <c r="C46" s="5">
+        <v>46199.567256180555</v>
+      </c>
       <c r="D46" s="5">
-        <v>46174.84277337963</v>
+        <v>46199.56984034722</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>172</v>
@@ -4632,9 +4640,11 @@
       <c r="B51" s="9">
         <v>46169.66924202546</v>
       </c>
-      <c r="C51" s="10"/>
+      <c r="C51" s="9">
+        <v>46199.57083833333</v>
+      </c>
       <c r="D51" s="9">
-        <v>46174.843210046296</v>
+        <v>46199.57084909722</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>189</v>
@@ -4682,10 +4692,10 @@
         <v>33</v>
       </c>
       <c r="T51" s="10">
-        <v>0</v>
-      </c>
-      <c r="U51" s="11" t="s">
-        <v>60</v>
+        <v>1</v>
+      </c>
+      <c r="U51" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -4695,9 +4705,11 @@
       <c r="B52" s="5">
         <v>46169.66924635417</v>
       </c>
-      <c r="C52" s="6"/>
+      <c r="C52" s="5">
+        <v>46199.57077982639</v>
+      </c>
       <c r="D52" s="5">
-        <v>46197.64419611111</v>
+        <v>46199.57078165509</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>104</v>
@@ -4748,9 +4760,11 @@
       <c r="B53" s="9">
         <v>46169.66925091435</v>
       </c>
-      <c r="C53" s="10"/>
+      <c r="C53" s="9">
+        <v>46199.570825</v>
+      </c>
       <c r="D53" s="9">
-        <v>46174.843159895834</v>
+        <v>46199.57082731482</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>194</v>
@@ -5611,7 +5625,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46174.84701244213</v>
+        <v>46199.56727501158</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>243</v>
@@ -5661,8 +5675,8 @@
       <c r="T68" s="6">
         <v>0</v>
       </c>
-      <c r="U68" s="11" t="s">
-        <v>60</v>
+      <c r="U68" s="12" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
@@ -5737,7 +5751,7 @@
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46174.84700815972</v>
+        <v>46199.57084185185</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>249</v>
@@ -5787,8 +5801,8 @@
       <c r="T70" s="6">
         <v>0</v>
       </c>
-      <c r="U70" s="11" t="s">
-        <v>60</v>
+      <c r="U70" s="12" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -4418,9 +4418,11 @@
       <c r="B47" s="9">
         <v>46169.66918849537</v>
       </c>
-      <c r="C47" s="10"/>
+      <c r="C47" s="9">
+        <v>46204.863598842596</v>
+      </c>
       <c r="D47" s="9">
-        <v>46174.84306996528</v>
+        <v>46204.863616284725</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>175</v>
@@ -4468,10 +4470,10 @@
         <v>33</v>
       </c>
       <c r="T47" s="10">
-        <v>0</v>
-      </c>
-      <c r="U47" s="11" t="s">
-        <v>60</v>
+        <v>1</v>
+      </c>
+      <c r="U47" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
@@ -4481,9 +4483,11 @@
       <c r="B48" s="5">
         <v>46169.66919252315</v>
       </c>
-      <c r="C48" s="6"/>
+      <c r="C48" s="5">
+        <v>46204.86350925926</v>
+      </c>
       <c r="D48" s="5">
-        <v>46197.64486568287</v>
+        <v>46204.863510995376</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>107</v>
@@ -4534,9 +4538,11 @@
       <c r="B49" s="9">
         <v>46169.66919734953</v>
       </c>
-      <c r="C49" s="10"/>
+      <c r="C49" s="9">
+        <v>46204.8635471875</v>
+      </c>
       <c r="D49" s="9">
-        <v>46174.84297715277</v>
+        <v>46204.8635487037</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>182</v>
@@ -4589,7 +4595,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46174.8430165625</v>
+        <v>46204.86355603009</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -6663,7 +6669,7 @@
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46174.8477944676</v>
+        <v>46204.86356525463</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>292</v>
@@ -6713,8 +6719,8 @@
       <c r="T86" s="6">
         <v>0</v>
       </c>
-      <c r="U86" s="11" t="s">
-        <v>60</v>
+      <c r="U86" s="12" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -6958,7 +6958,7 @@
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46174.84789755787</v>
+        <v>46204.89715550926</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>305</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -1805,13 +1805,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46169.66881761574</v>
+        <v>46169.502150949076</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.87136722222</v>
+        <v>46175.70470055555</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.87137862269</v>
+        <v>46175.704711956016</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1858,13 +1858,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46169.66894251158</v>
+        <v>46169.502275844905</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.87134412037</v>
+        <v>46175.7046774537</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.87136746528</v>
+        <v>46175.70470079861</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1921,13 +1921,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46169.66894603009</v>
+        <v>46169.50227936343</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.87134493055</v>
+        <v>46175.70467826389</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.87136771991</v>
+        <v>46175.70470105324</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1984,13 +1984,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="9">
-        <v>46169.66895021991</v>
+        <v>46169.50228355324</v>
       </c>
       <c r="C7" s="9">
-        <v>46175.8713453588</v>
+        <v>46175.70467869213</v>
       </c>
       <c r="D7" s="9">
-        <v>46175.87136748843</v>
+        <v>46175.70470082176</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>37</v>
@@ -2047,13 +2047,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46169.66895328704</v>
+        <v>46169.502286620365</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.871345798616</v>
+        <v>46175.704679131944</v>
       </c>
       <c r="D8" s="5">
-        <v>46175.87136746528</v>
+        <v>46175.70470079861</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -2110,13 +2110,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="9">
-        <v>46169.6689571875</v>
+        <v>46169.50229052083</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.87134641204</v>
+        <v>46175.704679745366</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.871368657405</v>
+        <v>46175.70470199074</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>44</v>
@@ -2173,11 +2173,11 @@
         <v>46</v>
       </c>
       <c r="B10" s="5">
-        <v>46169.6688215162</v>
+        <v>46169.50215484954</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46195.60097974537</v>
+        <v>46195.4343130787</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -2220,13 +2220,13 @@
         <v>49</v>
       </c>
       <c r="B11" s="9">
-        <v>46169.6689606713</v>
+        <v>46169.50229400463</v>
       </c>
       <c r="C11" s="9">
-        <v>46195.600972824075</v>
+        <v>46195.4343061574</v>
       </c>
       <c r="D11" s="9">
-        <v>46195.60099197917</v>
+        <v>46195.4343253125</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>50</v>
@@ -2285,11 +2285,11 @@
         <v>54</v>
       </c>
       <c r="B12" s="5">
-        <v>46169.66896575232</v>
+        <v>46169.50229908565</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46174.82117752315</v>
+        <v>46174.65451085648</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2348,11 +2348,11 @@
         <v>61</v>
       </c>
       <c r="B13" s="9">
-        <v>46169.668971666666</v>
+        <v>46169.502305</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="9">
-        <v>46191.686801284726</v>
+        <v>46191.520134618055</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>62</v>
@@ -2401,11 +2401,11 @@
         <v>63</v>
       </c>
       <c r="B14" s="5">
-        <v>46169.66882583333</v>
+        <v>46169.50215916667</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46192.97341535879</v>
+        <v>46192.80674869213</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>64</v>
@@ -2450,13 +2450,13 @@
         <v>67</v>
       </c>
       <c r="B15" s="9">
-        <v>46169.66899085648</v>
+        <v>46169.502324189816</v>
       </c>
       <c r="C15" s="9">
-        <v>46181.63678064814</v>
+        <v>46181.470113981486</v>
       </c>
       <c r="D15" s="9">
-        <v>46192.97339646991</v>
+        <v>46192.80672980324</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>68</v>
@@ -2515,13 +2515,13 @@
         <v>73</v>
       </c>
       <c r="B16" s="5">
-        <v>46169.66899618055</v>
+        <v>46169.50232951389</v>
       </c>
       <c r="C16" s="5">
-        <v>46181.63674427083</v>
+        <v>46181.47007760417</v>
       </c>
       <c r="D16" s="5">
-        <v>46192.97339646991</v>
+        <v>46192.80672980324</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>74</v>
@@ -2580,13 +2580,13 @@
         <v>77</v>
       </c>
       <c r="B17" s="9">
-        <v>46169.669002106486</v>
+        <v>46169.502335439814</v>
       </c>
       <c r="C17" s="9">
-        <v>46181.636749930556</v>
+        <v>46181.47008326389</v>
       </c>
       <c r="D17" s="9">
-        <v>46192.97339675926</v>
+        <v>46192.80673009259</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>78</v>
@@ -2645,13 +2645,13 @@
         <v>80</v>
       </c>
       <c r="B18" s="5">
-        <v>46169.66883001158</v>
+        <v>46169.50216334491</v>
       </c>
       <c r="C18" s="5">
-        <v>46197.64487326389</v>
+        <v>46197.478206597225</v>
       </c>
       <c r="D18" s="5">
-        <v>46197.64488530092</v>
+        <v>46197.47821863426</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>81</v>
@@ -2698,13 +2698,13 @@
         <v>83</v>
       </c>
       <c r="B19" s="9">
-        <v>46169.669016053245</v>
+        <v>46169.502349386574</v>
       </c>
       <c r="C19" s="9">
-        <v>46181.63682515046</v>
+        <v>46181.4701584838</v>
       </c>
       <c r="D19" s="9">
-        <v>46181.636840625</v>
+        <v>46181.47017395833</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>84</v>
@@ -2763,13 +2763,13 @@
         <v>86</v>
       </c>
       <c r="B20" s="5">
-        <v>46169.669021423615</v>
+        <v>46169.50235475694</v>
       </c>
       <c r="C20" s="5">
-        <v>46181.6368303125</v>
+        <v>46181.470163645834</v>
       </c>
       <c r="D20" s="5">
-        <v>46181.636847222224</v>
+        <v>46181.47018055555</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>87</v>
@@ -2828,13 +2828,13 @@
         <v>89</v>
       </c>
       <c r="B21" s="9">
-        <v>46169.66902680555</v>
+        <v>46169.50236013889</v>
       </c>
       <c r="C21" s="9">
-        <v>46181.63683986111</v>
+        <v>46181.470173194444</v>
       </c>
       <c r="D21" s="9">
-        <v>46181.636854895834</v>
+        <v>46181.47018822917</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>90</v>
@@ -2893,13 +2893,13 @@
         <v>93</v>
       </c>
       <c r="B22" s="5">
-        <v>46169.66903233796</v>
+        <v>46169.502365671295</v>
       </c>
       <c r="C22" s="5">
-        <v>46197.64318571759</v>
+        <v>46197.47651905092</v>
       </c>
       <c r="D22" s="5">
-        <v>46197.643735335645</v>
+        <v>46197.47706866898</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>94</v>
@@ -2958,13 +2958,13 @@
         <v>99</v>
       </c>
       <c r="B23" s="9">
-        <v>46169.669037291664</v>
+        <v>46169.502370625</v>
       </c>
       <c r="C23" s="9">
-        <v>46197.64404108796</v>
+        <v>46197.4773744213</v>
       </c>
       <c r="D23" s="9">
-        <v>46197.644057592595</v>
+        <v>46197.477390925924</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>100</v>
@@ -3023,13 +3023,13 @@
         <v>102</v>
       </c>
       <c r="B24" s="5">
-        <v>46169.66904123843</v>
+        <v>46169.50237457176</v>
       </c>
       <c r="C24" s="5">
-        <v>46197.64418927083</v>
+        <v>46197.47752260417</v>
       </c>
       <c r="D24" s="5">
-        <v>46197.64420756944</v>
+        <v>46197.47754090278</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>103</v>
@@ -3088,13 +3088,13 @@
         <v>105</v>
       </c>
       <c r="B25" s="9">
-        <v>46169.66904511574</v>
+        <v>46169.50237844908</v>
       </c>
       <c r="C25" s="9">
-        <v>46197.644859120366</v>
+        <v>46197.4781924537</v>
       </c>
       <c r="D25" s="9">
-        <v>46197.64487474537</v>
+        <v>46197.478208078704</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>106</v>
@@ -3153,13 +3153,13 @@
         <v>108</v>
       </c>
       <c r="B26" s="5">
-        <v>46169.66904878472</v>
+        <v>46169.50238211805</v>
       </c>
       <c r="C26" s="5">
-        <v>46195.601674432866</v>
+        <v>46195.4350077662</v>
       </c>
       <c r="D26" s="5">
-        <v>46195.60168921296</v>
+        <v>46195.4350225463</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>109</v>
@@ -3218,11 +3218,11 @@
         <v>111</v>
       </c>
       <c r="B27" s="9">
-        <v>46169.66883418981</v>
+        <v>46169.50216752315</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46182.63465987268</v>
+        <v>46182.46799320602</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>112</v>
@@ -3265,13 +3265,13 @@
         <v>114</v>
       </c>
       <c r="B28" s="5">
-        <v>46169.66908924768</v>
+        <v>46169.50242258102</v>
       </c>
       <c r="C28" s="5">
-        <v>46182.63465045139</v>
+        <v>46182.46798378472</v>
       </c>
       <c r="D28" s="5">
-        <v>46182.63466408565</v>
+        <v>46182.46799741898</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>115</v>
@@ -3330,13 +3330,13 @@
         <v>119</v>
       </c>
       <c r="B29" s="9">
-        <v>46169.66909520833</v>
+        <v>46169.502428541666</v>
       </c>
       <c r="C29" s="9">
-        <v>46182.63236193287</v>
+        <v>46182.465695266204</v>
       </c>
       <c r="D29" s="9">
-        <v>46182.63236322917</v>
+        <v>46182.4656965625</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>120</v>
@@ -3391,13 +3391,13 @@
         <v>122</v>
       </c>
       <c r="B30" s="5">
-        <v>46169.669100810184</v>
+        <v>46169.50243414352</v>
       </c>
       <c r="C30" s="5">
-        <v>46182.63463581019</v>
+        <v>46182.467969143516</v>
       </c>
       <c r="D30" s="5">
-        <v>46182.63463722222</v>
+        <v>46182.46797055556</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>123</v>
@@ -3452,13 +3452,13 @@
         <v>125</v>
       </c>
       <c r="B31" s="9">
-        <v>46169.669106284724</v>
+        <v>46169.50243961805</v>
       </c>
       <c r="C31" s="9">
-        <v>46182.634586817134</v>
+        <v>46182.46792015046</v>
       </c>
       <c r="D31" s="9">
-        <v>46182.63460042824</v>
+        <v>46182.467933761574</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>126</v>
@@ -3517,13 +3517,13 @@
         <v>129</v>
       </c>
       <c r="B32" s="5">
-        <v>46169.66911128472</v>
+        <v>46169.502444618054</v>
       </c>
       <c r="C32" s="5">
-        <v>46182.63180898148</v>
+        <v>46182.46514231482</v>
       </c>
       <c r="D32" s="5">
-        <v>46182.6318109375</v>
+        <v>46182.465144270835</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>130</v>
@@ -3578,13 +3578,13 @@
         <v>132</v>
       </c>
       <c r="B33" s="9">
-        <v>46169.669116805555</v>
+        <v>46169.50245013888</v>
       </c>
       <c r="C33" s="9">
-        <v>46182.63457177083</v>
+        <v>46182.46790510417</v>
       </c>
       <c r="D33" s="9">
-        <v>46182.63457327546</v>
+        <v>46182.4679066088</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>133</v>
@@ -3639,13 +3639,13 @@
         <v>135</v>
       </c>
       <c r="B34" s="5">
-        <v>46169.66912204861</v>
+        <v>46169.502455381946</v>
       </c>
       <c r="C34" s="5">
-        <v>46182.63442347222</v>
+        <v>46182.467756805556</v>
       </c>
       <c r="D34" s="5">
-        <v>46182.6344355787</v>
+        <v>46182.467768912036</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>136</v>
@@ -3704,13 +3704,13 @@
         <v>138</v>
       </c>
       <c r="B35" s="9">
-        <v>46169.66912711806</v>
+        <v>46169.50246045139</v>
       </c>
       <c r="C35" s="9">
-        <v>46182.63203811343</v>
+        <v>46182.46537144676</v>
       </c>
       <c r="D35" s="9">
-        <v>46182.63203959491</v>
+        <v>46182.46537292824</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>139</v>
@@ -3765,13 +3765,13 @@
         <v>141</v>
       </c>
       <c r="B36" s="5">
-        <v>46169.66913270833</v>
+        <v>46169.50246604167</v>
       </c>
       <c r="C36" s="5">
-        <v>46182.63440969907</v>
+        <v>46182.46774303241</v>
       </c>
       <c r="D36" s="5">
-        <v>46182.634411203704</v>
+        <v>46182.46774453703</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>142</v>
@@ -3826,13 +3826,13 @@
         <v>144</v>
       </c>
       <c r="B37" s="9">
-        <v>46169.66913809028</v>
+        <v>46169.502471423606</v>
       </c>
       <c r="C37" s="9">
-        <v>46182.634350636574</v>
+        <v>46182.46768396991</v>
       </c>
       <c r="D37" s="9">
-        <v>46182.6343528588</v>
+        <v>46182.46768619213</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>145</v>
@@ -3887,11 +3887,11 @@
         <v>147</v>
       </c>
       <c r="B38" s="5">
-        <v>46169.66914475695</v>
+        <v>46169.502478090275</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46195.68641738426</v>
+        <v>46195.51975071759</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>148</v>
@@ -3950,13 +3950,13 @@
         <v>150</v>
       </c>
       <c r="B39" s="9">
-        <v>46169.669149270834</v>
+        <v>46169.50248260416</v>
       </c>
       <c r="C39" s="9">
-        <v>46195.686411111106</v>
+        <v>46195.51974444445</v>
       </c>
       <c r="D39" s="9">
-        <v>46195.68641299769</v>
+        <v>46195.51974633102</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>110</v>
@@ -4005,11 +4005,11 @@
         <v>152</v>
       </c>
       <c r="B40" s="5">
-        <v>46169.66915408565</v>
+        <v>46169.502487418984</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46195.686418576384</v>
+        <v>46195.51975190973</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>153</v>
@@ -4058,11 +4058,11 @@
         <v>155</v>
       </c>
       <c r="B41" s="9">
-        <v>46169.66915865741</v>
+        <v>46169.502491990745</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46199.56919171296</v>
+        <v>46199.402525046295</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>156</v>
@@ -4121,13 +4121,13 @@
         <v>160</v>
       </c>
       <c r="B42" s="5">
-        <v>46169.66916377315</v>
+        <v>46169.502497106485</v>
       </c>
       <c r="C42" s="5">
-        <v>46199.56636615741</v>
+        <v>46199.399699490736</v>
       </c>
       <c r="D42" s="5">
-        <v>46199.56927892361</v>
+        <v>46199.40261225695</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>161</v>
@@ -4182,11 +4182,11 @@
         <v>163</v>
       </c>
       <c r="B43" s="9">
-        <v>46169.66916960648</v>
+        <v>46169.50250293982</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46199.566634780094</v>
+        <v>46199.39996811343</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>164</v>
@@ -4241,13 +4241,13 @@
         <v>166</v>
       </c>
       <c r="B44" s="5">
-        <v>46169.66917503472</v>
+        <v>46169.50250836805</v>
       </c>
       <c r="C44" s="5">
-        <v>46199.56727092592</v>
+        <v>46199.40060425926</v>
       </c>
       <c r="D44" s="5">
-        <v>46199.567282199074</v>
+        <v>46199.4006155324</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>167</v>
@@ -4306,13 +4306,13 @@
         <v>169</v>
       </c>
       <c r="B45" s="9">
-        <v>46169.669178888886</v>
+        <v>46169.50251222222</v>
       </c>
       <c r="C45" s="9">
-        <v>46199.56705996528</v>
+        <v>46199.40039329861</v>
       </c>
       <c r="D45" s="9">
-        <v>46199.569896354165</v>
+        <v>46199.4032296875</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>101</v>
@@ -4361,13 +4361,13 @@
         <v>171</v>
       </c>
       <c r="B46" s="5">
-        <v>46169.669183680555</v>
+        <v>46169.50251701389</v>
       </c>
       <c r="C46" s="5">
-        <v>46199.567256180555</v>
+        <v>46199.40058951388</v>
       </c>
       <c r="D46" s="5">
-        <v>46199.56984034722</v>
+        <v>46199.403173680555</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>172</v>
@@ -4416,13 +4416,13 @@
         <v>174</v>
       </c>
       <c r="B47" s="9">
-        <v>46169.66918849537</v>
+        <v>46169.502521828705</v>
       </c>
       <c r="C47" s="9">
-        <v>46204.863598842596</v>
+        <v>46204.696932175924</v>
       </c>
       <c r="D47" s="9">
-        <v>46204.863616284725</v>
+        <v>46204.69694961805</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>175</v>
@@ -4481,13 +4481,13 @@
         <v>179</v>
       </c>
       <c r="B48" s="5">
-        <v>46169.66919252315</v>
+        <v>46169.502525856486</v>
       </c>
       <c r="C48" s="5">
-        <v>46204.86350925926</v>
+        <v>46204.69684259259</v>
       </c>
       <c r="D48" s="5">
-        <v>46204.863510995376</v>
+        <v>46204.696844328704</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>107</v>
@@ -4536,13 +4536,13 @@
         <v>181</v>
       </c>
       <c r="B49" s="9">
-        <v>46169.66919734953</v>
+        <v>46169.502530682876</v>
       </c>
       <c r="C49" s="9">
-        <v>46204.8635471875</v>
+        <v>46204.69688052083</v>
       </c>
       <c r="D49" s="9">
-        <v>46204.8635487037</v>
+        <v>46204.69688203704</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>182</v>
@@ -4591,11 +4591,11 @@
         <v>184</v>
       </c>
       <c r="B50" s="5">
-        <v>46169.66920229167</v>
+        <v>46169.502535625</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46204.86355603009</v>
+        <v>46204.696889363426</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -4644,13 +4644,13 @@
         <v>188</v>
       </c>
       <c r="B51" s="9">
-        <v>46169.66924202546</v>
+        <v>46169.5025753588</v>
       </c>
       <c r="C51" s="9">
-        <v>46199.57083833333</v>
+        <v>46199.40417166667</v>
       </c>
       <c r="D51" s="9">
-        <v>46199.57084909722</v>
+        <v>46199.40418243056</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>189</v>
@@ -4709,13 +4709,13 @@
         <v>191</v>
       </c>
       <c r="B52" s="5">
-        <v>46169.66924635417</v>
+        <v>46169.5025796875</v>
       </c>
       <c r="C52" s="5">
-        <v>46199.57077982639</v>
+        <v>46199.40411315972</v>
       </c>
       <c r="D52" s="5">
-        <v>46199.57078165509</v>
+        <v>46199.40411498843</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>104</v>
@@ -4764,13 +4764,13 @@
         <v>193</v>
       </c>
       <c r="B53" s="9">
-        <v>46169.66925091435</v>
+        <v>46169.50258424769</v>
       </c>
       <c r="C53" s="9">
-        <v>46199.570825</v>
+        <v>46199.40415833333</v>
       </c>
       <c r="D53" s="9">
-        <v>46199.57082731482</v>
+        <v>46199.40416064815</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>194</v>
@@ -4819,11 +4819,11 @@
         <v>196</v>
       </c>
       <c r="B54" s="5">
-        <v>46169.669255659726</v>
+        <v>46169.502588993055</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46195.950137974534</v>
+        <v>46195.78347130787</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>197</v>
@@ -4868,13 +4868,13 @@
         <v>199</v>
       </c>
       <c r="B55" s="9">
-        <v>46169.66925896991</v>
+        <v>46169.50259230324</v>
       </c>
       <c r="C55" s="9">
-        <v>46195.950004328704</v>
+        <v>46195.78333766204</v>
       </c>
       <c r="D55" s="9">
-        <v>46197.71564204861</v>
+        <v>46197.54897538194</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>200</v>
@@ -4933,13 +4933,13 @@
         <v>205</v>
       </c>
       <c r="B56" s="5">
-        <v>46169.66926408565</v>
+        <v>46169.50259741898</v>
       </c>
       <c r="C56" s="5">
-        <v>46195.94997732639</v>
+        <v>46195.783310659725</v>
       </c>
       <c r="D56" s="5">
-        <v>46195.94997940972</v>
+        <v>46195.78331274306</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>206</v>
@@ -4988,13 +4988,13 @@
         <v>210</v>
       </c>
       <c r="B57" s="9">
-        <v>46169.66926952546</v>
+        <v>46169.502602858796</v>
       </c>
       <c r="C57" s="9">
-        <v>46195.9499871875</v>
+        <v>46195.78332052083</v>
       </c>
       <c r="D57" s="9">
-        <v>46195.94998958333</v>
+        <v>46195.78332291667</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>211</v>
@@ -5043,13 +5043,13 @@
         <v>213</v>
       </c>
       <c r="B58" s="5">
-        <v>46169.66929263889</v>
+        <v>46169.50262597222</v>
       </c>
       <c r="C58" s="5">
-        <v>46195.95012040509</v>
+        <v>46195.783453738426</v>
       </c>
       <c r="D58" s="5">
-        <v>46197.71567513889</v>
+        <v>46197.549008472226</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>214</v>
@@ -5108,13 +5108,13 @@
         <v>216</v>
       </c>
       <c r="B59" s="9">
-        <v>46169.66929775463</v>
+        <v>46169.50263108796</v>
       </c>
       <c r="C59" s="9">
-        <v>46195.950094699074</v>
+        <v>46195.7834280324</v>
       </c>
       <c r="D59" s="9">
-        <v>46195.950096458335</v>
+        <v>46195.78342979167</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>206</v>
@@ -5163,13 +5163,13 @@
         <v>219</v>
       </c>
       <c r="B60" s="5">
-        <v>46169.66930358796</v>
+        <v>46169.5026369213</v>
       </c>
       <c r="C60" s="5">
-        <v>46195.950105219905</v>
+        <v>46195.78343855324</v>
       </c>
       <c r="D60" s="5">
-        <v>46196.87985491898</v>
+        <v>46196.71318825231</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>211</v>
@@ -5218,13 +5218,13 @@
         <v>221</v>
       </c>
       <c r="B61" s="9">
-        <v>46169.669327048614</v>
+        <v>46169.50266038194</v>
       </c>
       <c r="C61" s="9">
-        <v>46196.87995266204</v>
+        <v>46196.71328599537</v>
       </c>
       <c r="D61" s="9">
-        <v>46196.879968090274</v>
+        <v>46196.71330142361</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>97</v>
@@ -5283,13 +5283,13 @@
         <v>223</v>
       </c>
       <c r="B62" s="5">
-        <v>46169.6693399537</v>
+        <v>46169.50267328703</v>
       </c>
       <c r="C62" s="5">
-        <v>46195.950422222224</v>
+        <v>46195.78375555556</v>
       </c>
       <c r="D62" s="5">
-        <v>46195.95042396991</v>
+        <v>46195.783757303245</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>206</v>
@@ -5338,11 +5338,11 @@
         <v>224</v>
       </c>
       <c r="B63" s="9">
-        <v>46169.669361203705</v>
+        <v>46169.502694537034</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46174.84660805555</v>
+        <v>46174.67994138889</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>225</v>
@@ -5401,11 +5401,11 @@
         <v>228</v>
       </c>
       <c r="B64" s="5">
-        <v>46169.66936501158</v>
+        <v>46169.502698344906</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46174.846919421296</v>
+        <v>46174.680252754624</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>206</v>
@@ -5454,11 +5454,11 @@
         <v>230</v>
       </c>
       <c r="B65" s="9">
-        <v>46169.669418136575</v>
+        <v>46169.5027514699</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46170.59324665509</v>
+        <v>46170.42657998843</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>231</v>
@@ -5501,11 +5501,11 @@
         <v>233</v>
       </c>
       <c r="B66" s="5">
-        <v>46169.66942685185</v>
+        <v>46169.50276018518</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46174.84701519676</v>
+        <v>46174.68034853009</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>234</v>
@@ -5564,11 +5564,11 @@
         <v>238</v>
       </c>
       <c r="B67" s="9">
-        <v>46169.669432361115</v>
+        <v>46169.502765694444</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46174.847163576385</v>
+        <v>46174.68049690972</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>239</v>
@@ -5627,11 +5627,11 @@
         <v>242</v>
       </c>
       <c r="B68" s="5">
-        <v>46169.66943836806</v>
+        <v>46169.50277170139</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46199.56727501158</v>
+        <v>46199.400608344906</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>243</v>
@@ -5690,11 +5690,11 @@
         <v>245</v>
       </c>
       <c r="B69" s="9">
-        <v>46169.669443692124</v>
+        <v>46169.50277702547</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46174.84716077546</v>
+        <v>46174.6804941088</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>246</v>
@@ -5753,11 +5753,11 @@
         <v>248</v>
       </c>
       <c r="B70" s="5">
-        <v>46169.669448368055</v>
+        <v>46169.50278170139</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46199.57084185185</v>
+        <v>46199.404175185184</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>249</v>
@@ -5816,11 +5816,11 @@
         <v>251</v>
       </c>
       <c r="B71" s="9">
-        <v>46169.66945298611</v>
+        <v>46169.50278631944</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46174.847156944445</v>
+        <v>46174.68049027778</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>250</v>
@@ -5879,11 +5879,11 @@
         <v>252</v>
       </c>
       <c r="B72" s="5">
-        <v>46169.66945778935</v>
+        <v>46169.502791122686</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46170.62754262731</v>
+        <v>46170.46087596065</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>253</v>
@@ -5926,11 +5926,11 @@
         <v>255</v>
       </c>
       <c r="B73" s="9">
-        <v>46169.66946104167</v>
+        <v>46169.502794375</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46174.84730037037</v>
+        <v>46174.680633703705</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>256</v>
@@ -5989,11 +5989,11 @@
         <v>260</v>
       </c>
       <c r="B74" s="5">
-        <v>46169.669467280095</v>
+        <v>46169.50280061342</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46174.84726460648</v>
+        <v>46174.68059793982</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>206</v>
@@ -6042,11 +6042,11 @@
         <v>263</v>
       </c>
       <c r="B75" s="9">
-        <v>46169.66947349537</v>
+        <v>46169.50280682871</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46174.84726170139</v>
+        <v>46174.68059503472</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>264</v>
@@ -6095,11 +6095,11 @@
         <v>266</v>
       </c>
       <c r="B76" s="5">
-        <v>46169.66950289352</v>
+        <v>46169.50283622685</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46174.847443506944</v>
+        <v>46174.68077684028</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>267</v>
@@ -6158,11 +6158,11 @@
         <v>268</v>
       </c>
       <c r="B77" s="9">
-        <v>46169.66950758102</v>
+        <v>46169.502840914356</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46196.87995929398</v>
+        <v>46196.71329262732</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>206</v>
@@ -6211,11 +6211,11 @@
         <v>271</v>
       </c>
       <c r="B78" s="5">
-        <v>46169.66951364583</v>
+        <v>46169.502846979165</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46196.87995984954</v>
+        <v>46196.71329318287</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>211</v>
@@ -6264,11 +6264,11 @@
         <v>274</v>
       </c>
       <c r="B79" s="9">
-        <v>46169.66953380787</v>
+        <v>46169.5028671412</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46197.84261425926</v>
+        <v>46197.675947592594</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>275</v>
@@ -6327,11 +6327,11 @@
         <v>276</v>
       </c>
       <c r="B80" s="5">
-        <v>46169.66953854167</v>
+        <v>46169.502871874996</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46197.84256122685</v>
+        <v>46197.67589456019</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>206</v>
@@ -6378,11 +6378,11 @@
         <v>278</v>
       </c>
       <c r="B81" s="9">
-        <v>46169.669544212964</v>
+        <v>46169.5028775463</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46197.84251650463</v>
+        <v>46197.675849837964</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>211</v>
@@ -6429,11 +6429,11 @@
         <v>281</v>
       </c>
       <c r="B82" s="5">
-        <v>46169.66960108797</v>
+        <v>46169.502934421296</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46171.686115625</v>
+        <v>46171.51944895834</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>231</v>
@@ -6476,11 +6476,11 @@
         <v>283</v>
       </c>
       <c r="B83" s="9">
-        <v>46169.66960956018</v>
+        <v>46169.50294289352</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46182.63458965278</v>
+        <v>46182.46792298611</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>284</v>
@@ -6539,11 +6539,11 @@
         <v>286</v>
       </c>
       <c r="B84" s="5">
-        <v>46169.6696165162</v>
+        <v>46169.50294984954</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46182.63465568287</v>
+        <v>46182.46798901621</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>287</v>
@@ -6602,11 +6602,11 @@
         <v>289</v>
       </c>
       <c r="B85" s="9">
-        <v>46169.669622939815</v>
+        <v>46169.50295627315</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46182.63442767361</v>
+        <v>46182.46776100695</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>290</v>
@@ -6665,11 +6665,11 @@
         <v>291</v>
       </c>
       <c r="B86" s="5">
-        <v>46169.66962980324</v>
+        <v>46169.502963136576</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46204.86356525463</v>
+        <v>46204.696898587965</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>292</v>
@@ -6728,11 +6728,11 @@
         <v>294</v>
       </c>
       <c r="B87" s="9">
-        <v>46169.669635185186</v>
+        <v>46169.502968518515</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46174.84778872685</v>
+        <v>46174.68112206018</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>58</v>
@@ -6791,11 +6791,11 @@
         <v>296</v>
       </c>
       <c r="B88" s="5">
-        <v>46169.66964790509</v>
+        <v>46169.50298123843</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46171.71448712963</v>
+        <v>46171.54782046296</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>297</v>
@@ -6838,11 +6838,11 @@
         <v>299</v>
       </c>
       <c r="B89" s="9">
-        <v>46169.66965109954</v>
+        <v>46169.50298443287</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46174.84790094907</v>
+        <v>46174.68123428241</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>300</v>
@@ -6901,11 +6901,11 @@
         <v>302</v>
       </c>
       <c r="B90" s="5">
-        <v>46169.6696568287</v>
+        <v>46169.50299016204</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46174.84798839121</v>
+        <v>46174.681321724536</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>206</v>
@@ -6954,11 +6954,11 @@
         <v>304</v>
       </c>
       <c r="B91" s="9">
-        <v>46169.669688622685</v>
+        <v>46169.503021956014</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46204.89715550926</v>
+        <v>46204.73048884259</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>305</v>
@@ -7017,11 +7017,11 @@
         <v>306</v>
       </c>
       <c r="B92" s="5">
-        <v>46169.66969347223</v>
+        <v>46169.503026805556</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46196.87997025463</v>
+        <v>46196.71330358797</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>206</v>
@@ -7068,11 +7068,11 @@
         <v>309</v>
       </c>
       <c r="B93" s="9">
-        <v>46169.66972681713</v>
+        <v>46169.50306015046</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46174.84789414352</v>
+        <v>46174.68122747685</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>310</v>
@@ -7131,11 +7131,11 @@
         <v>311</v>
       </c>
       <c r="B94" s="5">
-        <v>46169.66973180555</v>
+        <v>46169.50306513889</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46196.87996092593</v>
+        <v>46196.71329425926</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>206</v>
@@ -7184,11 +7184,11 @@
         <v>314</v>
       </c>
       <c r="B95" s="9">
-        <v>46169.66981054399</v>
+        <v>46169.503143877315</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46174.8478909375</v>
+        <v>46174.68122427083</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>315</v>
@@ -7247,11 +7247,11 @@
         <v>316</v>
       </c>
       <c r="B96" s="5">
-        <v>46169.66981724537</v>
+        <v>46169.503150578705</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46196.87997091435</v>
+        <v>46196.713304247685</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>206</v>
@@ -7300,11 +7300,11 @@
         <v>319</v>
       </c>
       <c r="B97" s="9">
-        <v>46169.669861041664</v>
+        <v>46169.503194375</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46174.8478862037</v>
+        <v>46174.68121953704</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>320</v>
@@ -7363,11 +7363,11 @@
         <v>321</v>
       </c>
       <c r="B98" s="5">
-        <v>46169.66986724537</v>
+        <v>46169.50320057871</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46174.84816675926</v>
+        <v>46174.68150009259</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>206</v>
@@ -7416,11 +7416,11 @@
         <v>323</v>
       </c>
       <c r="B99" s="9">
-        <v>46169.66990296297</v>
+        <v>46169.503236296296</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46174.84788545139</v>
+        <v>46174.681218784724</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>324</v>
@@ -7479,11 +7479,11 @@
         <v>326</v>
       </c>
       <c r="B100" s="5">
-        <v>46169.66994555556</v>
+        <v>46169.50327888889</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46174.848269317125</v>
+        <v>46174.68160265047</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>206</v>
@@ -7530,11 +7530,11 @@
         <v>328</v>
       </c>
       <c r="B101" s="9">
-        <v>46169.669978645834</v>
+        <v>46169.50331197916</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46174.82401747685</v>
+        <v>46174.65735081019</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>329</v>
@@ -7577,11 +7577,11 @@
         <v>331</v>
       </c>
       <c r="B102" s="5">
-        <v>46169.66998244213</v>
+        <v>46169.503315775466</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46174.84843513889</v>
+        <v>46174.68176847222</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>332</v>
@@ -7640,11 +7640,11 @@
         <v>336</v>
       </c>
       <c r="B103" s="9">
-        <v>46169.66998994213</v>
+        <v>46169.503323275465</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46174.84838837963</v>
+        <v>46174.681721712965</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>206</v>
@@ -7691,11 +7691,11 @@
         <v>338</v>
       </c>
       <c r="B104" s="5">
-        <v>46170.63118891204</v>
+        <v>46170.46452224537</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46174.848385474535</v>
+        <v>46174.68171880787</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>211</v>
@@ -7742,11 +7742,11 @@
         <v>339</v>
       </c>
       <c r="B105" s="9">
-        <v>46174.820955891206</v>
+        <v>46174.654289224534</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46174.848381284726</v>
+        <v>46174.681714618055</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>62</v>
@@ -7795,11 +7795,11 @@
         <v>341</v>
       </c>
       <c r="B106" s="5">
-        <v>46169.670044224535</v>
+        <v>46169.50337755787</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46174.848558831014</v>
+        <v>46174.68189216436</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>342</v>
@@ -7856,11 +7856,11 @@
         <v>343</v>
       </c>
       <c r="B107" s="9">
-        <v>46169.670049050925</v>
+        <v>46169.50338238426</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46174.848527152775</v>
+        <v>46174.68186048611</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>206</v>
@@ -7907,11 +7907,11 @@
         <v>345</v>
       </c>
       <c r="B108" s="5">
-        <v>46170.63213679398</v>
+        <v>46170.46547012731</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46174.848524270834</v>
+        <v>46174.68185760417</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>211</v>
@@ -7958,11 +7958,11 @@
         <v>346</v>
       </c>
       <c r="B109" s="9">
-        <v>46174.82099290509</v>
+        <v>46174.65432623842</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46174.84852028935</v>
+        <v>46174.681853622686</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>340</v>
@@ -8011,11 +8011,11 @@
         <v>347</v>
       </c>
       <c r="B110" s="5">
-        <v>46169.67013976852</v>
+        <v>46169.50347310185</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46174.84870307871</v>
+        <v>46174.682036412036</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>348</v>
@@ -8072,11 +8072,11 @@
         <v>349</v>
       </c>
       <c r="B111" s="9">
-        <v>46169.670151377315</v>
+        <v>46169.50348471064</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46174.848669872685</v>
+        <v>46174.68200320602</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>206</v>
@@ -8125,11 +8125,11 @@
         <v>351</v>
       </c>
       <c r="B112" s="5">
-        <v>46170.63285997685</v>
+        <v>46170.46619331019</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46174.848667314815</v>
+        <v>46174.68200064814</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>211</v>
@@ -8178,11 +8178,11 @@
         <v>352</v>
       </c>
       <c r="B113" s="9">
-        <v>46174.821024143515</v>
+        <v>46174.65435747685</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46174.84866336806</v>
+        <v>46174.68199670139</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>62</v>
@@ -8231,11 +8231,11 @@
         <v>353</v>
       </c>
       <c r="B114" s="5">
-        <v>46169.67021965278</v>
+        <v>46169.50355298611</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46174.84880980324</v>
+        <v>46174.682143136575</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>354</v>
@@ -8294,11 +8294,11 @@
         <v>356</v>
       </c>
       <c r="B115" s="9">
-        <v>46169.67022677083</v>
+        <v>46169.50356010417</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46174.84878571759</v>
+        <v>46174.68211905092</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>206</v>
@@ -8345,11 +8345,11 @@
         <v>357</v>
       </c>
       <c r="B116" s="5">
-        <v>46170.633581828704</v>
+        <v>46170.46691516203</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46174.84878314815</v>
+        <v>46174.68211648148</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>211</v>
@@ -8396,11 +8396,11 @@
         <v>358</v>
       </c>
       <c r="B117" s="9">
-        <v>46174.821057037036</v>
+        <v>46174.65439037037</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46174.84877914352</v>
+        <v>46174.68211247685</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>62</v>
@@ -8447,11 +8447,11 @@
         <v>359</v>
       </c>
       <c r="B118" s="5">
-        <v>46169.67031616898</v>
+        <v>46169.503649502316</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46174.82401751158</v>
+        <v>46174.65735084491</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>360</v>
@@ -8494,11 +8494,11 @@
         <v>362</v>
       </c>
       <c r="B119" s="9">
-        <v>46169.67031976852</v>
+        <v>46169.503653101856</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46174.84885483797</v>
+        <v>46174.6821881713</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>363</v>
@@ -8557,11 +8557,11 @@
         <v>366</v>
       </c>
       <c r="B120" s="5">
-        <v>46169.6703253125</v>
+        <v>46169.50365864583</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46192.97339644676</v>
+        <v>46192.80672978009</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>367</v>
@@ -8620,11 +8620,11 @@
         <v>368</v>
       </c>
       <c r="B121" s="9">
-        <v>46169.670332430556</v>
+        <v>46169.503665763885</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46174.82401726852</v>
+        <v>46174.65735060185</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>369</v>
@@ -8673,11 +8673,11 @@
         <v>371</v>
       </c>
       <c r="B122" s="5">
-        <v>46169.67033591435</v>
+        <v>46169.503669247686</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46174.848958703704</v>
+        <v>46174.68229203703</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>372</v>
@@ -8736,11 +8736,11 @@
         <v>374</v>
       </c>
       <c r="B123" s="9">
-        <v>46169.67034748843</v>
+        <v>46169.503680821756</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46174.84895586806</v>
+        <v>46174.68228920139</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>375</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1470" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1471" uniqueCount="376">
   <si>
     <t>50001558 -  GESVIAL</t>
   </si>
@@ -1805,13 +1805,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46169.502150949076</v>
+        <v>46169.66881761574</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.70470055555</v>
+        <v>46175.87136722222</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.704711956016</v>
+        <v>46175.87137862269</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1858,13 +1858,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46169.502275844905</v>
+        <v>46169.66894251158</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.7046774537</v>
+        <v>46175.87134412037</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.70470079861</v>
+        <v>46175.87136746528</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1921,13 +1921,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46169.50227936343</v>
+        <v>46169.66894603009</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.70467826389</v>
+        <v>46175.87134493055</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.70470105324</v>
+        <v>46175.87136771991</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1984,13 +1984,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="9">
-        <v>46169.50228355324</v>
+        <v>46169.66895021991</v>
       </c>
       <c r="C7" s="9">
-        <v>46175.70467869213</v>
+        <v>46175.8713453588</v>
       </c>
       <c r="D7" s="9">
-        <v>46175.70470082176</v>
+        <v>46175.87136748843</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>37</v>
@@ -2047,13 +2047,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46169.502286620365</v>
+        <v>46169.66895328704</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.704679131944</v>
+        <v>46175.871345798616</v>
       </c>
       <c r="D8" s="5">
-        <v>46175.70470079861</v>
+        <v>46175.87136746528</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -2110,13 +2110,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="9">
-        <v>46169.50229052083</v>
+        <v>46169.6689571875</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.704679745366</v>
+        <v>46175.87134641204</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.70470199074</v>
+        <v>46175.871368657405</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>44</v>
@@ -2173,11 +2173,11 @@
         <v>46</v>
       </c>
       <c r="B10" s="5">
-        <v>46169.50215484954</v>
+        <v>46169.6688215162</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46195.4343130787</v>
+        <v>46195.60097974537</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -2220,13 +2220,13 @@
         <v>49</v>
       </c>
       <c r="B11" s="9">
-        <v>46169.50229400463</v>
+        <v>46169.6689606713</v>
       </c>
       <c r="C11" s="9">
-        <v>46195.4343061574</v>
+        <v>46195.600972824075</v>
       </c>
       <c r="D11" s="9">
-        <v>46195.4343253125</v>
+        <v>46195.60099197917</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>50</v>
@@ -2285,11 +2285,11 @@
         <v>54</v>
       </c>
       <c r="B12" s="5">
-        <v>46169.50229908565</v>
+        <v>46169.66896575232</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46174.65451085648</v>
+        <v>46174.82117752315</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2348,11 +2348,11 @@
         <v>61</v>
       </c>
       <c r="B13" s="9">
-        <v>46169.502305</v>
+        <v>46169.668971666666</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="9">
-        <v>46191.520134618055</v>
+        <v>46191.686801284726</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>62</v>
@@ -2401,11 +2401,11 @@
         <v>63</v>
       </c>
       <c r="B14" s="5">
-        <v>46169.50215916667</v>
+        <v>46169.66882583333</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46192.80674869213</v>
+        <v>46192.97341535879</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>64</v>
@@ -2450,13 +2450,13 @@
         <v>67</v>
       </c>
       <c r="B15" s="9">
-        <v>46169.502324189816</v>
+        <v>46169.66899085648</v>
       </c>
       <c r="C15" s="9">
-        <v>46181.470113981486</v>
+        <v>46181.63678064814</v>
       </c>
       <c r="D15" s="9">
-        <v>46192.80672980324</v>
+        <v>46192.97339646991</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>68</v>
@@ -2515,13 +2515,13 @@
         <v>73</v>
       </c>
       <c r="B16" s="5">
-        <v>46169.50232951389</v>
+        <v>46169.66899618055</v>
       </c>
       <c r="C16" s="5">
-        <v>46181.47007760417</v>
+        <v>46181.63674427083</v>
       </c>
       <c r="D16" s="5">
-        <v>46192.80672980324</v>
+        <v>46192.97339646991</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>74</v>
@@ -2580,13 +2580,13 @@
         <v>77</v>
       </c>
       <c r="B17" s="9">
-        <v>46169.502335439814</v>
+        <v>46169.669002106486</v>
       </c>
       <c r="C17" s="9">
-        <v>46181.47008326389</v>
+        <v>46181.636749930556</v>
       </c>
       <c r="D17" s="9">
-        <v>46192.80673009259</v>
+        <v>46192.97339675926</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>78</v>
@@ -2645,13 +2645,13 @@
         <v>80</v>
       </c>
       <c r="B18" s="5">
-        <v>46169.50216334491</v>
+        <v>46169.66883001158</v>
       </c>
       <c r="C18" s="5">
-        <v>46197.478206597225</v>
+        <v>46197.64487326389</v>
       </c>
       <c r="D18" s="5">
-        <v>46197.47821863426</v>
+        <v>46197.64488530092</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>81</v>
@@ -2698,13 +2698,13 @@
         <v>83</v>
       </c>
       <c r="B19" s="9">
-        <v>46169.502349386574</v>
+        <v>46169.669016053245</v>
       </c>
       <c r="C19" s="9">
-        <v>46181.4701584838</v>
+        <v>46181.63682515046</v>
       </c>
       <c r="D19" s="9">
-        <v>46181.47017395833</v>
+        <v>46181.636840625</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>84</v>
@@ -2763,13 +2763,13 @@
         <v>86</v>
       </c>
       <c r="B20" s="5">
-        <v>46169.50235475694</v>
+        <v>46169.669021423615</v>
       </c>
       <c r="C20" s="5">
-        <v>46181.470163645834</v>
+        <v>46181.6368303125</v>
       </c>
       <c r="D20" s="5">
-        <v>46181.47018055555</v>
+        <v>46181.636847222224</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>87</v>
@@ -2828,13 +2828,13 @@
         <v>89</v>
       </c>
       <c r="B21" s="9">
-        <v>46169.50236013889</v>
+        <v>46169.66902680555</v>
       </c>
       <c r="C21" s="9">
-        <v>46181.470173194444</v>
+        <v>46181.63683986111</v>
       </c>
       <c r="D21" s="9">
-        <v>46181.47018822917</v>
+        <v>46181.636854895834</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>90</v>
@@ -2893,13 +2893,13 @@
         <v>93</v>
       </c>
       <c r="B22" s="5">
-        <v>46169.502365671295</v>
+        <v>46169.66903233796</v>
       </c>
       <c r="C22" s="5">
-        <v>46197.47651905092</v>
+        <v>46197.64318571759</v>
       </c>
       <c r="D22" s="5">
-        <v>46197.47706866898</v>
+        <v>46197.643735335645</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>94</v>
@@ -2958,13 +2958,13 @@
         <v>99</v>
       </c>
       <c r="B23" s="9">
-        <v>46169.502370625</v>
+        <v>46169.669037291664</v>
       </c>
       <c r="C23" s="9">
-        <v>46197.4773744213</v>
+        <v>46197.64404108796</v>
       </c>
       <c r="D23" s="9">
-        <v>46197.477390925924</v>
+        <v>46197.644057592595</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>100</v>
@@ -3023,13 +3023,13 @@
         <v>102</v>
       </c>
       <c r="B24" s="5">
-        <v>46169.50237457176</v>
+        <v>46169.66904123843</v>
       </c>
       <c r="C24" s="5">
-        <v>46197.47752260417</v>
+        <v>46197.64418927083</v>
       </c>
       <c r="D24" s="5">
-        <v>46197.47754090278</v>
+        <v>46197.64420756944</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>103</v>
@@ -3088,13 +3088,13 @@
         <v>105</v>
       </c>
       <c r="B25" s="9">
-        <v>46169.50237844908</v>
+        <v>46169.66904511574</v>
       </c>
       <c r="C25" s="9">
-        <v>46197.4781924537</v>
+        <v>46197.644859120366</v>
       </c>
       <c r="D25" s="9">
-        <v>46197.478208078704</v>
+        <v>46197.64487474537</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>106</v>
@@ -3153,13 +3153,13 @@
         <v>108</v>
       </c>
       <c r="B26" s="5">
-        <v>46169.50238211805</v>
+        <v>46169.66904878472</v>
       </c>
       <c r="C26" s="5">
-        <v>46195.4350077662</v>
+        <v>46195.601674432866</v>
       </c>
       <c r="D26" s="5">
-        <v>46195.4350225463</v>
+        <v>46195.60168921296</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>109</v>
@@ -3218,11 +3218,11 @@
         <v>111</v>
       </c>
       <c r="B27" s="9">
-        <v>46169.50216752315</v>
+        <v>46169.66883418981</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46182.46799320602</v>
+        <v>46205.61252570602</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>112</v>
@@ -3258,20 +3258,22 @@
       <c r="R27" s="10"/>
       <c r="S27" s="10"/>
       <c r="T27" s="10"/>
-      <c r="U27" s="10"/>
+      <c r="U27" s="12" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>114</v>
       </c>
       <c r="B28" s="5">
-        <v>46169.50242258102</v>
+        <v>46169.66908924768</v>
       </c>
       <c r="C28" s="5">
-        <v>46182.46798378472</v>
+        <v>46182.63465045139</v>
       </c>
       <c r="D28" s="5">
-        <v>46182.46799741898</v>
+        <v>46182.63466408565</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>115</v>
@@ -3330,13 +3332,13 @@
         <v>119</v>
       </c>
       <c r="B29" s="9">
-        <v>46169.502428541666</v>
+        <v>46169.66909520833</v>
       </c>
       <c r="C29" s="9">
-        <v>46182.465695266204</v>
+        <v>46182.63236193287</v>
       </c>
       <c r="D29" s="9">
-        <v>46182.4656965625</v>
+        <v>46182.63236322917</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>120</v>
@@ -3391,13 +3393,13 @@
         <v>122</v>
       </c>
       <c r="B30" s="5">
-        <v>46169.50243414352</v>
+        <v>46169.669100810184</v>
       </c>
       <c r="C30" s="5">
-        <v>46182.467969143516</v>
+        <v>46182.63463581019</v>
       </c>
       <c r="D30" s="5">
-        <v>46182.46797055556</v>
+        <v>46182.63463722222</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>123</v>
@@ -3452,13 +3454,13 @@
         <v>125</v>
       </c>
       <c r="B31" s="9">
-        <v>46169.50243961805</v>
+        <v>46169.669106284724</v>
       </c>
       <c r="C31" s="9">
-        <v>46182.46792015046</v>
+        <v>46182.634586817134</v>
       </c>
       <c r="D31" s="9">
-        <v>46182.467933761574</v>
+        <v>46182.63460042824</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>126</v>
@@ -3517,13 +3519,13 @@
         <v>129</v>
       </c>
       <c r="B32" s="5">
-        <v>46169.502444618054</v>
+        <v>46169.66911128472</v>
       </c>
       <c r="C32" s="5">
-        <v>46182.46514231482</v>
+        <v>46182.63180898148</v>
       </c>
       <c r="D32" s="5">
-        <v>46182.465144270835</v>
+        <v>46182.6318109375</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>130</v>
@@ -3578,13 +3580,13 @@
         <v>132</v>
       </c>
       <c r="B33" s="9">
-        <v>46169.50245013888</v>
+        <v>46169.669116805555</v>
       </c>
       <c r="C33" s="9">
-        <v>46182.46790510417</v>
+        <v>46182.63457177083</v>
       </c>
       <c r="D33" s="9">
-        <v>46182.4679066088</v>
+        <v>46182.63457327546</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>133</v>
@@ -3639,13 +3641,13 @@
         <v>135</v>
       </c>
       <c r="B34" s="5">
-        <v>46169.502455381946</v>
+        <v>46169.66912204861</v>
       </c>
       <c r="C34" s="5">
-        <v>46182.467756805556</v>
+        <v>46182.63442347222</v>
       </c>
       <c r="D34" s="5">
-        <v>46182.467768912036</v>
+        <v>46182.6344355787</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>136</v>
@@ -3704,13 +3706,13 @@
         <v>138</v>
       </c>
       <c r="B35" s="9">
-        <v>46169.50246045139</v>
+        <v>46169.66912711806</v>
       </c>
       <c r="C35" s="9">
-        <v>46182.46537144676</v>
+        <v>46182.63203811343</v>
       </c>
       <c r="D35" s="9">
-        <v>46182.46537292824</v>
+        <v>46182.63203959491</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>139</v>
@@ -3765,13 +3767,13 @@
         <v>141</v>
       </c>
       <c r="B36" s="5">
-        <v>46169.50246604167</v>
+        <v>46169.66913270833</v>
       </c>
       <c r="C36" s="5">
-        <v>46182.46774303241</v>
+        <v>46182.63440969907</v>
       </c>
       <c r="D36" s="5">
-        <v>46182.46774453703</v>
+        <v>46182.634411203704</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>142</v>
@@ -3826,13 +3828,13 @@
         <v>144</v>
       </c>
       <c r="B37" s="9">
-        <v>46169.502471423606</v>
+        <v>46169.66913809028</v>
       </c>
       <c r="C37" s="9">
-        <v>46182.46768396991</v>
+        <v>46182.634350636574</v>
       </c>
       <c r="D37" s="9">
-        <v>46182.46768619213</v>
+        <v>46182.6343528588</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>145</v>
@@ -3887,11 +3889,11 @@
         <v>147</v>
       </c>
       <c r="B38" s="5">
-        <v>46169.502478090275</v>
+        <v>46169.66914475695</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46195.51975071759</v>
+        <v>46195.68641738426</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>148</v>
@@ -3950,13 +3952,13 @@
         <v>150</v>
       </c>
       <c r="B39" s="9">
-        <v>46169.50248260416</v>
+        <v>46169.669149270834</v>
       </c>
       <c r="C39" s="9">
-        <v>46195.51974444445</v>
+        <v>46195.686411111106</v>
       </c>
       <c r="D39" s="9">
-        <v>46195.51974633102</v>
+        <v>46195.68641299769</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>110</v>
@@ -4005,11 +4007,11 @@
         <v>152</v>
       </c>
       <c r="B40" s="5">
-        <v>46169.502487418984</v>
+        <v>46169.66915408565</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46195.51975190973</v>
+        <v>46195.686418576384</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>153</v>
@@ -4058,11 +4060,11 @@
         <v>155</v>
       </c>
       <c r="B41" s="9">
-        <v>46169.502491990745</v>
+        <v>46169.66915865741</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46199.402525046295</v>
+        <v>46205.612521585645</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>156</v>
@@ -4110,10 +4112,10 @@
         <v>33</v>
       </c>
       <c r="T41" s="10">
-        <v>0</v>
-      </c>
-      <c r="U41" s="11" t="s">
-        <v>60</v>
+        <v>1</v>
+      </c>
+      <c r="U41" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
@@ -4121,13 +4123,13 @@
         <v>160</v>
       </c>
       <c r="B42" s="5">
-        <v>46169.502497106485</v>
+        <v>46169.66916377315</v>
       </c>
       <c r="C42" s="5">
-        <v>46199.399699490736</v>
+        <v>46199.56636615741</v>
       </c>
       <c r="D42" s="5">
-        <v>46199.40261225695</v>
+        <v>46199.56927892361</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>161</v>
@@ -4182,11 +4184,13 @@
         <v>163</v>
       </c>
       <c r="B43" s="9">
-        <v>46169.50250293982</v>
-      </c>
-      <c r="C43" s="10"/>
+        <v>46169.66916960648</v>
+      </c>
+      <c r="C43" s="9">
+        <v>46205.612468321764</v>
+      </c>
       <c r="D43" s="9">
-        <v>46199.39996811343</v>
+        <v>46205.61247092593</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>164</v>
@@ -4241,13 +4245,13 @@
         <v>166</v>
       </c>
       <c r="B44" s="5">
-        <v>46169.50250836805</v>
+        <v>46169.66917503472</v>
       </c>
       <c r="C44" s="5">
-        <v>46199.40060425926</v>
+        <v>46199.56727092592</v>
       </c>
       <c r="D44" s="5">
-        <v>46199.4006155324</v>
+        <v>46199.567282199074</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>167</v>
@@ -4306,13 +4310,13 @@
         <v>169</v>
       </c>
       <c r="B45" s="9">
-        <v>46169.50251222222</v>
+        <v>46169.669178888886</v>
       </c>
       <c r="C45" s="9">
-        <v>46199.40039329861</v>
+        <v>46199.56705996528</v>
       </c>
       <c r="D45" s="9">
-        <v>46199.4032296875</v>
+        <v>46199.569896354165</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>101</v>
@@ -4361,13 +4365,13 @@
         <v>171</v>
       </c>
       <c r="B46" s="5">
-        <v>46169.50251701389</v>
+        <v>46169.669183680555</v>
       </c>
       <c r="C46" s="5">
-        <v>46199.40058951388</v>
+        <v>46199.567256180555</v>
       </c>
       <c r="D46" s="5">
-        <v>46199.403173680555</v>
+        <v>46199.56984034722</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>172</v>
@@ -4416,13 +4420,13 @@
         <v>174</v>
       </c>
       <c r="B47" s="9">
-        <v>46169.502521828705</v>
+        <v>46169.66918849537</v>
       </c>
       <c r="C47" s="9">
-        <v>46204.696932175924</v>
+        <v>46204.863598842596</v>
       </c>
       <c r="D47" s="9">
-        <v>46204.69694961805</v>
+        <v>46204.863616284725</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>175</v>
@@ -4481,13 +4485,13 @@
         <v>179</v>
       </c>
       <c r="B48" s="5">
-        <v>46169.502525856486</v>
+        <v>46169.66919252315</v>
       </c>
       <c r="C48" s="5">
-        <v>46204.69684259259</v>
+        <v>46204.86350925926</v>
       </c>
       <c r="D48" s="5">
-        <v>46204.696844328704</v>
+        <v>46204.863510995376</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>107</v>
@@ -4536,13 +4540,13 @@
         <v>181</v>
       </c>
       <c r="B49" s="9">
-        <v>46169.502530682876</v>
+        <v>46169.66919734953</v>
       </c>
       <c r="C49" s="9">
-        <v>46204.69688052083</v>
+        <v>46204.8635471875</v>
       </c>
       <c r="D49" s="9">
-        <v>46204.69688203704</v>
+        <v>46204.8635487037</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>182</v>
@@ -4591,11 +4595,11 @@
         <v>184</v>
       </c>
       <c r="B50" s="5">
-        <v>46169.502535625</v>
+        <v>46169.66920229167</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46204.696889363426</v>
+        <v>46204.86355603009</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -4644,13 +4648,13 @@
         <v>188</v>
       </c>
       <c r="B51" s="9">
-        <v>46169.5025753588</v>
+        <v>46169.66924202546</v>
       </c>
       <c r="C51" s="9">
-        <v>46199.40417166667</v>
+        <v>46199.57083833333</v>
       </c>
       <c r="D51" s="9">
-        <v>46199.40418243056</v>
+        <v>46199.57084909722</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>189</v>
@@ -4709,13 +4713,13 @@
         <v>191</v>
       </c>
       <c r="B52" s="5">
-        <v>46169.5025796875</v>
+        <v>46169.66924635417</v>
       </c>
       <c r="C52" s="5">
-        <v>46199.40411315972</v>
+        <v>46199.57077982639</v>
       </c>
       <c r="D52" s="5">
-        <v>46199.40411498843</v>
+        <v>46199.57078165509</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>104</v>
@@ -4764,13 +4768,13 @@
         <v>193</v>
       </c>
       <c r="B53" s="9">
-        <v>46169.50258424769</v>
+        <v>46169.66925091435</v>
       </c>
       <c r="C53" s="9">
-        <v>46199.40415833333</v>
+        <v>46199.570825</v>
       </c>
       <c r="D53" s="9">
-        <v>46199.40416064815</v>
+        <v>46199.57082731482</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>194</v>
@@ -4819,11 +4823,11 @@
         <v>196</v>
       </c>
       <c r="B54" s="5">
-        <v>46169.502588993055</v>
+        <v>46169.669255659726</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46195.78347130787</v>
+        <v>46195.950137974534</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>197</v>
@@ -4868,13 +4872,13 @@
         <v>199</v>
       </c>
       <c r="B55" s="9">
-        <v>46169.50259230324</v>
+        <v>46169.66925896991</v>
       </c>
       <c r="C55" s="9">
-        <v>46195.78333766204</v>
+        <v>46195.950004328704</v>
       </c>
       <c r="D55" s="9">
-        <v>46197.54897538194</v>
+        <v>46197.71564204861</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>200</v>
@@ -4933,13 +4937,13 @@
         <v>205</v>
       </c>
       <c r="B56" s="5">
-        <v>46169.50259741898</v>
+        <v>46169.66926408565</v>
       </c>
       <c r="C56" s="5">
-        <v>46195.783310659725</v>
+        <v>46195.94997732639</v>
       </c>
       <c r="D56" s="5">
-        <v>46195.78331274306</v>
+        <v>46195.94997940972</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>206</v>
@@ -4988,13 +4992,13 @@
         <v>210</v>
       </c>
       <c r="B57" s="9">
-        <v>46169.502602858796</v>
+        <v>46169.66926952546</v>
       </c>
       <c r="C57" s="9">
-        <v>46195.78332052083</v>
+        <v>46195.9499871875</v>
       </c>
       <c r="D57" s="9">
-        <v>46195.78332291667</v>
+        <v>46195.94998958333</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>211</v>
@@ -5043,13 +5047,13 @@
         <v>213</v>
       </c>
       <c r="B58" s="5">
-        <v>46169.50262597222</v>
+        <v>46169.66929263889</v>
       </c>
       <c r="C58" s="5">
-        <v>46195.783453738426</v>
+        <v>46195.95012040509</v>
       </c>
       <c r="D58" s="5">
-        <v>46197.549008472226</v>
+        <v>46197.71567513889</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>214</v>
@@ -5108,13 +5112,13 @@
         <v>216</v>
       </c>
       <c r="B59" s="9">
-        <v>46169.50263108796</v>
+        <v>46169.66929775463</v>
       </c>
       <c r="C59" s="9">
-        <v>46195.7834280324</v>
+        <v>46195.950094699074</v>
       </c>
       <c r="D59" s="9">
-        <v>46195.78342979167</v>
+        <v>46195.950096458335</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>206</v>
@@ -5163,13 +5167,13 @@
         <v>219</v>
       </c>
       <c r="B60" s="5">
-        <v>46169.5026369213</v>
+        <v>46169.66930358796</v>
       </c>
       <c r="C60" s="5">
-        <v>46195.78343855324</v>
+        <v>46195.950105219905</v>
       </c>
       <c r="D60" s="5">
-        <v>46196.71318825231</v>
+        <v>46196.87985491898</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>211</v>
@@ -5218,13 +5222,13 @@
         <v>221</v>
       </c>
       <c r="B61" s="9">
-        <v>46169.50266038194</v>
+        <v>46169.669327048614</v>
       </c>
       <c r="C61" s="9">
-        <v>46196.71328599537</v>
+        <v>46196.87995266204</v>
       </c>
       <c r="D61" s="9">
-        <v>46196.71330142361</v>
+        <v>46196.879968090274</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>97</v>
@@ -5283,13 +5287,13 @@
         <v>223</v>
       </c>
       <c r="B62" s="5">
-        <v>46169.50267328703</v>
+        <v>46169.6693399537</v>
       </c>
       <c r="C62" s="5">
-        <v>46195.78375555556</v>
+        <v>46195.950422222224</v>
       </c>
       <c r="D62" s="5">
-        <v>46195.783757303245</v>
+        <v>46195.95042396991</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>206</v>
@@ -5338,11 +5342,11 @@
         <v>224</v>
       </c>
       <c r="B63" s="9">
-        <v>46169.502694537034</v>
+        <v>46169.669361203705</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46174.67994138889</v>
+        <v>46174.84660805555</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>225</v>
@@ -5401,11 +5405,11 @@
         <v>228</v>
       </c>
       <c r="B64" s="5">
-        <v>46169.502698344906</v>
+        <v>46169.66936501158</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46174.680252754624</v>
+        <v>46174.846919421296</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>206</v>
@@ -5454,11 +5458,11 @@
         <v>230</v>
       </c>
       <c r="B65" s="9">
-        <v>46169.5027514699</v>
+        <v>46169.669418136575</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46170.42657998843</v>
+        <v>46170.59324665509</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>231</v>
@@ -5501,11 +5505,11 @@
         <v>233</v>
       </c>
       <c r="B66" s="5">
-        <v>46169.50276018518</v>
+        <v>46169.66942685185</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46174.68034853009</v>
+        <v>46205.61248846065</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>234</v>
@@ -5555,8 +5559,8 @@
       <c r="T66" s="6">
         <v>0</v>
       </c>
-      <c r="U66" s="11" t="s">
-        <v>60</v>
+      <c r="U66" s="12" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5564,11 +5568,11 @@
         <v>238</v>
       </c>
       <c r="B67" s="9">
-        <v>46169.502765694444</v>
+        <v>46169.669432361115</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46174.68049690972</v>
+        <v>46174.847163576385</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>239</v>
@@ -5627,11 +5631,11 @@
         <v>242</v>
       </c>
       <c r="B68" s="5">
-        <v>46169.50277170139</v>
+        <v>46169.66943836806</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46199.400608344906</v>
+        <v>46199.56727501158</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>243</v>
@@ -5690,11 +5694,11 @@
         <v>245</v>
       </c>
       <c r="B69" s="9">
-        <v>46169.50277702547</v>
+        <v>46169.669443692124</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46174.6804941088</v>
+        <v>46174.84716077546</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>246</v>
@@ -5753,11 +5757,11 @@
         <v>248</v>
       </c>
       <c r="B70" s="5">
-        <v>46169.50278170139</v>
+        <v>46169.669448368055</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46199.404175185184</v>
+        <v>46199.57084185185</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>249</v>
@@ -5816,11 +5820,11 @@
         <v>251</v>
       </c>
       <c r="B71" s="9">
-        <v>46169.50278631944</v>
+        <v>46169.66945298611</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46174.68049027778</v>
+        <v>46174.847156944445</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>250</v>
@@ -5879,11 +5883,11 @@
         <v>252</v>
       </c>
       <c r="B72" s="5">
-        <v>46169.502791122686</v>
+        <v>46169.66945778935</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46170.46087596065</v>
+        <v>46170.62754262731</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>253</v>
@@ -5926,11 +5930,11 @@
         <v>255</v>
       </c>
       <c r="B73" s="9">
-        <v>46169.502794375</v>
+        <v>46169.66946104167</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46174.680633703705</v>
+        <v>46174.84730037037</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>256</v>
@@ -5989,11 +5993,11 @@
         <v>260</v>
       </c>
       <c r="B74" s="5">
-        <v>46169.50280061342</v>
+        <v>46169.669467280095</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46174.68059793982</v>
+        <v>46174.84726460648</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>206</v>
@@ -6042,11 +6046,11 @@
         <v>263</v>
       </c>
       <c r="B75" s="9">
-        <v>46169.50280682871</v>
+        <v>46169.66947349537</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46174.68059503472</v>
+        <v>46174.84726170139</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>264</v>
@@ -6095,11 +6099,11 @@
         <v>266</v>
       </c>
       <c r="B76" s="5">
-        <v>46169.50283622685</v>
+        <v>46169.66950289352</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46174.68077684028</v>
+        <v>46174.847443506944</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>267</v>
@@ -6158,11 +6162,11 @@
         <v>268</v>
       </c>
       <c r="B77" s="9">
-        <v>46169.502840914356</v>
+        <v>46169.66950758102</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46196.71329262732</v>
+        <v>46196.87995929398</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>206</v>
@@ -6211,11 +6215,11 @@
         <v>271</v>
       </c>
       <c r="B78" s="5">
-        <v>46169.502846979165</v>
+        <v>46169.66951364583</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46196.71329318287</v>
+        <v>46196.87995984954</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>211</v>
@@ -6264,11 +6268,11 @@
         <v>274</v>
       </c>
       <c r="B79" s="9">
-        <v>46169.5028671412</v>
+        <v>46169.66953380787</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46197.675947592594</v>
+        <v>46197.84261425926</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>275</v>
@@ -6327,11 +6331,11 @@
         <v>276</v>
       </c>
       <c r="B80" s="5">
-        <v>46169.502871874996</v>
+        <v>46169.66953854167</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46197.67589456019</v>
+        <v>46197.84256122685</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>206</v>
@@ -6378,11 +6382,11 @@
         <v>278</v>
       </c>
       <c r="B81" s="9">
-        <v>46169.5028775463</v>
+        <v>46169.669544212964</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46197.675849837964</v>
+        <v>46197.84251650463</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>211</v>
@@ -6429,11 +6433,11 @@
         <v>281</v>
       </c>
       <c r="B82" s="5">
-        <v>46169.502934421296</v>
+        <v>46169.66960108797</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46171.51944895834</v>
+        <v>46171.686115625</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>231</v>
@@ -6476,11 +6480,11 @@
         <v>283</v>
       </c>
       <c r="B83" s="9">
-        <v>46169.50294289352</v>
+        <v>46169.66960956018</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46182.46792298611</v>
+        <v>46182.63458965278</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>284</v>
@@ -6539,11 +6543,11 @@
         <v>286</v>
       </c>
       <c r="B84" s="5">
-        <v>46169.50294984954</v>
+        <v>46169.6696165162</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46182.46798901621</v>
+        <v>46182.63465568287</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>287</v>
@@ -6602,11 +6606,11 @@
         <v>289</v>
       </c>
       <c r="B85" s="9">
-        <v>46169.50295627315</v>
+        <v>46169.669622939815</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46182.46776100695</v>
+        <v>46182.63442767361</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>290</v>
@@ -6665,11 +6669,11 @@
         <v>291</v>
       </c>
       <c r="B86" s="5">
-        <v>46169.502963136576</v>
+        <v>46169.66962980324</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46204.696898587965</v>
+        <v>46204.86356525463</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>292</v>
@@ -6728,11 +6732,11 @@
         <v>294</v>
       </c>
       <c r="B87" s="9">
-        <v>46169.502968518515</v>
+        <v>46169.669635185186</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46174.68112206018</v>
+        <v>46174.84778872685</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>58</v>
@@ -6791,11 +6795,11 @@
         <v>296</v>
       </c>
       <c r="B88" s="5">
-        <v>46169.50298123843</v>
+        <v>46169.66964790509</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46171.54782046296</v>
+        <v>46171.71448712963</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>297</v>
@@ -6838,11 +6842,11 @@
         <v>299</v>
       </c>
       <c r="B89" s="9">
-        <v>46169.50298443287</v>
+        <v>46169.66965109954</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46174.68123428241</v>
+        <v>46174.84790094907</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>300</v>
@@ -6901,11 +6905,11 @@
         <v>302</v>
       </c>
       <c r="B90" s="5">
-        <v>46169.50299016204</v>
+        <v>46169.6696568287</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46174.681321724536</v>
+        <v>46174.84798839121</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>206</v>
@@ -6954,11 +6958,11 @@
         <v>304</v>
       </c>
       <c r="B91" s="9">
-        <v>46169.503021956014</v>
+        <v>46169.669688622685</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46204.73048884259</v>
+        <v>46204.89715550926</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>305</v>
@@ -7017,11 +7021,11 @@
         <v>306</v>
       </c>
       <c r="B92" s="5">
-        <v>46169.503026805556</v>
+        <v>46169.66969347223</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46196.71330358797</v>
+        <v>46196.87997025463</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>206</v>
@@ -7068,11 +7072,11 @@
         <v>309</v>
       </c>
       <c r="B93" s="9">
-        <v>46169.50306015046</v>
+        <v>46169.66972681713</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46174.68122747685</v>
+        <v>46174.84789414352</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>310</v>
@@ -7131,11 +7135,11 @@
         <v>311</v>
       </c>
       <c r="B94" s="5">
-        <v>46169.50306513889</v>
+        <v>46169.66973180555</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46196.71329425926</v>
+        <v>46196.87996092593</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>206</v>
@@ -7184,11 +7188,11 @@
         <v>314</v>
       </c>
       <c r="B95" s="9">
-        <v>46169.503143877315</v>
+        <v>46169.66981054399</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46174.68122427083</v>
+        <v>46174.8478909375</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>315</v>
@@ -7247,11 +7251,11 @@
         <v>316</v>
       </c>
       <c r="B96" s="5">
-        <v>46169.503150578705</v>
+        <v>46169.66981724537</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46196.713304247685</v>
+        <v>46196.87997091435</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>206</v>
@@ -7300,11 +7304,11 @@
         <v>319</v>
       </c>
       <c r="B97" s="9">
-        <v>46169.503194375</v>
+        <v>46169.669861041664</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46174.68121953704</v>
+        <v>46174.8478862037</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>320</v>
@@ -7363,11 +7367,11 @@
         <v>321</v>
       </c>
       <c r="B98" s="5">
-        <v>46169.50320057871</v>
+        <v>46169.66986724537</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46174.68150009259</v>
+        <v>46174.84816675926</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>206</v>
@@ -7416,11 +7420,11 @@
         <v>323</v>
       </c>
       <c r="B99" s="9">
-        <v>46169.503236296296</v>
+        <v>46169.66990296297</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46174.681218784724</v>
+        <v>46174.84788545139</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>324</v>
@@ -7479,11 +7483,11 @@
         <v>326</v>
       </c>
       <c r="B100" s="5">
-        <v>46169.50327888889</v>
+        <v>46169.66994555556</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46174.68160265047</v>
+        <v>46174.848269317125</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>206</v>
@@ -7530,11 +7534,11 @@
         <v>328</v>
       </c>
       <c r="B101" s="9">
-        <v>46169.50331197916</v>
+        <v>46169.669978645834</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46174.65735081019</v>
+        <v>46174.82401747685</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>329</v>
@@ -7577,11 +7581,11 @@
         <v>331</v>
       </c>
       <c r="B102" s="5">
-        <v>46169.503315775466</v>
+        <v>46169.66998244213</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46174.68176847222</v>
+        <v>46174.84843513889</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>332</v>
@@ -7640,11 +7644,11 @@
         <v>336</v>
       </c>
       <c r="B103" s="9">
-        <v>46169.503323275465</v>
+        <v>46169.66998994213</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46174.681721712965</v>
+        <v>46174.84838837963</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>206</v>
@@ -7691,11 +7695,11 @@
         <v>338</v>
       </c>
       <c r="B104" s="5">
-        <v>46170.46452224537</v>
+        <v>46170.63118891204</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46174.68171880787</v>
+        <v>46174.848385474535</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>211</v>
@@ -7742,11 +7746,11 @@
         <v>339</v>
       </c>
       <c r="B105" s="9">
-        <v>46174.654289224534</v>
+        <v>46174.820955891206</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46174.681714618055</v>
+        <v>46174.848381284726</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>62</v>
@@ -7795,11 +7799,11 @@
         <v>341</v>
       </c>
       <c r="B106" s="5">
-        <v>46169.50337755787</v>
+        <v>46169.670044224535</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46174.68189216436</v>
+        <v>46174.848558831014</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>342</v>
@@ -7856,11 +7860,11 @@
         <v>343</v>
       </c>
       <c r="B107" s="9">
-        <v>46169.50338238426</v>
+        <v>46169.670049050925</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46174.68186048611</v>
+        <v>46174.848527152775</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>206</v>
@@ -7907,11 +7911,11 @@
         <v>345</v>
       </c>
       <c r="B108" s="5">
-        <v>46170.46547012731</v>
+        <v>46170.63213679398</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46174.68185760417</v>
+        <v>46174.848524270834</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>211</v>
@@ -7958,11 +7962,11 @@
         <v>346</v>
       </c>
       <c r="B109" s="9">
-        <v>46174.65432623842</v>
+        <v>46174.82099290509</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46174.681853622686</v>
+        <v>46174.84852028935</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>340</v>
@@ -8011,11 +8015,11 @@
         <v>347</v>
       </c>
       <c r="B110" s="5">
-        <v>46169.50347310185</v>
+        <v>46169.67013976852</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46174.682036412036</v>
+        <v>46174.84870307871</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>348</v>
@@ -8072,11 +8076,11 @@
         <v>349</v>
       </c>
       <c r="B111" s="9">
-        <v>46169.50348471064</v>
+        <v>46169.670151377315</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46174.68200320602</v>
+        <v>46174.848669872685</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>206</v>
@@ -8125,11 +8129,11 @@
         <v>351</v>
       </c>
       <c r="B112" s="5">
-        <v>46170.46619331019</v>
+        <v>46170.63285997685</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46174.68200064814</v>
+        <v>46174.848667314815</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>211</v>
@@ -8178,11 +8182,11 @@
         <v>352</v>
       </c>
       <c r="B113" s="9">
-        <v>46174.65435747685</v>
+        <v>46174.821024143515</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46174.68199670139</v>
+        <v>46174.84866336806</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>62</v>
@@ -8231,11 +8235,11 @@
         <v>353</v>
       </c>
       <c r="B114" s="5">
-        <v>46169.50355298611</v>
+        <v>46169.67021965278</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46174.682143136575</v>
+        <v>46174.84880980324</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>354</v>
@@ -8294,11 +8298,11 @@
         <v>356</v>
       </c>
       <c r="B115" s="9">
-        <v>46169.50356010417</v>
+        <v>46169.67022677083</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46174.68211905092</v>
+        <v>46174.84878571759</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>206</v>
@@ -8345,11 +8349,11 @@
         <v>357</v>
       </c>
       <c r="B116" s="5">
-        <v>46170.46691516203</v>
+        <v>46170.633581828704</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46174.68211648148</v>
+        <v>46174.84878314815</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>211</v>
@@ -8396,11 +8400,11 @@
         <v>358</v>
       </c>
       <c r="B117" s="9">
-        <v>46174.65439037037</v>
+        <v>46174.821057037036</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46174.68211247685</v>
+        <v>46174.84877914352</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>62</v>
@@ -8447,11 +8451,11 @@
         <v>359</v>
       </c>
       <c r="B118" s="5">
-        <v>46169.503649502316</v>
+        <v>46169.67031616898</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46174.65735084491</v>
+        <v>46174.82401751158</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>360</v>
@@ -8494,11 +8498,11 @@
         <v>362</v>
       </c>
       <c r="B119" s="9">
-        <v>46169.503653101856</v>
+        <v>46169.67031976852</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46174.6821881713</v>
+        <v>46174.84885483797</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>363</v>
@@ -8557,11 +8561,11 @@
         <v>366</v>
       </c>
       <c r="B120" s="5">
-        <v>46169.50365864583</v>
+        <v>46169.6703253125</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46192.80672978009</v>
+        <v>46192.97339644676</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>367</v>
@@ -8620,11 +8624,11 @@
         <v>368</v>
       </c>
       <c r="B121" s="9">
-        <v>46169.503665763885</v>
+        <v>46169.670332430556</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46174.65735060185</v>
+        <v>46174.82401726852</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>369</v>
@@ -8673,11 +8677,11 @@
         <v>371</v>
       </c>
       <c r="B122" s="5">
-        <v>46169.503669247686</v>
+        <v>46169.67033591435</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46174.68229203703</v>
+        <v>46174.848958703704</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>372</v>
@@ -8736,11 +8740,11 @@
         <v>374</v>
       </c>
       <c r="B123" s="9">
-        <v>46169.503680821756</v>
+        <v>46169.67034748843</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46174.68228920139</v>
+        <v>46174.84895586806</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>375</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -6962,7 +6962,7 @@
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46204.89715550926</v>
+        <v>46205.901977002315</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>305</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -2899,7 +2899,7 @@
         <v>46197.64318571759</v>
       </c>
       <c r="D22" s="5">
-        <v>46197.643735335645</v>
+        <v>46206.55341104166</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>94</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1471" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1472" uniqueCount="376">
   <si>
     <t>50001558 -  GESVIAL</t>
   </si>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46205.61252570602</v>
+        <v>46209.82175228009</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>112</v>
@@ -4062,9 +4062,11 @@
       <c r="B41" s="9">
         <v>46169.66915865741</v>
       </c>
-      <c r="C41" s="10"/>
+      <c r="C41" s="9">
+        <v>46209.82174373843</v>
+      </c>
       <c r="D41" s="9">
-        <v>46205.612521585645</v>
+        <v>46209.82174662037</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>156</v>
@@ -6437,7 +6439,7 @@
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46171.686115625</v>
+        <v>46209.85402508102</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>231</v>
@@ -6473,7 +6475,9 @@
       <c r="R82" s="6"/>
       <c r="S82" s="6"/>
       <c r="T82" s="6"/>
-      <c r="U82" s="6"/>
+      <c r="U82" s="12" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
@@ -6482,9 +6486,11 @@
       <c r="B83" s="9">
         <v>46169.66960956018</v>
       </c>
-      <c r="C83" s="10"/>
+      <c r="C83" s="9">
+        <v>46209.84488153935</v>
+      </c>
       <c r="D83" s="9">
-        <v>46182.63458965278</v>
+        <v>46209.844928101855</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>284</v>
@@ -6532,10 +6538,10 @@
         <v>128</v>
       </c>
       <c r="T83" s="10">
-        <v>0</v>
-      </c>
-      <c r="U83" s="12" t="s">
-        <v>66</v>
+        <v>1</v>
+      </c>
+      <c r="U83" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
@@ -6545,9 +6551,11 @@
       <c r="B84" s="5">
         <v>46169.6696165162</v>
       </c>
-      <c r="C84" s="6"/>
+      <c r="C84" s="5">
+        <v>46209.844589050925</v>
+      </c>
       <c r="D84" s="5">
-        <v>46182.63465568287</v>
+        <v>46209.84471936343</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>287</v>
@@ -6595,10 +6603,10 @@
         <v>33</v>
       </c>
       <c r="T84" s="6">
-        <v>0</v>
-      </c>
-      <c r="U84" s="12" t="s">
-        <v>66</v>
+        <v>1</v>
+      </c>
+      <c r="U84" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6608,9 +6616,11 @@
       <c r="B85" s="9">
         <v>46169.669622939815</v>
       </c>
-      <c r="C85" s="10"/>
+      <c r="C85" s="9">
+        <v>46209.85400761574</v>
+      </c>
       <c r="D85" s="9">
-        <v>46182.63442767361</v>
+        <v>46209.85430440972</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>290</v>
@@ -6658,10 +6668,10 @@
         <v>33</v>
       </c>
       <c r="T85" s="10">
-        <v>0</v>
-      </c>
-      <c r="U85" s="12" t="s">
-        <v>66</v>
+        <v>1</v>
+      </c>
+      <c r="U85" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
@@ -6799,7 +6809,7 @@
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46171.71448712963</v>
+        <v>46209.84945282407</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>297</v>
@@ -6960,9 +6970,11 @@
       <c r="B91" s="9">
         <v>46169.669688622685</v>
       </c>
-      <c r="C91" s="10"/>
+      <c r="C91" s="9">
+        <v>46209.84929427083</v>
+      </c>
       <c r="D91" s="9">
-        <v>46205.901977002315</v>
+        <v>46209.8493094213</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>305</v>
@@ -7010,10 +7022,10 @@
         <v>33</v>
       </c>
       <c r="T91" s="10">
-        <v>0</v>
-      </c>
-      <c r="U91" s="11" t="s">
-        <v>60</v>
+        <v>1</v>
+      </c>
+      <c r="U91" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
@@ -7025,7 +7037,7 @@
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46196.87997025463</v>
+        <v>46209.84459753473</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>206</v>
@@ -7074,9 +7086,11 @@
       <c r="B93" s="9">
         <v>46169.66972681713</v>
       </c>
-      <c r="C93" s="10"/>
+      <c r="C93" s="9">
+        <v>46209.84944726852</v>
+      </c>
       <c r="D93" s="9">
-        <v>46174.84789414352</v>
+        <v>46209.84946481482</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>310</v>
@@ -7124,10 +7138,10 @@
         <v>33</v>
       </c>
       <c r="T93" s="10">
-        <v>0</v>
-      </c>
-      <c r="U93" s="11" t="s">
-        <v>60</v>
+        <v>1</v>
+      </c>
+      <c r="U93" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
@@ -7139,7 +7153,7 @@
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46196.87996092593</v>
+        <v>46209.844891030094</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>206</v>
@@ -7255,7 +7269,7 @@
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46196.87997091435</v>
+        <v>46209.85401892361</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>206</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1472" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1439" uniqueCount="365">
   <si>
     <t>50001558 -  GESVIAL</t>
   </si>
@@ -719,7 +719,7 @@
     <t>1215174260169824</t>
   </si>
   <si>
-    <t>OT 4344 - MANGA DE VENTILACION Ø1600MM,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4344 - MANGA DE VENTILACION Ø1600MM,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,Propuesta Mecanizado,Propuesta Fabricación externa ,propuesta Corte Laser,Propuesta Corte plasma ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A</t>
+    <t>OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,Propuesta Mecanizado,Propuesta Fabricación externa ,propuesta Corte Laser,Propuesta Corte plasma ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A</t>
   </si>
   <si>
     <t>1215174141207989</t>
@@ -776,7 +776,7 @@
     <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
   </si>
   <si>
-    <t>OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4344 - MANGA DE VENTILACION Ø1600MM x 50,Bodega:</t>
+    <t>OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,Bodega:</t>
   </si>
   <si>
     <t>1215174260282365</t>
@@ -794,9 +794,6 @@
     <t>Control de calidad Corte plasma</t>
   </si>
   <si>
-    <t>OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4344 - MANGA DE VENTILACION Ø1600MM x 50</t>
-  </si>
-  <si>
     <t>1215174141283554</t>
   </si>
   <si>
@@ -842,15 +839,6 @@
     <t>Preparación Materiales,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A</t>
   </si>
   <si>
-    <t>1215174166752264</t>
-  </si>
-  <si>
-    <t>OT 4344 - MANGA DE VENTILACION Ø1600MM x 50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,control de calidad corte laser </t>
-  </si>
-  <si>
     <t>1215174266589473</t>
   </si>
   <si>
@@ -866,15 +854,6 @@
     <t>Armado,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A</t>
   </si>
   <si>
-    <t>1215174166783266</t>
-  </si>
-  <si>
-    <t>OT 4344 - MANGA DE VENTILACION Ø1600MM x 50,check planos</t>
-  </si>
-  <si>
-    <t>Armado,OT 4344 - MANGA DE VENTILACION Ø1600MM</t>
-  </si>
-  <si>
     <t>1215174382789626</t>
   </si>
   <si>
@@ -887,15 +866,6 @@
     <t>Control de calidad Armado,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A</t>
   </si>
   <si>
-    <t>1215174141334795</t>
-  </si>
-  <si>
-    <t>OT 4344 - MANGA DE VENTILACION Ø1600MM,check planos</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,OT 4344 - MANGA DE VENTILACION Ø1600MM</t>
-  </si>
-  <si>
     <t>1215174266619637</t>
   </si>
   <si>
@@ -906,9 +876,6 @@
   </si>
   <si>
     <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,Bodega:</t>
   </si>
   <si>
     <t>1215174266650610</t>
@@ -1702,7 +1669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U123"/>
+  <dimension ref="A1:U120"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -5230,7 +5197,7 @@
         <v>46196.87995266204</v>
       </c>
       <c r="D61" s="9">
-        <v>46196.879968090274</v>
+        <v>46209.908330949074</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>97</v>
@@ -5574,7 +5541,7 @@
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46174.847163576385</v>
+        <v>46209.90823064814</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>239</v>
@@ -5700,7 +5667,7 @@
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46174.84716077546</v>
+        <v>46209.90823061342</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>246</v>
@@ -5736,7 +5703,7 @@
         <v>243</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>247</v>
+        <v>206</v>
       </c>
       <c r="Q69" s="9">
         <v>46260</v>
@@ -5756,7 +5723,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B70" s="5">
         <v>46169.669448368055</v>
@@ -5766,7 +5733,7 @@
         <v>46199.57084185185</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5799,7 +5766,7 @@
         <v>194</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q70" s="5">
         <v>46258</v>
@@ -5819,17 +5786,17 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B71" s="9">
         <v>46169.66945298611</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46174.847156944445</v>
+        <v>46209.90823069445</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
@@ -5859,10 +5826,10 @@
         <v>231</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>247</v>
+        <v>206</v>
       </c>
       <c r="Q71" s="9">
         <v>46260</v>
@@ -5882,17 +5849,17 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B72" s="5">
         <v>46169.66945778935</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46170.62754262731</v>
+        <v>46209.909264270835</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>25</v>
@@ -5916,7 +5883,7 @@
         <v>26</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>26</v>
@@ -5929,26 +5896,28 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B73" s="9">
         <v>46169.66946104167</v>
       </c>
-      <c r="C73" s="10"/>
+      <c r="C73" s="9">
+        <v>46209.90925715277</v>
+      </c>
       <c r="D73" s="9">
-        <v>46174.84730037037</v>
+        <v>46209.90937729167</v>
       </c>
       <c r="E73" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="F73" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G73" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="F73" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G73" s="10" t="s">
+      <c r="H73" s="10" t="s">
         <v>257</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>258</v>
       </c>
       <c r="I73" s="9">
         <v>46262</v>
@@ -5966,13 +5935,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q73" s="9">
         <v>46262</v>
@@ -5984,22 +5953,24 @@
         <v>33</v>
       </c>
       <c r="T73" s="10">
-        <v>0</v>
-      </c>
-      <c r="U73" s="11" t="s">
-        <v>60</v>
+        <v>1</v>
+      </c>
+      <c r="U73" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B74" s="5">
         <v>46169.669467280095</v>
       </c>
-      <c r="C74" s="6"/>
+      <c r="C74" s="5">
+        <v>46209.909371331014</v>
+      </c>
       <c r="D74" s="5">
-        <v>46174.84726460648</v>
+        <v>46209.90937271991</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>206</v>
@@ -6008,10 +5979,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="I74" s="5">
         <v>46262</v>
@@ -6029,13 +6000,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O74" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="P74" s="6" t="s">
         <v>261</v>
-      </c>
-      <c r="P74" s="6" t="s">
-        <v>262</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6045,32 +6016,32 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B75" s="9">
-        <v>46169.66947349537</v>
+        <v>46169.66950289352</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46174.84726170139</v>
+        <v>46209.90954123843</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="H75" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="H75" s="10" t="s">
-        <v>258</v>
-      </c>
       <c r="I75" s="9">
-        <v>46262</v>
+        <v>46273</v>
       </c>
       <c r="J75" s="9">
-        <v>46272</v>
+        <v>46293</v>
       </c>
       <c r="K75" s="10" t="s">
         <v>26</v>
@@ -6082,42 +6053,52 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>265</v>
+        <v>206</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="Q75" s="10"/>
-      <c r="R75" s="10"/>
-      <c r="S75" s="10"/>
-      <c r="T75" s="10"/>
-      <c r="U75" s="10"/>
+        <v>252</v>
+      </c>
+      <c r="Q75" s="9">
+        <v>46273</v>
+      </c>
+      <c r="R75" s="9">
+        <v>46293</v>
+      </c>
+      <c r="S75" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T75" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="U75" s="12" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B76" s="5">
-        <v>46169.66950289352</v>
+        <v>46169.66950758102</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46174.847443506944</v>
+        <v>46209.90937868056</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>267</v>
+        <v>206</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="I76" s="5">
         <v>46273</v>
@@ -6135,111 +6116,109 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>204</v>
+        <v>265</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q76" s="5">
-        <v>46273</v>
-      </c>
-      <c r="R76" s="5">
-        <v>46293</v>
-      </c>
-      <c r="S76" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T76" s="6">
-        <v>0</v>
-      </c>
-      <c r="U76" s="11" t="s">
-        <v>60</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="Q76" s="6"/>
+      <c r="R76" s="6"/>
+      <c r="S76" s="6"/>
+      <c r="T76" s="6"/>
+      <c r="U76" s="6"/>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B77" s="9">
-        <v>46169.66950758102</v>
+        <v>46169.66953380787</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46196.87995929398</v>
+        <v>46209.908330833336</v>
       </c>
       <c r="E77" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="F77" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G77" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H77" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="I77" s="9">
+        <v>46294</v>
+      </c>
+      <c r="J77" s="9">
+        <v>46294</v>
+      </c>
+      <c r="K77" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L77" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M77" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N77" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="O77" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="F77" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G77" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="I77" s="9">
-        <v>46273</v>
-      </c>
-      <c r="J77" s="9">
-        <v>46293</v>
-      </c>
-      <c r="K77" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L77" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M77" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N77" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="O77" s="10" t="s">
-        <v>269</v>
-      </c>
       <c r="P77" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="Q77" s="10"/>
-      <c r="R77" s="10"/>
-      <c r="S77" s="10"/>
-      <c r="T77" s="10"/>
-      <c r="U77" s="10"/>
+        <v>252</v>
+      </c>
+      <c r="Q77" s="9">
+        <v>46294</v>
+      </c>
+      <c r="R77" s="9">
+        <v>46294</v>
+      </c>
+      <c r="S77" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T77" s="10">
+        <v>0</v>
+      </c>
+      <c r="U77" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B78" s="5">
-        <v>46169.66951364583</v>
+        <v>46169.66953854167</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46196.87995984954</v>
+        <v>46197.84256122685</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>257</v>
+        <v>186</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="I78" s="5">
-        <v>46273</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="I78" s="6"/>
       <c r="J78" s="5">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="K78" s="6" t="s">
         <v>26</v>
@@ -6251,13 +6230,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6267,33 +6246,27 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B79" s="9">
-        <v>46169.66953380787</v>
+        <v>46169.66960108797</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46197.84261425926</v>
+        <v>46209.85402508102</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>275</v>
+        <v>231</v>
       </c>
       <c r="F79" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="I79" s="9">
-        <v>46294</v>
-      </c>
-      <c r="J79" s="9">
-        <v>46294</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H79" s="10"/>
+      <c r="I79" s="10"/>
+      <c r="J79" s="10"/>
       <c r="K79" s="10" t="s">
         <v>26</v>
       </c>
@@ -6301,59 +6274,55 @@
         <v>26</v>
       </c>
       <c r="M79" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>253</v>
+        <v>26</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>204</v>
+        <v>272</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q79" s="9">
-        <v>46294</v>
-      </c>
-      <c r="R79" s="9">
-        <v>46294</v>
-      </c>
-      <c r="S79" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T79" s="10">
-        <v>0</v>
-      </c>
-      <c r="U79" s="11" t="s">
-        <v>60</v>
+        <v>26</v>
+      </c>
+      <c r="Q79" s="10"/>
+      <c r="R79" s="10"/>
+      <c r="S79" s="10"/>
+      <c r="T79" s="10"/>
+      <c r="U79" s="12" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B80" s="5">
-        <v>46169.66953854167</v>
-      </c>
-      <c r="C80" s="6"/>
+        <v>46169.66960956018</v>
+      </c>
+      <c r="C80" s="5">
+        <v>46209.84488153935</v>
+      </c>
       <c r="D80" s="5">
-        <v>46197.84256122685</v>
+        <v>46209.844928101855</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>206</v>
+        <v>274</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>186</v>
+        <v>235</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="I80" s="6"/>
+        <v>236</v>
+      </c>
+      <c r="I80" s="5">
+        <v>46174</v>
+      </c>
       <c r="J80" s="5">
-        <v>46294</v>
+        <v>46174</v>
       </c>
       <c r="K80" s="6" t="s">
         <v>26</v>
@@ -6365,46 +6334,60 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>275</v>
+        <v>231</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>269</v>
+        <v>133</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="Q80" s="6"/>
-      <c r="R80" s="6"/>
-      <c r="S80" s="6"/>
-      <c r="T80" s="6"/>
-      <c r="U80" s="6"/>
+        <v>241</v>
+      </c>
+      <c r="Q80" s="5">
+        <v>46174</v>
+      </c>
+      <c r="R80" s="5">
+        <v>46174</v>
+      </c>
+      <c r="S80" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T80" s="6">
+        <v>1</v>
+      </c>
+      <c r="U80" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B81" s="9">
-        <v>46169.669544212964</v>
-      </c>
-      <c r="C81" s="10"/>
+        <v>46169.6696165162</v>
+      </c>
+      <c r="C81" s="9">
+        <v>46209.844589050925</v>
+      </c>
       <c r="D81" s="9">
-        <v>46197.84251650463</v>
+        <v>46209.84471936343</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>211</v>
+        <v>276</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>186</v>
+        <v>235</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="I81" s="10"/>
+        <v>236</v>
+      </c>
+      <c r="I81" s="9">
+        <v>46288</v>
+      </c>
       <c r="J81" s="9">
-        <v>46294</v>
+        <v>46288</v>
       </c>
       <c r="K81" s="10" t="s">
         <v>26</v>
@@ -6416,84 +6399,108 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>275</v>
+        <v>231</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>279</v>
+        <v>123</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>280</v>
-      </c>
-      <c r="Q81" s="10"/>
-      <c r="R81" s="10"/>
-      <c r="S81" s="10"/>
-      <c r="T81" s="10"/>
-      <c r="U81" s="10"/>
+        <v>277</v>
+      </c>
+      <c r="Q81" s="9">
+        <v>46288</v>
+      </c>
+      <c r="R81" s="9">
+        <v>46288</v>
+      </c>
+      <c r="S81" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T81" s="10">
+        <v>1</v>
+      </c>
+      <c r="U81" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B82" s="5">
-        <v>46169.66960108797</v>
-      </c>
-      <c r="C82" s="6"/>
+        <v>46169.669622939815</v>
+      </c>
+      <c r="C82" s="5">
+        <v>46209.85400761574</v>
+      </c>
       <c r="D82" s="5">
-        <v>46209.85402508102</v>
+        <v>46209.85430440972</v>
       </c>
       <c r="E82" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="F82" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G82" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="I82" s="5">
+        <v>46308</v>
+      </c>
+      <c r="J82" s="5">
+        <v>46308</v>
+      </c>
+      <c r="K82" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L82" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M82" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N82" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="F82" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G82" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H82" s="6"/>
-      <c r="I82" s="6"/>
-      <c r="J82" s="6"/>
-      <c r="K82" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L82" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M82" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="N82" s="6" t="s">
-        <v>26</v>
-      </c>
       <c r="O82" s="6" t="s">
-        <v>282</v>
+        <v>142</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q82" s="6"/>
-      <c r="R82" s="6"/>
-      <c r="S82" s="6"/>
-      <c r="T82" s="6"/>
-      <c r="U82" s="12" t="s">
-        <v>66</v>
+        <v>277</v>
+      </c>
+      <c r="Q82" s="5">
+        <v>46308</v>
+      </c>
+      <c r="R82" s="5">
+        <v>46308</v>
+      </c>
+      <c r="S82" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T82" s="6">
+        <v>1</v>
+      </c>
+      <c r="U82" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B83" s="9">
-        <v>46169.66960956018</v>
-      </c>
-      <c r="C83" s="9">
-        <v>46209.84488153935</v>
-      </c>
+        <v>46169.66962980324</v>
+      </c>
+      <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46209.844928101855</v>
+        <v>46204.86356525463</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6505,10 +6512,10 @@
         <v>236</v>
       </c>
       <c r="I83" s="9">
-        <v>46174</v>
+        <v>46287</v>
       </c>
       <c r="J83" s="9">
-        <v>46174</v>
+        <v>46287</v>
       </c>
       <c r="K83" s="10" t="s">
         <v>26</v>
@@ -6523,42 +6530,40 @@
         <v>231</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>133</v>
+        <v>182</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="Q83" s="9">
-        <v>46174</v>
+        <v>46287</v>
       </c>
       <c r="R83" s="9">
-        <v>46174</v>
-      </c>
-      <c r="S83" s="11" t="s">
-        <v>128</v>
+        <v>46287</v>
+      </c>
+      <c r="S83" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="T83" s="10">
-        <v>1</v>
-      </c>
-      <c r="U83" s="7" t="s">
-        <v>27</v>
+        <v>0</v>
+      </c>
+      <c r="U83" s="12" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B84" s="5">
-        <v>46169.6696165162</v>
-      </c>
-      <c r="C84" s="5">
-        <v>46209.844589050925</v>
-      </c>
+        <v>46169.669635185186</v>
+      </c>
+      <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46209.84471936343</v>
+        <v>46174.84778872685</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>287</v>
+        <v>58</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6570,10 +6575,10 @@
         <v>236</v>
       </c>
       <c r="I84" s="5">
-        <v>46288</v>
+        <v>46220</v>
       </c>
       <c r="J84" s="5">
-        <v>46288</v>
+        <v>46220</v>
       </c>
       <c r="K84" s="6" t="s">
         <v>26</v>
@@ -6588,58 +6593,50 @@
         <v>231</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="Q84" s="5">
-        <v>46288</v>
+        <v>46220</v>
       </c>
       <c r="R84" s="5">
-        <v>46288</v>
+        <v>46220</v>
       </c>
       <c r="S84" s="7" t="s">
         <v>33</v>
       </c>
       <c r="T84" s="6">
-        <v>1</v>
-      </c>
-      <c r="U84" s="7" t="s">
-        <v>27</v>
+        <v>0</v>
+      </c>
+      <c r="U84" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B85" s="9">
-        <v>46169.669622939815</v>
-      </c>
-      <c r="C85" s="9">
-        <v>46209.85400761574</v>
-      </c>
+        <v>46169.66964790509</v>
+      </c>
+      <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46209.85430440972</v>
+        <v>46209.84945282407</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="F85" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="I85" s="9">
-        <v>46308</v>
-      </c>
-      <c r="J85" s="9">
-        <v>46308</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H85" s="10"/>
+      <c r="I85" s="10"/>
+      <c r="J85" s="10"/>
       <c r="K85" s="10" t="s">
         <v>26</v>
       </c>
@@ -6647,61 +6644,51 @@
         <v>26</v>
       </c>
       <c r="M85" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>231</v>
+        <v>26</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>142</v>
+        <v>287</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>288</v>
-      </c>
-      <c r="Q85" s="9">
-        <v>46308</v>
-      </c>
-      <c r="R85" s="9">
-        <v>46308</v>
-      </c>
-      <c r="S85" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T85" s="10">
-        <v>1</v>
-      </c>
-      <c r="U85" s="7" t="s">
-        <v>27</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q85" s="10"/>
+      <c r="R85" s="10"/>
+      <c r="S85" s="10"/>
+      <c r="T85" s="10"/>
+      <c r="U85" s="10"/>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B86" s="5">
-        <v>46169.66962980324</v>
+        <v>46169.66965109954</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46204.86356525463</v>
+        <v>46174.84790094907</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>235</v>
+        <v>91</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>236</v>
+        <v>91</v>
       </c>
       <c r="I86" s="5">
-        <v>46287</v>
+        <v>46294</v>
       </c>
       <c r="J86" s="5">
-        <v>46287</v>
+        <v>46315</v>
       </c>
       <c r="K86" s="6" t="s">
         <v>26</v>
@@ -6713,19 +6700,19 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>231</v>
+        <v>286</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>182</v>
+        <v>290</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="Q86" s="5">
-        <v>46287</v>
+        <v>46294</v>
       </c>
       <c r="R86" s="5">
-        <v>46287</v>
+        <v>46315</v>
       </c>
       <c r="S86" s="7" t="s">
         <v>33</v>
@@ -6733,38 +6720,38 @@
       <c r="T86" s="6">
         <v>0</v>
       </c>
-      <c r="U86" s="12" t="s">
-        <v>66</v>
+      <c r="U86" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B87" s="9">
-        <v>46169.669635185186</v>
+        <v>46169.6696568287</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46174.84778872685</v>
+        <v>46174.84798839121</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>58</v>
+        <v>206</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>235</v>
+        <v>91</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>236</v>
+        <v>91</v>
       </c>
       <c r="I87" s="9">
-        <v>46220</v>
+        <v>46294</v>
       </c>
       <c r="J87" s="9">
-        <v>46220</v>
+        <v>46315</v>
       </c>
       <c r="K87" s="10" t="s">
         <v>26</v>
@@ -6776,53 +6763,51 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>231</v>
+        <v>289</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>153</v>
+        <v>292</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>295</v>
-      </c>
-      <c r="Q87" s="9">
-        <v>46220</v>
-      </c>
-      <c r="R87" s="9">
-        <v>46220</v>
-      </c>
-      <c r="S87" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T87" s="10">
-        <v>0</v>
-      </c>
-      <c r="U87" s="11" t="s">
-        <v>60</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="Q87" s="10"/>
+      <c r="R87" s="10"/>
+      <c r="S87" s="10"/>
+      <c r="T87" s="10"/>
+      <c r="U87" s="10"/>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B88" s="5">
-        <v>46169.66964790509</v>
-      </c>
-      <c r="C88" s="6"/>
+        <v>46169.669688622685</v>
+      </c>
+      <c r="C88" s="5">
+        <v>46209.84929427083</v>
+      </c>
       <c r="D88" s="5">
-        <v>46209.84945282407</v>
+        <v>46209.8493094213</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H88" s="6"/>
-      <c r="I88" s="6"/>
-      <c r="J88" s="6"/>
+        <v>91</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="I88" s="5">
+        <v>46316</v>
+      </c>
+      <c r="J88" s="5">
+        <v>46316</v>
+      </c>
       <c r="K88" s="6" t="s">
         <v>26</v>
       </c>
@@ -6830,36 +6815,46 @@
         <v>26</v>
       </c>
       <c r="M88" s="6" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>26</v>
+        <v>286</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>298</v>
+        <v>206</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q88" s="6"/>
-      <c r="R88" s="6"/>
-      <c r="S88" s="6"/>
-      <c r="T88" s="6"/>
-      <c r="U88" s="6"/>
+        <v>286</v>
+      </c>
+      <c r="Q88" s="5">
+        <v>46316</v>
+      </c>
+      <c r="R88" s="5">
+        <v>46316</v>
+      </c>
+      <c r="S88" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T88" s="6">
+        <v>1</v>
+      </c>
+      <c r="U88" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B89" s="9">
-        <v>46169.66965109954</v>
+        <v>46169.66969347223</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46174.84790094907</v>
+        <v>46209.84459753473</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>300</v>
+        <v>206</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6870,11 +6865,9 @@
       <c r="H89" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="I89" s="9">
-        <v>46294</v>
-      </c>
+      <c r="I89" s="10"/>
       <c r="J89" s="9">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="K89" s="10" t="s">
         <v>26</v>
@@ -6886,43 +6879,35 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="P89" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="Q89" s="9">
-        <v>46294</v>
-      </c>
-      <c r="R89" s="9">
-        <v>46315</v>
-      </c>
-      <c r="S89" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T89" s="10">
-        <v>0</v>
-      </c>
-      <c r="U89" s="11" t="s">
-        <v>60</v>
-      </c>
+      <c r="Q89" s="10"/>
+      <c r="R89" s="10"/>
+      <c r="S89" s="10"/>
+      <c r="T89" s="10"/>
+      <c r="U89" s="10"/>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B90" s="5">
-        <v>46169.6696568287</v>
-      </c>
-      <c r="C90" s="6"/>
+        <v>46169.66972681713</v>
+      </c>
+      <c r="C90" s="5">
+        <v>46209.84944726852</v>
+      </c>
       <c r="D90" s="5">
-        <v>46174.84798839121</v>
+        <v>46209.84946481482</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>206</v>
+        <v>299</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6934,10 +6919,10 @@
         <v>91</v>
       </c>
       <c r="I90" s="5">
-        <v>46294</v>
+        <v>46317</v>
       </c>
       <c r="J90" s="5">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="K90" s="6" t="s">
         <v>26</v>
@@ -6949,35 +6934,43 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>303</v>
+        <v>206</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q90" s="6"/>
-      <c r="R90" s="6"/>
-      <c r="S90" s="6"/>
-      <c r="T90" s="6"/>
-      <c r="U90" s="6"/>
+        <v>286</v>
+      </c>
+      <c r="Q90" s="5">
+        <v>46317</v>
+      </c>
+      <c r="R90" s="5">
+        <v>46317</v>
+      </c>
+      <c r="S90" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T90" s="6">
+        <v>1</v>
+      </c>
+      <c r="U90" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B91" s="9">
-        <v>46169.669688622685</v>
-      </c>
-      <c r="C91" s="9">
-        <v>46209.84929427083</v>
-      </c>
+        <v>46169.66973180555</v>
+      </c>
+      <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46209.8493094213</v>
+        <v>46209.844891030094</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>305</v>
+        <v>206</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6989,10 +6982,10 @@
         <v>91</v>
       </c>
       <c r="I91" s="9">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="J91" s="9">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="K91" s="10" t="s">
         <v>26</v>
@@ -7004,43 +6997,33 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>206</v>
+        <v>301</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q91" s="9">
-        <v>46316</v>
-      </c>
-      <c r="R91" s="9">
-        <v>46316</v>
-      </c>
-      <c r="S91" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T91" s="10">
-        <v>1</v>
-      </c>
-      <c r="U91" s="7" t="s">
-        <v>27</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="Q91" s="10"/>
+      <c r="R91" s="10"/>
+      <c r="S91" s="10"/>
+      <c r="T91" s="10"/>
+      <c r="U91" s="10"/>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B92" s="5">
-        <v>46169.66969347223</v>
+        <v>46169.66981054399</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46209.84459753473</v>
+        <v>46174.8478909375</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>206</v>
+        <v>304</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7051,9 +7034,11 @@
       <c r="H92" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="I92" s="6"/>
+      <c r="I92" s="5">
+        <v>46318</v>
+      </c>
       <c r="J92" s="5">
-        <v>46316</v>
+        <v>46318</v>
       </c>
       <c r="K92" s="6" t="s">
         <v>26</v>
@@ -7065,35 +7050,43 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>307</v>
+        <v>206</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="Q92" s="6"/>
-      <c r="R92" s="6"/>
-      <c r="S92" s="6"/>
-      <c r="T92" s="6"/>
-      <c r="U92" s="6"/>
+        <v>286</v>
+      </c>
+      <c r="Q92" s="5">
+        <v>46318</v>
+      </c>
+      <c r="R92" s="5">
+        <v>46318</v>
+      </c>
+      <c r="S92" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T92" s="6">
+        <v>0</v>
+      </c>
+      <c r="U92" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B93" s="9">
-        <v>46169.66972681713</v>
-      </c>
-      <c r="C93" s="9">
-        <v>46209.84944726852</v>
-      </c>
+        <v>46169.66981724537</v>
+      </c>
+      <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46209.84946481482</v>
+        <v>46209.85401892361</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>310</v>
+        <v>206</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7105,10 +7098,10 @@
         <v>91</v>
       </c>
       <c r="I93" s="9">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="J93" s="9">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="K93" s="10" t="s">
         <v>26</v>
@@ -7120,43 +7113,33 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>206</v>
+        <v>306</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q93" s="9">
-        <v>46317</v>
-      </c>
-      <c r="R93" s="9">
-        <v>46317</v>
-      </c>
-      <c r="S93" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T93" s="10">
-        <v>1</v>
-      </c>
-      <c r="U93" s="7" t="s">
-        <v>27</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="Q93" s="10"/>
+      <c r="R93" s="10"/>
+      <c r="S93" s="10"/>
+      <c r="T93" s="10"/>
+      <c r="U93" s="10"/>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B94" s="5">
-        <v>46169.66973180555</v>
+        <v>46169.669861041664</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46209.844891030094</v>
+        <v>46174.8478862037</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>206</v>
+        <v>309</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7168,10 +7151,10 @@
         <v>91</v>
       </c>
       <c r="I94" s="5">
-        <v>46317</v>
+        <v>46321</v>
       </c>
       <c r="J94" s="5">
-        <v>46317</v>
+        <v>46321</v>
       </c>
       <c r="K94" s="6" t="s">
         <v>26</v>
@@ -7183,33 +7166,43 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>312</v>
+        <v>206</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="Q94" s="6"/>
-      <c r="R94" s="6"/>
-      <c r="S94" s="6"/>
-      <c r="T94" s="6"/>
-      <c r="U94" s="6"/>
+        <v>286</v>
+      </c>
+      <c r="Q94" s="5">
+        <v>46321</v>
+      </c>
+      <c r="R94" s="5">
+        <v>46321</v>
+      </c>
+      <c r="S94" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T94" s="6">
+        <v>0</v>
+      </c>
+      <c r="U94" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B95" s="9">
-        <v>46169.66981054399</v>
+        <v>46169.66986724537</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46174.8478909375</v>
+        <v>46174.84816675926</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>315</v>
+        <v>206</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7221,10 +7214,10 @@
         <v>91</v>
       </c>
       <c r="I95" s="9">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="J95" s="9">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="K95" s="10" t="s">
         <v>26</v>
@@ -7236,43 +7229,33 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="O95" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q95" s="9">
-        <v>46318</v>
-      </c>
-      <c r="R95" s="9">
-        <v>46318</v>
-      </c>
-      <c r="S95" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T95" s="10">
-        <v>0</v>
-      </c>
-      <c r="U95" s="11" t="s">
-        <v>60</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="Q95" s="10"/>
+      <c r="R95" s="10"/>
+      <c r="S95" s="10"/>
+      <c r="T95" s="10"/>
+      <c r="U95" s="10"/>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B96" s="5">
-        <v>46169.66981724537</v>
+        <v>46169.66990296297</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46209.85401892361</v>
+        <v>46174.84788545139</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>206</v>
+        <v>313</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7284,10 +7267,10 @@
         <v>91</v>
       </c>
       <c r="I96" s="5">
-        <v>46318</v>
+        <v>46323</v>
       </c>
       <c r="J96" s="5">
-        <v>46318</v>
+        <v>46323</v>
       </c>
       <c r="K96" s="6" t="s">
         <v>26</v>
@@ -7299,33 +7282,43 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>315</v>
+        <v>286</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>317</v>
+        <v>206</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="Q96" s="6"/>
-      <c r="R96" s="6"/>
-      <c r="S96" s="6"/>
-      <c r="T96" s="6"/>
-      <c r="U96" s="6"/>
+        <v>314</v>
+      </c>
+      <c r="Q96" s="5">
+        <v>46323</v>
+      </c>
+      <c r="R96" s="5">
+        <v>46323</v>
+      </c>
+      <c r="S96" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T96" s="6">
+        <v>0</v>
+      </c>
+      <c r="U96" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B97" s="9">
-        <v>46169.669861041664</v>
+        <v>46169.66994555556</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46174.8478862037</v>
+        <v>46174.848269317125</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>320</v>
+        <v>206</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7336,11 +7329,9 @@
       <c r="H97" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="I97" s="9">
-        <v>46321</v>
-      </c>
+      <c r="I97" s="10"/>
       <c r="J97" s="9">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="K97" s="10" t="s">
         <v>26</v>
@@ -7352,59 +7343,43 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="O97" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q97" s="9">
-        <v>46321</v>
-      </c>
-      <c r="R97" s="9">
-        <v>46321</v>
-      </c>
-      <c r="S97" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T97" s="10">
-        <v>0</v>
-      </c>
-      <c r="U97" s="11" t="s">
-        <v>60</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="Q97" s="10"/>
+      <c r="R97" s="10"/>
+      <c r="S97" s="10"/>
+      <c r="T97" s="10"/>
+      <c r="U97" s="10"/>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="B98" s="5">
-        <v>46169.66986724537</v>
+        <v>46169.669978645834</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46174.84816675926</v>
+        <v>46174.82401747685</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>206</v>
+        <v>318</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="I98" s="5">
-        <v>46321</v>
-      </c>
-      <c r="J98" s="5">
-        <v>46321</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H98" s="6"/>
+      <c r="I98" s="6"/>
+      <c r="J98" s="6"/>
       <c r="K98" s="6" t="s">
         <v>26</v>
       </c>
@@ -7412,16 +7387,16 @@
         <v>26</v>
       </c>
       <c r="M98" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>320</v>
+        <v>26</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>206</v>
+        <v>319</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>322</v>
+        <v>26</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7431,56 +7406,56 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B99" s="9">
-        <v>46169.66990296297</v>
+        <v>46169.66998244213</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46174.84788545139</v>
+        <v>46174.84843513889</v>
       </c>
       <c r="E99" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="F99" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G99" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="H99" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="I99" s="9">
+        <v>46324</v>
+      </c>
+      <c r="J99" s="9">
+        <v>46324</v>
+      </c>
+      <c r="K99" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L99" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M99" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N99" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="O99" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="F99" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G99" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="I99" s="9">
-        <v>46323</v>
-      </c>
-      <c r="J99" s="9">
-        <v>46323</v>
-      </c>
-      <c r="K99" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L99" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M99" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N99" s="10" t="s">
-        <v>297</v>
-      </c>
-      <c r="O99" s="10" t="s">
-        <v>206</v>
-      </c>
       <c r="P99" s="10" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="Q99" s="9">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="R99" s="9">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="S99" s="7" t="s">
         <v>33</v>
@@ -7494,14 +7469,14 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B100" s="5">
-        <v>46169.66994555556</v>
+        <v>46169.66998994213</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46174.848269317125</v>
+        <v>46174.84838837963</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>206</v>
@@ -7510,14 +7485,14 @@
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>91</v>
+        <v>322</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>91</v>
+        <v>323</v>
       </c>
       <c r="I100" s="6"/>
       <c r="J100" s="5">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="K100" s="6" t="s">
         <v>26</v>
@@ -7529,13 +7504,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7545,27 +7520,31 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B101" s="9">
-        <v>46169.669978645834</v>
+        <v>46170.63118891204</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46174.82401747685</v>
+        <v>46209.90833168982</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>329</v>
+        <v>211</v>
       </c>
       <c r="F101" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H101" s="10"/>
+        <v>322</v>
+      </c>
+      <c r="H101" s="10" t="s">
+        <v>323</v>
+      </c>
       <c r="I101" s="10"/>
-      <c r="J101" s="10"/>
+      <c r="J101" s="9">
+        <v>46324</v>
+      </c>
       <c r="K101" s="10" t="s">
         <v>26</v>
       </c>
@@ -7573,16 +7552,16 @@
         <v>26</v>
       </c>
       <c r="M101" s="10" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>26</v>
+        <v>321</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>330</v>
+        <v>26</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>26</v>
+        <v>211</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7592,26 +7571,26 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B102" s="5">
-        <v>46169.66998244213</v>
+        <v>46174.820955891206</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46174.84843513889</v>
+        <v>46174.848381284726</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>332</v>
+        <v>62</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="I102" s="5">
         <v>46324</v>
@@ -7629,56 +7608,46 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>335</v>
+        <v>62</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="Q102" s="5">
-        <v>46324</v>
-      </c>
-      <c r="R102" s="5">
-        <v>46324</v>
-      </c>
-      <c r="S102" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T102" s="6">
-        <v>0</v>
-      </c>
-      <c r="U102" s="11" t="s">
-        <v>60</v>
-      </c>
+      <c r="Q102" s="6"/>
+      <c r="R102" s="6"/>
+      <c r="S102" s="6"/>
+      <c r="T102" s="6"/>
+      <c r="U102" s="6"/>
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="B103" s="9">
-        <v>46169.66998994213</v>
+        <v>46169.670044224535</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46174.84838837963</v>
+        <v>46174.848558831014</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>206</v>
+        <v>331</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>333</v>
+        <v>91</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>334</v>
+        <v>91</v>
       </c>
       <c r="I103" s="10"/>
       <c r="J103" s="9">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="K103" s="10" t="s">
         <v>26</v>
@@ -7690,46 +7659,56 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="O103" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>337</v>
-      </c>
-      <c r="Q103" s="10"/>
-      <c r="R103" s="10"/>
-      <c r="S103" s="10"/>
-      <c r="T103" s="10"/>
-      <c r="U103" s="10"/>
+        <v>318</v>
+      </c>
+      <c r="Q103" s="9">
+        <v>46325</v>
+      </c>
+      <c r="R103" s="9">
+        <v>46325</v>
+      </c>
+      <c r="S103" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T103" s="10">
+        <v>0</v>
+      </c>
+      <c r="U103" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="B104" s="5">
-        <v>46170.63118891204</v>
+        <v>46169.670049050925</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46174.848385474535</v>
+        <v>46174.848527152775</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>333</v>
+        <v>91</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>334</v>
+        <v>91</v>
       </c>
       <c r="I104" s="6"/>
       <c r="J104" s="5">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="K104" s="6" t="s">
         <v>26</v>
@@ -7741,13 +7720,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>211</v>
+        <v>333</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7757,32 +7736,30 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="B105" s="9">
-        <v>46174.820955891206</v>
+        <v>46170.63213679398</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46174.848381284726</v>
+        <v>46174.848524270834</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>62</v>
+        <v>211</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>333</v>
+        <v>91</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>334</v>
-      </c>
-      <c r="I105" s="9">
-        <v>46324</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="I105" s="10"/>
       <c r="J105" s="9">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="K105" s="10" t="s">
         <v>26</v>
@@ -7794,13 +7771,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>62</v>
+        <v>211</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>340</v>
+        <v>211</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7810,17 +7787,17 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="B106" s="5">
-        <v>46169.670044224535</v>
+        <v>46174.82099290509</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46174.848558831014</v>
+        <v>46174.84852028935</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7831,7 +7808,9 @@
       <c r="H106" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="I106" s="6"/>
+      <c r="I106" s="5">
+        <v>46325</v>
+      </c>
       <c r="J106" s="5">
         <v>46325</v>
       </c>
@@ -7845,56 +7824,46 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>206</v>
+        <v>62</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="Q106" s="5">
-        <v>46325</v>
-      </c>
-      <c r="R106" s="5">
-        <v>46325</v>
-      </c>
-      <c r="S106" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T106" s="6">
-        <v>0</v>
-      </c>
-      <c r="U106" s="11" t="s">
-        <v>60</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="Q106" s="6"/>
+      <c r="R106" s="6"/>
+      <c r="S106" s="6"/>
+      <c r="T106" s="6"/>
+      <c r="U106" s="6"/>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="B107" s="9">
-        <v>46169.670049050925</v>
+        <v>46169.67013976852</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46174.848527152775</v>
+        <v>46174.84870307871</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>206</v>
+        <v>337</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>91</v>
+        <v>256</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>91</v>
+        <v>257</v>
       </c>
       <c r="I107" s="10"/>
       <c r="J107" s="9">
-        <v>46325</v>
+        <v>46328</v>
       </c>
       <c r="K107" s="10" t="s">
         <v>26</v>
@@ -7906,46 +7875,58 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>342</v>
+        <v>318</v>
       </c>
       <c r="O107" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>344</v>
-      </c>
-      <c r="Q107" s="10"/>
-      <c r="R107" s="10"/>
-      <c r="S107" s="10"/>
-      <c r="T107" s="10"/>
-      <c r="U107" s="10"/>
+        <v>318</v>
+      </c>
+      <c r="Q107" s="9">
+        <v>46328</v>
+      </c>
+      <c r="R107" s="9">
+        <v>46328</v>
+      </c>
+      <c r="S107" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T107" s="10">
+        <v>0</v>
+      </c>
+      <c r="U107" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="B108" s="5">
-        <v>46170.63213679398</v>
+        <v>46169.670151377315</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46174.848524270834</v>
+        <v>46174.848669872685</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>91</v>
+        <v>256</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="I108" s="6"/>
+        <v>257</v>
+      </c>
+      <c r="I108" s="5">
+        <v>46328</v>
+      </c>
       <c r="J108" s="5">
-        <v>46325</v>
+        <v>46328</v>
       </c>
       <c r="K108" s="6" t="s">
         <v>26</v>
@@ -7957,13 +7938,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>211</v>
+        <v>339</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7973,32 +7954,32 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="B109" s="9">
-        <v>46174.82099290509</v>
+        <v>46170.63285997685</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46174.84852028935</v>
+        <v>46174.848667314815</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>340</v>
+        <v>211</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>91</v>
+        <v>256</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>91</v>
+        <v>257</v>
       </c>
       <c r="I109" s="9">
-        <v>46325</v>
+        <v>46328</v>
       </c>
       <c r="J109" s="9">
-        <v>46325</v>
+        <v>46328</v>
       </c>
       <c r="K109" s="10" t="s">
         <v>26</v>
@@ -8010,13 +7991,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>62</v>
+        <v>211</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>62</v>
+        <v>211</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -8026,28 +8007,30 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="B110" s="5">
-        <v>46169.67013976852</v>
+        <v>46174.821024143515</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46174.84870307871</v>
+        <v>46174.84866336806</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>348</v>
+        <v>62</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="H110" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="H110" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="I110" s="6"/>
+      <c r="I110" s="5">
+        <v>46328</v>
+      </c>
       <c r="J110" s="5">
         <v>46328</v>
       </c>
@@ -8061,58 +8044,48 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="O110" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="O110" s="6" t="s">
-        <v>206</v>
-      </c>
       <c r="P110" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="Q110" s="5">
-        <v>46328</v>
-      </c>
-      <c r="R110" s="5">
-        <v>46328</v>
-      </c>
-      <c r="S110" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T110" s="6">
-        <v>0</v>
-      </c>
-      <c r="U110" s="11" t="s">
-        <v>60</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="Q110" s="6"/>
+      <c r="R110" s="6"/>
+      <c r="S110" s="6"/>
+      <c r="T110" s="6"/>
+      <c r="U110" s="6"/>
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="B111" s="9">
-        <v>46169.670151377315</v>
+        <v>46169.67021965278</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46174.848669872685</v>
+        <v>46174.84880980324</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>206</v>
+        <v>343</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="H111" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="H111" s="10" t="s">
-        <v>258</v>
-      </c>
       <c r="I111" s="9">
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="J111" s="9">
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="K111" s="10" t="s">
         <v>26</v>
@@ -8124,48 +8097,56 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>348</v>
+        <v>318</v>
       </c>
       <c r="O111" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>350</v>
-      </c>
-      <c r="Q111" s="10"/>
-      <c r="R111" s="10"/>
-      <c r="S111" s="10"/>
-      <c r="T111" s="10"/>
-      <c r="U111" s="10"/>
+        <v>344</v>
+      </c>
+      <c r="Q111" s="9">
+        <v>46329</v>
+      </c>
+      <c r="R111" s="9">
+        <v>46329</v>
+      </c>
+      <c r="S111" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T111" s="10">
+        <v>0</v>
+      </c>
+      <c r="U111" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="B112" s="5">
-        <v>46170.63285997685</v>
+        <v>46169.67022677083</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46174.848667314815</v>
+        <v>46174.84878571759</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="H112" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="H112" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="I112" s="5">
-        <v>46328</v>
-      </c>
+      <c r="I112" s="6"/>
       <c r="J112" s="5">
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="K112" s="6" t="s">
         <v>26</v>
@@ -8177,13 +8158,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>211</v>
+        <v>343</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8193,32 +8174,30 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="B113" s="9">
-        <v>46174.821024143515</v>
+        <v>46170.633581828704</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46174.84866336806</v>
+        <v>46174.84878314815</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>62</v>
+        <v>211</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="H113" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="H113" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="I113" s="9">
-        <v>46328</v>
-      </c>
+      <c r="I113" s="10"/>
       <c r="J113" s="9">
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="K113" s="10" t="s">
         <v>26</v>
@@ -8230,13 +8209,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>340</v>
+        <v>211</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -8246,30 +8225,28 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="B114" s="5">
-        <v>46169.67021965278</v>
+        <v>46174.821057037036</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46174.84880980324</v>
+        <v>46174.84877914352</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>354</v>
+        <v>62</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="H114" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="H114" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="I114" s="5">
-        <v>46329</v>
-      </c>
+      <c r="I114" s="6"/>
       <c r="J114" s="5">
         <v>46329</v>
       </c>
@@ -8283,57 +8260,43 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>206</v>
+        <v>62</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="Q114" s="5">
-        <v>46329</v>
-      </c>
-      <c r="R114" s="5">
-        <v>46329</v>
-      </c>
-      <c r="S114" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T114" s="6">
-        <v>0</v>
-      </c>
-      <c r="U114" s="11" t="s">
-        <v>60</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q114" s="6"/>
+      <c r="R114" s="6"/>
+      <c r="S114" s="6"/>
+      <c r="T114" s="6"/>
+      <c r="U114" s="6"/>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="B115" s="9">
-        <v>46169.67022677083</v>
+        <v>46169.67031616898</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46174.84878571759</v>
+        <v>46174.82401751158</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>206</v>
+        <v>349</v>
       </c>
       <c r="F115" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="H115" s="10" t="s">
-        <v>258</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H115" s="10"/>
       <c r="I115" s="10"/>
-      <c r="J115" s="9">
-        <v>46329</v>
-      </c>
+      <c r="J115" s="10"/>
       <c r="K115" s="10" t="s">
         <v>26</v>
       </c>
@@ -8341,16 +8304,16 @@
         <v>26</v>
       </c>
       <c r="M115" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>354</v>
+        <v>26</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>206</v>
+        <v>350</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>354</v>
+        <v>26</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8360,30 +8323,32 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="B116" s="5">
-        <v>46170.633581828704</v>
+        <v>46169.67031976852</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46174.84878314815</v>
+        <v>46174.84885483797</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>211</v>
+        <v>352</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>257</v>
+        <v>353</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="I116" s="6"/>
+        <v>354</v>
+      </c>
+      <c r="I116" s="5">
+        <v>46330</v>
+      </c>
       <c r="J116" s="5">
-        <v>46329</v>
+        <v>46338</v>
       </c>
       <c r="K116" s="6" t="s">
         <v>26</v>
@@ -8395,46 +8360,58 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>211</v>
+        <v>343</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q116" s="6"/>
-      <c r="R116" s="6"/>
-      <c r="S116" s="6"/>
-      <c r="T116" s="6"/>
-      <c r="U116" s="6"/>
+        <v>349</v>
+      </c>
+      <c r="Q116" s="5">
+        <v>46330</v>
+      </c>
+      <c r="R116" s="5">
+        <v>46338</v>
+      </c>
+      <c r="S116" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T116" s="6">
+        <v>0</v>
+      </c>
+      <c r="U116" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B117" s="9">
-        <v>46174.821057037036</v>
+        <v>46169.6703253125</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46174.84877914352</v>
+        <v>46192.97339644676</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>62</v>
+        <v>356</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>257</v>
+        <v>69</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="I117" s="10"/>
+        <v>70</v>
+      </c>
+      <c r="I117" s="9">
+        <v>46330</v>
+      </c>
       <c r="J117" s="9">
-        <v>46329</v>
+        <v>46338</v>
       </c>
       <c r="K117" s="10" t="s">
         <v>26</v>
@@ -8446,33 +8423,43 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>62</v>
+        <v>343</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q117" s="10"/>
-      <c r="R117" s="10"/>
-      <c r="S117" s="10"/>
-      <c r="T117" s="10"/>
-      <c r="U117" s="10"/>
+        <v>349</v>
+      </c>
+      <c r="Q117" s="9">
+        <v>46330</v>
+      </c>
+      <c r="R117" s="9">
+        <v>46338</v>
+      </c>
+      <c r="S117" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T117" s="10">
+        <v>0</v>
+      </c>
+      <c r="U117" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B118" s="5">
-        <v>46169.67031616898</v>
+        <v>46169.670332430556</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46174.82401751158</v>
+        <v>46174.82401726852</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>25</v>
@@ -8496,39 +8483,45 @@
         <v>26</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
-      <c r="S118" s="6"/>
-      <c r="T118" s="6"/>
-      <c r="U118" s="6"/>
+      <c r="S118" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T118" s="6">
+        <v>0</v>
+      </c>
+      <c r="U118" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B119" s="9">
-        <v>46169.67031976852</v>
+        <v>46169.67033591435</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46174.84885483797</v>
+        <v>46174.848958703704</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>364</v>
+        <v>51</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>365</v>
+        <v>52</v>
       </c>
       <c r="I119" s="9">
         <v>46330</v>
@@ -8546,13 +8539,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q119" s="9">
         <v>46330</v>
@@ -8572,32 +8565,32 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B120" s="5">
-        <v>46169.6703253125</v>
+        <v>46169.67034748843</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46192.97339644676</v>
+        <v>46174.84895586806</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="I120" s="5">
-        <v>46330</v>
+        <v>46339</v>
       </c>
       <c r="J120" s="5">
-        <v>46338</v>
+        <v>46349</v>
       </c>
       <c r="K120" s="6" t="s">
         <v>26</v>
@@ -8609,19 +8602,19 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="Q120" s="5">
-        <v>46330</v>
+        <v>46339</v>
       </c>
       <c r="R120" s="5">
-        <v>46338</v>
+        <v>46349</v>
       </c>
       <c r="S120" s="7" t="s">
         <v>33</v>
@@ -8630,185 +8623,6 @@
         <v>0</v>
       </c>
       <c r="U120" s="11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="121" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A121" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="B121" s="9">
-        <v>46169.670332430556</v>
-      </c>
-      <c r="C121" s="10"/>
-      <c r="D121" s="9">
-        <v>46174.82401726852</v>
-      </c>
-      <c r="E121" s="10" t="s">
-        <v>369</v>
-      </c>
-      <c r="F121" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G121" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H121" s="10"/>
-      <c r="I121" s="10"/>
-      <c r="J121" s="10"/>
-      <c r="K121" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L121" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M121" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="N121" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O121" s="10" t="s">
-        <v>370</v>
-      </c>
-      <c r="P121" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q121" s="10"/>
-      <c r="R121" s="10"/>
-      <c r="S121" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T121" s="10">
-        <v>0</v>
-      </c>
-      <c r="U121" s="11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="122" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A122" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="B122" s="5">
-        <v>46169.67033591435</v>
-      </c>
-      <c r="C122" s="6"/>
-      <c r="D122" s="5">
-        <v>46174.848958703704</v>
-      </c>
-      <c r="E122" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="F122" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G122" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="H122" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="I122" s="5">
-        <v>46330</v>
-      </c>
-      <c r="J122" s="5">
-        <v>46338</v>
-      </c>
-      <c r="K122" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L122" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M122" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N122" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="O122" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="P122" s="6" t="s">
-        <v>373</v>
-      </c>
-      <c r="Q122" s="5">
-        <v>46330</v>
-      </c>
-      <c r="R122" s="5">
-        <v>46338</v>
-      </c>
-      <c r="S122" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T122" s="6">
-        <v>0</v>
-      </c>
-      <c r="U122" s="11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="123" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A123" s="8" t="s">
-        <v>374</v>
-      </c>
-      <c r="B123" s="9">
-        <v>46169.67034748843</v>
-      </c>
-      <c r="C123" s="10"/>
-      <c r="D123" s="9">
-        <v>46174.84895586806</v>
-      </c>
-      <c r="E123" s="10" t="s">
-        <v>375</v>
-      </c>
-      <c r="F123" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G123" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="H123" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="I123" s="9">
-        <v>46339</v>
-      </c>
-      <c r="J123" s="9">
-        <v>46349</v>
-      </c>
-      <c r="K123" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L123" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M123" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N123" s="10" t="s">
-        <v>369</v>
-      </c>
-      <c r="O123" s="10" t="s">
-        <v>372</v>
-      </c>
-      <c r="P123" s="10" t="s">
-        <v>369</v>
-      </c>
-      <c r="Q123" s="9">
-        <v>46339</v>
-      </c>
-      <c r="R123" s="9">
-        <v>46349</v>
-      </c>
-      <c r="S123" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T123" s="10">
-        <v>0</v>
-      </c>
-      <c r="U123" s="11" t="s">
         <v>60</v>
       </c>
     </row>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -4794,9 +4794,11 @@
       <c r="B54" s="5">
         <v>46169.669255659726</v>
       </c>
-      <c r="C54" s="6"/>
+      <c r="C54" s="5">
+        <v>46210.52485824074</v>
+      </c>
       <c r="D54" s="5">
-        <v>46195.950137974534</v>
+        <v>46210.52487434028</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>197</v>
@@ -4831,9 +4833,11 @@
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
       <c r="S54" s="6"/>
-      <c r="T54" s="6"/>
-      <c r="U54" s="12" t="s">
-        <v>66</v>
+      <c r="T54" s="6">
+        <v>1</v>
+      </c>
+      <c r="U54" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1439" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="365">
   <si>
     <t>50001558 -  GESVIAL</t>
   </si>
@@ -4566,9 +4566,11 @@
       <c r="B50" s="5">
         <v>46169.66920229167</v>
       </c>
-      <c r="C50" s="6"/>
+      <c r="C50" s="5">
+        <v>46210.65313320602</v>
+      </c>
       <c r="D50" s="5">
-        <v>46204.86355603009</v>
+        <v>46210.65313525463</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -5433,9 +5435,11 @@
       <c r="B65" s="9">
         <v>46169.669418136575</v>
       </c>
-      <c r="C65" s="10"/>
+      <c r="C65" s="9">
+        <v>46210.651971631945</v>
+      </c>
       <c r="D65" s="9">
-        <v>46170.59324665509</v>
+        <v>46210.65198340278</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>231</v>
@@ -5470,8 +5474,12 @@
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
       <c r="S65" s="10"/>
-      <c r="T65" s="10"/>
-      <c r="U65" s="10"/>
+      <c r="T65" s="10">
+        <v>1</v>
+      </c>
+      <c r="U65" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
@@ -5480,9 +5488,11 @@
       <c r="B66" s="5">
         <v>46169.66942685185</v>
       </c>
-      <c r="C66" s="6"/>
+      <c r="C66" s="5">
+        <v>46210.651376574075</v>
+      </c>
       <c r="D66" s="5">
-        <v>46205.61248846065</v>
+        <v>46210.651395196764</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>234</v>
@@ -5530,10 +5540,10 @@
         <v>33</v>
       </c>
       <c r="T66" s="6">
-        <v>0</v>
-      </c>
-      <c r="U66" s="12" t="s">
-        <v>66</v>
+        <v>1</v>
+      </c>
+      <c r="U66" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5543,9 +5553,11 @@
       <c r="B67" s="9">
         <v>46169.669432361115</v>
       </c>
-      <c r="C67" s="10"/>
+      <c r="C67" s="9">
+        <v>46210.65195509259</v>
+      </c>
       <c r="D67" s="9">
-        <v>46209.90823064814</v>
+        <v>46210.65197202546</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>239</v>
@@ -5593,10 +5605,10 @@
         <v>33</v>
       </c>
       <c r="T67" s="10">
-        <v>0</v>
-      </c>
-      <c r="U67" s="11" t="s">
-        <v>60</v>
+        <v>1</v>
+      </c>
+      <c r="U67" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5606,9 +5618,11 @@
       <c r="B68" s="5">
         <v>46169.66943836806</v>
       </c>
-      <c r="C68" s="6"/>
+      <c r="C68" s="5">
+        <v>46210.651382638884</v>
+      </c>
       <c r="D68" s="5">
-        <v>46199.56727501158</v>
+        <v>46210.65139929398</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>243</v>
@@ -5656,10 +5670,10 @@
         <v>33</v>
       </c>
       <c r="T68" s="6">
-        <v>0</v>
-      </c>
-      <c r="U68" s="12" t="s">
-        <v>66</v>
+        <v>1</v>
+      </c>
+      <c r="U68" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
@@ -5669,9 +5683,11 @@
       <c r="B69" s="9">
         <v>46169.669443692124</v>
       </c>
-      <c r="C69" s="10"/>
+      <c r="C69" s="9">
+        <v>46210.651959571755</v>
+      </c>
       <c r="D69" s="9">
-        <v>46209.90823061342</v>
+        <v>46210.651975879635</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>246</v>
@@ -5719,10 +5735,10 @@
         <v>33</v>
       </c>
       <c r="T69" s="10">
-        <v>0</v>
-      </c>
-      <c r="U69" s="11" t="s">
-        <v>60</v>
+        <v>1</v>
+      </c>
+      <c r="U69" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5732,9 +5748,11 @@
       <c r="B70" s="5">
         <v>46169.669448368055</v>
       </c>
-      <c r="C70" s="6"/>
+      <c r="C70" s="5">
+        <v>46210.65139943287</v>
+      </c>
       <c r="D70" s="5">
-        <v>46199.57084185185</v>
+        <v>46210.65141630787</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>248</v>
@@ -5782,10 +5800,10 @@
         <v>33</v>
       </c>
       <c r="T70" s="6">
-        <v>0</v>
-      </c>
-      <c r="U70" s="12" t="s">
-        <v>66</v>
+        <v>1</v>
+      </c>
+      <c r="U70" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -5795,9 +5813,11 @@
       <c r="B71" s="9">
         <v>46169.66945298611</v>
       </c>
-      <c r="C71" s="10"/>
+      <c r="C71" s="9">
+        <v>46210.6519625463</v>
+      </c>
       <c r="D71" s="9">
-        <v>46209.90823069445</v>
+        <v>46210.65197810185</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>249</v>
@@ -5845,10 +5865,10 @@
         <v>33</v>
       </c>
       <c r="T71" s="10">
-        <v>0</v>
-      </c>
-      <c r="U71" s="11" t="s">
-        <v>60</v>
+        <v>1</v>
+      </c>
+      <c r="U71" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
@@ -5974,7 +5994,7 @@
         <v>46209.909371331014</v>
       </c>
       <c r="D74" s="5">
-        <v>46209.90937271991</v>
+        <v>46210.65196928241</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>206</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="366">
   <si>
     <t>50001558 -  GESVIAL</t>
   </si>
@@ -499,6 +499,9 @@
   </si>
   <si>
     <t xml:space="preserve">Generación OC   ot 4343 ,fabricación tableros   ot 4343 </t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1215174084296068</t>
@@ -3860,7 +3863,7 @@
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46195.68641738426</v>
+        <v>46212.17798137732</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>148</v>
@@ -3904,8 +3907,8 @@
       <c r="R38" s="5">
         <v>46219</v>
       </c>
-      <c r="S38" s="7" t="s">
-        <v>33</v>
+      <c r="S38" s="12" t="s">
+        <v>150</v>
       </c>
       <c r="T38" s="6">
         <v>0</v>
@@ -3916,7 +3919,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B39" s="9">
         <v>46169.669149270834</v>
@@ -3961,7 +3964,7 @@
         <v>109</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -3971,7 +3974,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B40" s="5">
         <v>46169.66915408565</v>
@@ -3981,7 +3984,7 @@
         <v>46195.686418576384</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
@@ -4014,7 +4017,7 @@
         <v>110</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4024,7 +4027,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B41" s="9">
         <v>46169.66915865741</v>
@@ -4036,16 +4039,16 @@
         <v>46209.82174662037</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I41" s="9">
         <v>46245</v>
@@ -4066,7 +4069,7 @@
         <v>112</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P41" s="10" t="s">
         <v>112</v>
@@ -4089,7 +4092,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B42" s="5">
         <v>46169.66916377315</v>
@@ -4101,16 +4104,16 @@
         <v>46199.56927892361</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I42" s="5">
         <v>46245</v>
@@ -4128,13 +4131,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>94</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4150,7 +4153,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B43" s="9">
         <v>46169.66916960648</v>
@@ -4162,16 +4165,16 @@
         <v>46205.61247092593</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I43" s="9">
         <v>46247</v>
@@ -4189,13 +4192,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4211,7 +4214,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B44" s="5">
         <v>46169.66917503472</v>
@@ -4223,16 +4226,16 @@
         <v>46199.567282199074</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I44" s="5">
         <v>46245</v>
@@ -4253,7 +4256,7 @@
         <v>112</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>26</v>
@@ -4276,7 +4279,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B45" s="9">
         <v>46169.669178888886</v>
@@ -4294,10 +4297,10 @@
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I45" s="9">
         <v>46245</v>
@@ -4315,13 +4318,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>100</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4331,7 +4334,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B46" s="5">
         <v>46169.669183680555</v>
@@ -4343,16 +4346,16 @@
         <v>46199.56984034722</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I46" s="5">
         <v>46247</v>
@@ -4370,13 +4373,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>101</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4386,7 +4389,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B47" s="9">
         <v>46169.66918849537</v>
@@ -4398,16 +4401,16 @@
         <v>46204.863616284725</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I47" s="9">
         <v>46245</v>
@@ -4428,7 +4431,7 @@
         <v>112</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>26</v>
@@ -4451,7 +4454,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B48" s="5">
         <v>46169.66919252315</v>
@@ -4469,10 +4472,10 @@
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I48" s="5">
         <v>46245</v>
@@ -4490,13 +4493,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>106</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4506,7 +4509,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B49" s="9">
         <v>46169.66919734953</v>
@@ -4518,16 +4521,16 @@
         <v>46204.8635487037</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I49" s="9">
         <v>46254</v>
@@ -4545,13 +4548,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O49" s="10" t="s">
         <v>107</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4561,7 +4564,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
         <v>46169.66920229167</v>
@@ -4573,16 +4576,16 @@
         <v>46210.65313525463</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I50" s="5">
         <v>46286</v>
@@ -4600,10 +4603,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4616,7 +4619,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B51" s="9">
         <v>46169.66924202546</v>
@@ -4628,16 +4631,16 @@
         <v>46199.57084909722</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I51" s="9">
         <v>46245</v>
@@ -4658,7 +4661,7 @@
         <v>112</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P51" s="10" t="s">
         <v>26</v>
@@ -4681,7 +4684,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46169.66924635417</v>
@@ -4699,10 +4702,10 @@
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I52" s="5">
         <v>46245</v>
@@ -4720,13 +4723,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>103</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4736,7 +4739,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B53" s="9">
         <v>46169.66925091435</v>
@@ -4748,16 +4751,16 @@
         <v>46199.57082731482</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I53" s="9">
         <v>46247</v>
@@ -4775,13 +4778,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O53" s="10" t="s">
         <v>104</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4791,7 +4794,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B54" s="5">
         <v>46169.669255659726</v>
@@ -4803,7 +4806,7 @@
         <v>46210.52487434028</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>25</v>
@@ -4827,7 +4830,7 @@
         <v>26</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -4844,7 +4847,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B55" s="9">
         <v>46169.66925896991</v>
@@ -4856,16 +4859,16 @@
         <v>46197.71564204861</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I55" s="9">
         <v>46167</v>
@@ -4877,19 +4880,19 @@
         <v>26</v>
       </c>
       <c r="L55" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q55" s="9">
         <v>46167</v>
@@ -4909,7 +4912,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B56" s="5">
         <v>46169.66926408565</v>
@@ -4921,16 +4924,16 @@
         <v>46195.94997940972</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I56" s="5">
         <v>46167</v>
@@ -4948,13 +4951,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4964,7 +4967,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B57" s="9">
         <v>46169.66926952546</v>
@@ -4976,16 +4979,16 @@
         <v>46195.94998958333</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I57" s="9">
         <v>46167</v>
@@ -5003,13 +5006,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O57" s="10" t="s">
         <v>78</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -5019,7 +5022,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B58" s="5">
         <v>46169.66929263889</v>
@@ -5031,16 +5034,16 @@
         <v>46197.71567513889</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I58" s="5">
         <v>46220</v>
@@ -5058,13 +5061,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q58" s="5">
         <v>46220</v>
@@ -5084,7 +5087,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B59" s="9">
         <v>46169.66929775463</v>
@@ -5096,16 +5099,16 @@
         <v>46195.950096458335</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I59" s="9">
         <v>46181</v>
@@ -5123,13 +5126,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5139,7 +5142,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B60" s="5">
         <v>46169.66930358796</v>
@@ -5151,16 +5154,16 @@
         <v>46196.87985491898</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I60" s="5">
         <v>46181</v>
@@ -5178,13 +5181,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5194,7 +5197,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B61" s="9">
         <v>46169.669327048614</v>
@@ -5212,10 +5215,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I61" s="9">
         <v>46240</v>
@@ -5233,13 +5236,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q61" s="9">
         <v>46240</v>
@@ -5259,7 +5262,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B62" s="5">
         <v>46169.6693399537</v>
@@ -5271,16 +5274,16 @@
         <v>46195.95042396991</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I62" s="5">
         <v>46188</v>
@@ -5301,7 +5304,7 @@
         <v>97</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>97</v>
@@ -5314,7 +5317,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B63" s="9">
         <v>46169.669361203705</v>
@@ -5324,16 +5327,16 @@
         <v>46174.84660805555</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I63" s="9">
         <v>46322</v>
@@ -5351,10 +5354,10 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P63" s="10" t="s">
         <v>26</v>
@@ -5377,7 +5380,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B64" s="5">
         <v>46169.66936501158</v>
@@ -5387,16 +5390,16 @@
         <v>46174.846919421296</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I64" s="5">
         <v>46290</v>
@@ -5414,13 +5417,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5430,7 +5433,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B65" s="9">
         <v>46169.669418136575</v>
@@ -5442,7 +5445,7 @@
         <v>46210.65198340278</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>25</v>
@@ -5466,7 +5469,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P65" s="10" t="s">
         <v>26</v>
@@ -5483,7 +5486,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B66" s="5">
         <v>46169.66942685185</v>
@@ -5495,16 +5498,16 @@
         <v>46210.651395196764</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I66" s="5">
         <v>46258</v>
@@ -5522,13 +5525,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q66" s="5">
         <v>46258</v>
@@ -5548,7 +5551,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B67" s="9">
         <v>46169.669432361115</v>
@@ -5560,16 +5563,16 @@
         <v>46210.65197202546</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I67" s="9">
         <v>46260</v>
@@ -5587,13 +5590,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q67" s="9">
         <v>46260</v>
@@ -5613,7 +5616,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B68" s="5">
         <v>46169.66943836806</v>
@@ -5625,16 +5628,16 @@
         <v>46210.65139929398</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I68" s="5">
         <v>46258</v>
@@ -5652,13 +5655,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q68" s="5">
         <v>46258</v>
@@ -5678,7 +5681,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B69" s="9">
         <v>46169.669443692124</v>
@@ -5690,16 +5693,16 @@
         <v>46210.651975879635</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I69" s="9">
         <v>46260</v>
@@ -5717,13 +5720,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q69" s="9">
         <v>46260</v>
@@ -5743,7 +5746,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B70" s="5">
         <v>46169.669448368055</v>
@@ -5755,16 +5758,16 @@
         <v>46210.65141630787</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I70" s="5">
         <v>46258</v>
@@ -5782,13 +5785,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q70" s="5">
         <v>46258</v>
@@ -5808,7 +5811,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B71" s="9">
         <v>46169.66945298611</v>
@@ -5820,16 +5823,16 @@
         <v>46210.65197810185</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I71" s="9">
         <v>46260</v>
@@ -5847,13 +5850,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q71" s="9">
         <v>46260</v>
@@ -5873,7 +5876,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B72" s="5">
         <v>46169.66945778935</v>
@@ -5883,7 +5886,7 @@
         <v>46209.909264270835</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>25</v>
@@ -5907,7 +5910,7 @@
         <v>26</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>26</v>
@@ -5920,7 +5923,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B73" s="9">
         <v>46169.66946104167</v>
@@ -5932,16 +5935,16 @@
         <v>46209.90937729167</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I73" s="9">
         <v>46262</v>
@@ -5959,13 +5962,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q73" s="9">
         <v>46262</v>
@@ -5985,7 +5988,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B74" s="5">
         <v>46169.669467280095</v>
@@ -5997,16 +6000,16 @@
         <v>46210.65196928241</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I74" s="5">
         <v>46262</v>
@@ -6024,13 +6027,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6040,7 +6043,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B75" s="9">
         <v>46169.66950289352</v>
@@ -6050,16 +6053,16 @@
         <v>46209.90954123843</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I75" s="9">
         <v>46273</v>
@@ -6077,13 +6080,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q75" s="9">
         <v>46273</v>
@@ -6103,7 +6106,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B76" s="5">
         <v>46169.66950758102</v>
@@ -6113,16 +6116,16 @@
         <v>46209.90937868056</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I76" s="5">
         <v>46273</v>
@@ -6140,13 +6143,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6156,7 +6159,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B77" s="9">
         <v>46169.66953380787</v>
@@ -6166,16 +6169,16 @@
         <v>46209.908330833336</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I77" s="9">
         <v>46294</v>
@@ -6193,13 +6196,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q77" s="9">
         <v>46294</v>
@@ -6219,7 +6222,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B78" s="5">
         <v>46169.66953854167</v>
@@ -6229,16 +6232,16 @@
         <v>46197.84256122685</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -6254,13 +6257,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6270,7 +6273,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B79" s="9">
         <v>46169.66960108797</v>
@@ -6280,7 +6283,7 @@
         <v>46209.85402508102</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>25</v>
@@ -6304,7 +6307,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P79" s="10" t="s">
         <v>26</v>
@@ -6319,7 +6322,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B80" s="5">
         <v>46169.66960956018</v>
@@ -6331,16 +6334,16 @@
         <v>46209.844928101855</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I80" s="5">
         <v>46174</v>
@@ -6358,13 +6361,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>133</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q80" s="5">
         <v>46174</v>
@@ -6384,7 +6387,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B81" s="9">
         <v>46169.6696165162</v>
@@ -6396,16 +6399,16 @@
         <v>46209.84471936343</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I81" s="9">
         <v>46288</v>
@@ -6423,13 +6426,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>123</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q81" s="9">
         <v>46288</v>
@@ -6449,7 +6452,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B82" s="5">
         <v>46169.669622939815</v>
@@ -6461,16 +6464,16 @@
         <v>46209.85430440972</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I82" s="5">
         <v>46308</v>
@@ -6488,13 +6491,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>142</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q82" s="5">
         <v>46308</v>
@@ -6514,7 +6517,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B83" s="9">
         <v>46169.66962980324</v>
@@ -6524,16 +6527,16 @@
         <v>46204.86356525463</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I83" s="9">
         <v>46287</v>
@@ -6551,13 +6554,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q83" s="9">
         <v>46287</v>
@@ -6577,7 +6580,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B84" s="5">
         <v>46169.669635185186</v>
@@ -6593,10 +6596,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I84" s="5">
         <v>46220</v>
@@ -6614,13 +6617,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q84" s="5">
         <v>46220</v>
@@ -6640,7 +6643,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B85" s="9">
         <v>46169.66964790509</v>
@@ -6650,7 +6653,7 @@
         <v>46209.84945282407</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>25</v>
@@ -6674,7 +6677,7 @@
         <v>26</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>26</v>
@@ -6687,7 +6690,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B86" s="5">
         <v>46169.66965109954</v>
@@ -6697,7 +6700,7 @@
         <v>46174.84790094907</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6724,13 +6727,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q86" s="5">
         <v>46294</v>
@@ -6750,7 +6753,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B87" s="9">
         <v>46169.6696568287</v>
@@ -6760,7 +6763,7 @@
         <v>46174.84798839121</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6787,13 +6790,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6803,7 +6806,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B88" s="5">
         <v>46169.669688622685</v>
@@ -6815,7 +6818,7 @@
         <v>46209.8493094213</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6842,13 +6845,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q88" s="5">
         <v>46316</v>
@@ -6868,7 +6871,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B89" s="9">
         <v>46169.66969347223</v>
@@ -6878,7 +6881,7 @@
         <v>46209.84459753473</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6903,13 +6906,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6919,7 +6922,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B90" s="5">
         <v>46169.66972681713</v>
@@ -6931,7 +6934,7 @@
         <v>46209.84946481482</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6958,13 +6961,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q90" s="5">
         <v>46317</v>
@@ -6984,7 +6987,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B91" s="9">
         <v>46169.66973180555</v>
@@ -6994,7 +6997,7 @@
         <v>46209.844891030094</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -7021,13 +7024,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -7037,7 +7040,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B92" s="5">
         <v>46169.66981054399</v>
@@ -7047,7 +7050,7 @@
         <v>46174.8478909375</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7074,13 +7077,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q92" s="5">
         <v>46318</v>
@@ -7100,7 +7103,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B93" s="9">
         <v>46169.66981724537</v>
@@ -7110,7 +7113,7 @@
         <v>46209.85401892361</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7137,13 +7140,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7153,7 +7156,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B94" s="5">
         <v>46169.669861041664</v>
@@ -7163,7 +7166,7 @@
         <v>46174.8478862037</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7190,13 +7193,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q94" s="5">
         <v>46321</v>
@@ -7216,7 +7219,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B95" s="9">
         <v>46169.66986724537</v>
@@ -7226,7 +7229,7 @@
         <v>46174.84816675926</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7253,13 +7256,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7269,7 +7272,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B96" s="5">
         <v>46169.66990296297</v>
@@ -7279,7 +7282,7 @@
         <v>46174.84788545139</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7306,13 +7309,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q96" s="5">
         <v>46323</v>
@@ -7332,7 +7335,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B97" s="9">
         <v>46169.66994555556</v>
@@ -7342,7 +7345,7 @@
         <v>46174.848269317125</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7367,13 +7370,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7383,7 +7386,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B98" s="5">
         <v>46169.669978645834</v>
@@ -7393,7 +7396,7 @@
         <v>46174.82401747685</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>25</v>
@@ -7417,7 +7420,7 @@
         <v>26</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>26</v>
@@ -7430,7 +7433,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B99" s="9">
         <v>46169.66998244213</v>
@@ -7440,16 +7443,16 @@
         <v>46174.84843513889</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I99" s="9">
         <v>46324</v>
@@ -7467,13 +7470,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q99" s="9">
         <v>46324</v>
@@ -7493,7 +7496,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B100" s="5">
         <v>46169.66998994213</v>
@@ -7503,16 +7506,16 @@
         <v>46174.84838837963</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I100" s="6"/>
       <c r="J100" s="5">
@@ -7528,13 +7531,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7544,7 +7547,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B101" s="9">
         <v>46170.63118891204</v>
@@ -7554,16 +7557,16 @@
         <v>46209.90833168982</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="9">
@@ -7579,13 +7582,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7595,7 +7598,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B102" s="5">
         <v>46174.820955891206</v>
@@ -7611,10 +7614,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I102" s="5">
         <v>46324</v>
@@ -7632,13 +7635,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>62</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7648,7 +7651,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B103" s="9">
         <v>46169.670044224535</v>
@@ -7658,7 +7661,7 @@
         <v>46174.848558831014</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7683,13 +7686,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q103" s="9">
         <v>46325</v>
@@ -7709,7 +7712,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B104" s="5">
         <v>46169.670049050925</v>
@@ -7719,7 +7722,7 @@
         <v>46174.848527152775</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7744,13 +7747,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7760,7 +7763,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B105" s="9">
         <v>46170.63213679398</v>
@@ -7770,7 +7773,7 @@
         <v>46174.848524270834</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7795,13 +7798,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7811,7 +7814,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B106" s="5">
         <v>46174.82099290509</v>
@@ -7821,7 +7824,7 @@
         <v>46174.84852028935</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7848,7 +7851,7 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>62</v>
@@ -7864,7 +7867,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B107" s="9">
         <v>46169.67013976852</v>
@@ -7874,16 +7877,16 @@
         <v>46174.84870307871</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I107" s="10"/>
       <c r="J107" s="9">
@@ -7899,13 +7902,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q107" s="9">
         <v>46328</v>
@@ -7925,7 +7928,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B108" s="5">
         <v>46169.670151377315</v>
@@ -7935,16 +7938,16 @@
         <v>46174.848669872685</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I108" s="5">
         <v>46328</v>
@@ -7962,13 +7965,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7978,7 +7981,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B109" s="9">
         <v>46170.63285997685</v>
@@ -7988,16 +7991,16 @@
         <v>46174.848667314815</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I109" s="9">
         <v>46328</v>
@@ -8015,13 +8018,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -8031,7 +8034,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B110" s="5">
         <v>46174.821024143515</v>
@@ -8047,10 +8050,10 @@
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I110" s="5">
         <v>46328</v>
@@ -8068,10 +8071,10 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>62</v>
@@ -8084,7 +8087,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B111" s="9">
         <v>46169.67021965278</v>
@@ -8094,16 +8097,16 @@
         <v>46174.84880980324</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I111" s="9">
         <v>46329</v>
@@ -8121,13 +8124,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q111" s="9">
         <v>46329</v>
@@ -8147,7 +8150,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B112" s="5">
         <v>46169.67022677083</v>
@@ -8157,16 +8160,16 @@
         <v>46174.84878571759</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I112" s="6"/>
       <c r="J112" s="5">
@@ -8182,13 +8185,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8198,7 +8201,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B113" s="9">
         <v>46170.633581828704</v>
@@ -8208,16 +8211,16 @@
         <v>46174.84878314815</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I113" s="10"/>
       <c r="J113" s="9">
@@ -8233,10 +8236,10 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -8249,7 +8252,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B114" s="5">
         <v>46174.821057037036</v>
@@ -8265,10 +8268,10 @@
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I114" s="6"/>
       <c r="J114" s="5">
@@ -8284,7 +8287,7 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>62</v>
@@ -8300,7 +8303,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B115" s="9">
         <v>46169.67031616898</v>
@@ -8310,7 +8313,7 @@
         <v>46174.82401751158</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>25</v>
@@ -8334,7 +8337,7 @@
         <v>26</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P115" s="10" t="s">
         <v>26</v>
@@ -8347,7 +8350,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B116" s="5">
         <v>46169.67031976852</v>
@@ -8357,16 +8360,16 @@
         <v>46174.84885483797</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="I116" s="5">
         <v>46330</v>
@@ -8384,13 +8387,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q116" s="5">
         <v>46330</v>
@@ -8410,7 +8413,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B117" s="9">
         <v>46169.6703253125</v>
@@ -8420,7 +8423,7 @@
         <v>46192.97339644676</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8447,13 +8450,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q117" s="9">
         <v>46330</v>
@@ -8473,7 +8476,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B118" s="5">
         <v>46169.670332430556</v>
@@ -8483,7 +8486,7 @@
         <v>46174.82401726852</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>25</v>
@@ -8507,7 +8510,7 @@
         <v>26</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>26</v>
@@ -8526,7 +8529,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B119" s="9">
         <v>46169.67033591435</v>
@@ -8536,7 +8539,7 @@
         <v>46174.848958703704</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8563,13 +8566,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q119" s="9">
         <v>46330</v>
@@ -8589,7 +8592,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B120" s="5">
         <v>46169.67034748843</v>
@@ -8599,7 +8602,7 @@
         <v>46174.84895586806</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8626,13 +8629,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q120" s="5">
         <v>46339</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -243,9 +243,6 @@
     <t>Ingenieria basica Rodete,Ingenieria Detalle,Ingenieria Basica Motor</t>
   </si>
   <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
     <t>1215174266168927</t>
   </si>
   <si>
@@ -391,6 +388,9 @@
   </si>
   <si>
     <t>Materiales corte Laser ot 4342 -4344,Motor ot 4342,rodete ot 4342,Alabe ot 4342</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1215174084165958</t>
@@ -2373,9 +2373,11 @@
       <c r="B14" s="5">
         <v>46169.66882583333</v>
       </c>
-      <c r="C14" s="6"/>
+      <c r="C14" s="5">
+        <v>46212.79376377315</v>
+      </c>
       <c r="D14" s="5">
-        <v>46192.97341535879</v>
+        <v>46212.79378054398</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>64</v>
@@ -2410,14 +2412,16 @@
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
       <c r="S14" s="6"/>
-      <c r="T14" s="6"/>
-      <c r="U14" s="12" t="s">
-        <v>66</v>
+      <c r="T14" s="6">
+        <v>1</v>
+      </c>
+      <c r="U14" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B15" s="9">
         <v>46169.66899085648</v>
@@ -2429,16 +2433,16 @@
         <v>46192.97339646991</v>
       </c>
       <c r="E15" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="F15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15" s="10" t="s">
+      <c r="H15" s="10" t="s">
         <v>69</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>70</v>
       </c>
       <c r="I15" s="9">
         <v>46155</v>
@@ -2450,7 +2454,7 @@
         <v>26</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M15" s="10" t="s">
         <v>26</v>
@@ -2462,7 +2466,7 @@
         <v>40</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q15" s="9">
         <v>46155</v>
@@ -2482,7 +2486,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B16" s="5">
         <v>46169.66899618055</v>
@@ -2494,16 +2498,16 @@
         <v>46192.97339646991</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>69</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>70</v>
       </c>
       <c r="I16" s="5">
         <v>46155</v>
@@ -2515,7 +2519,7 @@
         <v>26</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M16" s="6" t="s">
         <v>26</v>
@@ -2527,7 +2531,7 @@
         <v>40</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q16" s="5">
         <v>46155</v>
@@ -2547,7 +2551,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B17" s="9">
         <v>46169.669002106486</v>
@@ -2559,16 +2563,16 @@
         <v>46192.97339675926</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H17" s="10" t="s">
         <v>69</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>70</v>
       </c>
       <c r="I17" s="9">
         <v>46155</v>
@@ -2592,7 +2596,7 @@
         <v>40</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q17" s="9">
         <v>46155</v>
@@ -2612,7 +2616,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B18" s="5">
         <v>46169.66883001158</v>
@@ -2624,7 +2628,7 @@
         <v>46197.64488530092</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>25</v>
@@ -2648,7 +2652,7 @@
         <v>26</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P18" s="6" t="s">
         <v>26</v>
@@ -2665,7 +2669,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B19" s="9">
         <v>46169.669016053245</v>
@@ -2677,16 +2681,16 @@
         <v>46181.636840625</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H19" s="10" t="s">
         <v>69</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>70</v>
       </c>
       <c r="I19" s="9">
         <v>46157</v>
@@ -2704,13 +2708,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q19" s="9">
         <v>46157</v>
@@ -2730,7 +2734,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B20" s="5">
         <v>46169.669021423615</v>
@@ -2742,16 +2746,16 @@
         <v>46181.636847222224</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="H20" s="6" t="s">
         <v>69</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>70</v>
       </c>
       <c r="I20" s="5">
         <v>46167</v>
@@ -2769,13 +2773,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Q20" s="5">
         <v>46167</v>
@@ -2795,7 +2799,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B21" s="9">
         <v>46169.66902680555</v>
@@ -2807,16 +2811,16 @@
         <v>46181.636854895834</v>
       </c>
       <c r="E21" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="F21" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>91</v>
-      </c>
       <c r="H21" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I21" s="9">
         <v>46167</v>
@@ -2834,13 +2838,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q21" s="9">
         <v>46167</v>
@@ -2860,7 +2864,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B22" s="5">
         <v>46169.66903233796</v>
@@ -2872,16 +2876,16 @@
         <v>46206.55341104166</v>
       </c>
       <c r="E22" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G22" s="6" t="s">
+      <c r="H22" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>96</v>
       </c>
       <c r="I22" s="5">
         <v>46241</v>
@@ -2899,13 +2903,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O22" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="P22" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="P22" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="Q22" s="5">
         <v>46241</v>
@@ -2925,7 +2929,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B23" s="9">
         <v>46169.669037291664</v>
@@ -2937,16 +2941,16 @@
         <v>46197.644057592595</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="H23" s="10" t="s">
         <v>95</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>96</v>
       </c>
       <c r="I23" s="9">
         <v>46241</v>
@@ -2964,13 +2968,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Q23" s="9">
         <v>46241</v>
@@ -2990,7 +2994,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B24" s="5">
         <v>46169.66904123843</v>
@@ -3002,16 +3006,16 @@
         <v>46197.64420756944</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>96</v>
       </c>
       <c r="I24" s="5">
         <v>46241</v>
@@ -3029,13 +3033,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Q24" s="5">
         <v>46241</v>
@@ -3055,7 +3059,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B25" s="9">
         <v>46169.66904511574</v>
@@ -3067,16 +3071,16 @@
         <v>46197.64487474537</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>95</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>96</v>
       </c>
       <c r="I25" s="9">
         <v>46241</v>
@@ -3094,13 +3098,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q25" s="9">
         <v>46241</v>
@@ -3120,7 +3124,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B26" s="5">
         <v>46169.66904878472</v>
@@ -3132,16 +3136,16 @@
         <v>46195.60168921296</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>69</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>70</v>
       </c>
       <c r="I26" s="5">
         <v>46157</v>
@@ -3159,13 +3163,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>50</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Q26" s="5">
         <v>46157</v>
@@ -3185,7 +3189,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B27" s="9">
         <v>46169.66883418981</v>
@@ -3195,7 +3199,7 @@
         <v>46209.82175228009</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>25</v>
@@ -3219,7 +3223,7 @@
         <v>26</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P27" s="10" t="s">
         <v>26</v>
@@ -3229,7 +3233,7 @@
       <c r="S27" s="10"/>
       <c r="T27" s="10"/>
       <c r="U27" s="12" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -3273,13 +3277,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>118</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q28" s="5">
         <v>46168</v>
@@ -3341,7 +3345,7 @@
         <v>115</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P29" s="10" t="s">
         <v>121</v>
@@ -3460,13 +3464,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O31" s="10" t="s">
         <v>127</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q31" s="9">
         <v>46168</v>
@@ -3528,7 +3532,7 @@
         <v>126</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>131</v>
@@ -3647,13 +3651,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>137</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q34" s="5">
         <v>46161</v>
@@ -3715,7 +3719,7 @@
         <v>136</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>140</v>
@@ -3893,7 +3897,7 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>149</v>
@@ -3931,7 +3935,7 @@
         <v>46195.68641299769</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
@@ -3961,7 +3965,7 @@
         <v>148</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>152</v>
@@ -4014,7 +4018,7 @@
         <v>148</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>155</v>
@@ -4066,13 +4070,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O41" s="10" t="s">
         <v>160</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q41" s="9">
         <v>46245</v>
@@ -4134,7 +4138,7 @@
         <v>157</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>163</v>
@@ -4253,7 +4257,7 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>169</v>
@@ -4291,7 +4295,7 @@
         <v>46199.569896354165</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
@@ -4321,7 +4325,7 @@
         <v>168</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P45" s="10" t="s">
         <v>171</v>
@@ -4376,7 +4380,7 @@
         <v>168</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>174</v>
@@ -4428,7 +4432,7 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>179</v>
@@ -4466,7 +4470,7 @@
         <v>46204.863510995376</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
@@ -4496,7 +4500,7 @@
         <v>176</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>181</v>
@@ -4551,7 +4555,7 @@
         <v>176</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>184</v>
@@ -4658,7 +4662,7 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O51" s="10" t="s">
         <v>191</v>
@@ -4696,7 +4700,7 @@
         <v>46199.57078165509</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -4726,7 +4730,7 @@
         <v>190</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>193</v>
@@ -4781,7 +4785,7 @@
         <v>190</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>196</v>
@@ -4954,7 +4958,7 @@
         <v>201</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>210</v>
@@ -5009,7 +5013,7 @@
         <v>201</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>213</v>
@@ -5209,7 +5213,7 @@
         <v>46209.908330949074</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
@@ -5301,13 +5305,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>207</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -6101,7 +6105,7 @@
         <v>0.1</v>
       </c>
       <c r="U75" s="12" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -6317,7 +6321,7 @@
       <c r="S79" s="10"/>
       <c r="T79" s="10"/>
       <c r="U79" s="12" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
@@ -6575,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="U83" s="12" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
@@ -6706,10 +6710,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I86" s="5">
         <v>46294</v>
@@ -6769,10 +6773,10 @@
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I87" s="9">
         <v>46294</v>
@@ -6824,10 +6828,10 @@
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I88" s="5">
         <v>46316</v>
@@ -6887,10 +6891,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I89" s="10"/>
       <c r="J89" s="9">
@@ -6940,10 +6944,10 @@
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I90" s="5">
         <v>46317</v>
@@ -7003,10 +7007,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I91" s="9">
         <v>46317</v>
@@ -7056,10 +7060,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I92" s="5">
         <v>46318</v>
@@ -7119,10 +7123,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I93" s="9">
         <v>46318</v>
@@ -7172,10 +7176,10 @@
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I94" s="5">
         <v>46321</v>
@@ -7235,10 +7239,10 @@
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I95" s="9">
         <v>46321</v>
@@ -7288,10 +7292,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I96" s="5">
         <v>46323</v>
@@ -7351,10 +7355,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I97" s="10"/>
       <c r="J97" s="9">
@@ -7667,10 +7671,10 @@
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I103" s="10"/>
       <c r="J103" s="9">
@@ -7728,10 +7732,10 @@
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I104" s="6"/>
       <c r="J104" s="5">
@@ -7779,10 +7783,10 @@
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I105" s="10"/>
       <c r="J105" s="9">
@@ -7830,10 +7834,10 @@
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I106" s="5">
         <v>46325</v>
@@ -8429,10 +8433,10 @@
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H117" s="10" t="s">
         <v>69</v>
-      </c>
-      <c r="H117" s="10" t="s">
-        <v>70</v>
       </c>
       <c r="I117" s="9">
         <v>46330</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -6591,7 +6591,7 @@
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46174.84778872685</v>
+        <v>46213.19847427083</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>58</v>
@@ -6635,8 +6635,8 @@
       <c r="R84" s="5">
         <v>46220</v>
       </c>
-      <c r="S84" s="7" t="s">
-        <v>33</v>
+      <c r="S84" s="12" t="s">
+        <v>150</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="367">
   <si>
     <t>50001558 -  GESVIAL</t>
   </si>
@@ -119,6 +119,32 @@
   </si>
   <si>
     <t>Apertura pedido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buen día,
+Para el pedido 1558, se tiene un ventilador ZVN 1-16-160/4 + VDF FC102 160Kw para Gesvial:
+    Planos para:
+        Ventilador ZVN 1-16-160/4 con motor WEG
+        Alcance: Tobera + Rejilla + 2FAR160/200 + Pieza Tipo A Ø1600mm
+        hgutierrez@zitron.com, Tu apoyo con los planos de fabricación.
+    Accesorios:
+        Manga de ventilación Ø1600mm: 50 metros.
+    Rodete:
+        Alabe s/ plano 2605.01
+        Código:  300007
+        Z10 N900
+    Tratamiento superficial:
+        Estándar Zitrón con 2 capas y color de terminación Blanco RAL 9001.
+    Datos eléctricos para el motor:
+        Motor WEG
+        160KW, 380 VAC, 50 Hz, IP55.
+        Frame 315S/M
+    Tableros eléctricos:
+        VDF 160 KW, 380 VAC, 50 Hz, IP54.
+        Danfoss FC102
+        Autosoportado
+    Fechas de entrega: 23/06/2026.
+ </t>
   </si>
   <si>
     <t>1215174259747298</t>
@@ -1897,7 +1923,7 @@
         <v>46175.87134493055</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.87136771991</v>
+        <v>46213.762757986115</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1919,7 +1945,7 @@
         <v>26</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="M6" s="6" t="s">
         <v>26</v>
@@ -1951,7 +1977,7 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="9">
         <v>46169.66895021991</v>
@@ -1963,7 +1989,7 @@
         <v>46175.87136748843</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F7" s="10" t="s">
         <v>26</v>
@@ -1982,7 +2008,7 @@
         <v>26</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M7" s="10" t="s">
         <v>26</v>
@@ -2014,7 +2040,7 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" s="5">
         <v>46169.66895328704</v>
@@ -2026,7 +2052,7 @@
         <v>46175.87136746528</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>26</v>
@@ -2045,7 +2071,7 @@
         <v>26</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M8" s="6" t="s">
         <v>26</v>
@@ -2057,7 +2083,7 @@
         <v>26</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q8" s="5">
         <v>46154</v>
@@ -2077,7 +2103,7 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B9" s="9">
         <v>46169.6689571875</v>
@@ -2089,7 +2115,7 @@
         <v>46175.871368657405</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>26</v>
@@ -2108,7 +2134,7 @@
         <v>26</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M9" s="10" t="s">
         <v>26</v>
@@ -2140,7 +2166,7 @@
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B10" s="5">
         <v>46169.6688215162</v>
@@ -2150,7 +2176,7 @@
         <v>46195.60097974537</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>25</v>
@@ -2174,7 +2200,7 @@
         <v>26</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P10" s="6" t="s">
         <v>26</v>
@@ -2187,7 +2213,7 @@
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" s="9">
         <v>46169.6689606713</v>
@@ -2199,16 +2225,16 @@
         <v>46195.60099197917</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I11" s="9">
         <v>46155</v>
@@ -2226,13 +2252,13 @@
         <v>26</v>
       </c>
       <c r="N11" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O11" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P11" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Q11" s="9">
         <v>46155</v>
@@ -2252,7 +2278,7 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B12" s="5">
         <v>46169.66896575232</v>
@@ -2262,16 +2288,16 @@
         <v>46174.82117752315</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I12" s="5">
         <v>46223</v>
@@ -2289,13 +2315,13 @@
         <v>26</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q12" s="5">
         <v>46223</v>
@@ -2310,12 +2336,12 @@
         <v>0</v>
       </c>
       <c r="U12" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B13" s="9">
         <v>46169.668971666666</v>
@@ -2325,16 +2351,16 @@
         <v>46191.686801284726</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I13" s="9">
         <v>46223</v>
@@ -2352,13 +2378,13 @@
         <v>26</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Q13" s="10"/>
       <c r="R13" s="10"/>
@@ -2368,7 +2394,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B14" s="5">
         <v>46169.66882583333</v>
@@ -2380,7 +2406,7 @@
         <v>46212.79378054398</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>25</v>
@@ -2404,7 +2430,7 @@
         <v>26</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P14" s="6" t="s">
         <v>26</v>
@@ -2421,7 +2447,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B15" s="9">
         <v>46169.66899085648</v>
@@ -2433,16 +2459,16 @@
         <v>46192.97339646991</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I15" s="9">
         <v>46155</v>
@@ -2454,19 +2480,19 @@
         <v>26</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M15" s="10" t="s">
         <v>26</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q15" s="9">
         <v>46155</v>
@@ -2486,7 +2512,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B16" s="5">
         <v>46169.66899618055</v>
@@ -2498,16 +2524,16 @@
         <v>46192.97339646991</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I16" s="5">
         <v>46155</v>
@@ -2519,19 +2545,19 @@
         <v>26</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q16" s="5">
         <v>46155</v>
@@ -2551,7 +2577,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B17" s="9">
         <v>46169.669002106486</v>
@@ -2563,16 +2589,16 @@
         <v>46192.97339675926</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I17" s="9">
         <v>46155</v>
@@ -2590,13 +2616,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q17" s="9">
         <v>46155</v>
@@ -2616,7 +2642,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B18" s="5">
         <v>46169.66883001158</v>
@@ -2628,7 +2654,7 @@
         <v>46197.64488530092</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>25</v>
@@ -2652,7 +2678,7 @@
         <v>26</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P18" s="6" t="s">
         <v>26</v>
@@ -2669,7 +2695,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B19" s="9">
         <v>46169.669016053245</v>
@@ -2681,16 +2707,16 @@
         <v>46181.636840625</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I19" s="9">
         <v>46157</v>
@@ -2708,13 +2734,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q19" s="9">
         <v>46157</v>
@@ -2734,7 +2760,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B20" s="5">
         <v>46169.669021423615</v>
@@ -2746,16 +2772,16 @@
         <v>46181.636847222224</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I20" s="5">
         <v>46167</v>
@@ -2773,13 +2799,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q20" s="5">
         <v>46167</v>
@@ -2799,7 +2825,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B21" s="9">
         <v>46169.66902680555</v>
@@ -2811,16 +2837,16 @@
         <v>46181.636854895834</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I21" s="9">
         <v>46167</v>
@@ -2838,13 +2864,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q21" s="9">
         <v>46167</v>
@@ -2864,7 +2890,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B22" s="5">
         <v>46169.66903233796</v>
@@ -2876,16 +2902,16 @@
         <v>46206.55341104166</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I22" s="5">
         <v>46241</v>
@@ -2903,13 +2929,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q22" s="5">
         <v>46241</v>
@@ -2929,7 +2955,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B23" s="9">
         <v>46169.669037291664</v>
@@ -2941,16 +2967,16 @@
         <v>46197.644057592595</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I23" s="9">
         <v>46241</v>
@@ -2968,13 +2994,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q23" s="9">
         <v>46241</v>
@@ -2994,7 +3020,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B24" s="5">
         <v>46169.66904123843</v>
@@ -3006,16 +3032,16 @@
         <v>46197.64420756944</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I24" s="5">
         <v>46241</v>
@@ -3033,13 +3059,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q24" s="5">
         <v>46241</v>
@@ -3059,7 +3085,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B25" s="9">
         <v>46169.66904511574</v>
@@ -3071,16 +3097,16 @@
         <v>46197.64487474537</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I25" s="9">
         <v>46241</v>
@@ -3098,13 +3124,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q25" s="9">
         <v>46241</v>
@@ -3124,7 +3150,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B26" s="5">
         <v>46169.66904878472</v>
@@ -3136,16 +3162,16 @@
         <v>46195.60168921296</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I26" s="5">
         <v>46157</v>
@@ -3163,13 +3189,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q26" s="5">
         <v>46157</v>
@@ -3189,7 +3215,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B27" s="9">
         <v>46169.66883418981</v>
@@ -3199,7 +3225,7 @@
         <v>46209.82175228009</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>25</v>
@@ -3223,7 +3249,7 @@
         <v>26</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P27" s="10" t="s">
         <v>26</v>
@@ -3233,12 +3259,12 @@
       <c r="S27" s="10"/>
       <c r="T27" s="10"/>
       <c r="U27" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B28" s="5">
         <v>46169.66908924768</v>
@@ -3250,16 +3276,16 @@
         <v>46182.63466408565</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I28" s="5">
         <v>46171</v>
@@ -3277,13 +3303,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q28" s="5">
         <v>46168</v>
@@ -3303,7 +3329,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B29" s="9">
         <v>46169.66909520833</v>
@@ -3315,16 +3341,16 @@
         <v>46182.63236322917</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I29" s="9">
         <v>46169</v>
@@ -3342,13 +3368,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3359,12 +3385,12 @@
         <v>0</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B30" s="5">
         <v>46169.669100810184</v>
@@ -3376,16 +3402,16 @@
         <v>46182.63463722222</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I30" s="5">
         <v>46171</v>
@@ -3403,13 +3429,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3420,12 +3446,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B31" s="9">
         <v>46169.669106284724</v>
@@ -3437,16 +3463,16 @@
         <v>46182.63460042824</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I31" s="9">
         <v>46168</v>
@@ -3464,13 +3490,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q31" s="9">
         <v>46168</v>
@@ -3479,7 +3505,7 @@
         <v>46171</v>
       </c>
       <c r="S31" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T31" s="10">
         <v>1</v>
@@ -3490,7 +3516,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B32" s="5">
         <v>46169.66911128472</v>
@@ -3502,16 +3528,16 @@
         <v>46182.6318109375</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I32" s="5">
         <v>46168</v>
@@ -3529,13 +3555,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3546,12 +3572,12 @@
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B33" s="9">
         <v>46169.669116805555</v>
@@ -3563,16 +3589,16 @@
         <v>46182.63457327546</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I33" s="9">
         <v>46170</v>
@@ -3590,13 +3616,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3607,12 +3633,12 @@
         <v>0</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B34" s="5">
         <v>46169.66912204861</v>
@@ -3624,16 +3650,16 @@
         <v>46182.6344355787</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I34" s="5">
         <v>46161</v>
@@ -3651,13 +3677,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q34" s="5">
         <v>46161</v>
@@ -3677,7 +3703,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B35" s="9">
         <v>46169.66912711806</v>
@@ -3689,16 +3715,16 @@
         <v>46182.63203959491</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I35" s="9">
         <v>46161</v>
@@ -3716,13 +3742,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3733,12 +3759,12 @@
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B36" s="5">
         <v>46169.66913270833</v>
@@ -3750,16 +3776,16 @@
         <v>46182.634411203704</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I36" s="5">
         <v>46182</v>
@@ -3777,13 +3803,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3794,12 +3820,12 @@
         <v>0</v>
       </c>
       <c r="U36" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B37" s="9">
         <v>46169.66913809028</v>
@@ -3811,16 +3837,16 @@
         <v>46182.6343528588</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I37" s="9">
         <v>46182</v>
@@ -3838,13 +3864,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3855,12 +3881,12 @@
         <v>0</v>
       </c>
       <c r="U37" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B38" s="5">
         <v>46169.66914475695</v>
@@ -3870,16 +3896,16 @@
         <v>46212.17798137732</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I38" s="5">
         <v>46161</v>
@@ -3897,10 +3923,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3912,18 +3938,18 @@
         <v>46219</v>
       </c>
       <c r="S38" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="T38" s="6">
         <v>0</v>
       </c>
       <c r="U38" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B39" s="9">
         <v>46169.669149270834</v>
@@ -3935,16 +3961,16 @@
         <v>46195.68641299769</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I39" s="9">
         <v>46161</v>
@@ -3962,13 +3988,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -3978,7 +4004,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B40" s="5">
         <v>46169.66915408565</v>
@@ -3988,16 +4014,16 @@
         <v>46195.686418576384</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I40" s="5">
         <v>46171</v>
@@ -4015,13 +4041,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4031,7 +4057,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B41" s="9">
         <v>46169.66915865741</v>
@@ -4043,16 +4069,16 @@
         <v>46209.82174662037</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I41" s="9">
         <v>46245</v>
@@ -4070,13 +4096,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q41" s="9">
         <v>46245</v>
@@ -4096,7 +4122,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B42" s="5">
         <v>46169.66916377315</v>
@@ -4108,16 +4134,16 @@
         <v>46199.56927892361</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I42" s="5">
         <v>46245</v>
@@ -4135,13 +4161,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4152,12 +4178,12 @@
         <v>0</v>
       </c>
       <c r="U42" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B43" s="9">
         <v>46169.66916960648</v>
@@ -4169,16 +4195,16 @@
         <v>46205.61247092593</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I43" s="9">
         <v>46247</v>
@@ -4196,13 +4222,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4213,12 +4239,12 @@
         <v>0</v>
       </c>
       <c r="U43" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B44" s="5">
         <v>46169.66917503472</v>
@@ -4230,16 +4256,16 @@
         <v>46199.567282199074</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I44" s="5">
         <v>46245</v>
@@ -4257,10 +4283,10 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>26</v>
@@ -4283,7 +4309,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B45" s="9">
         <v>46169.669178888886</v>
@@ -4295,16 +4321,16 @@
         <v>46199.569896354165</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I45" s="9">
         <v>46245</v>
@@ -4322,13 +4348,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4338,7 +4364,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B46" s="5">
         <v>46169.669183680555</v>
@@ -4350,16 +4376,16 @@
         <v>46199.56984034722</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I46" s="5">
         <v>46247</v>
@@ -4377,13 +4403,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4393,7 +4419,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B47" s="9">
         <v>46169.66918849537</v>
@@ -4405,16 +4431,16 @@
         <v>46204.863616284725</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I47" s="9">
         <v>46245</v>
@@ -4432,10 +4458,10 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>26</v>
@@ -4458,7 +4484,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B48" s="5">
         <v>46169.66919252315</v>
@@ -4470,16 +4496,16 @@
         <v>46204.863510995376</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I48" s="5">
         <v>46245</v>
@@ -4497,13 +4523,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4513,7 +4539,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B49" s="9">
         <v>46169.66919734953</v>
@@ -4525,16 +4551,16 @@
         <v>46204.8635487037</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I49" s="9">
         <v>46254</v>
@@ -4552,13 +4578,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4568,7 +4594,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B50" s="5">
         <v>46169.66920229167</v>
@@ -4580,16 +4606,16 @@
         <v>46210.65313525463</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I50" s="5">
         <v>46286</v>
@@ -4607,10 +4633,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4623,7 +4649,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B51" s="9">
         <v>46169.66924202546</v>
@@ -4635,16 +4661,16 @@
         <v>46199.57084909722</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I51" s="9">
         <v>46245</v>
@@ -4662,10 +4688,10 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P51" s="10" t="s">
         <v>26</v>
@@ -4688,7 +4714,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B52" s="5">
         <v>46169.66924635417</v>
@@ -4700,16 +4726,16 @@
         <v>46199.57078165509</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I52" s="5">
         <v>46245</v>
@@ -4727,13 +4753,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4743,7 +4769,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B53" s="9">
         <v>46169.66925091435</v>
@@ -4755,16 +4781,16 @@
         <v>46199.57082731482</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I53" s="9">
         <v>46247</v>
@@ -4782,13 +4808,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4798,7 +4824,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B54" s="5">
         <v>46169.669255659726</v>
@@ -4810,7 +4836,7 @@
         <v>46210.52487434028</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>25</v>
@@ -4834,7 +4860,7 @@
         <v>26</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -4851,7 +4877,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B55" s="9">
         <v>46169.66925896991</v>
@@ -4863,16 +4889,16 @@
         <v>46197.71564204861</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I55" s="9">
         <v>46167</v>
@@ -4884,19 +4910,19 @@
         <v>26</v>
       </c>
       <c r="L55" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q55" s="9">
         <v>46167</v>
@@ -4905,7 +4931,7 @@
         <v>46184</v>
       </c>
       <c r="S55" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T55" s="10">
         <v>1</v>
@@ -4916,7 +4942,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B56" s="5">
         <v>46169.66926408565</v>
@@ -4928,16 +4954,16 @@
         <v>46195.94997940972</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I56" s="5">
         <v>46167</v>
@@ -4955,13 +4981,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4971,7 +4997,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B57" s="9">
         <v>46169.66926952546</v>
@@ -4983,16 +5009,16 @@
         <v>46195.94998958333</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I57" s="9">
         <v>46167</v>
@@ -5010,13 +5036,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -5026,7 +5052,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B58" s="5">
         <v>46169.66929263889</v>
@@ -5038,16 +5064,16 @@
         <v>46197.71567513889</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I58" s="5">
         <v>46220</v>
@@ -5065,13 +5091,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q58" s="5">
         <v>46220</v>
@@ -5091,7 +5117,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B59" s="9">
         <v>46169.66929775463</v>
@@ -5103,16 +5129,16 @@
         <v>46195.950096458335</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I59" s="9">
         <v>46181</v>
@@ -5130,13 +5156,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5146,7 +5172,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B60" s="5">
         <v>46169.66930358796</v>
@@ -5158,16 +5184,16 @@
         <v>46196.87985491898</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I60" s="5">
         <v>46181</v>
@@ -5185,13 +5211,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5201,7 +5227,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B61" s="9">
         <v>46169.669327048614</v>
@@ -5213,16 +5239,16 @@
         <v>46209.908330949074</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I61" s="9">
         <v>46240</v>
@@ -5240,13 +5266,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q61" s="9">
         <v>46240</v>
@@ -5266,7 +5292,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B62" s="5">
         <v>46169.6693399537</v>
@@ -5278,16 +5304,16 @@
         <v>46195.95042396991</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I62" s="5">
         <v>46188</v>
@@ -5305,13 +5331,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5321,7 +5347,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B63" s="9">
         <v>46169.669361203705</v>
@@ -5331,16 +5357,16 @@
         <v>46174.84660805555</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I63" s="9">
         <v>46322</v>
@@ -5358,10 +5384,10 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P63" s="10" t="s">
         <v>26</v>
@@ -5379,12 +5405,12 @@
         <v>0</v>
       </c>
       <c r="U63" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B64" s="5">
         <v>46169.66936501158</v>
@@ -5394,16 +5420,16 @@
         <v>46174.846919421296</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I64" s="5">
         <v>46290</v>
@@ -5421,13 +5447,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5437,7 +5463,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B65" s="9">
         <v>46169.669418136575</v>
@@ -5449,7 +5475,7 @@
         <v>46210.65198340278</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>25</v>
@@ -5473,7 +5499,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P65" s="10" t="s">
         <v>26</v>
@@ -5490,7 +5516,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B66" s="5">
         <v>46169.66942685185</v>
@@ -5502,16 +5528,16 @@
         <v>46210.651395196764</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I66" s="5">
         <v>46258</v>
@@ -5529,13 +5555,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q66" s="5">
         <v>46258</v>
@@ -5555,7 +5581,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B67" s="9">
         <v>46169.669432361115</v>
@@ -5567,16 +5593,16 @@
         <v>46210.65197202546</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I67" s="9">
         <v>46260</v>
@@ -5594,13 +5620,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q67" s="9">
         <v>46260</v>
@@ -5620,7 +5646,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B68" s="5">
         <v>46169.66943836806</v>
@@ -5632,16 +5658,16 @@
         <v>46210.65139929398</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I68" s="5">
         <v>46258</v>
@@ -5659,13 +5685,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q68" s="5">
         <v>46258</v>
@@ -5685,7 +5711,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B69" s="9">
         <v>46169.669443692124</v>
@@ -5697,16 +5723,16 @@
         <v>46210.651975879635</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I69" s="9">
         <v>46260</v>
@@ -5724,13 +5750,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q69" s="9">
         <v>46260</v>
@@ -5750,7 +5776,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B70" s="5">
         <v>46169.669448368055</v>
@@ -5762,16 +5788,16 @@
         <v>46210.65141630787</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I70" s="5">
         <v>46258</v>
@@ -5789,13 +5815,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q70" s="5">
         <v>46258</v>
@@ -5815,7 +5841,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B71" s="9">
         <v>46169.66945298611</v>
@@ -5827,16 +5853,16 @@
         <v>46210.65197810185</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I71" s="9">
         <v>46260</v>
@@ -5854,13 +5880,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q71" s="9">
         <v>46260</v>
@@ -5880,7 +5906,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B72" s="5">
         <v>46169.66945778935</v>
@@ -5890,7 +5916,7 @@
         <v>46209.909264270835</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>25</v>
@@ -5914,7 +5940,7 @@
         <v>26</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>26</v>
@@ -5927,7 +5953,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B73" s="9">
         <v>46169.66946104167</v>
@@ -5939,16 +5965,16 @@
         <v>46209.90937729167</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I73" s="9">
         <v>46262</v>
@@ -5966,13 +5992,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q73" s="9">
         <v>46262</v>
@@ -5992,7 +6018,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B74" s="5">
         <v>46169.669467280095</v>
@@ -6004,16 +6030,16 @@
         <v>46210.65196928241</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I74" s="5">
         <v>46262</v>
@@ -6031,13 +6057,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6047,7 +6073,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B75" s="9">
         <v>46169.66950289352</v>
@@ -6057,16 +6083,16 @@
         <v>46209.90954123843</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I75" s="9">
         <v>46273</v>
@@ -6084,13 +6110,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q75" s="9">
         <v>46273</v>
@@ -6105,12 +6131,12 @@
         <v>0.1</v>
       </c>
       <c r="U75" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B76" s="5">
         <v>46169.66950758102</v>
@@ -6120,16 +6146,16 @@
         <v>46209.90937868056</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I76" s="5">
         <v>46273</v>
@@ -6147,13 +6173,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6163,7 +6189,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B77" s="9">
         <v>46169.66953380787</v>
@@ -6173,16 +6199,16 @@
         <v>46209.908330833336</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I77" s="9">
         <v>46294</v>
@@ -6200,13 +6226,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q77" s="9">
         <v>46294</v>
@@ -6221,12 +6247,12 @@
         <v>0</v>
       </c>
       <c r="U77" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B78" s="5">
         <v>46169.66953854167</v>
@@ -6236,16 +6262,16 @@
         <v>46197.84256122685</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -6261,13 +6287,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6277,7 +6303,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B79" s="9">
         <v>46169.66960108797</v>
@@ -6287,7 +6313,7 @@
         <v>46209.85402508102</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>25</v>
@@ -6311,7 +6337,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P79" s="10" t="s">
         <v>26</v>
@@ -6321,12 +6347,12 @@
       <c r="S79" s="10"/>
       <c r="T79" s="10"/>
       <c r="U79" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B80" s="5">
         <v>46169.66960956018</v>
@@ -6338,16 +6364,16 @@
         <v>46209.844928101855</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I80" s="5">
         <v>46174</v>
@@ -6365,13 +6391,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q80" s="5">
         <v>46174</v>
@@ -6380,7 +6406,7 @@
         <v>46174</v>
       </c>
       <c r="S80" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T80" s="6">
         <v>1</v>
@@ -6391,7 +6417,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B81" s="9">
         <v>46169.6696165162</v>
@@ -6403,16 +6429,16 @@
         <v>46209.84471936343</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I81" s="9">
         <v>46288</v>
@@ -6430,13 +6456,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q81" s="9">
         <v>46288</v>
@@ -6456,7 +6482,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B82" s="5">
         <v>46169.669622939815</v>
@@ -6468,16 +6494,16 @@
         <v>46209.85430440972</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I82" s="5">
         <v>46308</v>
@@ -6495,13 +6521,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q82" s="5">
         <v>46308</v>
@@ -6521,7 +6547,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B83" s="9">
         <v>46169.66962980324</v>
@@ -6531,16 +6557,16 @@
         <v>46204.86356525463</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I83" s="9">
         <v>46287</v>
@@ -6558,13 +6584,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q83" s="9">
         <v>46287</v>
@@ -6579,12 +6605,12 @@
         <v>0</v>
       </c>
       <c r="U83" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B84" s="5">
         <v>46169.669635185186</v>
@@ -6594,16 +6620,16 @@
         <v>46213.19847427083</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I84" s="5">
         <v>46220</v>
@@ -6621,13 +6647,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q84" s="5">
         <v>46220</v>
@@ -6636,18 +6662,18 @@
         <v>46220</v>
       </c>
       <c r="S84" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
       </c>
       <c r="U84" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B85" s="9">
         <v>46169.66964790509</v>
@@ -6657,7 +6683,7 @@
         <v>46209.84945282407</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>25</v>
@@ -6681,7 +6707,7 @@
         <v>26</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>26</v>
@@ -6694,7 +6720,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B86" s="5">
         <v>46169.66965109954</v>
@@ -6704,16 +6730,16 @@
         <v>46174.84790094907</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I86" s="5">
         <v>46294</v>
@@ -6731,13 +6757,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q86" s="5">
         <v>46294</v>
@@ -6752,12 +6778,12 @@
         <v>0</v>
       </c>
       <c r="U86" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B87" s="9">
         <v>46169.6696568287</v>
@@ -6767,16 +6793,16 @@
         <v>46174.84798839121</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I87" s="9">
         <v>46294</v>
@@ -6794,13 +6820,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6810,7 +6836,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B88" s="5">
         <v>46169.669688622685</v>
@@ -6822,16 +6848,16 @@
         <v>46209.8493094213</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I88" s="5">
         <v>46316</v>
@@ -6849,13 +6875,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q88" s="5">
         <v>46316</v>
@@ -6875,7 +6901,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B89" s="9">
         <v>46169.66969347223</v>
@@ -6885,16 +6911,16 @@
         <v>46209.84459753473</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I89" s="10"/>
       <c r="J89" s="9">
@@ -6910,13 +6936,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6926,7 +6952,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B90" s="5">
         <v>46169.66972681713</v>
@@ -6938,16 +6964,16 @@
         <v>46209.84946481482</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I90" s="5">
         <v>46317</v>
@@ -6965,13 +6991,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q90" s="5">
         <v>46317</v>
@@ -6991,7 +7017,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B91" s="9">
         <v>46169.66973180555</v>
@@ -7001,16 +7027,16 @@
         <v>46209.844891030094</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I91" s="9">
         <v>46317</v>
@@ -7028,13 +7054,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -7044,7 +7070,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B92" s="5">
         <v>46169.66981054399</v>
@@ -7054,16 +7080,16 @@
         <v>46174.8478909375</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I92" s="5">
         <v>46318</v>
@@ -7081,13 +7107,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q92" s="5">
         <v>46318</v>
@@ -7102,12 +7128,12 @@
         <v>0</v>
       </c>
       <c r="U92" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B93" s="9">
         <v>46169.66981724537</v>
@@ -7117,16 +7143,16 @@
         <v>46209.85401892361</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I93" s="9">
         <v>46318</v>
@@ -7144,13 +7170,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7160,7 +7186,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B94" s="5">
         <v>46169.669861041664</v>
@@ -7170,16 +7196,16 @@
         <v>46174.8478862037</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I94" s="5">
         <v>46321</v>
@@ -7197,13 +7223,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q94" s="5">
         <v>46321</v>
@@ -7218,12 +7244,12 @@
         <v>0</v>
       </c>
       <c r="U94" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B95" s="9">
         <v>46169.66986724537</v>
@@ -7233,16 +7259,16 @@
         <v>46174.84816675926</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I95" s="9">
         <v>46321</v>
@@ -7260,13 +7286,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7276,7 +7302,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B96" s="5">
         <v>46169.66990296297</v>
@@ -7286,16 +7312,16 @@
         <v>46174.84788545139</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I96" s="5">
         <v>46323</v>
@@ -7313,13 +7339,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q96" s="5">
         <v>46323</v>
@@ -7334,12 +7360,12 @@
         <v>0</v>
       </c>
       <c r="U96" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B97" s="9">
         <v>46169.66994555556</v>
@@ -7349,16 +7375,16 @@
         <v>46174.848269317125</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I97" s="10"/>
       <c r="J97" s="9">
@@ -7374,13 +7400,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7390,7 +7416,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B98" s="5">
         <v>46169.669978645834</v>
@@ -7400,7 +7426,7 @@
         <v>46174.82401747685</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>25</v>
@@ -7424,7 +7450,7 @@
         <v>26</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>26</v>
@@ -7437,7 +7463,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B99" s="9">
         <v>46169.66998244213</v>
@@ -7447,16 +7473,16 @@
         <v>46174.84843513889</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I99" s="9">
         <v>46324</v>
@@ -7474,13 +7500,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q99" s="9">
         <v>46324</v>
@@ -7495,12 +7521,12 @@
         <v>0</v>
       </c>
       <c r="U99" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B100" s="5">
         <v>46169.66998994213</v>
@@ -7510,16 +7536,16 @@
         <v>46174.84838837963</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I100" s="6"/>
       <c r="J100" s="5">
@@ -7535,13 +7561,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7551,7 +7577,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B101" s="9">
         <v>46170.63118891204</v>
@@ -7561,16 +7587,16 @@
         <v>46209.90833168982</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="9">
@@ -7586,13 +7612,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7602,7 +7628,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B102" s="5">
         <v>46174.820955891206</v>
@@ -7612,16 +7638,16 @@
         <v>46174.848381284726</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I102" s="5">
         <v>46324</v>
@@ -7639,13 +7665,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7655,7 +7681,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B103" s="9">
         <v>46169.670044224535</v>
@@ -7665,16 +7691,16 @@
         <v>46174.848558831014</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I103" s="10"/>
       <c r="J103" s="9">
@@ -7690,13 +7716,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q103" s="9">
         <v>46325</v>
@@ -7711,12 +7737,12 @@
         <v>0</v>
       </c>
       <c r="U103" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B104" s="5">
         <v>46169.670049050925</v>
@@ -7726,16 +7752,16 @@
         <v>46174.848527152775</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I104" s="6"/>
       <c r="J104" s="5">
@@ -7751,13 +7777,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7767,7 +7793,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B105" s="9">
         <v>46170.63213679398</v>
@@ -7777,16 +7803,16 @@
         <v>46174.848524270834</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I105" s="10"/>
       <c r="J105" s="9">
@@ -7802,13 +7828,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7818,7 +7844,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B106" s="5">
         <v>46174.82099290509</v>
@@ -7828,16 +7854,16 @@
         <v>46174.84852028935</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I106" s="5">
         <v>46325</v>
@@ -7855,13 +7881,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7871,7 +7897,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B107" s="9">
         <v>46169.67013976852</v>
@@ -7881,16 +7907,16 @@
         <v>46174.84870307871</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I107" s="10"/>
       <c r="J107" s="9">
@@ -7906,13 +7932,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q107" s="9">
         <v>46328</v>
@@ -7927,12 +7953,12 @@
         <v>0</v>
       </c>
       <c r="U107" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B108" s="5">
         <v>46169.670151377315</v>
@@ -7942,16 +7968,16 @@
         <v>46174.848669872685</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I108" s="5">
         <v>46328</v>
@@ -7969,13 +7995,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7985,7 +8011,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B109" s="9">
         <v>46170.63285997685</v>
@@ -7995,16 +8021,16 @@
         <v>46174.848667314815</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I109" s="9">
         <v>46328</v>
@@ -8022,13 +8048,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -8038,7 +8064,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B110" s="5">
         <v>46174.821024143515</v>
@@ -8048,16 +8074,16 @@
         <v>46174.84866336806</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I110" s="5">
         <v>46328</v>
@@ -8075,13 +8101,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8091,7 +8117,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B111" s="9">
         <v>46169.67021965278</v>
@@ -8101,16 +8127,16 @@
         <v>46174.84880980324</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I111" s="9">
         <v>46329</v>
@@ -8128,13 +8154,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q111" s="9">
         <v>46329</v>
@@ -8149,12 +8175,12 @@
         <v>0</v>
       </c>
       <c r="U111" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B112" s="5">
         <v>46169.67022677083</v>
@@ -8164,16 +8190,16 @@
         <v>46174.84878571759</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I112" s="6"/>
       <c r="J112" s="5">
@@ -8189,13 +8215,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8205,7 +8231,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B113" s="9">
         <v>46170.633581828704</v>
@@ -8215,16 +8241,16 @@
         <v>46174.84878314815</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I113" s="10"/>
       <c r="J113" s="9">
@@ -8240,10 +8266,10 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -8256,7 +8282,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B114" s="5">
         <v>46174.821057037036</v>
@@ -8266,16 +8292,16 @@
         <v>46174.84877914352</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I114" s="6"/>
       <c r="J114" s="5">
@@ -8291,10 +8317,10 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>26</v>
@@ -8307,7 +8333,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B115" s="9">
         <v>46169.67031616898</v>
@@ -8317,7 +8343,7 @@
         <v>46174.82401751158</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>25</v>
@@ -8341,7 +8367,7 @@
         <v>26</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P115" s="10" t="s">
         <v>26</v>
@@ -8354,7 +8380,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B116" s="5">
         <v>46169.67031976852</v>
@@ -8364,16 +8390,16 @@
         <v>46174.84885483797</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="I116" s="5">
         <v>46330</v>
@@ -8391,13 +8417,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q116" s="5">
         <v>46330</v>
@@ -8412,12 +8438,12 @@
         <v>0</v>
       </c>
       <c r="U116" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B117" s="9">
         <v>46169.6703253125</v>
@@ -8427,16 +8453,16 @@
         <v>46192.97339644676</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I117" s="9">
         <v>46330</v>
@@ -8454,13 +8480,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q117" s="9">
         <v>46330</v>
@@ -8475,12 +8501,12 @@
         <v>0</v>
       </c>
       <c r="U117" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B118" s="5">
         <v>46169.670332430556</v>
@@ -8490,7 +8516,7 @@
         <v>46174.82401726852</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>25</v>
@@ -8514,7 +8540,7 @@
         <v>26</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>26</v>
@@ -8528,12 +8554,12 @@
         <v>0</v>
       </c>
       <c r="U118" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B119" s="9">
         <v>46169.67033591435</v>
@@ -8543,16 +8569,16 @@
         <v>46174.848958703704</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I119" s="9">
         <v>46330</v>
@@ -8570,13 +8596,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q119" s="9">
         <v>46330</v>
@@ -8591,12 +8617,12 @@
         <v>0</v>
       </c>
       <c r="U119" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B120" s="5">
         <v>46169.67034748843</v>
@@ -8606,16 +8632,16 @@
         <v>46174.84895586806</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I120" s="5">
         <v>46339</v>
@@ -8633,13 +8659,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q120" s="5">
         <v>46339</v>
@@ -8654,7 +8680,7 @@
         <v>0</v>
       </c>
       <c r="U120" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1419" uniqueCount="364">
   <si>
     <t>50001558 -  GESVIAL</t>
   </si>
@@ -347,9 +347,6 @@
     <t>propuesta nucleo rodete</t>
   </si>
   <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
     <t>Propuesta compras:,Generación OC Rodete  ot 4342</t>
   </si>
   <si>
@@ -357,12 +354,6 @@
   </si>
   <si>
     <t>propuesta Corte Laser</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
   </si>
   <si>
     <t>check planos</t>
@@ -2843,11 +2834,9 @@
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H21" s="10"/>
       <c r="I21" s="9">
         <v>46167</v>
       </c>
@@ -2870,7 +2859,7 @@
         <v>74</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q21" s="9">
         <v>46167</v>
@@ -2890,7 +2879,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B22" s="5">
         <v>46169.66903233796</v>
@@ -2902,17 +2891,15 @@
         <v>46206.55341104166</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>96</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H22" s="6"/>
       <c r="I22" s="5">
         <v>46241</v>
       </c>
@@ -2932,10 +2919,10 @@
         <v>81</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="Q22" s="5">
         <v>46241</v>
@@ -2955,7 +2942,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B23" s="9">
         <v>46169.669037291664</v>
@@ -2967,17 +2954,15 @@
         <v>46197.644057592595</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>96</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H23" s="10"/>
       <c r="I23" s="9">
         <v>46241</v>
       </c>
@@ -2997,10 +2982,10 @@
         <v>81</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Q23" s="9">
         <v>46241</v>
@@ -3020,7 +3005,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B24" s="5">
         <v>46169.66904123843</v>
@@ -3032,17 +3017,15 @@
         <v>46197.64420756944</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>96</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H24" s="6"/>
       <c r="I24" s="5">
         <v>46241</v>
       </c>
@@ -3062,10 +3045,10 @@
         <v>81</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="Q24" s="5">
         <v>46241</v>
@@ -3085,7 +3068,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B25" s="9">
         <v>46169.66904511574</v>
@@ -3097,17 +3080,15 @@
         <v>46197.64487474537</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>96</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H25" s="10"/>
       <c r="I25" s="9">
         <v>46241</v>
       </c>
@@ -3127,10 +3108,10 @@
         <v>81</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="Q25" s="9">
         <v>46241</v>
@@ -3150,7 +3131,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B26" s="5">
         <v>46169.66904878472</v>
@@ -3162,7 +3143,7 @@
         <v>46195.60168921296</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -3195,7 +3176,7 @@
         <v>51</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="Q26" s="5">
         <v>46157</v>
@@ -3215,7 +3196,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B27" s="9">
         <v>46169.66883418981</v>
@@ -3225,7 +3206,7 @@
         <v>46209.82175228009</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>25</v>
@@ -3249,7 +3230,7 @@
         <v>26</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="P27" s="10" t="s">
         <v>26</v>
@@ -3259,12 +3240,12 @@
       <c r="S27" s="10"/>
       <c r="T27" s="10"/>
       <c r="U27" s="12" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B28" s="5">
         <v>46169.66908924768</v>
@@ -3276,16 +3257,16 @@
         <v>46182.63466408565</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I28" s="5">
         <v>46171</v>
@@ -3303,13 +3284,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="Q28" s="5">
         <v>46168</v>
@@ -3329,7 +3310,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B29" s="9">
         <v>46169.66909520833</v>
@@ -3341,16 +3322,16 @@
         <v>46182.63236322917</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I29" s="9">
         <v>46169</v>
@@ -3368,13 +3349,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="O29" s="10" t="s">
         <v>87</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3390,7 +3371,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B30" s="5">
         <v>46169.669100810184</v>
@@ -3402,16 +3383,16 @@
         <v>46182.63463722222</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I30" s="5">
         <v>46171</v>
@@ -3429,13 +3410,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3451,7 +3432,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B31" s="9">
         <v>46169.669106284724</v>
@@ -3463,16 +3444,16 @@
         <v>46182.63460042824</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I31" s="9">
         <v>46168</v>
@@ -3490,13 +3471,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="Q31" s="9">
         <v>46168</v>
@@ -3505,7 +3486,7 @@
         <v>46171</v>
       </c>
       <c r="S31" s="11" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="T31" s="10">
         <v>1</v>
@@ -3516,7 +3497,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B32" s="5">
         <v>46169.66911128472</v>
@@ -3528,16 +3509,16 @@
         <v>46182.6318109375</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I32" s="5">
         <v>46168</v>
@@ -3555,13 +3536,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>90</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3577,7 +3558,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B33" s="9">
         <v>46169.669116805555</v>
@@ -3589,16 +3570,16 @@
         <v>46182.63457327546</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I33" s="9">
         <v>46170</v>
@@ -3616,13 +3597,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3638,7 +3619,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B34" s="5">
         <v>46169.66912204861</v>
@@ -3650,16 +3631,16 @@
         <v>46182.6344355787</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I34" s="5">
         <v>46161</v>
@@ -3677,13 +3658,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="Q34" s="5">
         <v>46161</v>
@@ -3703,7 +3684,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B35" s="9">
         <v>46169.66912711806</v>
@@ -3715,16 +3696,16 @@
         <v>46182.63203959491</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I35" s="9">
         <v>46161</v>
@@ -3742,13 +3723,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="O35" s="10" t="s">
         <v>84</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3764,7 +3745,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B36" s="5">
         <v>46169.66913270833</v>
@@ -3776,16 +3757,16 @@
         <v>46182.634411203704</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I36" s="5">
         <v>46182</v>
@@ -3803,13 +3784,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="O36" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="O36" s="6" t="s">
-        <v>140</v>
-      </c>
       <c r="P36" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3825,7 +3806,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B37" s="9">
         <v>46169.66913809028</v>
@@ -3837,16 +3818,16 @@
         <v>46182.6343528588</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I37" s="9">
         <v>46182</v>
@@ -3864,13 +3845,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="O37" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="O37" s="10" t="s">
-        <v>140</v>
-      </c>
       <c r="P37" s="10" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3886,7 +3867,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B38" s="5">
         <v>46169.66914475695</v>
@@ -3896,16 +3877,16 @@
         <v>46212.17798137732</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I38" s="5">
         <v>46161</v>
@@ -3923,10 +3904,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3938,7 +3919,7 @@
         <v>46219</v>
       </c>
       <c r="S38" s="12" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="T38" s="6">
         <v>0</v>
@@ -3949,7 +3930,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B39" s="9">
         <v>46169.669149270834</v>
@@ -3961,16 +3942,16 @@
         <v>46195.68641299769</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I39" s="9">
         <v>46161</v>
@@ -3988,13 +3969,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -4004,7 +3985,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46169.66915408565</v>
@@ -4014,16 +3995,16 @@
         <v>46195.686418576384</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I40" s="5">
         <v>46171</v>
@@ -4041,13 +4022,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4057,7 +4038,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B41" s="9">
         <v>46169.66915865741</v>
@@ -4069,16 +4050,16 @@
         <v>46209.82174662037</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I41" s="9">
         <v>46245</v>
@@ -4096,13 +4077,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="Q41" s="9">
         <v>46245</v>
@@ -4122,7 +4103,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B42" s="5">
         <v>46169.66916377315</v>
@@ -4134,16 +4115,16 @@
         <v>46199.56927892361</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I42" s="5">
         <v>46245</v>
@@ -4161,13 +4142,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4183,7 +4164,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B43" s="9">
         <v>46169.66916960648</v>
@@ -4195,16 +4176,16 @@
         <v>46205.61247092593</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I43" s="9">
         <v>46247</v>
@@ -4222,13 +4203,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4244,7 +4225,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B44" s="5">
         <v>46169.66917503472</v>
@@ -4256,16 +4237,16 @@
         <v>46199.567282199074</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I44" s="5">
         <v>46245</v>
@@ -4283,10 +4264,10 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>26</v>
@@ -4309,7 +4290,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B45" s="9">
         <v>46169.669178888886</v>
@@ -4321,16 +4302,16 @@
         <v>46199.569896354165</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I45" s="9">
         <v>46245</v>
@@ -4348,13 +4329,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="O45" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="P45" s="10" t="s">
         <v>169</v>
-      </c>
-      <c r="O45" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="P45" s="10" t="s">
-        <v>172</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4364,7 +4345,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B46" s="5">
         <v>46169.669183680555</v>
@@ -4376,16 +4357,16 @@
         <v>46199.56984034722</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I46" s="5">
         <v>46247</v>
@@ -4403,13 +4384,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4419,7 +4400,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B47" s="9">
         <v>46169.66918849537</v>
@@ -4431,16 +4412,16 @@
         <v>46204.863616284725</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I47" s="9">
         <v>46245</v>
@@ -4458,10 +4439,10 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>26</v>
@@ -4484,7 +4465,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B48" s="5">
         <v>46169.66919252315</v>
@@ -4496,16 +4477,16 @@
         <v>46204.863510995376</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I48" s="5">
         <v>46245</v>
@@ -4523,13 +4504,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4539,7 +4520,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B49" s="9">
         <v>46169.66919734953</v>
@@ -4551,16 +4532,16 @@
         <v>46204.8635487037</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I49" s="9">
         <v>46254</v>
@@ -4578,13 +4559,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4594,7 +4575,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B50" s="5">
         <v>46169.66920229167</v>
@@ -4606,16 +4587,16 @@
         <v>46210.65313525463</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I50" s="5">
         <v>46286</v>
@@ -4633,10 +4614,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4649,7 +4630,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B51" s="9">
         <v>46169.66924202546</v>
@@ -4661,16 +4642,16 @@
         <v>46199.57084909722</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I51" s="9">
         <v>46245</v>
@@ -4688,10 +4669,10 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="P51" s="10" t="s">
         <v>26</v>
@@ -4714,7 +4695,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B52" s="5">
         <v>46169.66924635417</v>
@@ -4726,16 +4707,16 @@
         <v>46199.57078165509</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I52" s="5">
         <v>46245</v>
@@ -4753,13 +4734,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="O52" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="P52" s="6" t="s">
         <v>191</v>
-      </c>
-      <c r="O52" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="P52" s="6" t="s">
-        <v>194</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4769,7 +4750,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B53" s="9">
         <v>46169.66925091435</v>
@@ -4781,16 +4762,16 @@
         <v>46199.57082731482</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I53" s="9">
         <v>46247</v>
@@ -4808,13 +4789,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4824,7 +4805,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B54" s="5">
         <v>46169.669255659726</v>
@@ -4836,7 +4817,7 @@
         <v>46210.52487434028</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>25</v>
@@ -4860,7 +4841,7 @@
         <v>26</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -4877,7 +4858,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B55" s="9">
         <v>46169.66925896991</v>
@@ -4889,16 +4870,16 @@
         <v>46197.71564204861</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I55" s="9">
         <v>46167</v>
@@ -4910,19 +4891,19 @@
         <v>26</v>
       </c>
       <c r="L55" s="10" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="M55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="Q55" s="9">
         <v>46167</v>
@@ -4931,7 +4912,7 @@
         <v>46184</v>
       </c>
       <c r="S55" s="11" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="T55" s="10">
         <v>1</v>
@@ -4942,7 +4923,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B56" s="5">
         <v>46169.66926408565</v>
@@ -4954,16 +4935,16 @@
         <v>46195.94997940972</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I56" s="5">
         <v>46167</v>
@@ -4981,13 +4962,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4997,7 +4978,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B57" s="9">
         <v>46169.66926952546</v>
@@ -5009,16 +4990,16 @@
         <v>46195.94998958333</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I57" s="9">
         <v>46167</v>
@@ -5036,13 +5017,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="O57" s="10" t="s">
         <v>78</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -5052,7 +5033,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B58" s="5">
         <v>46169.66929263889</v>
@@ -5064,16 +5045,16 @@
         <v>46197.71567513889</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I58" s="5">
         <v>46220</v>
@@ -5091,13 +5072,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="Q58" s="5">
         <v>46220</v>
@@ -5117,7 +5098,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B59" s="9">
         <v>46169.66929775463</v>
@@ -5129,16 +5110,16 @@
         <v>46195.950096458335</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I59" s="9">
         <v>46181</v>
@@ -5156,13 +5137,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="O59" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="O59" s="10" t="s">
-        <v>219</v>
-      </c>
       <c r="P59" s="10" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5172,7 +5153,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B60" s="5">
         <v>46169.66930358796</v>
@@ -5184,16 +5165,16 @@
         <v>46196.87985491898</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I60" s="5">
         <v>46181</v>
@@ -5211,13 +5192,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5227,7 +5208,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B61" s="9">
         <v>46169.669327048614</v>
@@ -5239,16 +5220,16 @@
         <v>46209.908330949074</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I61" s="9">
         <v>46240</v>
@@ -5266,13 +5247,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="Q61" s="9">
         <v>46240</v>
@@ -5292,7 +5273,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B62" s="5">
         <v>46169.6693399537</v>
@@ -5304,16 +5285,16 @@
         <v>46195.95042396991</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I62" s="5">
         <v>46188</v>
@@ -5331,13 +5312,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5347,7 +5328,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B63" s="9">
         <v>46169.669361203705</v>
@@ -5357,16 +5338,16 @@
         <v>46174.84660805555</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I63" s="9">
         <v>46322</v>
@@ -5384,10 +5365,10 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="P63" s="10" t="s">
         <v>26</v>
@@ -5410,7 +5391,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B64" s="5">
         <v>46169.66936501158</v>
@@ -5420,16 +5401,16 @@
         <v>46174.846919421296</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I64" s="5">
         <v>46290</v>
@@ -5447,13 +5428,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5463,7 +5444,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B65" s="9">
         <v>46169.669418136575</v>
@@ -5475,7 +5456,7 @@
         <v>46210.65198340278</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>25</v>
@@ -5499,7 +5480,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="P65" s="10" t="s">
         <v>26</v>
@@ -5516,7 +5497,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B66" s="5">
         <v>46169.66942685185</v>
@@ -5528,16 +5509,16 @@
         <v>46210.651395196764</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="I66" s="5">
         <v>46258</v>
@@ -5555,13 +5536,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="Q66" s="5">
         <v>46258</v>
@@ -5581,7 +5562,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B67" s="9">
         <v>46169.669432361115</v>
@@ -5593,16 +5574,16 @@
         <v>46210.65197202546</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I67" s="9">
         <v>46260</v>
@@ -5620,13 +5601,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="Q67" s="9">
         <v>46260</v>
@@ -5646,7 +5627,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B68" s="5">
         <v>46169.66943836806</v>
@@ -5658,16 +5639,16 @@
         <v>46210.65139929398</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="I68" s="5">
         <v>46258</v>
@@ -5685,13 +5666,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Q68" s="5">
         <v>46258</v>
@@ -5711,7 +5692,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B69" s="9">
         <v>46169.669443692124</v>
@@ -5723,16 +5704,16 @@
         <v>46210.651975879635</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I69" s="9">
         <v>46260</v>
@@ -5750,13 +5731,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="Q69" s="9">
         <v>46260</v>
@@ -5776,7 +5757,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B70" s="5">
         <v>46169.669448368055</v>
@@ -5788,16 +5769,16 @@
         <v>46210.65141630787</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="I70" s="5">
         <v>46258</v>
@@ -5815,13 +5796,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="Q70" s="5">
         <v>46258</v>
@@ -5841,7 +5822,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B71" s="9">
         <v>46169.66945298611</v>
@@ -5853,16 +5834,16 @@
         <v>46210.65197810185</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I71" s="9">
         <v>46260</v>
@@ -5880,13 +5861,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="Q71" s="9">
         <v>46260</v>
@@ -5906,7 +5887,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B72" s="5">
         <v>46169.66945778935</v>
@@ -5916,7 +5897,7 @@
         <v>46209.909264270835</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>25</v>
@@ -5940,7 +5921,7 @@
         <v>26</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>26</v>
@@ -5953,7 +5934,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B73" s="9">
         <v>46169.66946104167</v>
@@ -5965,16 +5946,16 @@
         <v>46209.90937729167</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I73" s="9">
         <v>46262</v>
@@ -5992,13 +5973,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="Q73" s="9">
         <v>46262</v>
@@ -6018,7 +5999,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B74" s="5">
         <v>46169.669467280095</v>
@@ -6030,16 +6011,16 @@
         <v>46210.65196928241</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I74" s="5">
         <v>46262</v>
@@ -6057,13 +6038,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6073,7 +6054,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B75" s="9">
         <v>46169.66950289352</v>
@@ -6083,16 +6064,16 @@
         <v>46209.90954123843</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I75" s="9">
         <v>46273</v>
@@ -6110,13 +6091,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="Q75" s="9">
         <v>46273</v>
@@ -6131,12 +6112,12 @@
         <v>0.1</v>
       </c>
       <c r="U75" s="12" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B76" s="5">
         <v>46169.66950758102</v>
@@ -6146,16 +6127,16 @@
         <v>46209.90937868056</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I76" s="5">
         <v>46273</v>
@@ -6173,13 +6154,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="O76" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="P76" s="6" t="s">
         <v>265</v>
-      </c>
-      <c r="O76" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="P76" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6189,7 +6170,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B77" s="9">
         <v>46169.66953380787</v>
@@ -6199,16 +6180,16 @@
         <v>46209.908330833336</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I77" s="9">
         <v>46294</v>
@@ -6226,13 +6207,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="Q77" s="9">
         <v>46294</v>
@@ -6252,7 +6233,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B78" s="5">
         <v>46169.66953854167</v>
@@ -6262,16 +6243,16 @@
         <v>46197.84256122685</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -6287,13 +6268,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6303,7 +6284,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B79" s="9">
         <v>46169.66960108797</v>
@@ -6313,7 +6294,7 @@
         <v>46209.85402508102</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>25</v>
@@ -6337,7 +6318,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="P79" s="10" t="s">
         <v>26</v>
@@ -6347,12 +6328,12 @@
       <c r="S79" s="10"/>
       <c r="T79" s="10"/>
       <c r="U79" s="12" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B80" s="5">
         <v>46169.66960956018</v>
@@ -6364,16 +6345,16 @@
         <v>46209.844928101855</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="I80" s="5">
         <v>46174</v>
@@ -6391,13 +6372,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="Q80" s="5">
         <v>46174</v>
@@ -6406,7 +6387,7 @@
         <v>46174</v>
       </c>
       <c r="S80" s="11" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="T80" s="6">
         <v>1</v>
@@ -6417,7 +6398,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B81" s="9">
         <v>46169.6696165162</v>
@@ -6429,16 +6410,16 @@
         <v>46209.84471936343</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="I81" s="9">
         <v>46288</v>
@@ -6456,13 +6437,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="Q81" s="9">
         <v>46288</v>
@@ -6482,7 +6463,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B82" s="5">
         <v>46169.669622939815</v>
@@ -6494,16 +6475,16 @@
         <v>46209.85430440972</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="I82" s="5">
         <v>46308</v>
@@ -6521,13 +6502,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="Q82" s="5">
         <v>46308</v>
@@ -6547,7 +6528,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B83" s="9">
         <v>46169.66962980324</v>
@@ -6557,16 +6538,16 @@
         <v>46204.86356525463</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="I83" s="9">
         <v>46287</v>
@@ -6584,13 +6565,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Q83" s="9">
         <v>46287</v>
@@ -6605,12 +6586,12 @@
         <v>0</v>
       </c>
       <c r="U83" s="12" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B84" s="5">
         <v>46169.669635185186</v>
@@ -6626,10 +6607,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="I84" s="5">
         <v>46220</v>
@@ -6647,13 +6628,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="Q84" s="5">
         <v>46220</v>
@@ -6662,7 +6643,7 @@
         <v>46220</v>
       </c>
       <c r="S84" s="12" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
@@ -6673,7 +6654,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B85" s="9">
         <v>46169.66964790509</v>
@@ -6683,7 +6664,7 @@
         <v>46209.84945282407</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>25</v>
@@ -6707,7 +6688,7 @@
         <v>26</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>26</v>
@@ -6720,7 +6701,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B86" s="5">
         <v>46169.66965109954</v>
@@ -6730,17 +6711,15 @@
         <v>46174.84790094907</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H86" s="6"/>
       <c r="I86" s="5">
         <v>46294</v>
       </c>
@@ -6757,13 +6736,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="Q86" s="5">
         <v>46294</v>
@@ -6783,7 +6762,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B87" s="9">
         <v>46169.6696568287</v>
@@ -6793,17 +6772,15 @@
         <v>46174.84798839121</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H87" s="10"/>
       <c r="I87" s="9">
         <v>46294</v>
       </c>
@@ -6820,13 +6797,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="O87" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="O87" s="10" t="s">
-        <v>294</v>
-      </c>
       <c r="P87" s="10" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6836,7 +6813,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B88" s="5">
         <v>46169.669688622685</v>
@@ -6848,17 +6825,15 @@
         <v>46209.8493094213</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H88" s="6"/>
       <c r="I88" s="5">
         <v>46316</v>
       </c>
@@ -6875,13 +6850,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="Q88" s="5">
         <v>46316</v>
@@ -6901,7 +6876,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B89" s="9">
         <v>46169.66969347223</v>
@@ -6911,17 +6886,15 @@
         <v>46209.84459753473</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H89" s="10"/>
       <c r="I89" s="10"/>
       <c r="J89" s="9">
         <v>46316</v>
@@ -6936,13 +6909,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="O89" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="P89" s="10" t="s">
         <v>296</v>
-      </c>
-      <c r="O89" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="P89" s="10" t="s">
-        <v>299</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6952,7 +6925,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B90" s="5">
         <v>46169.66972681713</v>
@@ -6964,17 +6937,15 @@
         <v>46209.84946481482</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H90" s="6"/>
       <c r="I90" s="5">
         <v>46317</v>
       </c>
@@ -6991,13 +6962,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="Q90" s="5">
         <v>46317</v>
@@ -7017,7 +6988,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B91" s="9">
         <v>46169.66973180555</v>
@@ -7027,17 +6998,15 @@
         <v>46209.844891030094</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H91" s="10"/>
       <c r="I91" s="9">
         <v>46317</v>
       </c>
@@ -7054,13 +7023,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="O91" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="P91" s="10" t="s">
         <v>301</v>
-      </c>
-      <c r="O91" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="P91" s="10" t="s">
-        <v>304</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -7070,7 +7039,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B92" s="5">
         <v>46169.66981054399</v>
@@ -7080,17 +7049,15 @@
         <v>46174.8478909375</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H92" s="6"/>
       <c r="I92" s="5">
         <v>46318</v>
       </c>
@@ -7107,13 +7074,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="Q92" s="5">
         <v>46318</v>
@@ -7133,7 +7100,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B93" s="9">
         <v>46169.66981724537</v>
@@ -7143,17 +7110,15 @@
         <v>46209.85401892361</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H93" s="10"/>
       <c r="I93" s="9">
         <v>46318</v>
       </c>
@@ -7170,13 +7135,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="O93" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="P93" s="10" t="s">
         <v>306</v>
-      </c>
-      <c r="O93" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="P93" s="10" t="s">
-        <v>309</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7186,7 +7151,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B94" s="5">
         <v>46169.669861041664</v>
@@ -7196,17 +7161,15 @@
         <v>46174.8478862037</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H94" s="6"/>
       <c r="I94" s="5">
         <v>46321</v>
       </c>
@@ -7223,13 +7186,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="Q94" s="5">
         <v>46321</v>
@@ -7249,7 +7212,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B95" s="9">
         <v>46169.66986724537</v>
@@ -7259,17 +7222,15 @@
         <v>46174.84816675926</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="H95" s="10" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H95" s="10"/>
       <c r="I95" s="9">
         <v>46321</v>
       </c>
@@ -7286,13 +7247,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7302,7 +7263,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B96" s="5">
         <v>46169.66990296297</v>
@@ -7312,17 +7273,15 @@
         <v>46174.84788545139</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H96" s="6"/>
       <c r="I96" s="5">
         <v>46323</v>
       </c>
@@ -7339,13 +7298,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="Q96" s="5">
         <v>46323</v>
@@ -7365,7 +7324,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B97" s="9">
         <v>46169.66994555556</v>
@@ -7375,17 +7334,15 @@
         <v>46174.848269317125</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H97" s="10"/>
       <c r="I97" s="10"/>
       <c r="J97" s="9">
         <v>46323</v>
@@ -7400,13 +7357,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="O97" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="P97" s="10" t="s">
         <v>315</v>
-      </c>
-      <c r="O97" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="P97" s="10" t="s">
-        <v>318</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7416,7 +7373,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B98" s="5">
         <v>46169.669978645834</v>
@@ -7426,7 +7383,7 @@
         <v>46174.82401747685</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>25</v>
@@ -7450,7 +7407,7 @@
         <v>26</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>26</v>
@@ -7463,7 +7420,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B99" s="9">
         <v>46169.66998244213</v>
@@ -7473,16 +7430,16 @@
         <v>46174.84843513889</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="I99" s="9">
         <v>46324</v>
@@ -7500,13 +7457,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="Q99" s="9">
         <v>46324</v>
@@ -7526,7 +7483,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B100" s="5">
         <v>46169.66998994213</v>
@@ -7536,16 +7493,16 @@
         <v>46174.84838837963</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="I100" s="6"/>
       <c r="J100" s="5">
@@ -7561,13 +7518,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7577,7 +7534,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B101" s="9">
         <v>46170.63118891204</v>
@@ -7587,16 +7544,16 @@
         <v>46209.90833168982</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="9">
@@ -7612,13 +7569,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="O101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7628,7 +7585,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B102" s="5">
         <v>46174.820955891206</v>
@@ -7644,10 +7601,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="I102" s="5">
         <v>46324</v>
@@ -7665,13 +7622,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7681,7 +7638,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B103" s="9">
         <v>46169.670044224535</v>
@@ -7691,17 +7648,15 @@
         <v>46174.848558831014</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="H103" s="10" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H103" s="10"/>
       <c r="I103" s="10"/>
       <c r="J103" s="9">
         <v>46325</v>
@@ -7716,13 +7671,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="Q103" s="9">
         <v>46325</v>
@@ -7742,7 +7697,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B104" s="5">
         <v>46169.670049050925</v>
@@ -7752,17 +7707,15 @@
         <v>46174.848527152775</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H104" s="6"/>
       <c r="I104" s="6"/>
       <c r="J104" s="5">
         <v>46325</v>
@@ -7777,13 +7730,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7793,7 +7746,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B105" s="9">
         <v>46170.63213679398</v>
@@ -7803,17 +7756,15 @@
         <v>46174.848524270834</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="H105" s="10" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H105" s="10"/>
       <c r="I105" s="10"/>
       <c r="J105" s="9">
         <v>46325</v>
@@ -7828,13 +7779,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7844,7 +7795,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B106" s="5">
         <v>46174.82099290509</v>
@@ -7854,17 +7805,15 @@
         <v>46174.84852028935</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H106" s="6"/>
       <c r="I106" s="5">
         <v>46325</v>
       </c>
@@ -7881,7 +7830,7 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>63</v>
@@ -7897,7 +7846,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B107" s="9">
         <v>46169.67013976852</v>
@@ -7907,16 +7856,16 @@
         <v>46174.84870307871</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I107" s="10"/>
       <c r="J107" s="9">
@@ -7932,13 +7881,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="Q107" s="9">
         <v>46328</v>
@@ -7958,7 +7907,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B108" s="5">
         <v>46169.670151377315</v>
@@ -7968,16 +7917,16 @@
         <v>46174.848669872685</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I108" s="5">
         <v>46328</v>
@@ -7995,13 +7944,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8011,7 +7960,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B109" s="9">
         <v>46170.63285997685</v>
@@ -8021,16 +7970,16 @@
         <v>46174.848667314815</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I109" s="9">
         <v>46328</v>
@@ -8048,13 +7997,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -8064,7 +8013,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B110" s="5">
         <v>46174.821024143515</v>
@@ -8080,10 +8029,10 @@
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I110" s="5">
         <v>46328</v>
@@ -8101,10 +8050,10 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>63</v>
@@ -8117,7 +8066,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B111" s="9">
         <v>46169.67021965278</v>
@@ -8127,16 +8076,16 @@
         <v>46174.84880980324</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I111" s="9">
         <v>46329</v>
@@ -8154,13 +8103,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="Q111" s="9">
         <v>46329</v>
@@ -8180,7 +8129,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B112" s="5">
         <v>46169.67022677083</v>
@@ -8190,16 +8139,16 @@
         <v>46174.84878571759</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I112" s="6"/>
       <c r="J112" s="5">
@@ -8215,13 +8164,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8231,7 +8180,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B113" s="9">
         <v>46170.633581828704</v>
@@ -8241,16 +8190,16 @@
         <v>46174.84878314815</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I113" s="10"/>
       <c r="J113" s="9">
@@ -8266,10 +8215,10 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -8282,7 +8231,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B114" s="5">
         <v>46174.821057037036</v>
@@ -8298,10 +8247,10 @@
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I114" s="6"/>
       <c r="J114" s="5">
@@ -8317,7 +8266,7 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>63</v>
@@ -8333,7 +8282,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B115" s="9">
         <v>46169.67031616898</v>
@@ -8343,7 +8292,7 @@
         <v>46174.82401751158</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>25</v>
@@ -8367,7 +8316,7 @@
         <v>26</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="P115" s="10" t="s">
         <v>26</v>
@@ -8380,7 +8329,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B116" s="5">
         <v>46169.67031976852</v>
@@ -8390,16 +8339,16 @@
         <v>46174.84885483797</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="I116" s="5">
         <v>46330</v>
@@ -8417,13 +8366,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="Q116" s="5">
         <v>46330</v>
@@ -8443,7 +8392,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B117" s="9">
         <v>46169.6703253125</v>
@@ -8453,7 +8402,7 @@
         <v>46192.97339644676</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8480,13 +8429,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="Q117" s="9">
         <v>46330</v>
@@ -8506,7 +8455,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B118" s="5">
         <v>46169.670332430556</v>
@@ -8516,7 +8465,7 @@
         <v>46174.82401726852</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>25</v>
@@ -8540,7 +8489,7 @@
         <v>26</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>26</v>
@@ -8559,7 +8508,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B119" s="9">
         <v>46169.67033591435</v>
@@ -8569,7 +8518,7 @@
         <v>46174.848958703704</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8596,13 +8545,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="Q119" s="9">
         <v>46330</v>
@@ -8622,7 +8571,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B120" s="5">
         <v>46169.67034748843</v>
@@ -8632,7 +8581,7 @@
         <v>46174.84895586806</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8659,13 +8608,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="O120" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="O120" s="6" t="s">
-        <v>363</v>
-      </c>
       <c r="P120" s="6" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="Q120" s="5">
         <v>46339</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -3874,7 +3874,7 @@
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46212.17798137732</v>
+        <v>46219.16855451389</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>146</v>
@@ -3992,7 +3992,7 @@
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46195.686418576384</v>
+        <v>46219.16855109954</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>152</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -251,6 +251,9 @@
     <t xml:space="preserve">Coordinacion Entrega con Cliente,Ingenieria Servicios </t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>Tarea sin iniciar</t>
   </si>
   <si>
@@ -516,9 +519,6 @@
   </si>
   <si>
     <t xml:space="preserve">Generación OC   ot 4343 ,fabricación tableros   ot 4343 </t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1215174084296068</t>
@@ -1234,12 +1234,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFe8384f"/>
+        <fgColor rgb="FFeec300"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFeec300"/>
+        <fgColor rgb="FFe8384f"/>
       </patternFill>
     </fill>
   </fills>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46174.82117752315</v>
+        <v>46220.18415443287</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -2320,19 +2320,19 @@
       <c r="R12" s="5">
         <v>46227</v>
       </c>
-      <c r="S12" s="7" t="s">
-        <v>33</v>
+      <c r="S12" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T12" s="6">
         <v>0</v>
       </c>
-      <c r="U12" s="11" t="s">
-        <v>61</v>
+      <c r="U12" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B13" s="9">
         <v>46169.668971666666</v>
@@ -2342,7 +2342,7 @@
         <v>46191.686801284726</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>26</v>
@@ -2375,7 +2375,7 @@
         <v>59</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q13" s="10"/>
       <c r="R13" s="10"/>
@@ -2385,7 +2385,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B14" s="5">
         <v>46169.66882583333</v>
@@ -2397,7 +2397,7 @@
         <v>46212.79378054398</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>25</v>
@@ -2421,7 +2421,7 @@
         <v>26</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P14" s="6" t="s">
         <v>26</v>
@@ -2438,7 +2438,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B15" s="9">
         <v>46169.66899085648</v>
@@ -2450,16 +2450,16 @@
         <v>46192.97339646991</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I15" s="9">
         <v>46155</v>
@@ -2471,19 +2471,19 @@
         <v>26</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M15" s="10" t="s">
         <v>26</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O15" s="10" t="s">
         <v>41</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q15" s="9">
         <v>46155</v>
@@ -2503,7 +2503,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B16" s="5">
         <v>46169.66899618055</v>
@@ -2515,16 +2515,16 @@
         <v>46192.97339646991</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I16" s="5">
         <v>46155</v>
@@ -2536,19 +2536,19 @@
         <v>26</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>41</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q16" s="5">
         <v>46155</v>
@@ -2568,7 +2568,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B17" s="9">
         <v>46169.669002106486</v>
@@ -2580,16 +2580,16 @@
         <v>46192.97339675926</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I17" s="9">
         <v>46155</v>
@@ -2607,13 +2607,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O17" s="10" t="s">
         <v>41</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q17" s="9">
         <v>46155</v>
@@ -2633,7 +2633,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B18" s="5">
         <v>46169.66883001158</v>
@@ -2645,7 +2645,7 @@
         <v>46197.64488530092</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>25</v>
@@ -2669,7 +2669,7 @@
         <v>26</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P18" s="6" t="s">
         <v>26</v>
@@ -2686,7 +2686,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B19" s="9">
         <v>46169.669016053245</v>
@@ -2698,16 +2698,16 @@
         <v>46181.636840625</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I19" s="9">
         <v>46157</v>
@@ -2725,13 +2725,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q19" s="9">
         <v>46157</v>
@@ -2751,7 +2751,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B20" s="5">
         <v>46169.669021423615</v>
@@ -2763,16 +2763,16 @@
         <v>46181.636847222224</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I20" s="5">
         <v>46167</v>
@@ -2790,13 +2790,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q20" s="5">
         <v>46167</v>
@@ -2816,7 +2816,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B21" s="9">
         <v>46169.66902680555</v>
@@ -2828,7 +2828,7 @@
         <v>46181.636854895834</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
@@ -2853,13 +2853,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q21" s="9">
         <v>46167</v>
@@ -2879,7 +2879,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B22" s="5">
         <v>46169.66903233796</v>
@@ -2891,7 +2891,7 @@
         <v>46206.55341104166</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -2916,13 +2916,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q22" s="5">
         <v>46241</v>
@@ -2942,7 +2942,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B23" s="9">
         <v>46169.669037291664</v>
@@ -2954,7 +2954,7 @@
         <v>46197.644057592595</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
@@ -2979,13 +2979,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q23" s="9">
         <v>46241</v>
@@ -3005,7 +3005,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B24" s="5">
         <v>46169.66904123843</v>
@@ -3017,7 +3017,7 @@
         <v>46197.64420756944</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -3042,13 +3042,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q24" s="5">
         <v>46241</v>
@@ -3068,7 +3068,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B25" s="9">
         <v>46169.66904511574</v>
@@ -3080,7 +3080,7 @@
         <v>46197.64487474537</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
@@ -3105,13 +3105,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q25" s="9">
         <v>46241</v>
@@ -3131,7 +3131,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B26" s="5">
         <v>46169.66904878472</v>
@@ -3143,16 +3143,16 @@
         <v>46195.60168921296</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I26" s="5">
         <v>46157</v>
@@ -3170,13 +3170,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>51</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q26" s="5">
         <v>46157</v>
@@ -3196,7 +3196,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B27" s="9">
         <v>46169.66883418981</v>
@@ -3206,7 +3206,7 @@
         <v>46209.82175228009</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>25</v>
@@ -3230,7 +3230,7 @@
         <v>26</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P27" s="10" t="s">
         <v>26</v>
@@ -3239,13 +3239,13 @@
       <c r="R27" s="10"/>
       <c r="S27" s="10"/>
       <c r="T27" s="10"/>
-      <c r="U27" s="12" t="s">
-        <v>111</v>
+      <c r="U27" s="11" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B28" s="5">
         <v>46169.66908924768</v>
@@ -3257,16 +3257,16 @@
         <v>46182.63466408565</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I28" s="5">
         <v>46171</v>
@@ -3284,13 +3284,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q28" s="5">
         <v>46168</v>
@@ -3310,7 +3310,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B29" s="9">
         <v>46169.66909520833</v>
@@ -3322,16 +3322,16 @@
         <v>46182.63236322917</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I29" s="9">
         <v>46169</v>
@@ -3349,13 +3349,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3365,13 +3365,13 @@
       <c r="T29" s="10">
         <v>0</v>
       </c>
-      <c r="U29" s="11" t="s">
-        <v>61</v>
+      <c r="U29" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B30" s="5">
         <v>46169.669100810184</v>
@@ -3383,16 +3383,16 @@
         <v>46182.63463722222</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I30" s="5">
         <v>46171</v>
@@ -3410,13 +3410,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3426,13 +3426,13 @@
       <c r="T30" s="6">
         <v>0</v>
       </c>
-      <c r="U30" s="11" t="s">
-        <v>61</v>
+      <c r="U30" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B31" s="9">
         <v>46169.669106284724</v>
@@ -3444,16 +3444,16 @@
         <v>46182.63460042824</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I31" s="9">
         <v>46168</v>
@@ -3471,13 +3471,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q31" s="9">
         <v>46168</v>
@@ -3485,8 +3485,8 @@
       <c r="R31" s="9">
         <v>46171</v>
       </c>
-      <c r="S31" s="11" t="s">
-        <v>126</v>
+      <c r="S31" s="12" t="s">
+        <v>127</v>
       </c>
       <c r="T31" s="10">
         <v>1</v>
@@ -3497,7 +3497,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B32" s="5">
         <v>46169.66911128472</v>
@@ -3509,16 +3509,16 @@
         <v>46182.6318109375</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I32" s="5">
         <v>46168</v>
@@ -3536,13 +3536,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3552,13 +3552,13 @@
       <c r="T32" s="6">
         <v>0</v>
       </c>
-      <c r="U32" s="11" t="s">
-        <v>61</v>
+      <c r="U32" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B33" s="9">
         <v>46169.669116805555</v>
@@ -3570,16 +3570,16 @@
         <v>46182.63457327546</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I33" s="9">
         <v>46170</v>
@@ -3597,13 +3597,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3613,13 +3613,13 @@
       <c r="T33" s="10">
         <v>0</v>
       </c>
-      <c r="U33" s="11" t="s">
-        <v>61</v>
+      <c r="U33" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B34" s="5">
         <v>46169.66912204861</v>
@@ -3631,16 +3631,16 @@
         <v>46182.6344355787</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I34" s="5">
         <v>46161</v>
@@ -3658,13 +3658,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q34" s="5">
         <v>46161</v>
@@ -3684,7 +3684,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B35" s="9">
         <v>46169.66912711806</v>
@@ -3696,16 +3696,16 @@
         <v>46182.63203959491</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I35" s="9">
         <v>46161</v>
@@ -3723,13 +3723,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3739,13 +3739,13 @@
       <c r="T35" s="10">
         <v>0</v>
       </c>
-      <c r="U35" s="11" t="s">
-        <v>61</v>
+      <c r="U35" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B36" s="5">
         <v>46169.66913270833</v>
@@ -3757,16 +3757,16 @@
         <v>46182.634411203704</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I36" s="5">
         <v>46182</v>
@@ -3784,13 +3784,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3800,13 +3800,13 @@
       <c r="T36" s="6">
         <v>0</v>
       </c>
-      <c r="U36" s="11" t="s">
-        <v>61</v>
+      <c r="U36" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B37" s="9">
         <v>46169.66913809028</v>
@@ -3818,16 +3818,16 @@
         <v>46182.6343528588</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I37" s="9">
         <v>46182</v>
@@ -3845,13 +3845,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3861,32 +3861,32 @@
       <c r="T37" s="10">
         <v>0</v>
       </c>
-      <c r="U37" s="11" t="s">
-        <v>61</v>
+      <c r="U37" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B38" s="5">
         <v>46169.66914475695</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46219.16855451389</v>
+        <v>46220.19404127315</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I38" s="5">
         <v>46161</v>
@@ -3904,10 +3904,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3919,13 +3919,13 @@
         <v>46219</v>
       </c>
       <c r="S38" s="12" t="s">
-        <v>148</v>
+        <v>127</v>
       </c>
       <c r="T38" s="6">
         <v>0</v>
       </c>
-      <c r="U38" s="11" t="s">
-        <v>61</v>
+      <c r="U38" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
@@ -3942,16 +3942,16 @@
         <v>46195.68641299769</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I39" s="9">
         <v>46161</v>
@@ -3969,10 +3969,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>150</v>
@@ -4001,10 +4001,10 @@
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I40" s="5">
         <v>46171</v>
@@ -4022,10 +4022,10 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>153</v>
@@ -4077,13 +4077,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O41" s="10" t="s">
         <v>158</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q41" s="9">
         <v>46245</v>
@@ -4145,7 +4145,7 @@
         <v>155</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>161</v>
@@ -4158,8 +4158,8 @@
       <c r="T42" s="6">
         <v>0</v>
       </c>
-      <c r="U42" s="11" t="s">
-        <v>61</v>
+      <c r="U42" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
@@ -4219,8 +4219,8 @@
       <c r="T43" s="10">
         <v>0</v>
       </c>
-      <c r="U43" s="11" t="s">
-        <v>61</v>
+      <c r="U43" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -4264,7 +4264,7 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>167</v>
@@ -4302,7 +4302,7 @@
         <v>46199.569896354165</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
@@ -4332,7 +4332,7 @@
         <v>166</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P45" s="10" t="s">
         <v>169</v>
@@ -4387,7 +4387,7 @@
         <v>166</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>172</v>
@@ -4439,7 +4439,7 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>177</v>
@@ -4477,7 +4477,7 @@
         <v>46204.863510995376</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
@@ -4507,7 +4507,7 @@
         <v>174</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>179</v>
@@ -4562,7 +4562,7 @@
         <v>174</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>182</v>
@@ -4669,7 +4669,7 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O51" s="10" t="s">
         <v>189</v>
@@ -4707,7 +4707,7 @@
         <v>46199.57078165509</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -4737,7 +4737,7 @@
         <v>188</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>191</v>
@@ -4792,7 +4792,7 @@
         <v>188</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>194</v>
@@ -4911,8 +4911,8 @@
       <c r="R55" s="9">
         <v>46184</v>
       </c>
-      <c r="S55" s="11" t="s">
-        <v>126</v>
+      <c r="S55" s="12" t="s">
+        <v>127</v>
       </c>
       <c r="T55" s="10">
         <v>1</v>
@@ -4965,7 +4965,7 @@
         <v>199</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>208</v>
@@ -5020,7 +5020,7 @@
         <v>199</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>211</v>
@@ -5220,7 +5220,7 @@
         <v>46209.908330949074</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
@@ -5312,13 +5312,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>205</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5385,8 +5385,8 @@
       <c r="T63" s="10">
         <v>0</v>
       </c>
-      <c r="U63" s="11" t="s">
-        <v>61</v>
+      <c r="U63" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
@@ -6111,8 +6111,8 @@
       <c r="T75" s="10">
         <v>0.1</v>
       </c>
-      <c r="U75" s="12" t="s">
-        <v>111</v>
+      <c r="U75" s="11" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -6227,8 +6227,8 @@
       <c r="T77" s="10">
         <v>0</v>
       </c>
-      <c r="U77" s="11" t="s">
-        <v>61</v>
+      <c r="U77" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
@@ -6327,8 +6327,8 @@
       <c r="R79" s="10"/>
       <c r="S79" s="10"/>
       <c r="T79" s="10"/>
-      <c r="U79" s="12" t="s">
-        <v>111</v>
+      <c r="U79" s="11" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
@@ -6375,7 +6375,7 @@
         <v>230</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>240</v>
@@ -6386,8 +6386,8 @@
       <c r="R80" s="5">
         <v>46174</v>
       </c>
-      <c r="S80" s="11" t="s">
-        <v>126</v>
+      <c r="S80" s="12" t="s">
+        <v>127</v>
       </c>
       <c r="T80" s="6">
         <v>1</v>
@@ -6440,7 +6440,7 @@
         <v>230</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P81" s="10" t="s">
         <v>276</v>
@@ -6505,7 +6505,7 @@
         <v>230</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>276</v>
@@ -6585,8 +6585,8 @@
       <c r="T83" s="10">
         <v>0</v>
       </c>
-      <c r="U83" s="12" t="s">
-        <v>111</v>
+      <c r="U83" s="11" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
@@ -6598,7 +6598,7 @@
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46213.19847427083</v>
+        <v>46220.16920412037</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>59</v>
@@ -6642,14 +6642,14 @@
       <c r="R84" s="5">
         <v>46220</v>
       </c>
-      <c r="S84" s="12" t="s">
-        <v>148</v>
+      <c r="S84" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
       </c>
-      <c r="U84" s="11" t="s">
-        <v>61</v>
+      <c r="U84" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6756,8 +6756,8 @@
       <c r="T86" s="6">
         <v>0</v>
       </c>
-      <c r="U86" s="11" t="s">
-        <v>61</v>
+      <c r="U86" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
@@ -7094,8 +7094,8 @@
       <c r="T92" s="6">
         <v>0</v>
       </c>
-      <c r="U92" s="11" t="s">
-        <v>61</v>
+      <c r="U92" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
@@ -7206,8 +7206,8 @@
       <c r="T94" s="6">
         <v>0</v>
       </c>
-      <c r="U94" s="11" t="s">
-        <v>61</v>
+      <c r="U94" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -7318,8 +7318,8 @@
       <c r="T96" s="6">
         <v>0</v>
       </c>
-      <c r="U96" s="11" t="s">
-        <v>61</v>
+      <c r="U96" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
@@ -7477,8 +7477,8 @@
       <c r="T99" s="10">
         <v>0</v>
       </c>
-      <c r="U99" s="11" t="s">
-        <v>61</v>
+      <c r="U99" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
@@ -7595,7 +7595,7 @@
         <v>46174.848381284726</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7625,7 +7625,7 @@
         <v>320</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>328</v>
@@ -7691,8 +7691,8 @@
       <c r="T103" s="10">
         <v>0</v>
       </c>
-      <c r="U103" s="11" t="s">
-        <v>61</v>
+      <c r="U103" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
@@ -7833,10 +7833,10 @@
         <v>330</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7901,8 +7901,8 @@
       <c r="T107" s="10">
         <v>0</v>
       </c>
-      <c r="U107" s="11" t="s">
-        <v>61</v>
+      <c r="U107" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
@@ -8023,7 +8023,7 @@
         <v>46174.84866336806</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8056,7 +8056,7 @@
         <v>328</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8123,8 +8123,8 @@
       <c r="T111" s="10">
         <v>0</v>
       </c>
-      <c r="U111" s="11" t="s">
-        <v>61</v>
+      <c r="U111" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
@@ -8241,7 +8241,7 @@
         <v>46174.84877914352</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8269,7 +8269,7 @@
         <v>342</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>26</v>
@@ -8386,8 +8386,8 @@
       <c r="T116" s="6">
         <v>0</v>
       </c>
-      <c r="U116" s="11" t="s">
-        <v>61</v>
+      <c r="U116" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
@@ -8408,10 +8408,10 @@
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I117" s="9">
         <v>46330</v>
@@ -8449,8 +8449,8 @@
       <c r="T117" s="10">
         <v>0</v>
       </c>
-      <c r="U117" s="11" t="s">
-        <v>61</v>
+      <c r="U117" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
@@ -8502,8 +8502,8 @@
       <c r="T118" s="6">
         <v>0</v>
       </c>
-      <c r="U118" s="11" t="s">
-        <v>61</v>
+      <c r="U118" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
@@ -8565,8 +8565,8 @@
       <c r="T119" s="10">
         <v>0</v>
       </c>
-      <c r="U119" s="11" t="s">
-        <v>61</v>
+      <c r="U119" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
@@ -8628,8 +8628,8 @@
       <c r="T120" s="6">
         <v>0</v>
       </c>
-      <c r="U120" s="11" t="s">
-        <v>61</v>
+      <c r="U120" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -6598,7 +6598,7 @@
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46220.16920412037</v>
+        <v>46221.186868703706</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>59</v>
@@ -6642,8 +6642,8 @@
       <c r="R84" s="5">
         <v>46220</v>
       </c>
-      <c r="S84" s="11" t="s">
-        <v>61</v>
+      <c r="S84" s="12" t="s">
+        <v>127</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1419" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1438" uniqueCount="365">
   <si>
     <t>50001558 -  GESVIAL</t>
   </si>
@@ -348,6 +348,9 @@
   </si>
   <si>
     <t>propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
   </si>
   <si>
     <t>Propuesta compras:,Generación OC Rodete  ot 4342</t>
@@ -2825,7 +2828,7 @@
         <v>46181.63683986111</v>
       </c>
       <c r="D21" s="9">
-        <v>46181.636854895834</v>
+        <v>46223.56754458333</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>91</v>
@@ -2834,9 +2837,11 @@
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H21" s="10"/>
+        <v>92</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>92</v>
+      </c>
       <c r="I21" s="9">
         <v>46167</v>
       </c>
@@ -2859,7 +2864,7 @@
         <v>75</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q21" s="9">
         <v>46167</v>
@@ -2879,7 +2884,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B22" s="5">
         <v>46169.66903233796</v>
@@ -2888,18 +2893,20 @@
         <v>46197.64318571759</v>
       </c>
       <c r="D22" s="5">
-        <v>46206.55341104166</v>
+        <v>46223.567540601856</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H22" s="6"/>
+        <v>92</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>92</v>
+      </c>
       <c r="I22" s="5">
         <v>46241</v>
       </c>
@@ -2919,10 +2926,10 @@
         <v>82</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q22" s="5">
         <v>46241</v>
@@ -2942,7 +2949,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B23" s="9">
         <v>46169.669037291664</v>
@@ -2951,18 +2958,20 @@
         <v>46197.64404108796</v>
       </c>
       <c r="D23" s="9">
-        <v>46197.644057592595</v>
+        <v>46223.5675370949</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H23" s="10"/>
+        <v>92</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>92</v>
+      </c>
       <c r="I23" s="9">
         <v>46241</v>
       </c>
@@ -2982,10 +2991,10 @@
         <v>82</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q23" s="9">
         <v>46241</v>
@@ -3005,7 +3014,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B24" s="5">
         <v>46169.66904123843</v>
@@ -3014,18 +3023,20 @@
         <v>46197.64418927083</v>
       </c>
       <c r="D24" s="5">
-        <v>46197.64420756944</v>
+        <v>46223.567533877314</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H24" s="6"/>
+        <v>92</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>92</v>
+      </c>
       <c r="I24" s="5">
         <v>46241</v>
       </c>
@@ -3045,10 +3056,10 @@
         <v>82</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q24" s="5">
         <v>46241</v>
@@ -3068,7 +3079,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B25" s="9">
         <v>46169.66904511574</v>
@@ -3077,18 +3088,20 @@
         <v>46197.644859120366</v>
       </c>
       <c r="D25" s="9">
-        <v>46197.64487474537</v>
+        <v>46223.56752888889</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H25" s="10"/>
+        <v>92</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>92</v>
+      </c>
       <c r="I25" s="9">
         <v>46241</v>
       </c>
@@ -3108,10 +3121,10 @@
         <v>82</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q25" s="9">
         <v>46241</v>
@@ -3131,7 +3144,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B26" s="5">
         <v>46169.66904878472</v>
@@ -3143,7 +3156,7 @@
         <v>46195.60168921296</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -3176,7 +3189,7 @@
         <v>51</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q26" s="5">
         <v>46157</v>
@@ -3196,7 +3209,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B27" s="9">
         <v>46169.66883418981</v>
@@ -3206,7 +3219,7 @@
         <v>46209.82175228009</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>25</v>
@@ -3230,7 +3243,7 @@
         <v>26</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P27" s="10" t="s">
         <v>26</v>
@@ -3240,12 +3253,12 @@
       <c r="S27" s="10"/>
       <c r="T27" s="10"/>
       <c r="U27" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B28" s="5">
         <v>46169.66908924768</v>
@@ -3257,16 +3270,16 @@
         <v>46182.63466408565</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I28" s="5">
         <v>46171</v>
@@ -3284,13 +3297,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q28" s="5">
         <v>46168</v>
@@ -3310,7 +3323,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B29" s="9">
         <v>46169.66909520833</v>
@@ -3322,16 +3335,16 @@
         <v>46182.63236322917</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I29" s="9">
         <v>46169</v>
@@ -3349,13 +3362,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O29" s="10" t="s">
         <v>88</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3371,7 +3384,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B30" s="5">
         <v>46169.669100810184</v>
@@ -3383,16 +3396,16 @@
         <v>46182.63463722222</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I30" s="5">
         <v>46171</v>
@@ -3410,13 +3423,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3432,7 +3445,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B31" s="9">
         <v>46169.669106284724</v>
@@ -3444,16 +3457,16 @@
         <v>46182.63460042824</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I31" s="9">
         <v>46168</v>
@@ -3471,13 +3484,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q31" s="9">
         <v>46168</v>
@@ -3486,7 +3499,7 @@
         <v>46171</v>
       </c>
       <c r="S31" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T31" s="10">
         <v>1</v>
@@ -3497,7 +3510,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B32" s="5">
         <v>46169.66911128472</v>
@@ -3509,16 +3522,16 @@
         <v>46182.6318109375</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I32" s="5">
         <v>46168</v>
@@ -3536,13 +3549,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>91</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3558,7 +3571,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B33" s="9">
         <v>46169.669116805555</v>
@@ -3570,16 +3583,16 @@
         <v>46182.63457327546</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I33" s="9">
         <v>46170</v>
@@ -3597,13 +3610,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3619,7 +3632,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B34" s="5">
         <v>46169.66912204861</v>
@@ -3631,16 +3644,16 @@
         <v>46182.6344355787</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I34" s="5">
         <v>46161</v>
@@ -3658,13 +3671,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q34" s="5">
         <v>46161</v>
@@ -3684,7 +3697,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B35" s="9">
         <v>46169.66912711806</v>
@@ -3696,16 +3709,16 @@
         <v>46182.63203959491</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I35" s="9">
         <v>46161</v>
@@ -3723,13 +3736,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O35" s="10" t="s">
         <v>85</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3745,7 +3758,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B36" s="5">
         <v>46169.66913270833</v>
@@ -3757,16 +3770,16 @@
         <v>46182.634411203704</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I36" s="5">
         <v>46182</v>
@@ -3784,13 +3797,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3806,7 +3819,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B37" s="9">
         <v>46169.66913809028</v>
@@ -3818,16 +3831,16 @@
         <v>46182.6343528588</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I37" s="9">
         <v>46182</v>
@@ -3845,13 +3858,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3867,7 +3880,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B38" s="5">
         <v>46169.66914475695</v>
@@ -3877,16 +3890,16 @@
         <v>46220.19404127315</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I38" s="5">
         <v>46161</v>
@@ -3904,10 +3917,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3919,7 +3932,7 @@
         <v>46219</v>
       </c>
       <c r="S38" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T38" s="6">
         <v>0</v>
@@ -3930,7 +3943,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B39" s="9">
         <v>46169.669149270834</v>
@@ -3942,16 +3955,16 @@
         <v>46195.68641299769</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I39" s="9">
         <v>46161</v>
@@ -3969,13 +3982,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -3985,7 +3998,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B40" s="5">
         <v>46169.66915408565</v>
@@ -3995,16 +4008,16 @@
         <v>46219.16855109954</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I40" s="5">
         <v>46171</v>
@@ -4022,13 +4035,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4038,7 +4051,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B41" s="9">
         <v>46169.66915865741</v>
@@ -4050,16 +4063,16 @@
         <v>46209.82174662037</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I41" s="9">
         <v>46245</v>
@@ -4077,13 +4090,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q41" s="9">
         <v>46245</v>
@@ -4103,7 +4116,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B42" s="5">
         <v>46169.66916377315</v>
@@ -4115,16 +4128,16 @@
         <v>46199.56927892361</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I42" s="5">
         <v>46245</v>
@@ -4142,13 +4155,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4164,7 +4177,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B43" s="9">
         <v>46169.66916960648</v>
@@ -4176,16 +4189,16 @@
         <v>46205.61247092593</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I43" s="9">
         <v>46247</v>
@@ -4203,13 +4216,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4225,7 +4238,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B44" s="5">
         <v>46169.66917503472</v>
@@ -4237,16 +4250,16 @@
         <v>46199.567282199074</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I44" s="5">
         <v>46245</v>
@@ -4264,10 +4277,10 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>26</v>
@@ -4290,7 +4303,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B45" s="9">
         <v>46169.669178888886</v>
@@ -4302,16 +4315,16 @@
         <v>46199.569896354165</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I45" s="9">
         <v>46245</v>
@@ -4329,13 +4342,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4345,7 +4358,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B46" s="5">
         <v>46169.669183680555</v>
@@ -4357,16 +4370,16 @@
         <v>46199.56984034722</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I46" s="5">
         <v>46247</v>
@@ -4384,13 +4397,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4400,7 +4413,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B47" s="9">
         <v>46169.66918849537</v>
@@ -4412,16 +4425,16 @@
         <v>46204.863616284725</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I47" s="9">
         <v>46245</v>
@@ -4439,10 +4452,10 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>26</v>
@@ -4465,7 +4478,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B48" s="5">
         <v>46169.66919252315</v>
@@ -4477,16 +4490,16 @@
         <v>46204.863510995376</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I48" s="5">
         <v>46245</v>
@@ -4504,13 +4517,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4520,7 +4533,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B49" s="9">
         <v>46169.66919734953</v>
@@ -4532,16 +4545,16 @@
         <v>46204.8635487037</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I49" s="9">
         <v>46254</v>
@@ -4559,13 +4572,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4575,7 +4588,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
         <v>46169.66920229167</v>
@@ -4587,16 +4600,16 @@
         <v>46210.65313525463</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I50" s="5">
         <v>46286</v>
@@ -4614,10 +4627,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4630,7 +4643,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B51" s="9">
         <v>46169.66924202546</v>
@@ -4642,16 +4655,16 @@
         <v>46199.57084909722</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I51" s="9">
         <v>46245</v>
@@ -4669,10 +4682,10 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P51" s="10" t="s">
         <v>26</v>
@@ -4695,7 +4708,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B52" s="5">
         <v>46169.66924635417</v>
@@ -4707,16 +4720,16 @@
         <v>46199.57078165509</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I52" s="5">
         <v>46245</v>
@@ -4734,13 +4747,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4750,7 +4763,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B53" s="9">
         <v>46169.66925091435</v>
@@ -4762,16 +4775,16 @@
         <v>46199.57082731482</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I53" s="9">
         <v>46247</v>
@@ -4789,13 +4802,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4805,7 +4818,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B54" s="5">
         <v>46169.669255659726</v>
@@ -4817,7 +4830,7 @@
         <v>46210.52487434028</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>25</v>
@@ -4841,7 +4854,7 @@
         <v>26</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -4858,7 +4871,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B55" s="9">
         <v>46169.66925896991</v>
@@ -4870,16 +4883,16 @@
         <v>46197.71564204861</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I55" s="9">
         <v>46167</v>
@@ -4891,19 +4904,19 @@
         <v>26</v>
       </c>
       <c r="L55" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q55" s="9">
         <v>46167</v>
@@ -4912,7 +4925,7 @@
         <v>46184</v>
       </c>
       <c r="S55" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T55" s="10">
         <v>1</v>
@@ -4923,7 +4936,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B56" s="5">
         <v>46169.66926408565</v>
@@ -4935,16 +4948,16 @@
         <v>46195.94997940972</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I56" s="5">
         <v>46167</v>
@@ -4962,13 +4975,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>79</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4978,7 +4991,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B57" s="9">
         <v>46169.66926952546</v>
@@ -4990,16 +5003,16 @@
         <v>46195.94998958333</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I57" s="9">
         <v>46167</v>
@@ -5017,13 +5030,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O57" s="10" t="s">
         <v>79</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -5033,7 +5046,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B58" s="5">
         <v>46169.66929263889</v>
@@ -5045,16 +5058,16 @@
         <v>46197.71567513889</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I58" s="5">
         <v>46220</v>
@@ -5072,13 +5085,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q58" s="5">
         <v>46220</v>
@@ -5098,7 +5111,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B59" s="9">
         <v>46169.66929775463</v>
@@ -5110,16 +5123,16 @@
         <v>46195.950096458335</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I59" s="9">
         <v>46181</v>
@@ -5137,13 +5150,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5153,7 +5166,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B60" s="5">
         <v>46169.66930358796</v>
@@ -5165,16 +5178,16 @@
         <v>46196.87985491898</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I60" s="5">
         <v>46181</v>
@@ -5192,13 +5205,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5208,7 +5221,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B61" s="9">
         <v>46169.669327048614</v>
@@ -5220,16 +5233,16 @@
         <v>46209.908330949074</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I61" s="9">
         <v>46240</v>
@@ -5247,13 +5260,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q61" s="9">
         <v>46240</v>
@@ -5273,7 +5286,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B62" s="5">
         <v>46169.6693399537</v>
@@ -5285,16 +5298,16 @@
         <v>46195.95042396991</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I62" s="5">
         <v>46188</v>
@@ -5312,13 +5325,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5328,7 +5341,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B63" s="9">
         <v>46169.669361203705</v>
@@ -5338,16 +5351,16 @@
         <v>46174.84660805555</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I63" s="9">
         <v>46322</v>
@@ -5365,10 +5378,10 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P63" s="10" t="s">
         <v>26</v>
@@ -5391,7 +5404,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B64" s="5">
         <v>46169.66936501158</v>
@@ -5401,16 +5414,16 @@
         <v>46174.846919421296</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I64" s="5">
         <v>46290</v>
@@ -5428,13 +5441,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5444,7 +5457,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B65" s="9">
         <v>46169.669418136575</v>
@@ -5456,7 +5469,7 @@
         <v>46210.65198340278</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>25</v>
@@ -5480,7 +5493,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P65" s="10" t="s">
         <v>26</v>
@@ -5497,7 +5510,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B66" s="5">
         <v>46169.66942685185</v>
@@ -5509,16 +5522,16 @@
         <v>46210.651395196764</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I66" s="5">
         <v>46258</v>
@@ -5536,13 +5549,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q66" s="5">
         <v>46258</v>
@@ -5562,7 +5575,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B67" s="9">
         <v>46169.669432361115</v>
@@ -5574,16 +5587,16 @@
         <v>46210.65197202546</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I67" s="9">
         <v>46260</v>
@@ -5601,13 +5614,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q67" s="9">
         <v>46260</v>
@@ -5627,7 +5640,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B68" s="5">
         <v>46169.66943836806</v>
@@ -5639,16 +5652,16 @@
         <v>46210.65139929398</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I68" s="5">
         <v>46258</v>
@@ -5666,13 +5679,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q68" s="5">
         <v>46258</v>
@@ -5692,7 +5705,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B69" s="9">
         <v>46169.669443692124</v>
@@ -5704,16 +5717,16 @@
         <v>46210.651975879635</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I69" s="9">
         <v>46260</v>
@@ -5731,13 +5744,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q69" s="9">
         <v>46260</v>
@@ -5757,7 +5770,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B70" s="5">
         <v>46169.669448368055</v>
@@ -5769,16 +5782,16 @@
         <v>46210.65141630787</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I70" s="5">
         <v>46258</v>
@@ -5796,13 +5809,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q70" s="5">
         <v>46258</v>
@@ -5822,7 +5835,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B71" s="9">
         <v>46169.66945298611</v>
@@ -5834,16 +5847,16 @@
         <v>46210.65197810185</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I71" s="9">
         <v>46260</v>
@@ -5861,13 +5874,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q71" s="9">
         <v>46260</v>
@@ -5887,7 +5900,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B72" s="5">
         <v>46169.66945778935</v>
@@ -5897,7 +5910,7 @@
         <v>46209.909264270835</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>25</v>
@@ -5921,7 +5934,7 @@
         <v>26</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>26</v>
@@ -5934,7 +5947,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B73" s="9">
         <v>46169.66946104167</v>
@@ -5946,16 +5959,16 @@
         <v>46209.90937729167</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I73" s="9">
         <v>46262</v>
@@ -5973,13 +5986,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q73" s="9">
         <v>46262</v>
@@ -5999,7 +6012,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B74" s="5">
         <v>46169.669467280095</v>
@@ -6011,16 +6024,16 @@
         <v>46210.65196928241</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I74" s="5">
         <v>46262</v>
@@ -6038,13 +6051,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6054,7 +6067,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B75" s="9">
         <v>46169.66950289352</v>
@@ -6064,16 +6077,16 @@
         <v>46209.90954123843</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I75" s="9">
         <v>46273</v>
@@ -6091,13 +6104,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q75" s="9">
         <v>46273</v>
@@ -6112,12 +6125,12 @@
         <v>0.1</v>
       </c>
       <c r="U75" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B76" s="5">
         <v>46169.66950758102</v>
@@ -6127,16 +6140,16 @@
         <v>46209.90937868056</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I76" s="5">
         <v>46273</v>
@@ -6154,13 +6167,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6170,7 +6183,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B77" s="9">
         <v>46169.66953380787</v>
@@ -6180,16 +6193,16 @@
         <v>46209.908330833336</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I77" s="9">
         <v>46294</v>
@@ -6207,13 +6220,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q77" s="9">
         <v>46294</v>
@@ -6233,7 +6246,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B78" s="5">
         <v>46169.66953854167</v>
@@ -6243,16 +6256,16 @@
         <v>46197.84256122685</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -6268,13 +6281,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6284,7 +6297,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B79" s="9">
         <v>46169.66960108797</v>
@@ -6294,7 +6307,7 @@
         <v>46209.85402508102</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>25</v>
@@ -6318,7 +6331,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P79" s="10" t="s">
         <v>26</v>
@@ -6328,12 +6341,12 @@
       <c r="S79" s="10"/>
       <c r="T79" s="10"/>
       <c r="U79" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B80" s="5">
         <v>46169.66960956018</v>
@@ -6345,16 +6358,16 @@
         <v>46209.844928101855</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I80" s="5">
         <v>46174</v>
@@ -6372,13 +6385,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q80" s="5">
         <v>46174</v>
@@ -6387,7 +6400,7 @@
         <v>46174</v>
       </c>
       <c r="S80" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T80" s="6">
         <v>1</v>
@@ -6398,7 +6411,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B81" s="9">
         <v>46169.6696165162</v>
@@ -6410,16 +6423,16 @@
         <v>46209.84471936343</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I81" s="9">
         <v>46288</v>
@@ -6437,13 +6450,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q81" s="9">
         <v>46288</v>
@@ -6463,7 +6476,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B82" s="5">
         <v>46169.669622939815</v>
@@ -6475,16 +6488,16 @@
         <v>46209.85430440972</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I82" s="5">
         <v>46308</v>
@@ -6502,13 +6515,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q82" s="5">
         <v>46308</v>
@@ -6528,7 +6541,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B83" s="9">
         <v>46169.66962980324</v>
@@ -6538,16 +6551,16 @@
         <v>46204.86356525463</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I83" s="9">
         <v>46287</v>
@@ -6565,13 +6578,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q83" s="9">
         <v>46287</v>
@@ -6586,12 +6599,12 @@
         <v>0</v>
       </c>
       <c r="U83" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B84" s="5">
         <v>46169.669635185186</v>
@@ -6607,10 +6620,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I84" s="5">
         <v>46220</v>
@@ -6628,13 +6641,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q84" s="5">
         <v>46220</v>
@@ -6643,7 +6656,7 @@
         <v>46220</v>
       </c>
       <c r="S84" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
@@ -6654,17 +6667,17 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B85" s="9">
         <v>46169.66964790509</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46209.84945282407</v>
+        <v>46223.56797070602</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>25</v>
@@ -6688,7 +6701,7 @@
         <v>26</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>26</v>
@@ -6701,25 +6714,27 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B86" s="5">
         <v>46169.66965109954</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46174.84790094907</v>
+        <v>46223.56814725694</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H86" s="6"/>
+        <v>92</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>92</v>
+      </c>
       <c r="I86" s="5">
         <v>46294</v>
       </c>
@@ -6736,13 +6751,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q86" s="5">
         <v>46294</v>
@@ -6762,25 +6777,27 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B87" s="9">
         <v>46169.6696568287</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46174.84798839121</v>
+        <v>46223.5676475463</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H87" s="10"/>
+        <v>92</v>
+      </c>
+      <c r="H87" s="10" t="s">
+        <v>92</v>
+      </c>
       <c r="I87" s="9">
         <v>46294</v>
       </c>
@@ -6797,13 +6814,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6813,7 +6830,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B88" s="5">
         <v>46169.669688622685</v>
@@ -6822,18 +6839,20 @@
         <v>46209.84929427083</v>
       </c>
       <c r="D88" s="5">
-        <v>46209.8493094213</v>
+        <v>46223.568163460644</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H88" s="6"/>
+        <v>92</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>92</v>
+      </c>
       <c r="I88" s="5">
         <v>46316</v>
       </c>
@@ -6850,13 +6869,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q88" s="5">
         <v>46316</v>
@@ -6876,7 +6895,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B89" s="9">
         <v>46169.66969347223</v>
@@ -6886,7 +6905,7 @@
         <v>46209.84459753473</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6909,13 +6928,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6925,7 +6944,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B90" s="5">
         <v>46169.66972681713</v>
@@ -6934,18 +6953,20 @@
         <v>46209.84944726852</v>
       </c>
       <c r="D90" s="5">
-        <v>46209.84946481482</v>
+        <v>46223.56815898148</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H90" s="6"/>
+        <v>92</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>92</v>
+      </c>
       <c r="I90" s="5">
         <v>46317</v>
       </c>
@@ -6962,13 +6983,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q90" s="5">
         <v>46317</v>
@@ -6988,25 +7009,27 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B91" s="9">
         <v>46169.66973180555</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46209.844891030094</v>
+        <v>46223.56782162037</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H91" s="10"/>
+        <v>92</v>
+      </c>
+      <c r="H91" s="10" t="s">
+        <v>92</v>
+      </c>
       <c r="I91" s="9">
         <v>46317</v>
       </c>
@@ -7023,13 +7046,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -7039,25 +7062,27 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B92" s="5">
         <v>46169.66981054399</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46174.8478909375</v>
+        <v>46223.56814546297</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H92" s="6"/>
+        <v>92</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>92</v>
+      </c>
       <c r="I92" s="5">
         <v>46318</v>
       </c>
@@ -7074,13 +7099,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q92" s="5">
         <v>46318</v>
@@ -7100,25 +7125,27 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B93" s="9">
         <v>46169.66981724537</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46209.85401892361</v>
+        <v>46223.56789047454</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H93" s="10"/>
+        <v>92</v>
+      </c>
+      <c r="H93" s="10" t="s">
+        <v>92</v>
+      </c>
       <c r="I93" s="9">
         <v>46318</v>
       </c>
@@ -7135,13 +7162,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7151,25 +7178,27 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B94" s="5">
         <v>46169.669861041664</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46174.8478862037</v>
+        <v>46223.568144791665</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H94" s="6"/>
+        <v>92</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>92</v>
+      </c>
       <c r="I94" s="5">
         <v>46321</v>
       </c>
@@ -7186,13 +7215,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q94" s="5">
         <v>46321</v>
@@ -7212,25 +7241,27 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B95" s="9">
         <v>46169.66986724537</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46174.84816675926</v>
+        <v>46223.56796597222</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H95" s="10"/>
+        <v>92</v>
+      </c>
+      <c r="H95" s="10" t="s">
+        <v>92</v>
+      </c>
       <c r="I95" s="9">
         <v>46321</v>
       </c>
@@ -7247,13 +7278,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7263,25 +7294,27 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B96" s="5">
         <v>46169.66990296297</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46174.84788545139</v>
+        <v>46223.568144212964</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H96" s="6"/>
+        <v>92</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>92</v>
+      </c>
       <c r="I96" s="5">
         <v>46323</v>
       </c>
@@ -7298,13 +7331,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q96" s="5">
         <v>46323</v>
@@ -7324,7 +7357,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B97" s="9">
         <v>46169.66994555556</v>
@@ -7334,7 +7367,7 @@
         <v>46174.848269317125</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7357,13 +7390,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7373,7 +7406,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B98" s="5">
         <v>46169.669978645834</v>
@@ -7383,7 +7416,7 @@
         <v>46174.82401747685</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>25</v>
@@ -7407,7 +7440,7 @@
         <v>26</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>26</v>
@@ -7420,7 +7453,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B99" s="9">
         <v>46169.66998244213</v>
@@ -7430,16 +7463,16 @@
         <v>46174.84843513889</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I99" s="9">
         <v>46324</v>
@@ -7457,13 +7490,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q99" s="9">
         <v>46324</v>
@@ -7483,7 +7516,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B100" s="5">
         <v>46169.66998994213</v>
@@ -7493,16 +7526,16 @@
         <v>46174.84838837963</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I100" s="6"/>
       <c r="J100" s="5">
@@ -7518,13 +7551,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7534,7 +7567,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B101" s="9">
         <v>46170.63118891204</v>
@@ -7544,16 +7577,16 @@
         <v>46209.90833168982</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="9">
@@ -7569,13 +7602,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7585,7 +7618,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B102" s="5">
         <v>46174.820955891206</v>
@@ -7601,10 +7634,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I102" s="5">
         <v>46324</v>
@@ -7622,13 +7655,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>64</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7638,25 +7671,27 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B103" s="9">
         <v>46169.670044224535</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46174.848558831014</v>
+        <v>46223.56892738426</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H103" s="10"/>
+        <v>92</v>
+      </c>
+      <c r="H103" s="10" t="s">
+        <v>92</v>
+      </c>
       <c r="I103" s="10"/>
       <c r="J103" s="9">
         <v>46325</v>
@@ -7671,13 +7706,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q103" s="9">
         <v>46325</v>
@@ -7697,25 +7732,27 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B104" s="5">
         <v>46169.670049050925</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46174.848527152775</v>
+        <v>46223.568262175926</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H104" s="6"/>
+        <v>92</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>92</v>
+      </c>
       <c r="I104" s="6"/>
       <c r="J104" s="5">
         <v>46325</v>
@@ -7730,13 +7767,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7746,25 +7783,27 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B105" s="9">
         <v>46170.63213679398</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46174.848524270834</v>
+        <v>46223.56826151621</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H105" s="10"/>
+        <v>92</v>
+      </c>
+      <c r="H105" s="10" t="s">
+        <v>92</v>
+      </c>
       <c r="I105" s="10"/>
       <c r="J105" s="9">
         <v>46325</v>
@@ -7779,13 +7818,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7795,25 +7834,27 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B106" s="5">
         <v>46174.82099290509</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46174.84852028935</v>
+        <v>46223.5682608912</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H106" s="6"/>
+        <v>92</v>
+      </c>
+      <c r="H106" s="6" t="s">
+        <v>92</v>
+      </c>
       <c r="I106" s="5">
         <v>46325</v>
       </c>
@@ -7830,7 +7871,7 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>64</v>
@@ -7846,7 +7887,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B107" s="9">
         <v>46169.67013976852</v>
@@ -7856,16 +7897,16 @@
         <v>46174.84870307871</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I107" s="10"/>
       <c r="J107" s="9">
@@ -7881,13 +7922,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q107" s="9">
         <v>46328</v>
@@ -7907,7 +7948,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B108" s="5">
         <v>46169.670151377315</v>
@@ -7917,16 +7958,16 @@
         <v>46174.848669872685</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I108" s="5">
         <v>46328</v>
@@ -7944,13 +7985,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7960,7 +8001,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B109" s="9">
         <v>46170.63285997685</v>
@@ -7970,16 +8011,16 @@
         <v>46174.848667314815</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I109" s="9">
         <v>46328</v>
@@ -7997,13 +8038,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -8013,7 +8054,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B110" s="5">
         <v>46174.821024143515</v>
@@ -8029,10 +8070,10 @@
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I110" s="5">
         <v>46328</v>
@@ -8050,10 +8091,10 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>64</v>
@@ -8066,7 +8107,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B111" s="9">
         <v>46169.67021965278</v>
@@ -8076,16 +8117,16 @@
         <v>46174.84880980324</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I111" s="9">
         <v>46329</v>
@@ -8103,13 +8144,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q111" s="9">
         <v>46329</v>
@@ -8129,7 +8170,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B112" s="5">
         <v>46169.67022677083</v>
@@ -8139,16 +8180,16 @@
         <v>46174.84878571759</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I112" s="6"/>
       <c r="J112" s="5">
@@ -8164,13 +8205,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8180,7 +8221,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B113" s="9">
         <v>46170.633581828704</v>
@@ -8190,16 +8231,16 @@
         <v>46174.84878314815</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I113" s="10"/>
       <c r="J113" s="9">
@@ -8215,10 +8256,10 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -8231,7 +8272,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B114" s="5">
         <v>46174.821057037036</v>
@@ -8247,10 +8288,10 @@
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I114" s="6"/>
       <c r="J114" s="5">
@@ -8266,7 +8307,7 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>64</v>
@@ -8282,7 +8323,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B115" s="9">
         <v>46169.67031616898</v>
@@ -8292,7 +8333,7 @@
         <v>46174.82401751158</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>25</v>
@@ -8316,7 +8357,7 @@
         <v>26</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P115" s="10" t="s">
         <v>26</v>
@@ -8329,7 +8370,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B116" s="5">
         <v>46169.67031976852</v>
@@ -8339,16 +8380,16 @@
         <v>46174.84885483797</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="I116" s="5">
         <v>46330</v>
@@ -8366,13 +8407,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q116" s="5">
         <v>46330</v>
@@ -8392,7 +8433,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B117" s="9">
         <v>46169.6703253125</v>
@@ -8402,7 +8443,7 @@
         <v>46192.97339644676</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8429,13 +8470,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q117" s="9">
         <v>46330</v>
@@ -8455,7 +8496,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B118" s="5">
         <v>46169.670332430556</v>
@@ -8465,7 +8506,7 @@
         <v>46174.82401726852</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>25</v>
@@ -8489,7 +8530,7 @@
         <v>26</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>26</v>
@@ -8508,7 +8549,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B119" s="9">
         <v>46169.67033591435</v>
@@ -8518,7 +8559,7 @@
         <v>46174.848958703704</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8545,13 +8586,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q119" s="9">
         <v>46330</v>
@@ -8571,7 +8612,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B120" s="5">
         <v>46169.67034748843</v>
@@ -8581,7 +8622,7 @@
         <v>46174.84895586806</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8608,13 +8649,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q120" s="5">
         <v>46339</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1438" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="365">
   <si>
     <t>50001558 -  GESVIAL</t>
   </si>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46209.84459753473</v>
+        <v>46223.83603929398</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>206</v>
@@ -6911,9 +6911,11 @@
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H89" s="10"/>
+        <v>92</v>
+      </c>
+      <c r="H89" s="10" t="s">
+        <v>92</v>
+      </c>
       <c r="I89" s="10"/>
       <c r="J89" s="9">
         <v>46316</v>
@@ -7364,7 +7366,7 @@
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46174.848269317125</v>
+        <v>46223.836147291666</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>206</v>
@@ -7373,9 +7375,11 @@
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H97" s="10"/>
+        <v>92</v>
+      </c>
+      <c r="H97" s="10" t="s">
+        <v>92</v>
+      </c>
       <c r="I97" s="10"/>
       <c r="J97" s="9">
         <v>46323</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -850,7 +850,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A</t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1215174141301410</t>
@@ -5956,7 +5956,7 @@
         <v>46209.90925715277</v>
       </c>
       <c r="D73" s="9">
-        <v>46209.90937729167</v>
+        <v>46224.87838667824</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>255</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -850,7 +850,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
   </si>
   <si>
     <t>1215174141301410</t>
@@ -5956,7 +5956,7 @@
         <v>46209.90925715277</v>
       </c>
       <c r="D73" s="9">
-        <v>46224.87838667824</v>
+        <v>46225.00959501158</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>255</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -850,7 +850,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
+    <t xml:space="preserve">OT2 4307 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
   </si>
   <si>
     <t>1215174141301410</t>
@@ -5956,7 +5956,7 @@
         <v>46209.90925715277</v>
       </c>
       <c r="D73" s="9">
-        <v>46225.00959501158</v>
+        <v>46225.58945533565</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>255</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="366">
   <si>
     <t>50001558 -  GESVIAL</t>
   </si>
@@ -350,6 +350,9 @@
     <t>propuesta nucleo rodete</t>
   </si>
   <si>
+    <t>NATALYA ESPINOZA</t>
+  </si>
+  <si>
     <t>nespinoza@zitron.com</t>
   </si>
   <si>
@@ -850,7 +853,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT2 4307 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1215174141301410</t>
@@ -2840,7 +2843,7 @@
         <v>92</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I21" s="9">
         <v>46167</v>
@@ -2864,7 +2867,7 @@
         <v>75</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q21" s="9">
         <v>46167</v>
@@ -2884,7 +2887,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B22" s="5">
         <v>46169.66903233796</v>
@@ -2896,7 +2899,7 @@
         <v>46223.567540601856</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -2905,7 +2908,7 @@
         <v>92</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I22" s="5">
         <v>46241</v>
@@ -2926,10 +2929,10 @@
         <v>82</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q22" s="5">
         <v>46241</v>
@@ -2949,7 +2952,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B23" s="9">
         <v>46169.669037291664</v>
@@ -2961,7 +2964,7 @@
         <v>46223.5675370949</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
@@ -2970,7 +2973,7 @@
         <v>92</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I23" s="9">
         <v>46241</v>
@@ -2991,10 +2994,10 @@
         <v>82</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q23" s="9">
         <v>46241</v>
@@ -3014,7 +3017,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B24" s="5">
         <v>46169.66904123843</v>
@@ -3026,7 +3029,7 @@
         <v>46223.567533877314</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -3035,7 +3038,7 @@
         <v>92</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I24" s="5">
         <v>46241</v>
@@ -3056,10 +3059,10 @@
         <v>82</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q24" s="5">
         <v>46241</v>
@@ -3079,7 +3082,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B25" s="9">
         <v>46169.66904511574</v>
@@ -3091,7 +3094,7 @@
         <v>46223.56752888889</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
@@ -3100,7 +3103,7 @@
         <v>92</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I25" s="9">
         <v>46241</v>
@@ -3121,10 +3124,10 @@
         <v>82</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q25" s="9">
         <v>46241</v>
@@ -3144,7 +3147,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B26" s="5">
         <v>46169.66904878472</v>
@@ -3156,7 +3159,7 @@
         <v>46195.60168921296</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -3189,7 +3192,7 @@
         <v>51</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q26" s="5">
         <v>46157</v>
@@ -3209,7 +3212,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B27" s="9">
         <v>46169.66883418981</v>
@@ -3219,7 +3222,7 @@
         <v>46209.82175228009</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>25</v>
@@ -3243,7 +3246,7 @@
         <v>26</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P27" s="10" t="s">
         <v>26</v>
@@ -3253,12 +3256,12 @@
       <c r="S27" s="10"/>
       <c r="T27" s="10"/>
       <c r="U27" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B28" s="5">
         <v>46169.66908924768</v>
@@ -3270,16 +3273,16 @@
         <v>46182.63466408565</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I28" s="5">
         <v>46171</v>
@@ -3297,13 +3300,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q28" s="5">
         <v>46168</v>
@@ -3323,7 +3326,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B29" s="9">
         <v>46169.66909520833</v>
@@ -3335,16 +3338,16 @@
         <v>46182.63236322917</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I29" s="9">
         <v>46169</v>
@@ -3362,13 +3365,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O29" s="10" t="s">
         <v>88</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3384,7 +3387,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B30" s="5">
         <v>46169.669100810184</v>
@@ -3396,16 +3399,16 @@
         <v>46182.63463722222</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I30" s="5">
         <v>46171</v>
@@ -3423,13 +3426,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3445,7 +3448,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B31" s="9">
         <v>46169.669106284724</v>
@@ -3457,16 +3460,16 @@
         <v>46182.63460042824</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I31" s="9">
         <v>46168</v>
@@ -3484,13 +3487,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q31" s="9">
         <v>46168</v>
@@ -3499,7 +3502,7 @@
         <v>46171</v>
       </c>
       <c r="S31" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T31" s="10">
         <v>1</v>
@@ -3510,7 +3513,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B32" s="5">
         <v>46169.66911128472</v>
@@ -3522,16 +3525,16 @@
         <v>46182.6318109375</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I32" s="5">
         <v>46168</v>
@@ -3549,13 +3552,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>91</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3571,7 +3574,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B33" s="9">
         <v>46169.669116805555</v>
@@ -3583,16 +3586,16 @@
         <v>46182.63457327546</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I33" s="9">
         <v>46170</v>
@@ -3610,13 +3613,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3632,7 +3635,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B34" s="5">
         <v>46169.66912204861</v>
@@ -3644,16 +3647,16 @@
         <v>46182.6344355787</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I34" s="5">
         <v>46161</v>
@@ -3671,13 +3674,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q34" s="5">
         <v>46161</v>
@@ -3697,7 +3700,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B35" s="9">
         <v>46169.66912711806</v>
@@ -3709,16 +3712,16 @@
         <v>46182.63203959491</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I35" s="9">
         <v>46161</v>
@@ -3736,13 +3739,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O35" s="10" t="s">
         <v>85</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3758,7 +3761,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B36" s="5">
         <v>46169.66913270833</v>
@@ -3770,16 +3773,16 @@
         <v>46182.634411203704</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I36" s="5">
         <v>46182</v>
@@ -3797,13 +3800,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3819,7 +3822,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B37" s="9">
         <v>46169.66913809028</v>
@@ -3831,16 +3834,16 @@
         <v>46182.6343528588</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I37" s="9">
         <v>46182</v>
@@ -3858,13 +3861,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3880,7 +3883,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B38" s="5">
         <v>46169.66914475695</v>
@@ -3890,16 +3893,16 @@
         <v>46220.19404127315</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I38" s="5">
         <v>46161</v>
@@ -3917,10 +3920,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3932,7 +3935,7 @@
         <v>46219</v>
       </c>
       <c r="S38" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T38" s="6">
         <v>0</v>
@@ -3943,7 +3946,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B39" s="9">
         <v>46169.669149270834</v>
@@ -3955,16 +3958,16 @@
         <v>46195.68641299769</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I39" s="9">
         <v>46161</v>
@@ -3982,13 +3985,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -3998,7 +4001,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B40" s="5">
         <v>46169.66915408565</v>
@@ -4008,16 +4011,16 @@
         <v>46219.16855109954</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I40" s="5">
         <v>46171</v>
@@ -4035,13 +4038,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4051,7 +4054,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B41" s="9">
         <v>46169.66915865741</v>
@@ -4063,16 +4066,16 @@
         <v>46209.82174662037</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I41" s="9">
         <v>46245</v>
@@ -4090,13 +4093,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q41" s="9">
         <v>46245</v>
@@ -4116,7 +4119,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B42" s="5">
         <v>46169.66916377315</v>
@@ -4128,16 +4131,16 @@
         <v>46199.56927892361</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I42" s="5">
         <v>46245</v>
@@ -4155,13 +4158,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4177,7 +4180,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B43" s="9">
         <v>46169.66916960648</v>
@@ -4189,16 +4192,16 @@
         <v>46205.61247092593</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I43" s="9">
         <v>46247</v>
@@ -4216,13 +4219,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4238,7 +4241,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B44" s="5">
         <v>46169.66917503472</v>
@@ -4250,16 +4253,16 @@
         <v>46199.567282199074</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I44" s="5">
         <v>46245</v>
@@ -4277,10 +4280,10 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>26</v>
@@ -4303,7 +4306,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B45" s="9">
         <v>46169.669178888886</v>
@@ -4315,16 +4318,16 @@
         <v>46199.569896354165</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I45" s="9">
         <v>46245</v>
@@ -4342,13 +4345,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4358,7 +4361,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B46" s="5">
         <v>46169.669183680555</v>
@@ -4370,16 +4373,16 @@
         <v>46199.56984034722</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I46" s="5">
         <v>46247</v>
@@ -4397,13 +4400,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4413,7 +4416,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B47" s="9">
         <v>46169.66918849537</v>
@@ -4425,16 +4428,16 @@
         <v>46204.863616284725</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I47" s="9">
         <v>46245</v>
@@ -4452,10 +4455,10 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>26</v>
@@ -4478,7 +4481,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B48" s="5">
         <v>46169.66919252315</v>
@@ -4490,16 +4493,16 @@
         <v>46204.863510995376</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I48" s="5">
         <v>46245</v>
@@ -4517,13 +4520,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4533,7 +4536,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B49" s="9">
         <v>46169.66919734953</v>
@@ -4545,16 +4548,16 @@
         <v>46204.8635487037</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I49" s="9">
         <v>46254</v>
@@ -4572,13 +4575,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4588,7 +4591,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
         <v>46169.66920229167</v>
@@ -4600,16 +4603,16 @@
         <v>46210.65313525463</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I50" s="5">
         <v>46286</v>
@@ -4627,10 +4630,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4643,7 +4646,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B51" s="9">
         <v>46169.66924202546</v>
@@ -4655,16 +4658,16 @@
         <v>46199.57084909722</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I51" s="9">
         <v>46245</v>
@@ -4682,10 +4685,10 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P51" s="10" t="s">
         <v>26</v>
@@ -4708,7 +4711,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46169.66924635417</v>
@@ -4720,16 +4723,16 @@
         <v>46199.57078165509</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I52" s="5">
         <v>46245</v>
@@ -4747,13 +4750,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4763,7 +4766,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B53" s="9">
         <v>46169.66925091435</v>
@@ -4775,16 +4778,16 @@
         <v>46199.57082731482</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I53" s="9">
         <v>46247</v>
@@ -4802,13 +4805,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4818,7 +4821,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B54" s="5">
         <v>46169.669255659726</v>
@@ -4830,7 +4833,7 @@
         <v>46210.52487434028</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>25</v>
@@ -4854,7 +4857,7 @@
         <v>26</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -4871,7 +4874,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B55" s="9">
         <v>46169.66925896991</v>
@@ -4883,16 +4886,16 @@
         <v>46197.71564204861</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I55" s="9">
         <v>46167</v>
@@ -4904,19 +4907,19 @@
         <v>26</v>
       </c>
       <c r="L55" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q55" s="9">
         <v>46167</v>
@@ -4925,7 +4928,7 @@
         <v>46184</v>
       </c>
       <c r="S55" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T55" s="10">
         <v>1</v>
@@ -4936,7 +4939,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B56" s="5">
         <v>46169.66926408565</v>
@@ -4948,16 +4951,16 @@
         <v>46195.94997940972</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I56" s="5">
         <v>46167</v>
@@ -4975,13 +4978,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>79</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4991,7 +4994,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B57" s="9">
         <v>46169.66926952546</v>
@@ -5003,16 +5006,16 @@
         <v>46195.94998958333</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I57" s="9">
         <v>46167</v>
@@ -5030,13 +5033,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O57" s="10" t="s">
         <v>79</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -5046,7 +5049,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B58" s="5">
         <v>46169.66929263889</v>
@@ -5058,16 +5061,16 @@
         <v>46197.71567513889</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I58" s="5">
         <v>46220</v>
@@ -5085,13 +5088,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q58" s="5">
         <v>46220</v>
@@ -5111,7 +5114,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B59" s="9">
         <v>46169.66929775463</v>
@@ -5123,16 +5126,16 @@
         <v>46195.950096458335</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I59" s="9">
         <v>46181</v>
@@ -5150,13 +5153,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5166,7 +5169,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B60" s="5">
         <v>46169.66930358796</v>
@@ -5178,16 +5181,16 @@
         <v>46196.87985491898</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I60" s="5">
         <v>46181</v>
@@ -5205,13 +5208,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5221,7 +5224,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B61" s="9">
         <v>46169.669327048614</v>
@@ -5233,16 +5236,16 @@
         <v>46209.908330949074</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I61" s="9">
         <v>46240</v>
@@ -5260,13 +5263,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q61" s="9">
         <v>46240</v>
@@ -5286,7 +5289,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B62" s="5">
         <v>46169.6693399537</v>
@@ -5298,16 +5301,16 @@
         <v>46195.95042396991</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I62" s="5">
         <v>46188</v>
@@ -5325,13 +5328,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5341,7 +5344,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B63" s="9">
         <v>46169.669361203705</v>
@@ -5351,16 +5354,16 @@
         <v>46174.84660805555</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I63" s="9">
         <v>46322</v>
@@ -5378,10 +5381,10 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P63" s="10" t="s">
         <v>26</v>
@@ -5404,7 +5407,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B64" s="5">
         <v>46169.66936501158</v>
@@ -5414,16 +5417,16 @@
         <v>46174.846919421296</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I64" s="5">
         <v>46290</v>
@@ -5441,13 +5444,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5457,7 +5460,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B65" s="9">
         <v>46169.669418136575</v>
@@ -5469,7 +5472,7 @@
         <v>46210.65198340278</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>25</v>
@@ -5493,7 +5496,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P65" s="10" t="s">
         <v>26</v>
@@ -5510,7 +5513,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B66" s="5">
         <v>46169.66942685185</v>
@@ -5522,16 +5525,16 @@
         <v>46210.651395196764</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I66" s="5">
         <v>46258</v>
@@ -5549,13 +5552,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q66" s="5">
         <v>46258</v>
@@ -5575,7 +5578,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B67" s="9">
         <v>46169.669432361115</v>
@@ -5587,16 +5590,16 @@
         <v>46210.65197202546</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I67" s="9">
         <v>46260</v>
@@ -5614,13 +5617,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q67" s="9">
         <v>46260</v>
@@ -5640,7 +5643,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B68" s="5">
         <v>46169.66943836806</v>
@@ -5652,16 +5655,16 @@
         <v>46210.65139929398</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I68" s="5">
         <v>46258</v>
@@ -5679,13 +5682,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q68" s="5">
         <v>46258</v>
@@ -5705,7 +5708,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B69" s="9">
         <v>46169.669443692124</v>
@@ -5717,16 +5720,16 @@
         <v>46210.651975879635</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I69" s="9">
         <v>46260</v>
@@ -5744,13 +5747,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q69" s="9">
         <v>46260</v>
@@ -5770,7 +5773,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B70" s="5">
         <v>46169.669448368055</v>
@@ -5782,16 +5785,16 @@
         <v>46210.65141630787</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I70" s="5">
         <v>46258</v>
@@ -5809,13 +5812,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q70" s="5">
         <v>46258</v>
@@ -5835,7 +5838,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B71" s="9">
         <v>46169.66945298611</v>
@@ -5847,16 +5850,16 @@
         <v>46210.65197810185</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I71" s="9">
         <v>46260</v>
@@ -5874,13 +5877,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q71" s="9">
         <v>46260</v>
@@ -5900,7 +5903,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B72" s="5">
         <v>46169.66945778935</v>
@@ -5910,7 +5913,7 @@
         <v>46209.909264270835</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>25</v>
@@ -5934,7 +5937,7 @@
         <v>26</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>26</v>
@@ -5947,7 +5950,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B73" s="9">
         <v>46169.66946104167</v>
@@ -5956,19 +5959,19 @@
         <v>46209.90925715277</v>
       </c>
       <c r="D73" s="9">
-        <v>46225.58945533565</v>
+        <v>46225.8618784375</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I73" s="9">
         <v>46262</v>
@@ -5986,13 +5989,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q73" s="9">
         <v>46262</v>
@@ -6012,7 +6015,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B74" s="5">
         <v>46169.669467280095</v>
@@ -6024,16 +6027,16 @@
         <v>46210.65196928241</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I74" s="5">
         <v>46262</v>
@@ -6051,13 +6054,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6067,7 +6070,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B75" s="9">
         <v>46169.66950289352</v>
@@ -6077,16 +6080,16 @@
         <v>46209.90954123843</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I75" s="9">
         <v>46273</v>
@@ -6104,13 +6107,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q75" s="9">
         <v>46273</v>
@@ -6125,12 +6128,12 @@
         <v>0.1</v>
       </c>
       <c r="U75" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B76" s="5">
         <v>46169.66950758102</v>
@@ -6140,16 +6143,16 @@
         <v>46209.90937868056</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I76" s="5">
         <v>46273</v>
@@ -6167,13 +6170,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6183,7 +6186,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B77" s="9">
         <v>46169.66953380787</v>
@@ -6193,16 +6196,16 @@
         <v>46209.908330833336</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I77" s="9">
         <v>46294</v>
@@ -6220,13 +6223,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q77" s="9">
         <v>46294</v>
@@ -6246,7 +6249,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B78" s="5">
         <v>46169.66953854167</v>
@@ -6256,16 +6259,16 @@
         <v>46197.84256122685</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -6281,13 +6284,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6297,7 +6300,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B79" s="9">
         <v>46169.66960108797</v>
@@ -6307,7 +6310,7 @@
         <v>46209.85402508102</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>25</v>
@@ -6331,7 +6334,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P79" s="10" t="s">
         <v>26</v>
@@ -6341,12 +6344,12 @@
       <c r="S79" s="10"/>
       <c r="T79" s="10"/>
       <c r="U79" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B80" s="5">
         <v>46169.66960956018</v>
@@ -6358,16 +6361,16 @@
         <v>46209.844928101855</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I80" s="5">
         <v>46174</v>
@@ -6385,13 +6388,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q80" s="5">
         <v>46174</v>
@@ -6400,7 +6403,7 @@
         <v>46174</v>
       </c>
       <c r="S80" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T80" s="6">
         <v>1</v>
@@ -6411,7 +6414,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B81" s="9">
         <v>46169.6696165162</v>
@@ -6423,16 +6426,16 @@
         <v>46209.84471936343</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I81" s="9">
         <v>46288</v>
@@ -6450,13 +6453,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q81" s="9">
         <v>46288</v>
@@ -6476,7 +6479,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B82" s="5">
         <v>46169.669622939815</v>
@@ -6488,16 +6491,16 @@
         <v>46209.85430440972</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I82" s="5">
         <v>46308</v>
@@ -6515,13 +6518,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q82" s="5">
         <v>46308</v>
@@ -6541,7 +6544,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B83" s="9">
         <v>46169.66962980324</v>
@@ -6551,16 +6554,16 @@
         <v>46204.86356525463</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I83" s="9">
         <v>46287</v>
@@ -6578,13 +6581,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q83" s="9">
         <v>46287</v>
@@ -6599,12 +6602,12 @@
         <v>0</v>
       </c>
       <c r="U83" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B84" s="5">
         <v>46169.669635185186</v>
@@ -6620,10 +6623,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I84" s="5">
         <v>46220</v>
@@ -6641,13 +6644,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q84" s="5">
         <v>46220</v>
@@ -6656,7 +6659,7 @@
         <v>46220</v>
       </c>
       <c r="S84" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
@@ -6667,7 +6670,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B85" s="9">
         <v>46169.66964790509</v>
@@ -6677,7 +6680,7 @@
         <v>46223.56797070602</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>25</v>
@@ -6701,7 +6704,7 @@
         <v>26</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>26</v>
@@ -6714,7 +6717,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B86" s="5">
         <v>46169.66965109954</v>
@@ -6724,7 +6727,7 @@
         <v>46223.56814725694</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6733,7 +6736,7 @@
         <v>92</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I86" s="5">
         <v>46294</v>
@@ -6751,13 +6754,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q86" s="5">
         <v>46294</v>
@@ -6777,7 +6780,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B87" s="9">
         <v>46169.6696568287</v>
@@ -6787,7 +6790,7 @@
         <v>46223.5676475463</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6796,7 +6799,7 @@
         <v>92</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I87" s="9">
         <v>46294</v>
@@ -6814,13 +6817,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6830,7 +6833,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B88" s="5">
         <v>46169.669688622685</v>
@@ -6842,7 +6845,7 @@
         <v>46223.568163460644</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6851,7 +6854,7 @@
         <v>92</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I88" s="5">
         <v>46316</v>
@@ -6869,13 +6872,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q88" s="5">
         <v>46316</v>
@@ -6895,7 +6898,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B89" s="9">
         <v>46169.66969347223</v>
@@ -6905,7 +6908,7 @@
         <v>46223.83603929398</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6914,7 +6917,7 @@
         <v>92</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I89" s="10"/>
       <c r="J89" s="9">
@@ -6930,13 +6933,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6946,7 +6949,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B90" s="5">
         <v>46169.66972681713</v>
@@ -6958,7 +6961,7 @@
         <v>46223.56815898148</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6967,7 +6970,7 @@
         <v>92</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I90" s="5">
         <v>46317</v>
@@ -6985,13 +6988,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q90" s="5">
         <v>46317</v>
@@ -7011,7 +7014,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B91" s="9">
         <v>46169.66973180555</v>
@@ -7021,7 +7024,7 @@
         <v>46223.56782162037</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -7030,7 +7033,7 @@
         <v>92</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I91" s="9">
         <v>46317</v>
@@ -7048,13 +7051,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -7064,7 +7067,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B92" s="5">
         <v>46169.66981054399</v>
@@ -7074,7 +7077,7 @@
         <v>46223.56814546297</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7083,7 +7086,7 @@
         <v>92</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I92" s="5">
         <v>46318</v>
@@ -7101,13 +7104,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q92" s="5">
         <v>46318</v>
@@ -7127,7 +7130,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B93" s="9">
         <v>46169.66981724537</v>
@@ -7137,7 +7140,7 @@
         <v>46223.56789047454</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7146,7 +7149,7 @@
         <v>92</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I93" s="9">
         <v>46318</v>
@@ -7164,13 +7167,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7180,7 +7183,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B94" s="5">
         <v>46169.669861041664</v>
@@ -7190,7 +7193,7 @@
         <v>46223.568144791665</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7199,7 +7202,7 @@
         <v>92</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I94" s="5">
         <v>46321</v>
@@ -7217,13 +7220,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q94" s="5">
         <v>46321</v>
@@ -7243,7 +7246,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B95" s="9">
         <v>46169.66986724537</v>
@@ -7253,7 +7256,7 @@
         <v>46223.56796597222</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7262,7 +7265,7 @@
         <v>92</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I95" s="9">
         <v>46321</v>
@@ -7280,13 +7283,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7296,7 +7299,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B96" s="5">
         <v>46169.66990296297</v>
@@ -7306,7 +7309,7 @@
         <v>46223.568144212964</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7315,7 +7318,7 @@
         <v>92</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I96" s="5">
         <v>46323</v>
@@ -7333,13 +7336,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q96" s="5">
         <v>46323</v>
@@ -7359,7 +7362,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B97" s="9">
         <v>46169.66994555556</v>
@@ -7369,7 +7372,7 @@
         <v>46223.836147291666</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7378,7 +7381,7 @@
         <v>92</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I97" s="10"/>
       <c r="J97" s="9">
@@ -7394,13 +7397,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7410,7 +7413,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B98" s="5">
         <v>46169.669978645834</v>
@@ -7420,7 +7423,7 @@
         <v>46174.82401747685</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>25</v>
@@ -7444,7 +7447,7 @@
         <v>26</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>26</v>
@@ -7457,7 +7460,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B99" s="9">
         <v>46169.66998244213</v>
@@ -7467,16 +7470,16 @@
         <v>46174.84843513889</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I99" s="9">
         <v>46324</v>
@@ -7494,13 +7497,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q99" s="9">
         <v>46324</v>
@@ -7520,7 +7523,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B100" s="5">
         <v>46169.66998994213</v>
@@ -7530,16 +7533,16 @@
         <v>46174.84838837963</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I100" s="6"/>
       <c r="J100" s="5">
@@ -7555,13 +7558,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7571,7 +7574,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B101" s="9">
         <v>46170.63118891204</v>
@@ -7581,16 +7584,16 @@
         <v>46209.90833168982</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="9">
@@ -7606,13 +7609,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7622,7 +7625,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B102" s="5">
         <v>46174.820955891206</v>
@@ -7638,10 +7641,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I102" s="5">
         <v>46324</v>
@@ -7659,13 +7662,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>64</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7675,7 +7678,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B103" s="9">
         <v>46169.670044224535</v>
@@ -7685,7 +7688,7 @@
         <v>46223.56892738426</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7694,7 +7697,7 @@
         <v>92</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I103" s="10"/>
       <c r="J103" s="9">
@@ -7710,13 +7713,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q103" s="9">
         <v>46325</v>
@@ -7736,7 +7739,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B104" s="5">
         <v>46169.670049050925</v>
@@ -7746,7 +7749,7 @@
         <v>46223.568262175926</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7755,7 +7758,7 @@
         <v>92</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I104" s="6"/>
       <c r="J104" s="5">
@@ -7771,13 +7774,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7787,7 +7790,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B105" s="9">
         <v>46170.63213679398</v>
@@ -7797,7 +7800,7 @@
         <v>46223.56826151621</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7806,7 +7809,7 @@
         <v>92</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I105" s="10"/>
       <c r="J105" s="9">
@@ -7822,13 +7825,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7838,7 +7841,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B106" s="5">
         <v>46174.82099290509</v>
@@ -7848,7 +7851,7 @@
         <v>46223.5682608912</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7857,7 +7860,7 @@
         <v>92</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I106" s="5">
         <v>46325</v>
@@ -7875,7 +7878,7 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>64</v>
@@ -7891,7 +7894,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B107" s="9">
         <v>46169.67013976852</v>
@@ -7901,16 +7904,16 @@
         <v>46174.84870307871</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I107" s="10"/>
       <c r="J107" s="9">
@@ -7926,13 +7929,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q107" s="9">
         <v>46328</v>
@@ -7952,7 +7955,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B108" s="5">
         <v>46169.670151377315</v>
@@ -7962,16 +7965,16 @@
         <v>46174.848669872685</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I108" s="5">
         <v>46328</v>
@@ -7989,13 +7992,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8005,7 +8008,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B109" s="9">
         <v>46170.63285997685</v>
@@ -8015,16 +8018,16 @@
         <v>46174.848667314815</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I109" s="9">
         <v>46328</v>
@@ -8042,13 +8045,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -8058,7 +8061,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B110" s="5">
         <v>46174.821024143515</v>
@@ -8074,10 +8077,10 @@
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I110" s="5">
         <v>46328</v>
@@ -8095,10 +8098,10 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>64</v>
@@ -8111,7 +8114,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B111" s="9">
         <v>46169.67021965278</v>
@@ -8121,16 +8124,16 @@
         <v>46174.84880980324</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I111" s="9">
         <v>46329</v>
@@ -8148,13 +8151,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q111" s="9">
         <v>46329</v>
@@ -8174,7 +8177,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B112" s="5">
         <v>46169.67022677083</v>
@@ -8184,16 +8187,16 @@
         <v>46174.84878571759</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I112" s="6"/>
       <c r="J112" s="5">
@@ -8209,13 +8212,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8225,7 +8228,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B113" s="9">
         <v>46170.633581828704</v>
@@ -8235,16 +8238,16 @@
         <v>46174.84878314815</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I113" s="10"/>
       <c r="J113" s="9">
@@ -8260,10 +8263,10 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -8276,7 +8279,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B114" s="5">
         <v>46174.821057037036</v>
@@ -8292,10 +8295,10 @@
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I114" s="6"/>
       <c r="J114" s="5">
@@ -8311,7 +8314,7 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>64</v>
@@ -8327,7 +8330,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B115" s="9">
         <v>46169.67031616898</v>
@@ -8337,7 +8340,7 @@
         <v>46174.82401751158</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>25</v>
@@ -8361,7 +8364,7 @@
         <v>26</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P115" s="10" t="s">
         <v>26</v>
@@ -8374,7 +8377,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B116" s="5">
         <v>46169.67031976852</v>
@@ -8384,16 +8387,16 @@
         <v>46174.84885483797</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="I116" s="5">
         <v>46330</v>
@@ -8411,13 +8414,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q116" s="5">
         <v>46330</v>
@@ -8437,7 +8440,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B117" s="9">
         <v>46169.6703253125</v>
@@ -8447,7 +8450,7 @@
         <v>46192.97339644676</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8474,13 +8477,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q117" s="9">
         <v>46330</v>
@@ -8500,7 +8503,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B118" s="5">
         <v>46169.670332430556</v>
@@ -8510,7 +8513,7 @@
         <v>46174.82401726852</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>25</v>
@@ -8534,7 +8537,7 @@
         <v>26</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>26</v>
@@ -8553,7 +8556,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B119" s="9">
         <v>46169.67033591435</v>
@@ -8563,7 +8566,7 @@
         <v>46174.848958703704</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8590,13 +8593,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q119" s="9">
         <v>46330</v>
@@ -8616,7 +8619,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B120" s="5">
         <v>46169.67034748843</v>
@@ -8626,7 +8629,7 @@
         <v>46174.84895586806</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8653,13 +8656,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q120" s="5">
         <v>46339</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="365">
   <si>
     <t>50001558 -  GESVIAL</t>
   </si>
@@ -251,7 +251,7 @@
     <t xml:space="preserve">Coordinacion Entrega con Cliente,Ingenieria Servicios </t>
   </si>
   <si>
-    <t>Media</t>
+    <t>Alta</t>
   </si>
   <si>
     <t>Tarea sin iniciar</t>
@@ -459,9 +459,6 @@
   </si>
   <si>
     <t>Fabricación Rodete  ot 4342,Generación OC Rodete  ot 4342</t>
-  </si>
-  <si>
-    <t>Alta</t>
   </si>
   <si>
     <t>1215174266247592</t>
@@ -1240,12 +1237,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFeec300"/>
+        <fgColor rgb="FFe8384f"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFe8384f"/>
+        <fgColor rgb="FFeec300"/>
       </patternFill>
     </fill>
   </fills>
@@ -2282,7 +2279,7 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46220.18415443287</v>
+        <v>46228.18121699074</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -2332,7 +2329,7 @@
       <c r="T12" s="6">
         <v>0</v>
       </c>
-      <c r="U12" s="12" t="s">
+      <c r="U12" s="11" t="s">
         <v>62</v>
       </c>
     </row>
@@ -2345,7 +2342,7 @@
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="9">
-        <v>46191.686801284726</v>
+        <v>46227.169055879625</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>64</v>
@@ -3255,7 +3252,7 @@
       <c r="R27" s="10"/>
       <c r="S27" s="10"/>
       <c r="T27" s="10"/>
-      <c r="U27" s="11" t="s">
+      <c r="U27" s="12" t="s">
         <v>114</v>
       </c>
     </row>
@@ -3381,7 +3378,7 @@
       <c r="T29" s="10">
         <v>0</v>
       </c>
-      <c r="U29" s="12" t="s">
+      <c r="U29" s="11" t="s">
         <v>62</v>
       </c>
     </row>
@@ -3442,7 +3439,7 @@
       <c r="T30" s="6">
         <v>0</v>
       </c>
-      <c r="U30" s="12" t="s">
+      <c r="U30" s="11" t="s">
         <v>62</v>
       </c>
     </row>
@@ -3501,8 +3498,8 @@
       <c r="R31" s="9">
         <v>46171</v>
       </c>
-      <c r="S31" s="12" t="s">
-        <v>129</v>
+      <c r="S31" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T31" s="10">
         <v>1</v>
@@ -3513,7 +3510,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B32" s="5">
         <v>46169.66911128472</v>
@@ -3525,7 +3522,7 @@
         <v>46182.6318109375</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
@@ -3558,7 +3555,7 @@
         <v>91</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3568,13 +3565,13 @@
       <c r="T32" s="6">
         <v>0</v>
       </c>
-      <c r="U32" s="12" t="s">
+      <c r="U32" s="11" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B33" s="9">
         <v>46169.669116805555</v>
@@ -3586,7 +3583,7 @@
         <v>46182.63457327546</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
@@ -3616,10 +3613,10 @@
         <v>127</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3629,13 +3626,13 @@
       <c r="T33" s="10">
         <v>0</v>
       </c>
-      <c r="U33" s="12" t="s">
+      <c r="U33" s="11" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B34" s="5">
         <v>46169.66912204861</v>
@@ -3647,7 +3644,7 @@
         <v>46182.6344355787</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -3677,7 +3674,7 @@
         <v>112</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>112</v>
@@ -3700,7 +3697,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B35" s="9">
         <v>46169.66912711806</v>
@@ -3712,7 +3709,7 @@
         <v>46182.63203959491</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
@@ -3739,13 +3736,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O35" s="10" t="s">
         <v>85</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3755,13 +3752,13 @@
       <c r="T35" s="10">
         <v>0</v>
       </c>
-      <c r="U35" s="12" t="s">
+      <c r="U35" s="11" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B36" s="5">
         <v>46169.66913270833</v>
@@ -3773,7 +3770,7 @@
         <v>46182.634411203704</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -3800,13 +3797,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3816,13 +3813,13 @@
       <c r="T36" s="6">
         <v>0</v>
       </c>
-      <c r="U36" s="12" t="s">
+      <c r="U36" s="11" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B37" s="9">
         <v>46169.66913809028</v>
@@ -3834,7 +3831,7 @@
         <v>46182.6343528588</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
@@ -3861,13 +3858,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3877,13 +3874,13 @@
       <c r="T37" s="10">
         <v>0</v>
       </c>
-      <c r="U37" s="12" t="s">
+      <c r="U37" s="11" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B38" s="5">
         <v>46169.66914475695</v>
@@ -3893,7 +3890,7 @@
         <v>46220.19404127315</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -3923,7 +3920,7 @@
         <v>112</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3934,19 +3931,19 @@
       <c r="R38" s="5">
         <v>46219</v>
       </c>
-      <c r="S38" s="12" t="s">
-        <v>129</v>
+      <c r="S38" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T38" s="6">
         <v>0</v>
       </c>
-      <c r="U38" s="12" t="s">
+      <c r="U38" s="11" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B39" s="9">
         <v>46169.669149270834</v>
@@ -3985,13 +3982,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O39" s="10" t="s">
         <v>109</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -4001,7 +3998,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B40" s="5">
         <v>46169.66915408565</v>
@@ -4011,7 +4008,7 @@
         <v>46219.16855109954</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
@@ -4038,13 +4035,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>110</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4054,7 +4051,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B41" s="9">
         <v>46169.66915865741</v>
@@ -4066,16 +4063,16 @@
         <v>46209.82174662037</v>
       </c>
       <c r="E41" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="F41" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G41" s="10" t="s">
+      <c r="H41" s="10" t="s">
         <v>158</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>159</v>
       </c>
       <c r="I41" s="9">
         <v>46245</v>
@@ -4096,7 +4093,7 @@
         <v>112</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P41" s="10" t="s">
         <v>112</v>
@@ -4119,7 +4116,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B42" s="5">
         <v>46169.66916377315</v>
@@ -4131,16 +4128,16 @@
         <v>46199.56927892361</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I42" s="5">
         <v>46245</v>
@@ -4158,13 +4155,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>96</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4174,13 +4171,13 @@
       <c r="T42" s="6">
         <v>0</v>
       </c>
-      <c r="U42" s="12" t="s">
+      <c r="U42" s="11" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B43" s="9">
         <v>46169.66916960648</v>
@@ -4192,16 +4189,16 @@
         <v>46205.61247092593</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H43" s="10" t="s">
         <v>158</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>159</v>
       </c>
       <c r="I43" s="9">
         <v>46247</v>
@@ -4219,13 +4216,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4235,13 +4232,13 @@
       <c r="T43" s="10">
         <v>0</v>
       </c>
-      <c r="U43" s="12" t="s">
+      <c r="U43" s="11" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B44" s="5">
         <v>46169.66917503472</v>
@@ -4253,16 +4250,16 @@
         <v>46199.567282199074</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I44" s="5">
         <v>46245</v>
@@ -4283,7 +4280,7 @@
         <v>112</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>26</v>
@@ -4306,7 +4303,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B45" s="9">
         <v>46169.669178888886</v>
@@ -4324,10 +4321,10 @@
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>158</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>159</v>
       </c>
       <c r="I45" s="9">
         <v>46245</v>
@@ -4345,13 +4342,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>100</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4361,7 +4358,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B46" s="5">
         <v>46169.669183680555</v>
@@ -4373,16 +4370,16 @@
         <v>46199.56984034722</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I46" s="5">
         <v>46247</v>
@@ -4400,13 +4397,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>101</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4416,7 +4413,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B47" s="9">
         <v>46169.66918849537</v>
@@ -4428,16 +4425,16 @@
         <v>46204.863616284725</v>
       </c>
       <c r="E47" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="F47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="10" t="s">
+      <c r="H47" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="I47" s="9">
         <v>46245</v>
@@ -4458,7 +4455,7 @@
         <v>112</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>26</v>
@@ -4481,7 +4478,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B48" s="5">
         <v>46169.66919252315</v>
@@ -4499,10 +4496,10 @@
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I48" s="5">
         <v>46245</v>
@@ -4520,13 +4517,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>106</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4536,7 +4533,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B49" s="9">
         <v>46169.66919734953</v>
@@ -4548,16 +4545,16 @@
         <v>46204.8635487037</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="I49" s="9">
         <v>46254</v>
@@ -4575,13 +4572,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O49" s="10" t="s">
         <v>107</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4591,7 +4588,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
         <v>46169.66920229167</v>
@@ -4603,16 +4600,16 @@
         <v>46210.65313525463</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="H50" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I50" s="5">
         <v>46286</v>
@@ -4630,10 +4627,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4646,7 +4643,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B51" s="9">
         <v>46169.66924202546</v>
@@ -4658,16 +4655,16 @@
         <v>46199.57084909722</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>158</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>159</v>
       </c>
       <c r="I51" s="9">
         <v>46245</v>
@@ -4688,7 +4685,7 @@
         <v>112</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P51" s="10" t="s">
         <v>26</v>
@@ -4711,7 +4708,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B52" s="5">
         <v>46169.66924635417</v>
@@ -4729,10 +4726,10 @@
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I52" s="5">
         <v>46245</v>
@@ -4750,13 +4747,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>103</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4766,7 +4763,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B53" s="9">
         <v>46169.66925091435</v>
@@ -4778,16 +4775,16 @@
         <v>46199.57082731482</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>158</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>159</v>
       </c>
       <c r="I53" s="9">
         <v>46247</v>
@@ -4805,13 +4802,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O53" s="10" t="s">
         <v>104</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4821,7 +4818,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B54" s="5">
         <v>46169.669255659726</v>
@@ -4833,7 +4830,7 @@
         <v>46210.52487434028</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>25</v>
@@ -4857,7 +4854,7 @@
         <v>26</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -4874,7 +4871,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B55" s="9">
         <v>46169.66925896991</v>
@@ -4886,16 +4883,16 @@
         <v>46197.71564204861</v>
       </c>
       <c r="E55" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G55" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G55" s="10" t="s">
+      <c r="H55" s="10" t="s">
         <v>202</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>203</v>
       </c>
       <c r="I55" s="9">
         <v>46167</v>
@@ -4907,19 +4904,19 @@
         <v>26</v>
       </c>
       <c r="L55" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="M55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N55" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="O55" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="M55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N55" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="O55" s="10" t="s">
-        <v>205</v>
-      </c>
       <c r="P55" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q55" s="9">
         <v>46167</v>
@@ -4927,8 +4924,8 @@
       <c r="R55" s="9">
         <v>46184</v>
       </c>
-      <c r="S55" s="12" t="s">
-        <v>129</v>
+      <c r="S55" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T55" s="10">
         <v>1</v>
@@ -4939,7 +4936,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B56" s="5">
         <v>46169.66926408565</v>
@@ -4951,16 +4948,16 @@
         <v>46195.94997940972</v>
       </c>
       <c r="E56" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G56" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="F56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G56" s="6" t="s">
+      <c r="H56" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I56" s="5">
         <v>46167</v>
@@ -4978,13 +4975,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>79</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4994,7 +4991,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B57" s="9">
         <v>46169.66926952546</v>
@@ -5006,16 +5003,16 @@
         <v>46195.94998958333</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I57" s="9">
         <v>46167</v>
@@ -5033,13 +5030,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O57" s="10" t="s">
         <v>79</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -5049,7 +5046,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B58" s="5">
         <v>46169.66929263889</v>
@@ -5061,16 +5058,16 @@
         <v>46197.71567513889</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="I58" s="5">
         <v>46220</v>
@@ -5088,13 +5085,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q58" s="5">
         <v>46220</v>
@@ -5114,7 +5111,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B59" s="9">
         <v>46169.66929775463</v>
@@ -5126,16 +5123,16 @@
         <v>46195.950096458335</v>
       </c>
       <c r="E59" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G59" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="F59" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G59" s="10" t="s">
+      <c r="H59" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I59" s="9">
         <v>46181</v>
@@ -5153,13 +5150,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O59" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="P59" s="10" t="s">
         <v>218</v>
-      </c>
-      <c r="P59" s="10" t="s">
-        <v>219</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5169,7 +5166,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B60" s="5">
         <v>46169.66930358796</v>
@@ -5181,16 +5178,16 @@
         <v>46196.87985491898</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I60" s="5">
         <v>46181</v>
@@ -5208,13 +5205,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5224,7 +5221,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B61" s="9">
         <v>46169.669327048614</v>
@@ -5242,10 +5239,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I61" s="9">
         <v>46240</v>
@@ -5263,13 +5260,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q61" s="9">
         <v>46240</v>
@@ -5289,7 +5286,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B62" s="5">
         <v>46169.6693399537</v>
@@ -5301,16 +5298,16 @@
         <v>46195.95042396991</v>
       </c>
       <c r="E62" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G62" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="F62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G62" s="6" t="s">
+      <c r="H62" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I62" s="5">
         <v>46188</v>
@@ -5331,7 +5328,7 @@
         <v>97</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>97</v>
@@ -5344,7 +5341,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B63" s="9">
         <v>46169.669361203705</v>
@@ -5354,16 +5351,16 @@
         <v>46174.84660805555</v>
       </c>
       <c r="E63" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="F63" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G63" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="F63" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G63" s="10" t="s">
+      <c r="H63" s="10" t="s">
         <v>227</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>228</v>
       </c>
       <c r="I63" s="9">
         <v>46322</v>
@@ -5381,10 +5378,10 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P63" s="10" t="s">
         <v>26</v>
@@ -5401,13 +5398,13 @@
       <c r="T63" s="10">
         <v>0</v>
       </c>
-      <c r="U63" s="12" t="s">
+      <c r="U63" s="11" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B64" s="5">
         <v>46169.66936501158</v>
@@ -5417,16 +5414,16 @@
         <v>46174.846919421296</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>227</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>228</v>
       </c>
       <c r="I64" s="5">
         <v>46290</v>
@@ -5444,13 +5441,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5460,7 +5457,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B65" s="9">
         <v>46169.669418136575</v>
@@ -5472,7 +5469,7 @@
         <v>46210.65198340278</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>25</v>
@@ -5496,7 +5493,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P65" s="10" t="s">
         <v>26</v>
@@ -5513,7 +5510,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B66" s="5">
         <v>46169.66942685185</v>
@@ -5525,16 +5522,16 @@
         <v>46210.651395196764</v>
       </c>
       <c r="E66" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G66" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="F66" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G66" s="6" t="s">
+      <c r="H66" s="6" t="s">
         <v>236</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>237</v>
       </c>
       <c r="I66" s="5">
         <v>46258</v>
@@ -5552,13 +5549,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Q66" s="5">
         <v>46258</v>
@@ -5578,7 +5575,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B67" s="9">
         <v>46169.669432361115</v>
@@ -5590,16 +5587,16 @@
         <v>46210.65197202546</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I67" s="9">
         <v>46260</v>
@@ -5617,13 +5614,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O67" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="P67" s="10" t="s">
         <v>241</v>
-      </c>
-      <c r="P67" s="10" t="s">
-        <v>242</v>
       </c>
       <c r="Q67" s="9">
         <v>46260</v>
@@ -5643,7 +5640,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B68" s="5">
         <v>46169.66943836806</v>
@@ -5655,16 +5652,16 @@
         <v>46210.65139929398</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>236</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>237</v>
       </c>
       <c r="I68" s="5">
         <v>46258</v>
@@ -5682,13 +5679,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q68" s="5">
         <v>46258</v>
@@ -5708,7 +5705,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B69" s="9">
         <v>46169.669443692124</v>
@@ -5720,16 +5717,16 @@
         <v>46210.651975879635</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I69" s="9">
         <v>46260</v>
@@ -5747,13 +5744,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q69" s="9">
         <v>46260</v>
@@ -5773,7 +5770,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B70" s="5">
         <v>46169.669448368055</v>
@@ -5785,16 +5782,16 @@
         <v>46210.65141630787</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>236</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>237</v>
       </c>
       <c r="I70" s="5">
         <v>46258</v>
@@ -5812,13 +5809,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q70" s="5">
         <v>46258</v>
@@ -5838,7 +5835,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B71" s="9">
         <v>46169.66945298611</v>
@@ -5850,16 +5847,16 @@
         <v>46210.65197810185</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H71" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I71" s="9">
         <v>46260</v>
@@ -5877,13 +5874,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q71" s="9">
         <v>46260</v>
@@ -5903,7 +5900,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B72" s="5">
         <v>46169.66945778935</v>
@@ -5913,7 +5910,7 @@
         <v>46209.909264270835</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>25</v>
@@ -5937,7 +5934,7 @@
         <v>26</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>26</v>
@@ -5950,7 +5947,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B73" s="9">
         <v>46169.66946104167</v>
@@ -5962,16 +5959,16 @@
         <v>46225.8618784375</v>
       </c>
       <c r="E73" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="F73" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G73" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="F73" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G73" s="10" t="s">
+      <c r="H73" s="10" t="s">
         <v>257</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>258</v>
       </c>
       <c r="I73" s="9">
         <v>46262</v>
@@ -5989,13 +5986,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q73" s="9">
         <v>46262</v>
@@ -6015,7 +6012,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B74" s="5">
         <v>46169.669467280095</v>
@@ -6027,16 +6024,16 @@
         <v>46210.65196928241</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="I74" s="5">
         <v>46262</v>
@@ -6054,13 +6051,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O74" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="P74" s="6" t="s">
         <v>261</v>
-      </c>
-      <c r="P74" s="6" t="s">
-        <v>262</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6070,7 +6067,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B75" s="9">
         <v>46169.66950289352</v>
@@ -6080,16 +6077,16 @@
         <v>46209.90954123843</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="H75" s="10" t="s">
         <v>257</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>258</v>
       </c>
       <c r="I75" s="9">
         <v>46273</v>
@@ -6107,13 +6104,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q75" s="9">
         <v>46273</v>
@@ -6127,13 +6124,13 @@
       <c r="T75" s="10">
         <v>0.1</v>
       </c>
-      <c r="U75" s="11" t="s">
+      <c r="U75" s="12" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B76" s="5">
         <v>46169.66950758102</v>
@@ -6143,16 +6140,16 @@
         <v>46209.90937868056</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="I76" s="5">
         <v>46273</v>
@@ -6170,13 +6167,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O76" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="P76" s="6" t="s">
         <v>266</v>
-      </c>
-      <c r="P76" s="6" t="s">
-        <v>267</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6186,7 +6183,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B77" s="9">
         <v>46169.66953380787</v>
@@ -6196,16 +6193,16 @@
         <v>46209.908330833336</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H77" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I77" s="9">
         <v>46294</v>
@@ -6223,13 +6220,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q77" s="9">
         <v>46294</v>
@@ -6243,13 +6240,13 @@
       <c r="T77" s="10">
         <v>0</v>
       </c>
-      <c r="U77" s="12" t="s">
+      <c r="U77" s="11" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B78" s="5">
         <v>46169.66953854167</v>
@@ -6259,16 +6256,16 @@
         <v>46197.84256122685</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -6284,13 +6281,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6300,7 +6297,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B79" s="9">
         <v>46169.66960108797</v>
@@ -6310,7 +6307,7 @@
         <v>46209.85402508102</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>25</v>
@@ -6334,7 +6331,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P79" s="10" t="s">
         <v>26</v>
@@ -6343,13 +6340,13 @@
       <c r="R79" s="10"/>
       <c r="S79" s="10"/>
       <c r="T79" s="10"/>
-      <c r="U79" s="11" t="s">
+      <c r="U79" s="12" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B80" s="5">
         <v>46169.66960956018</v>
@@ -6361,16 +6358,16 @@
         <v>46209.844928101855</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>236</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>237</v>
       </c>
       <c r="I80" s="5">
         <v>46174</v>
@@ -6388,13 +6385,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q80" s="5">
         <v>46174</v>
@@ -6402,8 +6399,8 @@
       <c r="R80" s="5">
         <v>46174</v>
       </c>
-      <c r="S80" s="12" t="s">
-        <v>129</v>
+      <c r="S80" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T80" s="6">
         <v>1</v>
@@ -6414,7 +6411,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B81" s="9">
         <v>46169.6696165162</v>
@@ -6426,16 +6423,16 @@
         <v>46209.84471936343</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="H81" s="10" t="s">
         <v>236</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>237</v>
       </c>
       <c r="I81" s="9">
         <v>46288</v>
@@ -6453,13 +6450,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>124</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q81" s="9">
         <v>46288</v>
@@ -6479,7 +6476,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B82" s="5">
         <v>46169.669622939815</v>
@@ -6491,16 +6488,16 @@
         <v>46209.85430440972</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>236</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>237</v>
       </c>
       <c r="I82" s="5">
         <v>46308</v>
@@ -6518,13 +6515,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q82" s="5">
         <v>46308</v>
@@ -6544,7 +6541,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B83" s="9">
         <v>46169.66962980324</v>
@@ -6554,16 +6551,16 @@
         <v>46204.86356525463</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="H83" s="10" t="s">
         <v>236</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>237</v>
       </c>
       <c r="I83" s="9">
         <v>46287</v>
@@ -6581,13 +6578,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Q83" s="9">
         <v>46287</v>
@@ -6601,13 +6598,13 @@
       <c r="T83" s="10">
         <v>0</v>
       </c>
-      <c r="U83" s="11" t="s">
+      <c r="U83" s="12" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B84" s="5">
         <v>46169.669635185186</v>
@@ -6623,10 +6620,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>236</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>237</v>
       </c>
       <c r="I84" s="5">
         <v>46220</v>
@@ -6644,13 +6641,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Q84" s="5">
         <v>46220</v>
@@ -6658,19 +6655,19 @@
       <c r="R84" s="5">
         <v>46220</v>
       </c>
-      <c r="S84" s="12" t="s">
-        <v>129</v>
+      <c r="S84" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
       </c>
-      <c r="U84" s="12" t="s">
+      <c r="U84" s="11" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B85" s="9">
         <v>46169.66964790509</v>
@@ -6680,7 +6677,7 @@
         <v>46223.56797070602</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>25</v>
@@ -6704,7 +6701,7 @@
         <v>26</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>26</v>
@@ -6717,7 +6714,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B86" s="5">
         <v>46169.66965109954</v>
@@ -6727,7 +6724,7 @@
         <v>46223.56814725694</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6754,13 +6751,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q86" s="5">
         <v>46294</v>
@@ -6774,13 +6771,13 @@
       <c r="T86" s="6">
         <v>0</v>
       </c>
-      <c r="U86" s="12" t="s">
+      <c r="U86" s="11" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B87" s="9">
         <v>46169.6696568287</v>
@@ -6790,7 +6787,7 @@
         <v>46223.5676475463</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6817,13 +6814,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6833,7 +6830,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B88" s="5">
         <v>46169.669688622685</v>
@@ -6845,7 +6842,7 @@
         <v>46223.568163460644</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6872,13 +6869,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q88" s="5">
         <v>46316</v>
@@ -6898,7 +6895,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B89" s="9">
         <v>46169.66969347223</v>
@@ -6908,7 +6905,7 @@
         <v>46223.83603929398</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6933,13 +6930,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O89" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="P89" s="10" t="s">
         <v>297</v>
-      </c>
-      <c r="P89" s="10" t="s">
-        <v>298</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6949,7 +6946,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B90" s="5">
         <v>46169.66972681713</v>
@@ -6961,7 +6958,7 @@
         <v>46223.56815898148</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6988,13 +6985,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q90" s="5">
         <v>46317</v>
@@ -7014,7 +7011,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B91" s="9">
         <v>46169.66973180555</v>
@@ -7024,7 +7021,7 @@
         <v>46223.56782162037</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -7051,13 +7048,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O91" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="P91" s="10" t="s">
         <v>302</v>
-      </c>
-      <c r="P91" s="10" t="s">
-        <v>303</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -7067,7 +7064,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B92" s="5">
         <v>46169.66981054399</v>
@@ -7077,7 +7074,7 @@
         <v>46223.56814546297</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7104,13 +7101,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q92" s="5">
         <v>46318</v>
@@ -7124,13 +7121,13 @@
       <c r="T92" s="6">
         <v>0</v>
       </c>
-      <c r="U92" s="12" t="s">
+      <c r="U92" s="11" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B93" s="9">
         <v>46169.66981724537</v>
@@ -7140,7 +7137,7 @@
         <v>46223.56789047454</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7167,13 +7164,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O93" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="P93" s="10" t="s">
         <v>307</v>
-      </c>
-      <c r="P93" s="10" t="s">
-        <v>308</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7183,7 +7180,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B94" s="5">
         <v>46169.669861041664</v>
@@ -7193,7 +7190,7 @@
         <v>46223.568144791665</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7220,13 +7217,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q94" s="5">
         <v>46321</v>
@@ -7240,13 +7237,13 @@
       <c r="T94" s="6">
         <v>0</v>
       </c>
-      <c r="U94" s="12" t="s">
+      <c r="U94" s="11" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B95" s="9">
         <v>46169.66986724537</v>
@@ -7256,7 +7253,7 @@
         <v>46223.56796597222</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7283,13 +7280,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7299,7 +7296,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B96" s="5">
         <v>46169.66990296297</v>
@@ -7309,7 +7306,7 @@
         <v>46223.568144212964</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7336,13 +7333,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q96" s="5">
         <v>46323</v>
@@ -7356,13 +7353,13 @@
       <c r="T96" s="6">
         <v>0</v>
       </c>
-      <c r="U96" s="12" t="s">
+      <c r="U96" s="11" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B97" s="9">
         <v>46169.66994555556</v>
@@ -7372,7 +7369,7 @@
         <v>46223.836147291666</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7397,13 +7394,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7413,7 +7410,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B98" s="5">
         <v>46169.669978645834</v>
@@ -7423,7 +7420,7 @@
         <v>46174.82401747685</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>25</v>
@@ -7447,7 +7444,7 @@
         <v>26</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>26</v>
@@ -7460,7 +7457,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B99" s="9">
         <v>46169.66998244213</v>
@@ -7470,16 +7467,16 @@
         <v>46174.84843513889</v>
       </c>
       <c r="E99" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="F99" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G99" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="F99" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G99" s="10" t="s">
+      <c r="H99" s="10" t="s">
         <v>323</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>324</v>
       </c>
       <c r="I99" s="9">
         <v>46324</v>
@@ -7497,13 +7494,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q99" s="9">
         <v>46324</v>
@@ -7517,13 +7514,13 @@
       <c r="T99" s="10">
         <v>0</v>
       </c>
-      <c r="U99" s="12" t="s">
+      <c r="U99" s="11" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B100" s="5">
         <v>46169.66998994213</v>
@@ -7533,16 +7530,16 @@
         <v>46174.84838837963</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="H100" s="6" t="s">
         <v>323</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>324</v>
       </c>
       <c r="I100" s="6"/>
       <c r="J100" s="5">
@@ -7558,13 +7555,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7574,7 +7571,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B101" s="9">
         <v>46170.63118891204</v>
@@ -7584,16 +7581,16 @@
         <v>46209.90833168982</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="H101" s="10" t="s">
         <v>323</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>324</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="9">
@@ -7609,13 +7606,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7625,7 +7622,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B102" s="5">
         <v>46174.820955891206</v>
@@ -7641,10 +7638,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="H102" s="6" t="s">
         <v>323</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>324</v>
       </c>
       <c r="I102" s="5">
         <v>46324</v>
@@ -7662,13 +7659,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>64</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7678,7 +7675,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B103" s="9">
         <v>46169.670044224535</v>
@@ -7688,7 +7685,7 @@
         <v>46223.56892738426</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7713,13 +7710,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q103" s="9">
         <v>46325</v>
@@ -7733,13 +7730,13 @@
       <c r="T103" s="10">
         <v>0</v>
       </c>
-      <c r="U103" s="12" t="s">
+      <c r="U103" s="11" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B104" s="5">
         <v>46169.670049050925</v>
@@ -7749,7 +7746,7 @@
         <v>46223.568262175926</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7774,13 +7771,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7790,7 +7787,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B105" s="9">
         <v>46170.63213679398</v>
@@ -7800,7 +7797,7 @@
         <v>46223.56826151621</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7825,13 +7822,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7841,7 +7838,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B106" s="5">
         <v>46174.82099290509</v>
@@ -7851,7 +7848,7 @@
         <v>46223.5682608912</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7878,7 +7875,7 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>64</v>
@@ -7894,7 +7891,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B107" s="9">
         <v>46169.67013976852</v>
@@ -7904,16 +7901,16 @@
         <v>46174.84870307871</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="H107" s="10" t="s">
         <v>257</v>
-      </c>
-      <c r="H107" s="10" t="s">
-        <v>258</v>
       </c>
       <c r="I107" s="10"/>
       <c r="J107" s="9">
@@ -7929,13 +7926,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q107" s="9">
         <v>46328</v>
@@ -7949,13 +7946,13 @@
       <c r="T107" s="10">
         <v>0</v>
       </c>
-      <c r="U107" s="12" t="s">
+      <c r="U107" s="11" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B108" s="5">
         <v>46169.670151377315</v>
@@ -7965,16 +7962,16 @@
         <v>46174.848669872685</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="H108" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="I108" s="5">
         <v>46328</v>
@@ -7992,13 +7989,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8008,7 +8005,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B109" s="9">
         <v>46170.63285997685</v>
@@ -8018,16 +8015,16 @@
         <v>46174.848667314815</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="H109" s="10" t="s">
         <v>257</v>
-      </c>
-      <c r="H109" s="10" t="s">
-        <v>258</v>
       </c>
       <c r="I109" s="9">
         <v>46328</v>
@@ -8045,13 +8042,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -8061,7 +8058,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B110" s="5">
         <v>46174.821024143515</v>
@@ -8077,10 +8074,10 @@
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="H110" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="I110" s="5">
         <v>46328</v>
@@ -8098,10 +8095,10 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>64</v>
@@ -8114,7 +8111,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B111" s="9">
         <v>46169.67021965278</v>
@@ -8124,16 +8121,16 @@
         <v>46174.84880980324</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="H111" s="10" t="s">
         <v>257</v>
-      </c>
-      <c r="H111" s="10" t="s">
-        <v>258</v>
       </c>
       <c r="I111" s="9">
         <v>46329</v>
@@ -8151,13 +8148,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Q111" s="9">
         <v>46329</v>
@@ -8171,13 +8168,13 @@
       <c r="T111" s="10">
         <v>0</v>
       </c>
-      <c r="U111" s="12" t="s">
+      <c r="U111" s="11" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B112" s="5">
         <v>46169.67022677083</v>
@@ -8187,16 +8184,16 @@
         <v>46174.84878571759</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="H112" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="I112" s="6"/>
       <c r="J112" s="5">
@@ -8212,13 +8209,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8228,7 +8225,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B113" s="9">
         <v>46170.633581828704</v>
@@ -8238,16 +8235,16 @@
         <v>46174.84878314815</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="H113" s="10" t="s">
         <v>257</v>
-      </c>
-      <c r="H113" s="10" t="s">
-        <v>258</v>
       </c>
       <c r="I113" s="10"/>
       <c r="J113" s="9">
@@ -8263,10 +8260,10 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -8279,7 +8276,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B114" s="5">
         <v>46174.821057037036</v>
@@ -8295,10 +8292,10 @@
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="H114" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="H114" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="I114" s="6"/>
       <c r="J114" s="5">
@@ -8314,7 +8311,7 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>64</v>
@@ -8330,7 +8327,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B115" s="9">
         <v>46169.67031616898</v>
@@ -8340,7 +8337,7 @@
         <v>46174.82401751158</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>25</v>
@@ -8364,7 +8361,7 @@
         <v>26</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P115" s="10" t="s">
         <v>26</v>
@@ -8377,7 +8374,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B116" s="5">
         <v>46169.67031976852</v>
@@ -8387,16 +8384,16 @@
         <v>46174.84885483797</v>
       </c>
       <c r="E116" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="F116" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G116" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="F116" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G116" s="6" t="s">
+      <c r="H116" s="6" t="s">
         <v>354</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>355</v>
       </c>
       <c r="I116" s="5">
         <v>46330</v>
@@ -8414,13 +8411,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Q116" s="5">
         <v>46330</v>
@@ -8434,13 +8431,13 @@
       <c r="T116" s="6">
         <v>0</v>
       </c>
-      <c r="U116" s="12" t="s">
+      <c r="U116" s="11" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B117" s="9">
         <v>46169.6703253125</v>
@@ -8450,7 +8447,7 @@
         <v>46192.97339644676</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8477,13 +8474,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Q117" s="9">
         <v>46330</v>
@@ -8497,13 +8494,13 @@
       <c r="T117" s="10">
         <v>0</v>
       </c>
-      <c r="U117" s="12" t="s">
+      <c r="U117" s="11" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B118" s="5">
         <v>46169.670332430556</v>
@@ -8513,7 +8510,7 @@
         <v>46174.82401726852</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>25</v>
@@ -8537,7 +8534,7 @@
         <v>26</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>26</v>
@@ -8550,13 +8547,13 @@
       <c r="T118" s="6">
         <v>0</v>
       </c>
-      <c r="U118" s="12" t="s">
+      <c r="U118" s="11" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B119" s="9">
         <v>46169.67033591435</v>
@@ -8566,7 +8563,7 @@
         <v>46174.848958703704</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8593,13 +8590,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="Q119" s="9">
         <v>46330</v>
@@ -8613,13 +8610,13 @@
       <c r="T119" s="10">
         <v>0</v>
       </c>
-      <c r="U119" s="12" t="s">
+      <c r="U119" s="11" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B120" s="5">
         <v>46169.67034748843</v>
@@ -8629,7 +8626,7 @@
         <v>46174.84895586806</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8656,13 +8653,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="Q120" s="5">
         <v>46339</v>
@@ -8676,7 +8673,7 @@
       <c r="T120" s="6">
         <v>0</v>
       </c>
-      <c r="U120" s="12" t="s">
+      <c r="U120" s="11" t="s">
         <v>62</v>
       </c>
     </row>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="365">
   <si>
     <t>50001558 -  GESVIAL</t>
   </si>
@@ -850,7 +850,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+    <t xml:space="preserve">OT2 4307 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
   </si>
   <si>
     <t>1215174141301410</t>
@@ -2165,9 +2165,11 @@
       <c r="B10" s="5">
         <v>46169.6688215162</v>
       </c>
-      <c r="C10" s="6"/>
+      <c r="C10" s="5">
+        <v>46231.513086886574</v>
+      </c>
       <c r="D10" s="5">
-        <v>46195.60097974537</v>
+        <v>46231.52879856482</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2202,8 +2204,12 @@
       <c r="Q10" s="6"/>
       <c r="R10" s="6"/>
       <c r="S10" s="6"/>
-      <c r="T10" s="6"/>
-      <c r="U10" s="6"/>
+      <c r="T10" s="6">
+        <v>1</v>
+      </c>
+      <c r="U10" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
@@ -2279,7 +2285,7 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46228.18121699074</v>
+        <v>46231.52879386574</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -5956,7 +5962,7 @@
         <v>46209.90925715277</v>
       </c>
       <c r="D73" s="9">
-        <v>46225.8618784375</v>
+        <v>46231.560382615746</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>255</v>
@@ -7464,7 +7470,7 @@
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46174.84843513889</v>
+        <v>46231.52879813657</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>321</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -5962,7 +5962,7 @@
         <v>46209.90925715277</v>
       </c>
       <c r="D73" s="9">
-        <v>46231.560382615746</v>
+        <v>46231.65309703704</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>255</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="366">
   <si>
     <t>50001558 -  GESVIAL</t>
   </si>
@@ -722,6 +722,9 @@
   </si>
   <si>
     <t>OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4344 - MANGA DE VENTILACION Ø1600MM</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1215174382581715</t>
@@ -5061,7 +5064,7 @@
         <v>46195.95012040509</v>
       </c>
       <c r="D58" s="5">
-        <v>46197.71567513889</v>
+        <v>46232.17505278935</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>214</v>
@@ -5105,8 +5108,8 @@
       <c r="R58" s="5">
         <v>46239</v>
       </c>
-      <c r="S58" s="7" t="s">
-        <v>33</v>
+      <c r="S58" s="12" t="s">
+        <v>216</v>
       </c>
       <c r="T58" s="6">
         <v>1</v>
@@ -5117,7 +5120,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B59" s="9">
         <v>46169.66929775463</v>
@@ -5159,10 +5162,10 @@
         <v>214</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5172,7 +5175,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B60" s="5">
         <v>46169.66930358796</v>
@@ -5214,7 +5217,7 @@
         <v>214</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>214</v>
@@ -5227,7 +5230,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B61" s="9">
         <v>46169.669327048614</v>
@@ -5272,7 +5275,7 @@
         <v>206</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q61" s="9">
         <v>46240</v>
@@ -5292,7 +5295,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B62" s="5">
         <v>46169.6693399537</v>
@@ -5347,7 +5350,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B63" s="9">
         <v>46169.669361203705</v>
@@ -5357,16 +5360,16 @@
         <v>46174.84660805555</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I63" s="9">
         <v>46322</v>
@@ -5410,7 +5413,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B64" s="5">
         <v>46169.66936501158</v>
@@ -5426,10 +5429,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I64" s="5">
         <v>46290</v>
@@ -5447,13 +5450,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5463,7 +5466,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B65" s="9">
         <v>46169.669418136575</v>
@@ -5475,7 +5478,7 @@
         <v>46210.65198340278</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>25</v>
@@ -5499,7 +5502,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P65" s="10" t="s">
         <v>26</v>
@@ -5516,7 +5519,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B66" s="5">
         <v>46169.66942685185</v>
@@ -5528,16 +5531,16 @@
         <v>46210.651395196764</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I66" s="5">
         <v>46258</v>
@@ -5555,13 +5558,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>164</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q66" s="5">
         <v>46258</v>
@@ -5581,7 +5584,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B67" s="9">
         <v>46169.669432361115</v>
@@ -5593,7 +5596,7 @@
         <v>46210.65197202546</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -5620,13 +5623,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q67" s="9">
         <v>46260</v>
@@ -5646,7 +5649,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B68" s="5">
         <v>46169.66943836806</v>
@@ -5658,16 +5661,16 @@
         <v>46210.65139929398</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I68" s="5">
         <v>46258</v>
@@ -5685,13 +5688,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>172</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q68" s="5">
         <v>46258</v>
@@ -5711,7 +5714,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B69" s="9">
         <v>46169.669443692124</v>
@@ -5723,7 +5726,7 @@
         <v>46210.651975879635</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -5750,10 +5753,10 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P69" s="10" t="s">
         <v>206</v>
@@ -5776,7 +5779,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B70" s="5">
         <v>46169.669448368055</v>
@@ -5788,16 +5791,16 @@
         <v>46210.65141630787</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I70" s="5">
         <v>46258</v>
@@ -5815,13 +5818,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>194</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q70" s="5">
         <v>46258</v>
@@ -5841,7 +5844,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B71" s="9">
         <v>46169.66945298611</v>
@@ -5853,7 +5856,7 @@
         <v>46210.65197810185</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
@@ -5880,10 +5883,10 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>206</v>
@@ -5906,7 +5909,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B72" s="5">
         <v>46169.66945778935</v>
@@ -5916,7 +5919,7 @@
         <v>46209.909264270835</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>25</v>
@@ -5940,7 +5943,7 @@
         <v>26</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>26</v>
@@ -5953,7 +5956,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B73" s="9">
         <v>46169.66946104167</v>
@@ -5965,16 +5968,16 @@
         <v>46231.65309703704</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I73" s="9">
         <v>46262</v>
@@ -5992,13 +5995,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q73" s="9">
         <v>46262</v>
@@ -6018,7 +6021,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B74" s="5">
         <v>46169.669467280095</v>
@@ -6036,10 +6039,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I74" s="5">
         <v>46262</v>
@@ -6057,13 +6060,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6073,7 +6076,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B75" s="9">
         <v>46169.66950289352</v>
@@ -6083,16 +6086,16 @@
         <v>46209.90954123843</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I75" s="9">
         <v>46273</v>
@@ -6110,13 +6113,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O75" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q75" s="9">
         <v>46273</v>
@@ -6136,7 +6139,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B76" s="5">
         <v>46169.66950758102</v>
@@ -6152,10 +6155,10 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I76" s="5">
         <v>46273</v>
@@ -6173,13 +6176,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6189,7 +6192,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B77" s="9">
         <v>46169.66953380787</v>
@@ -6199,7 +6202,7 @@
         <v>46209.908330833336</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6226,13 +6229,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O77" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q77" s="9">
         <v>46294</v>
@@ -6252,7 +6255,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B78" s="5">
         <v>46169.66953854167</v>
@@ -6287,13 +6290,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6303,7 +6306,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B79" s="9">
         <v>46169.66960108797</v>
@@ -6313,7 +6316,7 @@
         <v>46209.85402508102</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>25</v>
@@ -6337,7 +6340,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P79" s="10" t="s">
         <v>26</v>
@@ -6352,7 +6355,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B80" s="5">
         <v>46169.66960956018</v>
@@ -6364,16 +6367,16 @@
         <v>46209.844928101855</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I80" s="5">
         <v>46174</v>
@@ -6391,13 +6394,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>133</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q80" s="5">
         <v>46174</v>
@@ -6417,7 +6420,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B81" s="9">
         <v>46169.6696165162</v>
@@ -6429,16 +6432,16 @@
         <v>46209.84471936343</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I81" s="9">
         <v>46288</v>
@@ -6456,13 +6459,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>124</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q81" s="9">
         <v>46288</v>
@@ -6482,7 +6485,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B82" s="5">
         <v>46169.669622939815</v>
@@ -6494,16 +6497,16 @@
         <v>46209.85430440972</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I82" s="5">
         <v>46308</v>
@@ -6521,13 +6524,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>142</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q82" s="5">
         <v>46308</v>
@@ -6547,7 +6550,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B83" s="9">
         <v>46169.66962980324</v>
@@ -6557,16 +6560,16 @@
         <v>46204.86356525463</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I83" s="9">
         <v>46287</v>
@@ -6584,13 +6587,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O83" s="10" t="s">
         <v>182</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q83" s="9">
         <v>46287</v>
@@ -6610,7 +6613,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B84" s="5">
         <v>46169.669635185186</v>
@@ -6626,10 +6629,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I84" s="5">
         <v>46220</v>
@@ -6647,13 +6650,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>153</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q84" s="5">
         <v>46220</v>
@@ -6673,7 +6676,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B85" s="9">
         <v>46169.66964790509</v>
@@ -6683,7 +6686,7 @@
         <v>46223.56797070602</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>25</v>
@@ -6707,7 +6710,7 @@
         <v>26</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>26</v>
@@ -6720,7 +6723,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B86" s="5">
         <v>46169.66965109954</v>
@@ -6730,7 +6733,7 @@
         <v>46223.56814725694</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6757,13 +6760,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q86" s="5">
         <v>46294</v>
@@ -6783,7 +6786,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B87" s="9">
         <v>46169.6696568287</v>
@@ -6820,13 +6823,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6836,7 +6839,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B88" s="5">
         <v>46169.669688622685</v>
@@ -6848,7 +6851,7 @@
         <v>46223.568163460644</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6875,13 +6878,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q88" s="5">
         <v>46316</v>
@@ -6901,7 +6904,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B89" s="9">
         <v>46169.66969347223</v>
@@ -6936,13 +6939,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6952,7 +6955,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B90" s="5">
         <v>46169.66972681713</v>
@@ -6964,7 +6967,7 @@
         <v>46223.56815898148</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6991,13 +6994,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q90" s="5">
         <v>46317</v>
@@ -7017,7 +7020,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B91" s="9">
         <v>46169.66973180555</v>
@@ -7054,13 +7057,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -7070,7 +7073,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B92" s="5">
         <v>46169.66981054399</v>
@@ -7080,7 +7083,7 @@
         <v>46223.56814546297</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7107,13 +7110,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q92" s="5">
         <v>46318</v>
@@ -7133,7 +7136,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B93" s="9">
         <v>46169.66981724537</v>
@@ -7170,13 +7173,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7186,7 +7189,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B94" s="5">
         <v>46169.669861041664</v>
@@ -7196,7 +7199,7 @@
         <v>46223.568144791665</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7223,13 +7226,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q94" s="5">
         <v>46321</v>
@@ -7249,7 +7252,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B95" s="9">
         <v>46169.66986724537</v>
@@ -7286,13 +7289,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O95" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7302,7 +7305,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B96" s="5">
         <v>46169.66990296297</v>
@@ -7312,7 +7315,7 @@
         <v>46223.568144212964</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7339,13 +7342,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q96" s="5">
         <v>46323</v>
@@ -7365,7 +7368,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B97" s="9">
         <v>46169.66994555556</v>
@@ -7400,13 +7403,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O97" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7416,7 +7419,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B98" s="5">
         <v>46169.669978645834</v>
@@ -7426,7 +7429,7 @@
         <v>46174.82401747685</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>25</v>
@@ -7450,7 +7453,7 @@
         <v>26</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>26</v>
@@ -7463,7 +7466,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B99" s="9">
         <v>46169.66998244213</v>
@@ -7473,16 +7476,16 @@
         <v>46231.52879813657</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I99" s="9">
         <v>46324</v>
@@ -7500,13 +7503,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q99" s="9">
         <v>46324</v>
@@ -7526,7 +7529,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B100" s="5">
         <v>46169.66998994213</v>
@@ -7542,10 +7545,10 @@
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I100" s="6"/>
       <c r="J100" s="5">
@@ -7561,13 +7564,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7577,7 +7580,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B101" s="9">
         <v>46170.63118891204</v>
@@ -7593,10 +7596,10 @@
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="9">
@@ -7612,7 +7615,7 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O101" s="10" t="s">
         <v>26</v>
@@ -7628,7 +7631,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B102" s="5">
         <v>46174.820955891206</v>
@@ -7644,10 +7647,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I102" s="5">
         <v>46324</v>
@@ -7665,13 +7668,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>64</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7681,7 +7684,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B103" s="9">
         <v>46169.670044224535</v>
@@ -7691,7 +7694,7 @@
         <v>46223.56892738426</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7716,13 +7719,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O103" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q103" s="9">
         <v>46325</v>
@@ -7742,7 +7745,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B104" s="5">
         <v>46169.670049050925</v>
@@ -7777,13 +7780,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7793,7 +7796,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B105" s="9">
         <v>46170.63213679398</v>
@@ -7828,7 +7831,7 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O105" s="10" t="s">
         <v>211</v>
@@ -7844,7 +7847,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B106" s="5">
         <v>46174.82099290509</v>
@@ -7854,7 +7857,7 @@
         <v>46223.5682608912</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7881,7 +7884,7 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>64</v>
@@ -7897,7 +7900,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B107" s="9">
         <v>46169.67013976852</v>
@@ -7907,16 +7910,16 @@
         <v>46174.84870307871</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I107" s="10"/>
       <c r="J107" s="9">
@@ -7932,13 +7935,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O107" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q107" s="9">
         <v>46328</v>
@@ -7958,7 +7961,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B108" s="5">
         <v>46169.670151377315</v>
@@ -7974,10 +7977,10 @@
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I108" s="5">
         <v>46328</v>
@@ -7995,13 +7998,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8011,7 +8014,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B109" s="9">
         <v>46170.63285997685</v>
@@ -8027,10 +8030,10 @@
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I109" s="9">
         <v>46328</v>
@@ -8048,7 +8051,7 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O109" s="10" t="s">
         <v>211</v>
@@ -8064,7 +8067,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B110" s="5">
         <v>46174.821024143515</v>
@@ -8080,10 +8083,10 @@
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I110" s="5">
         <v>46328</v>
@@ -8101,10 +8104,10 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>64</v>
@@ -8117,7 +8120,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B111" s="9">
         <v>46169.67021965278</v>
@@ -8127,16 +8130,16 @@
         <v>46174.84880980324</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I111" s="9">
         <v>46329</v>
@@ -8154,13 +8157,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O111" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q111" s="9">
         <v>46329</v>
@@ -8180,7 +8183,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B112" s="5">
         <v>46169.67022677083</v>
@@ -8196,10 +8199,10 @@
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I112" s="6"/>
       <c r="J112" s="5">
@@ -8215,13 +8218,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8231,7 +8234,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B113" s="9">
         <v>46170.633581828704</v>
@@ -8247,10 +8250,10 @@
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I113" s="10"/>
       <c r="J113" s="9">
@@ -8266,7 +8269,7 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O113" s="10" t="s">
         <v>211</v>
@@ -8282,7 +8285,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B114" s="5">
         <v>46174.821057037036</v>
@@ -8298,10 +8301,10 @@
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I114" s="6"/>
       <c r="J114" s="5">
@@ -8317,7 +8320,7 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>64</v>
@@ -8333,7 +8336,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B115" s="9">
         <v>46169.67031616898</v>
@@ -8343,7 +8346,7 @@
         <v>46174.82401751158</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>25</v>
@@ -8367,7 +8370,7 @@
         <v>26</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P115" s="10" t="s">
         <v>26</v>
@@ -8380,7 +8383,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B116" s="5">
         <v>46169.67031976852</v>
@@ -8390,16 +8393,16 @@
         <v>46174.84885483797</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="I116" s="5">
         <v>46330</v>
@@ -8417,13 +8420,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q116" s="5">
         <v>46330</v>
@@ -8443,7 +8446,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B117" s="9">
         <v>46169.6703253125</v>
@@ -8453,7 +8456,7 @@
         <v>46192.97339644676</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8480,13 +8483,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q117" s="9">
         <v>46330</v>
@@ -8506,7 +8509,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B118" s="5">
         <v>46169.670332430556</v>
@@ -8516,7 +8519,7 @@
         <v>46174.82401726852</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>25</v>
@@ -8540,7 +8543,7 @@
         <v>26</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>26</v>
@@ -8559,7 +8562,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B119" s="9">
         <v>46169.67033591435</v>
@@ -8569,7 +8572,7 @@
         <v>46174.848958703704</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8596,13 +8599,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q119" s="9">
         <v>46330</v>
@@ -8622,7 +8625,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B120" s="5">
         <v>46169.67034748843</v>
@@ -8632,7 +8635,7 @@
         <v>46174.84895586806</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8659,13 +8662,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q120" s="5">
         <v>46339</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -853,7 +853,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT2 4307 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+    <t xml:space="preserve">OT2 4307 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
   </si>
   <si>
     <t>1215174141301410</t>
@@ -5965,7 +5965,7 @@
         <v>46209.90925715277</v>
       </c>
       <c r="D73" s="9">
-        <v>46231.65309703704</v>
+        <v>46232.8359834838</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>256</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -254,7 +254,7 @@
     <t>Alta</t>
   </si>
   <si>
-    <t>Tarea sin iniciar</t>
+    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1215174266151878</t>
@@ -416,9 +416,6 @@
     <t>Materiales corte Laser ot 4342 -4344,Motor ot 4342,rodete ot 4342,Alabe ot 4342</t>
   </si>
   <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
     <t>1215174084165958</t>
   </si>
   <si>
@@ -441,6 +438,9 @@
   </si>
   <si>
     <t>Fabricación Alabe  ot 4342,Alabe ot 4342</t>
+  </si>
+  <si>
+    <t>Tarea sin iniciar</t>
   </si>
   <si>
     <t>1215174266235863</t>
@@ -853,7 +853,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT2 4307 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4</t>
   </si>
   <si>
     <t>1215174141301410</t>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46231.52879386574</v>
+        <v>46233.51768284722</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -2338,7 +2338,7 @@
       <c r="T12" s="6">
         <v>0</v>
       </c>
-      <c r="U12" s="11" t="s">
+      <c r="U12" s="12" t="s">
         <v>62</v>
       </c>
     </row>
@@ -3262,12 +3262,12 @@
       <c r="S27" s="10"/>
       <c r="T27" s="10"/>
       <c r="U27" s="12" t="s">
-        <v>114</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B28" s="5">
         <v>46169.66908924768</v>
@@ -3279,16 +3279,16 @@
         <v>46182.63466408565</v>
       </c>
       <c r="E28" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G28" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="F28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G28" s="6" t="s">
+      <c r="H28" s="6" t="s">
         <v>117</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>118</v>
       </c>
       <c r="I28" s="5">
         <v>46171</v>
@@ -3309,7 +3309,7 @@
         <v>112</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>112</v>
@@ -3332,7 +3332,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B29" s="9">
         <v>46169.66909520833</v>
@@ -3344,16 +3344,16 @@
         <v>46182.63236322917</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>117</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>118</v>
       </c>
       <c r="I29" s="9">
         <v>46169</v>
@@ -3371,13 +3371,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O29" s="10" t="s">
         <v>88</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3388,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -3411,10 +3411,10 @@
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>117</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>118</v>
       </c>
       <c r="I30" s="5">
         <v>46171</v>
@@ -3432,10 +3432,10 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>125</v>
@@ -3449,7 +3449,7 @@
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -3472,10 +3472,10 @@
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H31" s="10" t="s">
         <v>117</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>118</v>
       </c>
       <c r="I31" s="9">
         <v>46168</v>
@@ -3537,10 +3537,10 @@
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>117</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>118</v>
       </c>
       <c r="I32" s="5">
         <v>46168</v>
@@ -3575,7 +3575,7 @@
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
@@ -3598,10 +3598,10 @@
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H33" s="10" t="s">
         <v>117</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>118</v>
       </c>
       <c r="I33" s="9">
         <v>46170</v>
@@ -3636,7 +3636,7 @@
         <v>0</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -3659,10 +3659,10 @@
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>117</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>118</v>
       </c>
       <c r="I34" s="5">
         <v>46161</v>
@@ -3724,10 +3724,10 @@
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H35" s="10" t="s">
         <v>117</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>118</v>
       </c>
       <c r="I35" s="9">
         <v>46161</v>
@@ -3762,7 +3762,7 @@
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
@@ -3785,10 +3785,10 @@
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>117</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>118</v>
       </c>
       <c r="I36" s="5">
         <v>46182</v>
@@ -3823,7 +3823,7 @@
         <v>0</v>
       </c>
       <c r="U36" s="11" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -3846,10 +3846,10 @@
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>117</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>118</v>
       </c>
       <c r="I37" s="9">
         <v>46182</v>
@@ -3884,7 +3884,7 @@
         <v>0</v>
       </c>
       <c r="U37" s="11" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
@@ -3905,10 +3905,10 @@
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>117</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>118</v>
       </c>
       <c r="I38" s="5">
         <v>46161</v>
@@ -3947,7 +3947,7 @@
         <v>0</v>
       </c>
       <c r="U38" s="11" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
@@ -3970,10 +3970,10 @@
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H39" s="10" t="s">
         <v>117</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>118</v>
       </c>
       <c r="I39" s="9">
         <v>46161</v>
@@ -4023,10 +4023,10 @@
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>117</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>118</v>
       </c>
       <c r="I40" s="5">
         <v>46171</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="U42" s="11" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
@@ -4242,7 +4242,7 @@
         <v>0</v>
       </c>
       <c r="U43" s="11" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -5239,7 +5239,7 @@
         <v>46196.87995266204</v>
       </c>
       <c r="D61" s="9">
-        <v>46209.908330949074</v>
+        <v>46233.1715408912</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>97</v>
@@ -5283,8 +5283,8 @@
       <c r="R61" s="9">
         <v>46240</v>
       </c>
-      <c r="S61" s="7" t="s">
-        <v>33</v>
+      <c r="S61" s="12" t="s">
+        <v>216</v>
       </c>
       <c r="T61" s="10">
         <v>1</v>
@@ -5408,7 +5408,7 @@
         <v>0</v>
       </c>
       <c r="U63" s="11" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
@@ -6134,7 +6134,7 @@
         <v>0.1</v>
       </c>
       <c r="U75" s="12" t="s">
-        <v>114</v>
+        <v>62</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -6250,7 +6250,7 @@
         <v>0</v>
       </c>
       <c r="U77" s="11" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
@@ -6350,7 +6350,7 @@
       <c r="S79" s="10"/>
       <c r="T79" s="10"/>
       <c r="U79" s="12" t="s">
-        <v>114</v>
+        <v>62</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
@@ -6608,7 +6608,7 @@
         <v>0</v>
       </c>
       <c r="U83" s="12" t="s">
-        <v>114</v>
+        <v>62</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
@@ -6671,7 +6671,7 @@
         <v>0</v>
       </c>
       <c r="U84" s="11" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6781,7 +6781,7 @@
         <v>0</v>
       </c>
       <c r="U86" s="11" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
@@ -7131,7 +7131,7 @@
         <v>0</v>
       </c>
       <c r="U92" s="11" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
@@ -7247,7 +7247,7 @@
         <v>0</v>
       </c>
       <c r="U94" s="11" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -7363,7 +7363,7 @@
         <v>0</v>
       </c>
       <c r="U96" s="11" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
@@ -7524,7 +7524,7 @@
         <v>0</v>
       </c>
       <c r="U99" s="11" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
@@ -7740,7 +7740,7 @@
         <v>0</v>
       </c>
       <c r="U103" s="11" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
@@ -7956,7 +7956,7 @@
         <v>0</v>
       </c>
       <c r="U107" s="11" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
@@ -8178,7 +8178,7 @@
         <v>0</v>
       </c>
       <c r="U111" s="11" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
@@ -8441,7 +8441,7 @@
         <v>0</v>
       </c>
       <c r="U116" s="11" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
@@ -8504,7 +8504,7 @@
         <v>0</v>
       </c>
       <c r="U117" s="11" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
@@ -8557,7 +8557,7 @@
         <v>0</v>
       </c>
       <c r="U118" s="11" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
@@ -8620,7 +8620,7 @@
         <v>0</v>
       </c>
       <c r="U119" s="11" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
@@ -8683,7 +8683,7 @@
         <v>0</v>
       </c>
       <c r="U120" s="11" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -5965,7 +5965,7 @@
         <v>46209.90925715277</v>
       </c>
       <c r="D73" s="9">
-        <v>46232.8359834838</v>
+        <v>46233.64825993056</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>256</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -371,6 +371,9 @@
     <t>Generación OC materiales corte Laser ot 4342 -4344,Propuesta compras:</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1215174266192358</t>
   </si>
   <si>
@@ -722,9 +725,6 @@
   </si>
   <si>
     <t>OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4344 - MANGA DE VENTILACION Ø1600MM</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1215174382581715</t>
@@ -2406,7 +2406,7 @@
         <v>46212.79376377315</v>
       </c>
       <c r="D14" s="5">
-        <v>46212.79378054398</v>
+        <v>46237.54330734954</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>66</v>
@@ -2902,7 +2902,7 @@
         <v>46197.64318571759</v>
       </c>
       <c r="D22" s="5">
-        <v>46223.567540601856</v>
+        <v>46237.203411678245</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>96</v>
@@ -2946,8 +2946,8 @@
       <c r="R22" s="5">
         <v>46244</v>
       </c>
-      <c r="S22" s="7" t="s">
-        <v>33</v>
+      <c r="S22" s="12" t="s">
+        <v>99</v>
       </c>
       <c r="T22" s="6">
         <v>1</v>
@@ -2958,7 +2958,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B23" s="9">
         <v>46169.669037291664</v>
@@ -2967,10 +2967,10 @@
         <v>46197.64404108796</v>
       </c>
       <c r="D23" s="9">
-        <v>46223.5675370949</v>
+        <v>46237.20341185185</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
@@ -3003,7 +3003,7 @@
         <v>97</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q23" s="9">
         <v>46241</v>
@@ -3011,8 +3011,8 @@
       <c r="R23" s="9">
         <v>46244</v>
       </c>
-      <c r="S23" s="7" t="s">
-        <v>33</v>
+      <c r="S23" s="12" t="s">
+        <v>99</v>
       </c>
       <c r="T23" s="10">
         <v>1</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B24" s="5">
         <v>46169.66904123843</v>
@@ -3032,10 +3032,10 @@
         <v>46197.64418927083</v>
       </c>
       <c r="D24" s="5">
-        <v>46223.567533877314</v>
+        <v>46237.20341185185</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -3068,7 +3068,7 @@
         <v>97</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q24" s="5">
         <v>46241</v>
@@ -3076,8 +3076,8 @@
       <c r="R24" s="5">
         <v>46244</v>
       </c>
-      <c r="S24" s="7" t="s">
-        <v>33</v>
+      <c r="S24" s="12" t="s">
+        <v>99</v>
       </c>
       <c r="T24" s="6">
         <v>1</v>
@@ -3088,7 +3088,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B25" s="9">
         <v>46169.66904511574</v>
@@ -3097,10 +3097,10 @@
         <v>46197.644859120366</v>
       </c>
       <c r="D25" s="9">
-        <v>46223.56752888889</v>
+        <v>46237.20341173611</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
@@ -3133,7 +3133,7 @@
         <v>97</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q25" s="9">
         <v>46241</v>
@@ -3141,8 +3141,8 @@
       <c r="R25" s="9">
         <v>46244</v>
       </c>
-      <c r="S25" s="7" t="s">
-        <v>33</v>
+      <c r="S25" s="12" t="s">
+        <v>99</v>
       </c>
       <c r="T25" s="10">
         <v>1</v>
@@ -3153,7 +3153,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B26" s="5">
         <v>46169.66904878472</v>
@@ -3165,7 +3165,7 @@
         <v>46195.60168921296</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -3198,7 +3198,7 @@
         <v>51</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q26" s="5">
         <v>46157</v>
@@ -3218,7 +3218,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B27" s="9">
         <v>46169.66883418981</v>
@@ -3228,7 +3228,7 @@
         <v>46209.82175228009</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>25</v>
@@ -3252,7 +3252,7 @@
         <v>26</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P27" s="10" t="s">
         <v>26</v>
@@ -3267,7 +3267,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B28" s="5">
         <v>46169.66908924768</v>
@@ -3279,16 +3279,16 @@
         <v>46182.63466408565</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I28" s="5">
         <v>46171</v>
@@ -3306,13 +3306,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q28" s="5">
         <v>46168</v>
@@ -3332,7 +3332,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B29" s="9">
         <v>46169.66909520833</v>
@@ -3344,16 +3344,16 @@
         <v>46182.63236322917</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I29" s="9">
         <v>46169</v>
@@ -3371,13 +3371,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O29" s="10" t="s">
         <v>88</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3388,12 +3388,12 @@
         <v>0</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B30" s="5">
         <v>46169.669100810184</v>
@@ -3405,16 +3405,16 @@
         <v>46182.63463722222</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I30" s="5">
         <v>46171</v>
@@ -3432,13 +3432,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3449,12 +3449,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B31" s="9">
         <v>46169.669106284724</v>
@@ -3466,16 +3466,16 @@
         <v>46182.63460042824</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I31" s="9">
         <v>46168</v>
@@ -3493,13 +3493,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q31" s="9">
         <v>46168</v>
@@ -3519,7 +3519,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B32" s="5">
         <v>46169.66911128472</v>
@@ -3531,16 +3531,16 @@
         <v>46182.6318109375</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I32" s="5">
         <v>46168</v>
@@ -3558,13 +3558,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>91</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3575,12 +3575,12 @@
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B33" s="9">
         <v>46169.669116805555</v>
@@ -3592,16 +3592,16 @@
         <v>46182.63457327546</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I33" s="9">
         <v>46170</v>
@@ -3619,13 +3619,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3636,12 +3636,12 @@
         <v>0</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B34" s="5">
         <v>46169.66912204861</v>
@@ -3653,16 +3653,16 @@
         <v>46182.6344355787</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I34" s="5">
         <v>46161</v>
@@ -3680,13 +3680,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q34" s="5">
         <v>46161</v>
@@ -3706,7 +3706,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B35" s="9">
         <v>46169.66912711806</v>
@@ -3718,16 +3718,16 @@
         <v>46182.63203959491</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I35" s="9">
         <v>46161</v>
@@ -3745,13 +3745,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O35" s="10" t="s">
         <v>85</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3762,12 +3762,12 @@
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B36" s="5">
         <v>46169.66913270833</v>
@@ -3779,16 +3779,16 @@
         <v>46182.634411203704</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I36" s="5">
         <v>46182</v>
@@ -3806,13 +3806,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3823,12 +3823,12 @@
         <v>0</v>
       </c>
       <c r="U36" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B37" s="9">
         <v>46169.66913809028</v>
@@ -3840,16 +3840,16 @@
         <v>46182.6343528588</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I37" s="9">
         <v>46182</v>
@@ -3867,13 +3867,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3884,12 +3884,12 @@
         <v>0</v>
       </c>
       <c r="U37" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B38" s="5">
         <v>46169.66914475695</v>
@@ -3899,16 +3899,16 @@
         <v>46220.19404127315</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I38" s="5">
         <v>46161</v>
@@ -3926,10 +3926,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3947,12 +3947,12 @@
         <v>0</v>
       </c>
       <c r="U38" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B39" s="9">
         <v>46169.669149270834</v>
@@ -3964,16 +3964,16 @@
         <v>46195.68641299769</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I39" s="9">
         <v>46161</v>
@@ -3991,13 +3991,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -4007,7 +4007,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B40" s="5">
         <v>46169.66915408565</v>
@@ -4017,16 +4017,16 @@
         <v>46219.16855109954</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I40" s="5">
         <v>46171</v>
@@ -4044,13 +4044,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4060,7 +4060,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B41" s="9">
         <v>46169.66915865741</v>
@@ -4072,16 +4072,16 @@
         <v>46209.82174662037</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I41" s="9">
         <v>46245</v>
@@ -4099,13 +4099,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q41" s="9">
         <v>46245</v>
@@ -4125,7 +4125,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B42" s="5">
         <v>46169.66916377315</v>
@@ -4137,16 +4137,16 @@
         <v>46199.56927892361</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I42" s="5">
         <v>46245</v>
@@ -4164,13 +4164,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>96</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4181,12 +4181,12 @@
         <v>0</v>
       </c>
       <c r="U42" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B43" s="9">
         <v>46169.66916960648</v>
@@ -4198,16 +4198,16 @@
         <v>46205.61247092593</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I43" s="9">
         <v>46247</v>
@@ -4225,13 +4225,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4242,12 +4242,12 @@
         <v>0</v>
       </c>
       <c r="U43" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B44" s="5">
         <v>46169.66917503472</v>
@@ -4259,16 +4259,16 @@
         <v>46199.567282199074</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I44" s="5">
         <v>46245</v>
@@ -4286,10 +4286,10 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>26</v>
@@ -4312,7 +4312,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B45" s="9">
         <v>46169.669178888886</v>
@@ -4324,16 +4324,16 @@
         <v>46199.569896354165</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I45" s="9">
         <v>46245</v>
@@ -4351,13 +4351,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4367,7 +4367,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B46" s="5">
         <v>46169.669183680555</v>
@@ -4379,16 +4379,16 @@
         <v>46199.56984034722</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I46" s="5">
         <v>46247</v>
@@ -4406,13 +4406,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4422,7 +4422,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B47" s="9">
         <v>46169.66918849537</v>
@@ -4434,16 +4434,16 @@
         <v>46204.863616284725</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I47" s="9">
         <v>46245</v>
@@ -4461,10 +4461,10 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>26</v>
@@ -4487,7 +4487,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B48" s="5">
         <v>46169.66919252315</v>
@@ -4499,16 +4499,16 @@
         <v>46204.863510995376</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I48" s="5">
         <v>46245</v>
@@ -4526,13 +4526,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4542,7 +4542,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B49" s="9">
         <v>46169.66919734953</v>
@@ -4554,16 +4554,16 @@
         <v>46204.8635487037</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I49" s="9">
         <v>46254</v>
@@ -4581,13 +4581,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4597,7 +4597,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
         <v>46169.66920229167</v>
@@ -4609,16 +4609,16 @@
         <v>46210.65313525463</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I50" s="5">
         <v>46286</v>
@@ -4636,10 +4636,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4652,7 +4652,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B51" s="9">
         <v>46169.66924202546</v>
@@ -4664,16 +4664,16 @@
         <v>46199.57084909722</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I51" s="9">
         <v>46245</v>
@@ -4691,10 +4691,10 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P51" s="10" t="s">
         <v>26</v>
@@ -4717,7 +4717,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46169.66924635417</v>
@@ -4729,16 +4729,16 @@
         <v>46199.57078165509</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I52" s="5">
         <v>46245</v>
@@ -4756,13 +4756,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4772,7 +4772,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B53" s="9">
         <v>46169.66925091435</v>
@@ -4784,16 +4784,16 @@
         <v>46199.57082731482</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I53" s="9">
         <v>46247</v>
@@ -4811,13 +4811,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4827,7 +4827,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B54" s="5">
         <v>46169.669255659726</v>
@@ -4839,7 +4839,7 @@
         <v>46210.52487434028</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>25</v>
@@ -4863,7 +4863,7 @@
         <v>26</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -4880,7 +4880,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B55" s="9">
         <v>46169.66925896991</v>
@@ -4892,16 +4892,16 @@
         <v>46197.71564204861</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I55" s="9">
         <v>46167</v>
@@ -4913,19 +4913,19 @@
         <v>26</v>
       </c>
       <c r="L55" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q55" s="9">
         <v>46167</v>
@@ -4945,7 +4945,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B56" s="5">
         <v>46169.66926408565</v>
@@ -4957,16 +4957,16 @@
         <v>46195.94997940972</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I56" s="5">
         <v>46167</v>
@@ -4984,13 +4984,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>79</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5000,7 +5000,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B57" s="9">
         <v>46169.66926952546</v>
@@ -5012,16 +5012,16 @@
         <v>46195.94998958333</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I57" s="9">
         <v>46167</v>
@@ -5039,13 +5039,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O57" s="10" t="s">
         <v>79</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -5055,7 +5055,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B58" s="5">
         <v>46169.66929263889</v>
@@ -5067,16 +5067,16 @@
         <v>46232.17505278935</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I58" s="5">
         <v>46220</v>
@@ -5094,13 +5094,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q58" s="5">
         <v>46220</v>
@@ -5109,7 +5109,7 @@
         <v>46239</v>
       </c>
       <c r="S58" s="12" t="s">
-        <v>216</v>
+        <v>99</v>
       </c>
       <c r="T58" s="6">
         <v>1</v>
@@ -5132,16 +5132,16 @@
         <v>46195.950096458335</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I59" s="9">
         <v>46181</v>
@@ -5159,7 +5159,7 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O59" s="10" t="s">
         <v>218</v>
@@ -5187,16 +5187,16 @@
         <v>46196.87985491898</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I60" s="5">
         <v>46181</v>
@@ -5214,13 +5214,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>221</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5248,10 +5248,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I61" s="9">
         <v>46240</v>
@@ -5269,10 +5269,10 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>223</v>
@@ -5284,7 +5284,7 @@
         <v>46240</v>
       </c>
       <c r="S61" s="12" t="s">
-        <v>216</v>
+        <v>99</v>
       </c>
       <c r="T61" s="10">
         <v>1</v>
@@ -5307,16 +5307,16 @@
         <v>46195.95042396991</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I62" s="5">
         <v>46188</v>
@@ -5337,7 +5337,7 @@
         <v>97</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>97</v>
@@ -5387,10 +5387,10 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P63" s="10" t="s">
         <v>26</v>
@@ -5408,7 +5408,7 @@
         <v>0</v>
       </c>
       <c r="U63" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
@@ -5423,7 +5423,7 @@
         <v>46174.846919421296</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5453,7 +5453,7 @@
         <v>226</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>230</v>
@@ -5561,7 +5561,7 @@
         <v>232</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>238</v>
@@ -5602,10 +5602,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I67" s="9">
         <v>46260</v>
@@ -5691,7 +5691,7 @@
         <v>232</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>245</v>
@@ -5732,10 +5732,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I69" s="9">
         <v>46260</v>
@@ -5759,7 +5759,7 @@
         <v>244</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q69" s="9">
         <v>46260</v>
@@ -5821,7 +5821,7 @@
         <v>232</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>250</v>
@@ -5862,10 +5862,10 @@
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I71" s="9">
         <v>46260</v>
@@ -5889,7 +5889,7 @@
         <v>249</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q71" s="9">
         <v>46260</v>
@@ -6033,7 +6033,7 @@
         <v>46210.65196928241</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -6116,7 +6116,7 @@
         <v>253</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P75" s="10" t="s">
         <v>253</v>
@@ -6149,7 +6149,7 @@
         <v>46209.90937868056</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6208,10 +6208,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I77" s="9">
         <v>46294</v>
@@ -6232,7 +6232,7 @@
         <v>253</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>253</v>
@@ -6250,7 +6250,7 @@
         <v>0</v>
       </c>
       <c r="U77" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
@@ -6265,16 +6265,16 @@
         <v>46197.84256122685</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -6397,7 +6397,7 @@
         <v>232</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>242</v>
@@ -6462,7 +6462,7 @@
         <v>232</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P81" s="10" t="s">
         <v>278</v>
@@ -6527,7 +6527,7 @@
         <v>232</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>278</v>
@@ -6590,7 +6590,7 @@
         <v>232</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P83" s="10" t="s">
         <v>283</v>
@@ -6653,7 +6653,7 @@
         <v>232</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>285</v>
@@ -6671,7 +6671,7 @@
         <v>0</v>
       </c>
       <c r="U84" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46223.56814725694</v>
+        <v>46237.54425690972</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>290</v>
@@ -6780,8 +6780,8 @@
       <c r="T86" s="6">
         <v>0</v>
       </c>
-      <c r="U86" s="11" t="s">
-        <v>122</v>
+      <c r="U86" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
@@ -6796,7 +6796,7 @@
         <v>46223.5676475463</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6881,7 +6881,7 @@
         <v>287</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>287</v>
@@ -6914,7 +6914,7 @@
         <v>46223.83603929398</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6997,7 +6997,7 @@
         <v>287</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>287</v>
@@ -7030,7 +7030,7 @@
         <v>46223.56782162037</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -7080,7 +7080,7 @@
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46223.56814546297</v>
+        <v>46237.54429445602</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>305</v>
@@ -7113,7 +7113,7 @@
         <v>287</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>287</v>
@@ -7130,8 +7130,8 @@
       <c r="T92" s="6">
         <v>0</v>
       </c>
-      <c r="U92" s="11" t="s">
-        <v>122</v>
+      <c r="U92" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
@@ -7146,7 +7146,7 @@
         <v>46223.56789047454</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7229,7 +7229,7 @@
         <v>287</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>287</v>
@@ -7247,7 +7247,7 @@
         <v>0</v>
       </c>
       <c r="U94" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -7262,7 +7262,7 @@
         <v>46223.56796597222</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7292,7 +7292,7 @@
         <v>310</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P95" s="10" t="s">
         <v>312</v>
@@ -7345,7 +7345,7 @@
         <v>287</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>315</v>
@@ -7363,7 +7363,7 @@
         <v>0</v>
       </c>
       <c r="U96" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
@@ -7378,7 +7378,7 @@
         <v>46223.836147291666</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7406,7 +7406,7 @@
         <v>314</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P97" s="10" t="s">
         <v>317</v>
@@ -7524,7 +7524,7 @@
         <v>0</v>
       </c>
       <c r="U99" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
@@ -7539,7 +7539,7 @@
         <v>46174.84838837963</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7567,7 +7567,7 @@
         <v>322</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>327</v>
@@ -7590,7 +7590,7 @@
         <v>46209.90833168982</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7621,7 +7621,7 @@
         <v>26</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7722,7 +7722,7 @@
         <v>319</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P103" s="10" t="s">
         <v>319</v>
@@ -7740,7 +7740,7 @@
         <v>0</v>
       </c>
       <c r="U103" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
@@ -7755,7 +7755,7 @@
         <v>46223.568262175926</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7783,7 +7783,7 @@
         <v>332</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P104" s="6" t="s">
         <v>334</v>
@@ -7806,7 +7806,7 @@
         <v>46223.56826151621</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7834,10 +7834,10 @@
         <v>332</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7938,7 +7938,7 @@
         <v>319</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P107" s="10" t="s">
         <v>319</v>
@@ -7956,7 +7956,7 @@
         <v>0</v>
       </c>
       <c r="U107" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
@@ -7971,7 +7971,7 @@
         <v>46174.848669872685</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8001,7 +8001,7 @@
         <v>338</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>340</v>
@@ -8024,7 +8024,7 @@
         <v>46174.848667314815</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -8054,10 +8054,10 @@
         <v>338</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -8160,7 +8160,7 @@
         <v>319</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P111" s="10" t="s">
         <v>345</v>
@@ -8178,7 +8178,7 @@
         <v>0</v>
       </c>
       <c r="U111" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
@@ -8193,7 +8193,7 @@
         <v>46174.84878571759</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8221,7 +8221,7 @@
         <v>344</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>344</v>
@@ -8244,7 +8244,7 @@
         <v>46174.84878314815</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -8272,7 +8272,7 @@
         <v>344</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -8441,7 +8441,7 @@
         <v>0</v>
       </c>
       <c r="U116" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
@@ -8504,7 +8504,7 @@
         <v>0</v>
       </c>
       <c r="U117" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
@@ -8557,7 +8557,7 @@
         <v>0</v>
       </c>
       <c r="U118" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
@@ -8620,7 +8620,7 @@
         <v>0</v>
       </c>
       <c r="U119" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
@@ -8683,7 +8683,7 @@
         <v>0</v>
       </c>
       <c r="U120" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -853,7 +853,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4</t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
   </si>
   <si>
     <t>1215174141301410</t>
@@ -5965,7 +5965,7 @@
         <v>46209.90925715277</v>
       </c>
       <c r="D73" s="9">
-        <v>46233.64825993056</v>
+        <v>46237.570507048615</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>256</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -5965,7 +5965,7 @@
         <v>46209.90925715277</v>
       </c>
       <c r="D73" s="9">
-        <v>46237.570507048615</v>
+        <v>46237.81015846065</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>256</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -218,6 +218,9 @@
     <t>Ingenieria Electrica,Revision Tableros</t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
     <t>1215174166380025</t>
   </si>
   <si>
@@ -252,9 +255,6 @@
   </si>
   <si>
     <t>Alta</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1215174266151878</t>
@@ -1240,12 +1240,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFe8384f"/>
+        <fgColor rgb="FFeec300"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFeec300"/>
+        <fgColor rgb="FFe8384f"/>
       </patternFill>
     </fill>
   </fills>
@@ -2172,7 +2172,7 @@
         <v>46231.513086886574</v>
       </c>
       <c r="D10" s="5">
-        <v>46231.52879856482</v>
+        <v>46238.48975555555</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2210,13 +2210,13 @@
       <c r="T10" s="6">
         <v>1</v>
       </c>
-      <c r="U10" s="7" t="s">
-        <v>27</v>
+      <c r="U10" s="11" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B11" s="9">
         <v>46169.6689606713</v>
@@ -2228,16 +2228,16 @@
         <v>46195.60099197917</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I11" s="9">
         <v>46155</v>
@@ -2261,7 +2261,7 @@
         <v>41</v>
       </c>
       <c r="P11" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q11" s="9">
         <v>46155</v>
@@ -2281,26 +2281,28 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B12" s="5">
         <v>46169.66896575232</v>
       </c>
-      <c r="C12" s="6"/>
+      <c r="C12" s="5">
+        <v>46238.48972837963</v>
+      </c>
       <c r="D12" s="5">
-        <v>46233.51768284722</v>
+        <v>46238.48974535879</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I12" s="5">
         <v>46223</v>
@@ -2321,10 +2323,10 @@
         <v>48</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q12" s="5">
         <v>46223</v>
@@ -2332,14 +2334,14 @@
       <c r="R12" s="5">
         <v>46227</v>
       </c>
-      <c r="S12" s="11" t="s">
-        <v>61</v>
+      <c r="S12" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="T12" s="6">
-        <v>0</v>
-      </c>
-      <c r="U12" s="12" t="s">
-        <v>62</v>
+        <v>1</v>
+      </c>
+      <c r="U12" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
@@ -2349,9 +2351,11 @@
       <c r="B13" s="9">
         <v>46169.668971666666</v>
       </c>
-      <c r="C13" s="10"/>
+      <c r="C13" s="9">
+        <v>46238.48971166667</v>
+      </c>
       <c r="D13" s="9">
-        <v>46227.169055879625</v>
+        <v>46238.48971369213</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>64</v>
@@ -2360,10 +2364,10 @@
         <v>26</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I13" s="9">
         <v>46223</v>
@@ -2381,10 +2385,10 @@
         <v>26</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P13" s="10" t="s">
         <v>64</v>
@@ -2946,7 +2950,7 @@
       <c r="R22" s="5">
         <v>46244</v>
       </c>
-      <c r="S22" s="12" t="s">
+      <c r="S22" s="11" t="s">
         <v>99</v>
       </c>
       <c r="T22" s="6">
@@ -3011,7 +3015,7 @@
       <c r="R23" s="9">
         <v>46244</v>
       </c>
-      <c r="S23" s="12" t="s">
+      <c r="S23" s="11" t="s">
         <v>99</v>
       </c>
       <c r="T23" s="10">
@@ -3076,7 +3080,7 @@
       <c r="R24" s="5">
         <v>46244</v>
       </c>
-      <c r="S24" s="12" t="s">
+      <c r="S24" s="11" t="s">
         <v>99</v>
       </c>
       <c r="T24" s="6">
@@ -3141,7 +3145,7 @@
       <c r="R25" s="9">
         <v>46244</v>
       </c>
-      <c r="S25" s="12" t="s">
+      <c r="S25" s="11" t="s">
         <v>99</v>
       </c>
       <c r="T25" s="10">
@@ -3195,7 +3199,7 @@
         <v>82</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>111</v>
@@ -3261,8 +3265,8 @@
       <c r="R27" s="10"/>
       <c r="S27" s="10"/>
       <c r="T27" s="10"/>
-      <c r="U27" s="12" t="s">
-        <v>62</v>
+      <c r="U27" s="11" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -3387,7 +3391,7 @@
       <c r="T29" s="10">
         <v>0</v>
       </c>
-      <c r="U29" s="11" t="s">
+      <c r="U29" s="12" t="s">
         <v>123</v>
       </c>
     </row>
@@ -3448,7 +3452,7 @@
       <c r="T30" s="6">
         <v>0</v>
       </c>
-      <c r="U30" s="11" t="s">
+      <c r="U30" s="12" t="s">
         <v>123</v>
       </c>
     </row>
@@ -3507,8 +3511,8 @@
       <c r="R31" s="9">
         <v>46171</v>
       </c>
-      <c r="S31" s="11" t="s">
-        <v>61</v>
+      <c r="S31" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="T31" s="10">
         <v>1</v>
@@ -3574,7 +3578,7 @@
       <c r="T32" s="6">
         <v>0</v>
       </c>
-      <c r="U32" s="11" t="s">
+      <c r="U32" s="12" t="s">
         <v>123</v>
       </c>
     </row>
@@ -3635,7 +3639,7 @@
       <c r="T33" s="10">
         <v>0</v>
       </c>
-      <c r="U33" s="11" t="s">
+      <c r="U33" s="12" t="s">
         <v>123</v>
       </c>
     </row>
@@ -3761,7 +3765,7 @@
       <c r="T35" s="10">
         <v>0</v>
       </c>
-      <c r="U35" s="11" t="s">
+      <c r="U35" s="12" t="s">
         <v>123</v>
       </c>
     </row>
@@ -3822,7 +3826,7 @@
       <c r="T36" s="6">
         <v>0</v>
       </c>
-      <c r="U36" s="11" t="s">
+      <c r="U36" s="12" t="s">
         <v>123</v>
       </c>
     </row>
@@ -3883,7 +3887,7 @@
       <c r="T37" s="10">
         <v>0</v>
       </c>
-      <c r="U37" s="11" t="s">
+      <c r="U37" s="12" t="s">
         <v>123</v>
       </c>
     </row>
@@ -3940,13 +3944,13 @@
       <c r="R38" s="5">
         <v>46219</v>
       </c>
-      <c r="S38" s="11" t="s">
-        <v>61</v>
+      <c r="S38" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="T38" s="6">
         <v>0</v>
       </c>
-      <c r="U38" s="11" t="s">
+      <c r="U38" s="12" t="s">
         <v>123</v>
       </c>
     </row>
@@ -4180,7 +4184,7 @@
       <c r="T42" s="6">
         <v>0</v>
       </c>
-      <c r="U42" s="11" t="s">
+      <c r="U42" s="12" t="s">
         <v>123</v>
       </c>
     </row>
@@ -4241,7 +4245,7 @@
       <c r="T43" s="10">
         <v>0</v>
       </c>
-      <c r="U43" s="11" t="s">
+      <c r="U43" s="12" t="s">
         <v>123</v>
       </c>
     </row>
@@ -4933,8 +4937,8 @@
       <c r="R55" s="9">
         <v>46184</v>
       </c>
-      <c r="S55" s="11" t="s">
-        <v>61</v>
+      <c r="S55" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="T55" s="10">
         <v>1</v>
@@ -5108,7 +5112,7 @@
       <c r="R58" s="5">
         <v>46239</v>
       </c>
-      <c r="S58" s="12" t="s">
+      <c r="S58" s="11" t="s">
         <v>99</v>
       </c>
       <c r="T58" s="6">
@@ -5283,7 +5287,7 @@
       <c r="R61" s="9">
         <v>46240</v>
       </c>
-      <c r="S61" s="12" t="s">
+      <c r="S61" s="11" t="s">
         <v>99</v>
       </c>
       <c r="T61" s="10">
@@ -5407,7 +5411,7 @@
       <c r="T63" s="10">
         <v>0</v>
       </c>
-      <c r="U63" s="11" t="s">
+      <c r="U63" s="12" t="s">
         <v>123</v>
       </c>
     </row>
@@ -6133,8 +6137,8 @@
       <c r="T75" s="10">
         <v>0.1</v>
       </c>
-      <c r="U75" s="12" t="s">
-        <v>62</v>
+      <c r="U75" s="11" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -6249,7 +6253,7 @@
       <c r="T77" s="10">
         <v>0</v>
       </c>
-      <c r="U77" s="11" t="s">
+      <c r="U77" s="12" t="s">
         <v>123</v>
       </c>
     </row>
@@ -6349,8 +6353,8 @@
       <c r="R79" s="10"/>
       <c r="S79" s="10"/>
       <c r="T79" s="10"/>
-      <c r="U79" s="12" t="s">
-        <v>62</v>
+      <c r="U79" s="11" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
@@ -6408,8 +6412,8 @@
       <c r="R80" s="5">
         <v>46174</v>
       </c>
-      <c r="S80" s="11" t="s">
-        <v>61</v>
+      <c r="S80" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="T80" s="6">
         <v>1</v>
@@ -6607,8 +6611,8 @@
       <c r="T83" s="10">
         <v>0</v>
       </c>
-      <c r="U83" s="12" t="s">
-        <v>62</v>
+      <c r="U83" s="11" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
@@ -6623,7 +6627,7 @@
         <v>46221.186868703706</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6664,13 +6668,13 @@
       <c r="R84" s="5">
         <v>46220</v>
       </c>
-      <c r="S84" s="11" t="s">
-        <v>61</v>
+      <c r="S84" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
       </c>
-      <c r="U84" s="11" t="s">
+      <c r="U84" s="12" t="s">
         <v>123</v>
       </c>
     </row>
@@ -7130,8 +7134,8 @@
       <c r="T92" s="6">
         <v>0</v>
       </c>
-      <c r="U92" s="12" t="s">
-        <v>62</v>
+      <c r="U92" s="11" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
@@ -7246,7 +7250,7 @@
       <c r="T94" s="6">
         <v>0</v>
       </c>
-      <c r="U94" s="11" t="s">
+      <c r="U94" s="12" t="s">
         <v>123</v>
       </c>
     </row>
@@ -7362,7 +7366,7 @@
       <c r="T96" s="6">
         <v>0</v>
       </c>
-      <c r="U96" s="11" t="s">
+      <c r="U96" s="12" t="s">
         <v>123</v>
       </c>
     </row>
@@ -7473,7 +7477,7 @@
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46231.52879813657</v>
+        <v>46238.48974153935</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>322</v>
@@ -7523,7 +7527,7 @@
       <c r="T99" s="10">
         <v>0</v>
       </c>
-      <c r="U99" s="11" t="s">
+      <c r="U99" s="12" t="s">
         <v>123</v>
       </c>
     </row>
@@ -7638,7 +7642,7 @@
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46174.848381284726</v>
+        <v>46238.48971945602</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>64</v>
@@ -7739,7 +7743,7 @@
       <c r="T103" s="10">
         <v>0</v>
       </c>
-      <c r="U103" s="11" t="s">
+      <c r="U103" s="12" t="s">
         <v>123</v>
       </c>
     </row>
@@ -7955,7 +7959,7 @@
       <c r="T107" s="10">
         <v>0</v>
       </c>
-      <c r="U107" s="11" t="s">
+      <c r="U107" s="12" t="s">
         <v>123</v>
       </c>
     </row>
@@ -8177,7 +8181,7 @@
       <c r="T111" s="10">
         <v>0</v>
       </c>
-      <c r="U111" s="11" t="s">
+      <c r="U111" s="12" t="s">
         <v>123</v>
       </c>
     </row>
@@ -8440,7 +8444,7 @@
       <c r="T116" s="6">
         <v>0</v>
       </c>
-      <c r="U116" s="11" t="s">
+      <c r="U116" s="12" t="s">
         <v>123</v>
       </c>
     </row>
@@ -8503,7 +8507,7 @@
       <c r="T117" s="10">
         <v>0</v>
       </c>
-      <c r="U117" s="11" t="s">
+      <c r="U117" s="12" t="s">
         <v>123</v>
       </c>
     </row>
@@ -8556,7 +8560,7 @@
       <c r="T118" s="6">
         <v>0</v>
       </c>
-      <c r="U118" s="11" t="s">
+      <c r="U118" s="12" t="s">
         <v>123</v>
       </c>
     </row>
@@ -8578,10 +8582,10 @@
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I119" s="9">
         <v>46330</v>
@@ -8619,7 +8623,7 @@
       <c r="T119" s="10">
         <v>0</v>
       </c>
-      <c r="U119" s="11" t="s">
+      <c r="U119" s="12" t="s">
         <v>123</v>
       </c>
     </row>
@@ -8641,10 +8645,10 @@
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I120" s="5">
         <v>46339</v>
@@ -8682,7 +8686,7 @@
       <c r="T120" s="6">
         <v>0</v>
       </c>
-      <c r="U120" s="11" t="s">
+      <c r="U120" s="12" t="s">
         <v>123</v>
       </c>
     </row>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -853,7 +853,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
   </si>
   <si>
     <t>1215174141301410</t>
@@ -3227,9 +3227,11 @@
       <c r="B27" s="9">
         <v>46169.66883418981</v>
       </c>
-      <c r="C27" s="10"/>
+      <c r="C27" s="9">
+        <v>46239.59647607639</v>
+      </c>
       <c r="D27" s="9">
-        <v>46209.82175228009</v>
+        <v>46239.59649340277</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>113</v>
@@ -3264,9 +3266,11 @@
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
       <c r="S27" s="10"/>
-      <c r="T27" s="10"/>
-      <c r="U27" s="11" t="s">
-        <v>50</v>
+      <c r="T27" s="10">
+        <v>1</v>
+      </c>
+      <c r="U27" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -3898,9 +3902,11 @@
       <c r="B38" s="5">
         <v>46169.66914475695</v>
       </c>
-      <c r="C38" s="6"/>
+      <c r="C38" s="5">
+        <v>46239.5964540162</v>
+      </c>
       <c r="D38" s="5">
-        <v>46220.19404127315</v>
+        <v>46239.596476666666</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>149</v>
@@ -3948,10 +3954,10 @@
         <v>62</v>
       </c>
       <c r="T38" s="6">
-        <v>0</v>
-      </c>
-      <c r="U38" s="12" t="s">
-        <v>123</v>
+        <v>1</v>
+      </c>
+      <c r="U38" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
@@ -5969,7 +5975,7 @@
         <v>46209.90925715277</v>
       </c>
       <c r="D73" s="9">
-        <v>46237.81015846065</v>
+        <v>46239.5742378588</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>256</v>
@@ -6559,9 +6565,11 @@
       <c r="B83" s="9">
         <v>46169.66962980324</v>
       </c>
-      <c r="C83" s="10"/>
+      <c r="C83" s="9">
+        <v>46239.596492094905</v>
+      </c>
       <c r="D83" s="9">
-        <v>46204.86356525463</v>
+        <v>46239.59650748843</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>282</v>
@@ -6609,10 +6617,10 @@
         <v>33</v>
       </c>
       <c r="T83" s="10">
-        <v>0</v>
-      </c>
-      <c r="U83" s="11" t="s">
-        <v>50</v>
+        <v>1</v>
+      </c>
+      <c r="U83" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
@@ -6734,7 +6742,7 @@
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46237.54425690972</v>
+        <v>46239.596496921295</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>290</v>
@@ -6797,7 +6805,7 @@
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46223.5676475463</v>
+        <v>46239.59649744213</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>207</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -853,7 +853,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200</t>
   </si>
   <si>
     <t>1215174141301410</t>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -5074,7 +5074,7 @@
         <v>46195.95012040509</v>
       </c>
       <c r="D58" s="5">
-        <v>46232.17505278935</v>
+        <v>46240.1885688426</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>215</v>
@@ -5118,8 +5118,8 @@
       <c r="R58" s="5">
         <v>46239</v>
       </c>
-      <c r="S58" s="11" t="s">
-        <v>99</v>
+      <c r="S58" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="T58" s="6">
         <v>1</v>
@@ -5975,7 +5975,7 @@
         <v>46209.90925715277</v>
       </c>
       <c r="D73" s="9">
-        <v>46239.5742378588</v>
+        <v>46240.5827005787</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>256</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1403" uniqueCount="358">
   <si>
     <t>50001558 -  GESVIAL</t>
   </si>
@@ -1111,7 +1111,7 @@
     <t>Despacho</t>
   </si>
   <si>
-    <t>Logistica:,Instalación componentes,Costos,Gestion</t>
+    <t>Logistica:,Costos,Gestion</t>
   </si>
   <si>
     <t>1215174167408579</t>
@@ -1148,30 +1148,6 @@
   </si>
   <si>
     <t>Costos</t>
-  </si>
-  <si>
-    <t>1215174267257524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puesta En Marcha </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instalación componentes,Pruebas de Instalacion Componentes </t>
-  </si>
-  <si>
-    <t>1215174167493195</t>
-  </si>
-  <si>
-    <t>Instalación componentes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puesta En Marcha ,Pruebas de Instalacion Componentes </t>
-  </si>
-  <si>
-    <t>1215174167493217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pruebas de Instalacion Componentes </t>
   </si>
 </sst>
 </file>
@@ -1695,7 +1671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U120"/>
+  <dimension ref="A1:U117"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -8139,7 +8115,7 @@
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46174.84880980324</v>
+        <v>46240.717242997685</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>344</v>
@@ -8516,185 +8492,6 @@
         <v>0</v>
       </c>
       <c r="U117" s="12" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="118" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A118" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="B118" s="5">
-        <v>46169.670332430556</v>
-      </c>
-      <c r="C118" s="6"/>
-      <c r="D118" s="5">
-        <v>46174.82401726852</v>
-      </c>
-      <c r="E118" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="F118" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G118" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H118" s="6"/>
-      <c r="I118" s="6"/>
-      <c r="J118" s="6"/>
-      <c r="K118" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L118" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M118" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="N118" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O118" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="P118" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q118" s="6"/>
-      <c r="R118" s="6"/>
-      <c r="S118" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T118" s="6">
-        <v>0</v>
-      </c>
-      <c r="U118" s="12" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="119" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A119" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="B119" s="9">
-        <v>46169.67033591435</v>
-      </c>
-      <c r="C119" s="10"/>
-      <c r="D119" s="9">
-        <v>46174.848958703704</v>
-      </c>
-      <c r="E119" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="F119" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G119" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="H119" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="I119" s="9">
-        <v>46330</v>
-      </c>
-      <c r="J119" s="9">
-        <v>46338</v>
-      </c>
-      <c r="K119" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L119" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M119" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N119" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="O119" s="10" t="s">
-        <v>344</v>
-      </c>
-      <c r="P119" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="Q119" s="9">
-        <v>46330</v>
-      </c>
-      <c r="R119" s="9">
-        <v>46338</v>
-      </c>
-      <c r="S119" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T119" s="10">
-        <v>0</v>
-      </c>
-      <c r="U119" s="12" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="120" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A120" s="4" t="s">
-        <v>364</v>
-      </c>
-      <c r="B120" s="5">
-        <v>46169.67034748843</v>
-      </c>
-      <c r="C120" s="6"/>
-      <c r="D120" s="5">
-        <v>46174.84895586806</v>
-      </c>
-      <c r="E120" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="F120" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G120" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="H120" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="I120" s="5">
-        <v>46339</v>
-      </c>
-      <c r="J120" s="5">
-        <v>46349</v>
-      </c>
-      <c r="K120" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L120" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M120" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N120" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="O120" s="6" t="s">
-        <v>362</v>
-      </c>
-      <c r="P120" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="Q120" s="5">
-        <v>46339</v>
-      </c>
-      <c r="R120" s="5">
-        <v>46349</v>
-      </c>
-      <c r="S120" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T120" s="6">
-        <v>0</v>
-      </c>
-      <c r="U120" s="12" t="s">
         <v>123</v>
       </c>
     </row>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -5225,7 +5225,7 @@
         <v>46196.87995266204</v>
       </c>
       <c r="D61" s="9">
-        <v>46233.1715408912</v>
+        <v>46241.167933206016</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>97</v>
@@ -5269,8 +5269,8 @@
       <c r="R61" s="9">
         <v>46240</v>
       </c>
-      <c r="S61" s="11" t="s">
-        <v>99</v>
+      <c r="S61" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="T61" s="10">
         <v>1</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -853,7 +853,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200</t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200</t>
   </si>
   <si>
     <t>1215174141301410</t>
@@ -5951,7 +5951,7 @@
         <v>46209.90925715277</v>
       </c>
       <c r="D73" s="9">
-        <v>46240.5827005787</v>
+        <v>46244.582035300926</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>256</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -853,7 +853,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200</t>
+    <t xml:space="preserve">OT2 4307 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4390 -ZVN 1-12-110/4 + TOB + REJ </t>
   </si>
   <si>
     <t>1215174141301410</t>
@@ -5951,7 +5951,7 @@
         <v>46209.90925715277</v>
       </c>
       <c r="D73" s="9">
-        <v>46244.582035300926</v>
+        <v>46244.81646861111</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>256</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1403" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1403" uniqueCount="357">
   <si>
     <t>50001558 -  GESVIAL</t>
   </si>
@@ -371,9 +371,6 @@
     <t>Generación OC materiales corte Laser ot 4342 -4344,Propuesta compras:</t>
   </si>
   <si>
-    <t>Media</t>
-  </si>
-  <si>
     <t>1215174266192358</t>
   </si>
   <si>
@@ -853,7 +850,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT2 4307 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4390 -ZVN 1-12-110/4 + TOB + REJ </t>
+    <t xml:space="preserve">OT2 4307 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ </t>
   </si>
   <si>
     <t>1215174141301410</t>
@@ -2882,7 +2879,7 @@
         <v>46197.64318571759</v>
       </c>
       <c r="D22" s="5">
-        <v>46237.203411678245</v>
+        <v>46245.1986161574</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>96</v>
@@ -2926,8 +2923,8 @@
       <c r="R22" s="5">
         <v>46244</v>
       </c>
-      <c r="S22" s="11" t="s">
-        <v>99</v>
+      <c r="S22" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="T22" s="6">
         <v>1</v>
@@ -2938,7 +2935,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B23" s="9">
         <v>46169.669037291664</v>
@@ -2947,10 +2944,10 @@
         <v>46197.64404108796</v>
       </c>
       <c r="D23" s="9">
-        <v>46237.20341185185</v>
+        <v>46245.19861603009</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
@@ -2983,7 +2980,7 @@
         <v>97</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Q23" s="9">
         <v>46241</v>
@@ -2991,8 +2988,8 @@
       <c r="R23" s="9">
         <v>46244</v>
       </c>
-      <c r="S23" s="11" t="s">
-        <v>99</v>
+      <c r="S23" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="T23" s="10">
         <v>1</v>
@@ -3003,7 +3000,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B24" s="5">
         <v>46169.66904123843</v>
@@ -3012,10 +3009,10 @@
         <v>46197.64418927083</v>
       </c>
       <c r="D24" s="5">
-        <v>46237.20341185185</v>
+        <v>46245.19861599537</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -3048,7 +3045,7 @@
         <v>97</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q24" s="5">
         <v>46241</v>
@@ -3056,8 +3053,8 @@
       <c r="R24" s="5">
         <v>46244</v>
       </c>
-      <c r="S24" s="11" t="s">
-        <v>99</v>
+      <c r="S24" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="T24" s="6">
         <v>1</v>
@@ -3068,7 +3065,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B25" s="9">
         <v>46169.66904511574</v>
@@ -3077,10 +3074,10 @@
         <v>46197.644859120366</v>
       </c>
       <c r="D25" s="9">
-        <v>46237.20341173611</v>
+        <v>46245.19861627315</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
@@ -3113,7 +3110,7 @@
         <v>97</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Q25" s="9">
         <v>46241</v>
@@ -3121,8 +3118,8 @@
       <c r="R25" s="9">
         <v>46244</v>
       </c>
-      <c r="S25" s="11" t="s">
-        <v>99</v>
+      <c r="S25" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="T25" s="10">
         <v>1</v>
@@ -3133,7 +3130,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B26" s="5">
         <v>46169.66904878472</v>
@@ -3145,7 +3142,7 @@
         <v>46195.60168921296</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -3178,7 +3175,7 @@
         <v>52</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Q26" s="5">
         <v>46157</v>
@@ -3198,7 +3195,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B27" s="9">
         <v>46169.66883418981</v>
@@ -3210,7 +3207,7 @@
         <v>46239.59649340277</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>25</v>
@@ -3234,7 +3231,7 @@
         <v>26</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P27" s="10" t="s">
         <v>26</v>
@@ -3251,7 +3248,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B28" s="5">
         <v>46169.66908924768</v>
@@ -3263,16 +3260,16 @@
         <v>46182.63466408565</v>
       </c>
       <c r="E28" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G28" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="F28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G28" s="6" t="s">
+      <c r="H28" s="6" t="s">
         <v>117</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>118</v>
       </c>
       <c r="I28" s="5">
         <v>46171</v>
@@ -3290,13 +3287,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q28" s="5">
         <v>46168</v>
@@ -3316,7 +3313,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B29" s="9">
         <v>46169.66909520833</v>
@@ -3328,16 +3325,16 @@
         <v>46182.63236322917</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>117</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>118</v>
       </c>
       <c r="I29" s="9">
         <v>46169</v>
@@ -3355,13 +3352,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O29" s="10" t="s">
         <v>88</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3372,12 +3369,12 @@
         <v>0</v>
       </c>
       <c r="U29" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B30" s="5">
         <v>46169.669100810184</v>
@@ -3389,16 +3386,16 @@
         <v>46182.63463722222</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>117</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>118</v>
       </c>
       <c r="I30" s="5">
         <v>46171</v>
@@ -3416,13 +3413,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3433,12 +3430,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B31" s="9">
         <v>46169.669106284724</v>
@@ -3450,16 +3447,16 @@
         <v>46182.63460042824</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H31" s="10" t="s">
         <v>117</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>118</v>
       </c>
       <c r="I31" s="9">
         <v>46168</v>
@@ -3477,13 +3474,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q31" s="9">
         <v>46168</v>
@@ -3503,7 +3500,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B32" s="5">
         <v>46169.66911128472</v>
@@ -3515,16 +3512,16 @@
         <v>46182.6318109375</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>117</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>118</v>
       </c>
       <c r="I32" s="5">
         <v>46168</v>
@@ -3542,13 +3539,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>91</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3559,12 +3556,12 @@
         <v>0</v>
       </c>
       <c r="U32" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B33" s="9">
         <v>46169.669116805555</v>
@@ -3576,16 +3573,16 @@
         <v>46182.63457327546</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H33" s="10" t="s">
         <v>117</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>118</v>
       </c>
       <c r="I33" s="9">
         <v>46170</v>
@@ -3603,13 +3600,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3620,12 +3617,12 @@
         <v>0</v>
       </c>
       <c r="U33" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B34" s="5">
         <v>46169.66912204861</v>
@@ -3637,16 +3634,16 @@
         <v>46182.6344355787</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>117</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>118</v>
       </c>
       <c r="I34" s="5">
         <v>46161</v>
@@ -3664,13 +3661,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q34" s="5">
         <v>46161</v>
@@ -3690,7 +3687,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B35" s="9">
         <v>46169.66912711806</v>
@@ -3702,16 +3699,16 @@
         <v>46182.63203959491</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H35" s="10" t="s">
         <v>117</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>118</v>
       </c>
       <c r="I35" s="9">
         <v>46161</v>
@@ -3729,13 +3726,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O35" s="10" t="s">
         <v>85</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3746,12 +3743,12 @@
         <v>0</v>
       </c>
       <c r="U35" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B36" s="5">
         <v>46169.66913270833</v>
@@ -3763,16 +3760,16 @@
         <v>46182.634411203704</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>117</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>118</v>
       </c>
       <c r="I36" s="5">
         <v>46182</v>
@@ -3790,13 +3787,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3807,12 +3804,12 @@
         <v>0</v>
       </c>
       <c r="U36" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B37" s="9">
         <v>46169.66913809028</v>
@@ -3824,16 +3821,16 @@
         <v>46182.6343528588</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>117</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>118</v>
       </c>
       <c r="I37" s="9">
         <v>46182</v>
@@ -3851,13 +3848,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3868,12 +3865,12 @@
         <v>0</v>
       </c>
       <c r="U37" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B38" s="5">
         <v>46169.66914475695</v>
@@ -3885,16 +3882,16 @@
         <v>46239.596476666666</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>117</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>118</v>
       </c>
       <c r="I38" s="5">
         <v>46161</v>
@@ -3912,10 +3909,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3938,7 +3935,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B39" s="9">
         <v>46169.669149270834</v>
@@ -3950,16 +3947,16 @@
         <v>46195.68641299769</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H39" s="10" t="s">
         <v>117</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>118</v>
       </c>
       <c r="I39" s="9">
         <v>46161</v>
@@ -3977,13 +3974,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -3993,7 +3990,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B40" s="5">
         <v>46169.66915408565</v>
@@ -4003,16 +4000,16 @@
         <v>46219.16855109954</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>117</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>118</v>
       </c>
       <c r="I40" s="5">
         <v>46171</v>
@@ -4030,13 +4027,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4046,7 +4043,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B41" s="9">
         <v>46169.66915865741</v>
@@ -4058,16 +4055,16 @@
         <v>46209.82174662037</v>
       </c>
       <c r="E41" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="F41" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G41" s="10" t="s">
+      <c r="H41" s="10" t="s">
         <v>158</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>159</v>
       </c>
       <c r="I41" s="9">
         <v>46245</v>
@@ -4085,13 +4082,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q41" s="9">
         <v>46245</v>
@@ -4111,7 +4108,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B42" s="5">
         <v>46169.66916377315</v>
@@ -4123,16 +4120,16 @@
         <v>46199.56927892361</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I42" s="5">
         <v>46245</v>
@@ -4150,13 +4147,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>96</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4167,12 +4164,12 @@
         <v>0</v>
       </c>
       <c r="U42" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B43" s="9">
         <v>46169.66916960648</v>
@@ -4184,16 +4181,16 @@
         <v>46205.61247092593</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H43" s="10" t="s">
         <v>158</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>159</v>
       </c>
       <c r="I43" s="9">
         <v>46247</v>
@@ -4211,13 +4208,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4228,12 +4225,12 @@
         <v>0</v>
       </c>
       <c r="U43" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B44" s="5">
         <v>46169.66917503472</v>
@@ -4245,16 +4242,16 @@
         <v>46199.567282199074</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I44" s="5">
         <v>46245</v>
@@ -4272,10 +4269,10 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>26</v>
@@ -4298,7 +4295,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B45" s="9">
         <v>46169.669178888886</v>
@@ -4310,16 +4307,16 @@
         <v>46199.569896354165</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>158</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>159</v>
       </c>
       <c r="I45" s="9">
         <v>46245</v>
@@ -4337,13 +4334,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4353,7 +4350,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B46" s="5">
         <v>46169.669183680555</v>
@@ -4365,16 +4362,16 @@
         <v>46199.56984034722</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I46" s="5">
         <v>46247</v>
@@ -4392,13 +4389,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4408,7 +4405,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B47" s="9">
         <v>46169.66918849537</v>
@@ -4420,16 +4417,16 @@
         <v>46204.863616284725</v>
       </c>
       <c r="E47" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="F47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="10" t="s">
+      <c r="H47" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="I47" s="9">
         <v>46245</v>
@@ -4447,10 +4444,10 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>26</v>
@@ -4473,7 +4470,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B48" s="5">
         <v>46169.66919252315</v>
@@ -4485,16 +4482,16 @@
         <v>46204.863510995376</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I48" s="5">
         <v>46245</v>
@@ -4512,13 +4509,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4528,7 +4525,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B49" s="9">
         <v>46169.66919734953</v>
@@ -4540,16 +4537,16 @@
         <v>46204.8635487037</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="I49" s="9">
         <v>46254</v>
@@ -4567,13 +4564,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4583,7 +4580,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
         <v>46169.66920229167</v>
@@ -4595,16 +4592,16 @@
         <v>46210.65313525463</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="H50" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I50" s="5">
         <v>46286</v>
@@ -4622,10 +4619,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4638,7 +4635,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B51" s="9">
         <v>46169.66924202546</v>
@@ -4650,16 +4647,16 @@
         <v>46199.57084909722</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>158</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>159</v>
       </c>
       <c r="I51" s="9">
         <v>46245</v>
@@ -4677,10 +4674,10 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P51" s="10" t="s">
         <v>26</v>
@@ -4703,7 +4700,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B52" s="5">
         <v>46169.66924635417</v>
@@ -4715,16 +4712,16 @@
         <v>46199.57078165509</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I52" s="5">
         <v>46245</v>
@@ -4742,13 +4739,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4758,7 +4755,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B53" s="9">
         <v>46169.66925091435</v>
@@ -4770,16 +4767,16 @@
         <v>46199.57082731482</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>158</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>159</v>
       </c>
       <c r="I53" s="9">
         <v>46247</v>
@@ -4797,13 +4794,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4813,7 +4810,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B54" s="5">
         <v>46169.669255659726</v>
@@ -4825,7 +4822,7 @@
         <v>46210.52487434028</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>25</v>
@@ -4849,7 +4846,7 @@
         <v>26</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -4866,7 +4863,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B55" s="9">
         <v>46169.66925896991</v>
@@ -4878,16 +4875,16 @@
         <v>46197.71564204861</v>
       </c>
       <c r="E55" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G55" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G55" s="10" t="s">
+      <c r="H55" s="10" t="s">
         <v>202</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>203</v>
       </c>
       <c r="I55" s="9">
         <v>46167</v>
@@ -4899,19 +4896,19 @@
         <v>26</v>
       </c>
       <c r="L55" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="M55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N55" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="O55" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="M55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N55" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="O55" s="10" t="s">
-        <v>205</v>
-      </c>
       <c r="P55" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q55" s="9">
         <v>46167</v>
@@ -4931,7 +4928,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B56" s="5">
         <v>46169.66926408565</v>
@@ -4943,16 +4940,16 @@
         <v>46195.94997940972</v>
       </c>
       <c r="E56" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G56" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="F56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G56" s="6" t="s">
+      <c r="H56" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I56" s="5">
         <v>46167</v>
@@ -4970,13 +4967,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>79</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4986,7 +4983,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B57" s="9">
         <v>46169.66926952546</v>
@@ -4998,16 +4995,16 @@
         <v>46195.94998958333</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I57" s="9">
         <v>46167</v>
@@ -5025,13 +5022,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O57" s="10" t="s">
         <v>79</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -5041,7 +5038,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B58" s="5">
         <v>46169.66929263889</v>
@@ -5053,16 +5050,16 @@
         <v>46240.1885688426</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="I58" s="5">
         <v>46220</v>
@@ -5080,13 +5077,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q58" s="5">
         <v>46220</v>
@@ -5106,7 +5103,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B59" s="9">
         <v>46169.66929775463</v>
@@ -5118,16 +5115,16 @@
         <v>46195.950096458335</v>
       </c>
       <c r="E59" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G59" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="F59" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G59" s="10" t="s">
+      <c r="H59" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I59" s="9">
         <v>46181</v>
@@ -5145,13 +5142,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O59" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="P59" s="10" t="s">
         <v>218</v>
-      </c>
-      <c r="P59" s="10" t="s">
-        <v>219</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5161,7 +5158,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B60" s="5">
         <v>46169.66930358796</v>
@@ -5173,16 +5170,16 @@
         <v>46196.87985491898</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I60" s="5">
         <v>46181</v>
@@ -5200,13 +5197,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5216,7 +5213,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B61" s="9">
         <v>46169.669327048614</v>
@@ -5234,10 +5231,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I61" s="9">
         <v>46240</v>
@@ -5255,13 +5252,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q61" s="9">
         <v>46240</v>
@@ -5281,7 +5278,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B62" s="5">
         <v>46169.6693399537</v>
@@ -5293,16 +5290,16 @@
         <v>46195.95042396991</v>
       </c>
       <c r="E62" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G62" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="F62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G62" s="6" t="s">
+      <c r="H62" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I62" s="5">
         <v>46188</v>
@@ -5323,7 +5320,7 @@
         <v>97</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>97</v>
@@ -5336,7 +5333,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B63" s="9">
         <v>46169.669361203705</v>
@@ -5346,16 +5343,16 @@
         <v>46174.84660805555</v>
       </c>
       <c r="E63" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="F63" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G63" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="F63" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G63" s="10" t="s">
+      <c r="H63" s="10" t="s">
         <v>227</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>228</v>
       </c>
       <c r="I63" s="9">
         <v>46322</v>
@@ -5373,10 +5370,10 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P63" s="10" t="s">
         <v>26</v>
@@ -5394,12 +5391,12 @@
         <v>0</v>
       </c>
       <c r="U63" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B64" s="5">
         <v>46169.66936501158</v>
@@ -5409,16 +5406,16 @@
         <v>46174.846919421296</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>227</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>228</v>
       </c>
       <c r="I64" s="5">
         <v>46290</v>
@@ -5436,13 +5433,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5452,7 +5449,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B65" s="9">
         <v>46169.669418136575</v>
@@ -5464,7 +5461,7 @@
         <v>46210.65198340278</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>25</v>
@@ -5488,7 +5485,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P65" s="10" t="s">
         <v>26</v>
@@ -5505,7 +5502,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B66" s="5">
         <v>46169.66942685185</v>
@@ -5517,16 +5514,16 @@
         <v>46210.651395196764</v>
       </c>
       <c r="E66" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G66" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="F66" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G66" s="6" t="s">
+      <c r="H66" s="6" t="s">
         <v>236</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>237</v>
       </c>
       <c r="I66" s="5">
         <v>46258</v>
@@ -5544,13 +5541,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Q66" s="5">
         <v>46258</v>
@@ -5570,7 +5567,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B67" s="9">
         <v>46169.669432361115</v>
@@ -5582,16 +5579,16 @@
         <v>46210.65197202546</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I67" s="9">
         <v>46260</v>
@@ -5609,13 +5606,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O67" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="P67" s="10" t="s">
         <v>241</v>
-      </c>
-      <c r="P67" s="10" t="s">
-        <v>242</v>
       </c>
       <c r="Q67" s="9">
         <v>46260</v>
@@ -5635,7 +5632,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B68" s="5">
         <v>46169.66943836806</v>
@@ -5647,16 +5644,16 @@
         <v>46210.65139929398</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>236</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>237</v>
       </c>
       <c r="I68" s="5">
         <v>46258</v>
@@ -5674,13 +5671,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q68" s="5">
         <v>46258</v>
@@ -5700,7 +5697,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B69" s="9">
         <v>46169.669443692124</v>
@@ -5712,16 +5709,16 @@
         <v>46210.651975879635</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I69" s="9">
         <v>46260</v>
@@ -5739,13 +5736,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q69" s="9">
         <v>46260</v>
@@ -5765,7 +5762,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B70" s="5">
         <v>46169.669448368055</v>
@@ -5777,16 +5774,16 @@
         <v>46210.65141630787</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>236</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>237</v>
       </c>
       <c r="I70" s="5">
         <v>46258</v>
@@ -5804,13 +5801,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q70" s="5">
         <v>46258</v>
@@ -5830,7 +5827,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B71" s="9">
         <v>46169.66945298611</v>
@@ -5842,16 +5839,16 @@
         <v>46210.65197810185</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H71" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I71" s="9">
         <v>46260</v>
@@ -5869,13 +5866,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q71" s="9">
         <v>46260</v>
@@ -5895,7 +5892,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B72" s="5">
         <v>46169.66945778935</v>
@@ -5905,7 +5902,7 @@
         <v>46209.909264270835</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>25</v>
@@ -5929,7 +5926,7 @@
         <v>26</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>26</v>
@@ -5942,7 +5939,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B73" s="9">
         <v>46169.66946104167</v>
@@ -5951,19 +5948,19 @@
         <v>46209.90925715277</v>
       </c>
       <c r="D73" s="9">
-        <v>46244.81646861111</v>
+        <v>46244.91622328704</v>
       </c>
       <c r="E73" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="F73" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G73" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="F73" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G73" s="10" t="s">
+      <c r="H73" s="10" t="s">
         <v>257</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>258</v>
       </c>
       <c r="I73" s="9">
         <v>46262</v>
@@ -5981,13 +5978,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q73" s="9">
         <v>46262</v>
@@ -6007,7 +6004,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B74" s="5">
         <v>46169.669467280095</v>
@@ -6019,16 +6016,16 @@
         <v>46210.65196928241</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="I74" s="5">
         <v>46262</v>
@@ -6046,13 +6043,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O74" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="P74" s="6" t="s">
         <v>261</v>
-      </c>
-      <c r="P74" s="6" t="s">
-        <v>262</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6062,7 +6059,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B75" s="9">
         <v>46169.66950289352</v>
@@ -6072,16 +6069,16 @@
         <v>46209.90954123843</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="H75" s="10" t="s">
         <v>257</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>258</v>
       </c>
       <c r="I75" s="9">
         <v>46273</v>
@@ -6099,13 +6096,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q75" s="9">
         <v>46273</v>
@@ -6125,7 +6122,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B76" s="5">
         <v>46169.66950758102</v>
@@ -6135,16 +6132,16 @@
         <v>46209.90937868056</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="I76" s="5">
         <v>46273</v>
@@ -6162,13 +6159,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O76" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="P76" s="6" t="s">
         <v>266</v>
-      </c>
-      <c r="P76" s="6" t="s">
-        <v>267</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6178,7 +6175,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B77" s="9">
         <v>46169.66953380787</v>
@@ -6188,16 +6185,16 @@
         <v>46209.908330833336</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H77" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I77" s="9">
         <v>46294</v>
@@ -6215,13 +6212,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q77" s="9">
         <v>46294</v>
@@ -6236,12 +6233,12 @@
         <v>0</v>
       </c>
       <c r="U77" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B78" s="5">
         <v>46169.66953854167</v>
@@ -6251,16 +6248,16 @@
         <v>46197.84256122685</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -6276,13 +6273,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6292,7 +6289,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B79" s="9">
         <v>46169.66960108797</v>
@@ -6302,7 +6299,7 @@
         <v>46209.85402508102</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>25</v>
@@ -6326,7 +6323,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P79" s="10" t="s">
         <v>26</v>
@@ -6341,7 +6338,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B80" s="5">
         <v>46169.66960956018</v>
@@ -6353,16 +6350,16 @@
         <v>46209.844928101855</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>236</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>237</v>
       </c>
       <c r="I80" s="5">
         <v>46174</v>
@@ -6380,13 +6377,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q80" s="5">
         <v>46174</v>
@@ -6406,7 +6403,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B81" s="9">
         <v>46169.6696165162</v>
@@ -6418,16 +6415,16 @@
         <v>46209.84471936343</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="H81" s="10" t="s">
         <v>236</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>237</v>
       </c>
       <c r="I81" s="9">
         <v>46288</v>
@@ -6445,13 +6442,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q81" s="9">
         <v>46288</v>
@@ -6471,7 +6468,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B82" s="5">
         <v>46169.669622939815</v>
@@ -6483,16 +6480,16 @@
         <v>46209.85430440972</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>236</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>237</v>
       </c>
       <c r="I82" s="5">
         <v>46308</v>
@@ -6510,13 +6507,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q82" s="5">
         <v>46308</v>
@@ -6536,7 +6533,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B83" s="9">
         <v>46169.66962980324</v>
@@ -6548,16 +6545,16 @@
         <v>46239.59650748843</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="H83" s="10" t="s">
         <v>236</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>237</v>
       </c>
       <c r="I83" s="9">
         <v>46287</v>
@@ -6575,13 +6572,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Q83" s="9">
         <v>46287</v>
@@ -6601,7 +6598,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B84" s="5">
         <v>46169.669635185186</v>
@@ -6617,10 +6614,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>236</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>237</v>
       </c>
       <c r="I84" s="5">
         <v>46220</v>
@@ -6638,13 +6635,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Q84" s="5">
         <v>46220</v>
@@ -6659,12 +6656,12 @@
         <v>0</v>
       </c>
       <c r="U84" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B85" s="9">
         <v>46169.66964790509</v>
@@ -6674,7 +6671,7 @@
         <v>46223.56797070602</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>25</v>
@@ -6698,7 +6695,7 @@
         <v>26</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>26</v>
@@ -6711,7 +6708,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B86" s="5">
         <v>46169.66965109954</v>
@@ -6721,7 +6718,7 @@
         <v>46239.596496921295</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6748,13 +6745,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q86" s="5">
         <v>46294</v>
@@ -6774,7 +6771,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B87" s="9">
         <v>46169.6696568287</v>
@@ -6784,7 +6781,7 @@
         <v>46239.59649744213</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6811,13 +6808,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6827,7 +6824,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B88" s="5">
         <v>46169.669688622685</v>
@@ -6839,7 +6836,7 @@
         <v>46223.568163460644</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6866,13 +6863,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q88" s="5">
         <v>46316</v>
@@ -6892,7 +6889,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B89" s="9">
         <v>46169.66969347223</v>
@@ -6902,7 +6899,7 @@
         <v>46223.83603929398</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6927,13 +6924,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O89" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="P89" s="10" t="s">
         <v>297</v>
-      </c>
-      <c r="P89" s="10" t="s">
-        <v>298</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6943,7 +6940,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B90" s="5">
         <v>46169.66972681713</v>
@@ -6955,7 +6952,7 @@
         <v>46223.56815898148</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6982,13 +6979,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q90" s="5">
         <v>46317</v>
@@ -7008,7 +7005,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B91" s="9">
         <v>46169.66973180555</v>
@@ -7018,7 +7015,7 @@
         <v>46223.56782162037</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -7045,13 +7042,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O91" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="P91" s="10" t="s">
         <v>302</v>
-      </c>
-      <c r="P91" s="10" t="s">
-        <v>303</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -7061,7 +7058,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B92" s="5">
         <v>46169.66981054399</v>
@@ -7071,7 +7068,7 @@
         <v>46237.54429445602</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7098,13 +7095,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q92" s="5">
         <v>46318</v>
@@ -7124,7 +7121,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B93" s="9">
         <v>46169.66981724537</v>
@@ -7134,7 +7131,7 @@
         <v>46223.56789047454</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7161,13 +7158,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O93" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="P93" s="10" t="s">
         <v>307</v>
-      </c>
-      <c r="P93" s="10" t="s">
-        <v>308</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7177,7 +7174,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B94" s="5">
         <v>46169.669861041664</v>
@@ -7187,7 +7184,7 @@
         <v>46223.568144791665</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7214,13 +7211,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q94" s="5">
         <v>46321</v>
@@ -7235,12 +7232,12 @@
         <v>0</v>
       </c>
       <c r="U94" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B95" s="9">
         <v>46169.66986724537</v>
@@ -7250,7 +7247,7 @@
         <v>46223.56796597222</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7277,13 +7274,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7293,7 +7290,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B96" s="5">
         <v>46169.66990296297</v>
@@ -7303,7 +7300,7 @@
         <v>46223.568144212964</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7330,13 +7327,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q96" s="5">
         <v>46323</v>
@@ -7351,12 +7348,12 @@
         <v>0</v>
       </c>
       <c r="U96" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B97" s="9">
         <v>46169.66994555556</v>
@@ -7366,7 +7363,7 @@
         <v>46223.836147291666</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7391,13 +7388,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7407,7 +7404,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B98" s="5">
         <v>46169.669978645834</v>
@@ -7417,7 +7414,7 @@
         <v>46174.82401747685</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>25</v>
@@ -7441,7 +7438,7 @@
         <v>26</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>26</v>
@@ -7454,7 +7451,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B99" s="9">
         <v>46169.66998244213</v>
@@ -7464,16 +7461,16 @@
         <v>46238.48974153935</v>
       </c>
       <c r="E99" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="F99" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G99" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="F99" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G99" s="10" t="s">
+      <c r="H99" s="10" t="s">
         <v>323</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>324</v>
       </c>
       <c r="I99" s="9">
         <v>46324</v>
@@ -7491,13 +7488,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q99" s="9">
         <v>46324</v>
@@ -7512,12 +7509,12 @@
         <v>0</v>
       </c>
       <c r="U99" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B100" s="5">
         <v>46169.66998994213</v>
@@ -7527,16 +7524,16 @@
         <v>46174.84838837963</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="H100" s="6" t="s">
         <v>323</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>324</v>
       </c>
       <c r="I100" s="6"/>
       <c r="J100" s="5">
@@ -7552,13 +7549,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7568,7 +7565,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B101" s="9">
         <v>46170.63118891204</v>
@@ -7578,16 +7575,16 @@
         <v>46209.90833168982</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="H101" s="10" t="s">
         <v>323</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>324</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="9">
@@ -7603,13 +7600,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7619,7 +7616,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B102" s="5">
         <v>46174.820955891206</v>
@@ -7635,10 +7632,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="H102" s="6" t="s">
         <v>323</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>324</v>
       </c>
       <c r="I102" s="5">
         <v>46324</v>
@@ -7656,13 +7653,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>64</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7672,7 +7669,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B103" s="9">
         <v>46169.670044224535</v>
@@ -7682,7 +7679,7 @@
         <v>46223.56892738426</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7707,13 +7704,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q103" s="9">
         <v>46325</v>
@@ -7728,12 +7725,12 @@
         <v>0</v>
       </c>
       <c r="U103" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B104" s="5">
         <v>46169.670049050925</v>
@@ -7743,7 +7740,7 @@
         <v>46223.568262175926</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7768,13 +7765,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7784,7 +7781,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B105" s="9">
         <v>46170.63213679398</v>
@@ -7794,7 +7791,7 @@
         <v>46223.56826151621</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7819,13 +7816,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7835,7 +7832,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B106" s="5">
         <v>46174.82099290509</v>
@@ -7845,7 +7842,7 @@
         <v>46223.5682608912</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7872,7 +7869,7 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>64</v>
@@ -7888,7 +7885,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B107" s="9">
         <v>46169.67013976852</v>
@@ -7898,16 +7895,16 @@
         <v>46174.84870307871</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="H107" s="10" t="s">
         <v>257</v>
-      </c>
-      <c r="H107" s="10" t="s">
-        <v>258</v>
       </c>
       <c r="I107" s="10"/>
       <c r="J107" s="9">
@@ -7923,13 +7920,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q107" s="9">
         <v>46328</v>
@@ -7944,12 +7941,12 @@
         <v>0</v>
       </c>
       <c r="U107" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B108" s="5">
         <v>46169.670151377315</v>
@@ -7959,16 +7956,16 @@
         <v>46174.848669872685</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="H108" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="I108" s="5">
         <v>46328</v>
@@ -7986,13 +7983,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8002,7 +7999,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B109" s="9">
         <v>46170.63285997685</v>
@@ -8012,16 +8009,16 @@
         <v>46174.848667314815</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="H109" s="10" t="s">
         <v>257</v>
-      </c>
-      <c r="H109" s="10" t="s">
-        <v>258</v>
       </c>
       <c r="I109" s="9">
         <v>46328</v>
@@ -8039,13 +8036,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -8055,7 +8052,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B110" s="5">
         <v>46174.821024143515</v>
@@ -8071,10 +8068,10 @@
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="H110" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="I110" s="5">
         <v>46328</v>
@@ -8092,10 +8089,10 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>64</v>
@@ -8108,7 +8105,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B111" s="9">
         <v>46169.67021965278</v>
@@ -8118,16 +8115,16 @@
         <v>46240.717242997685</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="H111" s="10" t="s">
         <v>257</v>
-      </c>
-      <c r="H111" s="10" t="s">
-        <v>258</v>
       </c>
       <c r="I111" s="9">
         <v>46329</v>
@@ -8145,13 +8142,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Q111" s="9">
         <v>46329</v>
@@ -8166,12 +8163,12 @@
         <v>0</v>
       </c>
       <c r="U111" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B112" s="5">
         <v>46169.67022677083</v>
@@ -8181,16 +8178,16 @@
         <v>46174.84878571759</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="H112" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="I112" s="6"/>
       <c r="J112" s="5">
@@ -8206,13 +8203,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8222,7 +8219,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B113" s="9">
         <v>46170.633581828704</v>
@@ -8232,16 +8229,16 @@
         <v>46174.84878314815</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="H113" s="10" t="s">
         <v>257</v>
-      </c>
-      <c r="H113" s="10" t="s">
-        <v>258</v>
       </c>
       <c r="I113" s="10"/>
       <c r="J113" s="9">
@@ -8257,10 +8254,10 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -8273,7 +8270,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B114" s="5">
         <v>46174.821057037036</v>
@@ -8289,10 +8286,10 @@
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="H114" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="H114" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="I114" s="6"/>
       <c r="J114" s="5">
@@ -8308,7 +8305,7 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>64</v>
@@ -8324,7 +8321,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B115" s="9">
         <v>46169.67031616898</v>
@@ -8334,7 +8331,7 @@
         <v>46174.82401751158</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>25</v>
@@ -8358,7 +8355,7 @@
         <v>26</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P115" s="10" t="s">
         <v>26</v>
@@ -8371,7 +8368,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B116" s="5">
         <v>46169.67031976852</v>
@@ -8381,16 +8378,16 @@
         <v>46174.84885483797</v>
       </c>
       <c r="E116" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="F116" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G116" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="F116" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G116" s="6" t="s">
+      <c r="H116" s="6" t="s">
         <v>354</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>355</v>
       </c>
       <c r="I116" s="5">
         <v>46330</v>
@@ -8408,13 +8405,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Q116" s="5">
         <v>46330</v>
@@ -8429,12 +8426,12 @@
         <v>0</v>
       </c>
       <c r="U116" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B117" s="9">
         <v>46169.6703253125</v>
@@ -8444,7 +8441,7 @@
         <v>46192.97339644676</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8471,13 +8468,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Q117" s="9">
         <v>46330</v>
@@ -8492,7 +8489,7 @@
         <v>0</v>
       </c>
       <c r="U117" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1403" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1403" uniqueCount="358">
   <si>
     <t>50001558 -  GESVIAL</t>
   </si>
@@ -552,6 +552,9 @@
   </si>
   <si>
     <t xml:space="preserve">Generación OC materiales corte Laser ot 4342 -4344,Fabricacion Corte Laser ot 4342 -4344 </t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1215174084306570</t>
@@ -4052,7 +4055,7 @@
         <v>46209.82174373843</v>
       </c>
       <c r="D41" s="9">
-        <v>46209.82174662037</v>
+        <v>46248.17429667824</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>156</v>
@@ -4096,8 +4099,8 @@
       <c r="R41" s="9">
         <v>46255</v>
       </c>
-      <c r="S41" s="7" t="s">
-        <v>33</v>
+      <c r="S41" s="11" t="s">
+        <v>160</v>
       </c>
       <c r="T41" s="10">
         <v>1</v>
@@ -4108,7 +4111,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B42" s="5">
         <v>46169.66916377315</v>
@@ -4120,7 +4123,7 @@
         <v>46199.56927892361</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
@@ -4153,7 +4156,7 @@
         <v>96</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4169,7 +4172,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B43" s="9">
         <v>46169.66916960648</v>
@@ -4181,7 +4184,7 @@
         <v>46205.61247092593</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
@@ -4211,10 +4214,10 @@
         <v>156</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4230,7 +4233,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B44" s="5">
         <v>46169.66917503472</v>
@@ -4239,10 +4242,10 @@
         <v>46199.56727092592</v>
       </c>
       <c r="D44" s="5">
-        <v>46199.567282199074</v>
+        <v>46248.17429556713</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
@@ -4272,7 +4275,7 @@
         <v>112</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>26</v>
@@ -4283,8 +4286,8 @@
       <c r="R44" s="5">
         <v>46255</v>
       </c>
-      <c r="S44" s="7" t="s">
-        <v>33</v>
+      <c r="S44" s="11" t="s">
+        <v>160</v>
       </c>
       <c r="T44" s="6">
         <v>1</v>
@@ -4295,7 +4298,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B45" s="9">
         <v>46169.669178888886</v>
@@ -4334,13 +4337,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>100</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4350,7 +4353,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B46" s="5">
         <v>46169.669183680555</v>
@@ -4362,7 +4365,7 @@
         <v>46199.56984034722</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
@@ -4389,13 +4392,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>101</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4405,7 +4408,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B47" s="9">
         <v>46169.66918849537</v>
@@ -4417,16 +4420,16 @@
         <v>46204.863616284725</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I47" s="9">
         <v>46245</v>
@@ -4447,7 +4450,7 @@
         <v>112</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>26</v>
@@ -4470,7 +4473,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B48" s="5">
         <v>46169.66919252315</v>
@@ -4488,10 +4491,10 @@
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I48" s="5">
         <v>46245</v>
@@ -4509,13 +4512,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>106</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4525,7 +4528,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B49" s="9">
         <v>46169.66919734953</v>
@@ -4537,16 +4540,16 @@
         <v>46204.8635487037</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I49" s="9">
         <v>46254</v>
@@ -4564,13 +4567,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O49" s="10" t="s">
         <v>107</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4580,7 +4583,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
         <v>46169.66920229167</v>
@@ -4592,16 +4595,16 @@
         <v>46210.65313525463</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I50" s="5">
         <v>46286</v>
@@ -4619,10 +4622,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4635,7 +4638,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B51" s="9">
         <v>46169.66924202546</v>
@@ -4644,10 +4647,10 @@
         <v>46199.57083833333</v>
       </c>
       <c r="D51" s="9">
-        <v>46199.57084909722</v>
+        <v>46248.174295624995</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
@@ -4677,7 +4680,7 @@
         <v>112</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P51" s="10" t="s">
         <v>26</v>
@@ -4688,8 +4691,8 @@
       <c r="R51" s="9">
         <v>46255</v>
       </c>
-      <c r="S51" s="7" t="s">
-        <v>33</v>
+      <c r="S51" s="11" t="s">
+        <v>160</v>
       </c>
       <c r="T51" s="10">
         <v>1</v>
@@ -4700,7 +4703,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46169.66924635417</v>
@@ -4739,13 +4742,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>103</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4755,7 +4758,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B53" s="9">
         <v>46169.66925091435</v>
@@ -4767,7 +4770,7 @@
         <v>46199.57082731482</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
@@ -4794,13 +4797,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O53" s="10" t="s">
         <v>104</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4810,7 +4813,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B54" s="5">
         <v>46169.669255659726</v>
@@ -4822,7 +4825,7 @@
         <v>46210.52487434028</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>25</v>
@@ -4846,7 +4849,7 @@
         <v>26</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -4863,7 +4866,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B55" s="9">
         <v>46169.66925896991</v>
@@ -4875,16 +4878,16 @@
         <v>46197.71564204861</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I55" s="9">
         <v>46167</v>
@@ -4896,19 +4899,19 @@
         <v>26</v>
       </c>
       <c r="L55" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q55" s="9">
         <v>46167</v>
@@ -4928,7 +4931,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B56" s="5">
         <v>46169.66926408565</v>
@@ -4940,16 +4943,16 @@
         <v>46195.94997940972</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I56" s="5">
         <v>46167</v>
@@ -4967,13 +4970,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>79</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4983,7 +4986,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B57" s="9">
         <v>46169.66926952546</v>
@@ -4995,16 +4998,16 @@
         <v>46195.94998958333</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I57" s="9">
         <v>46167</v>
@@ -5022,13 +5025,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O57" s="10" t="s">
         <v>79</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -5038,7 +5041,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B58" s="5">
         <v>46169.66929263889</v>
@@ -5050,16 +5053,16 @@
         <v>46240.1885688426</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I58" s="5">
         <v>46220</v>
@@ -5077,13 +5080,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q58" s="5">
         <v>46220</v>
@@ -5103,7 +5106,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B59" s="9">
         <v>46169.66929775463</v>
@@ -5115,16 +5118,16 @@
         <v>46195.950096458335</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I59" s="9">
         <v>46181</v>
@@ -5142,13 +5145,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5158,7 +5161,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B60" s="5">
         <v>46169.66930358796</v>
@@ -5170,16 +5173,16 @@
         <v>46196.87985491898</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I60" s="5">
         <v>46181</v>
@@ -5197,13 +5200,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5213,7 +5216,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B61" s="9">
         <v>46169.669327048614</v>
@@ -5231,10 +5234,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I61" s="9">
         <v>46240</v>
@@ -5252,13 +5255,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q61" s="9">
         <v>46240</v>
@@ -5278,7 +5281,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B62" s="5">
         <v>46169.6693399537</v>
@@ -5290,16 +5293,16 @@
         <v>46195.95042396991</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I62" s="5">
         <v>46188</v>
@@ -5320,7 +5323,7 @@
         <v>97</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>97</v>
@@ -5333,7 +5336,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B63" s="9">
         <v>46169.669361203705</v>
@@ -5343,16 +5346,16 @@
         <v>46174.84660805555</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I63" s="9">
         <v>46322</v>
@@ -5370,10 +5373,10 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P63" s="10" t="s">
         <v>26</v>
@@ -5396,7 +5399,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B64" s="5">
         <v>46169.66936501158</v>
@@ -5406,16 +5409,16 @@
         <v>46174.846919421296</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I64" s="5">
         <v>46290</v>
@@ -5433,13 +5436,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5449,7 +5452,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B65" s="9">
         <v>46169.669418136575</v>
@@ -5461,7 +5464,7 @@
         <v>46210.65198340278</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>25</v>
@@ -5485,7 +5488,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P65" s="10" t="s">
         <v>26</v>
@@ -5502,7 +5505,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B66" s="5">
         <v>46169.66942685185</v>
@@ -5514,16 +5517,16 @@
         <v>46210.651395196764</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I66" s="5">
         <v>46258</v>
@@ -5541,13 +5544,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q66" s="5">
         <v>46258</v>
@@ -5567,7 +5570,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B67" s="9">
         <v>46169.669432361115</v>
@@ -5579,16 +5582,16 @@
         <v>46210.65197202546</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I67" s="9">
         <v>46260</v>
@@ -5606,13 +5609,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q67" s="9">
         <v>46260</v>
@@ -5632,7 +5635,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B68" s="5">
         <v>46169.66943836806</v>
@@ -5644,16 +5647,16 @@
         <v>46210.65139929398</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I68" s="5">
         <v>46258</v>
@@ -5671,13 +5674,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q68" s="5">
         <v>46258</v>
@@ -5697,7 +5700,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B69" s="9">
         <v>46169.669443692124</v>
@@ -5709,16 +5712,16 @@
         <v>46210.651975879635</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I69" s="9">
         <v>46260</v>
@@ -5736,13 +5739,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q69" s="9">
         <v>46260</v>
@@ -5762,7 +5765,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B70" s="5">
         <v>46169.669448368055</v>
@@ -5774,16 +5777,16 @@
         <v>46210.65141630787</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I70" s="5">
         <v>46258</v>
@@ -5801,13 +5804,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q70" s="5">
         <v>46258</v>
@@ -5827,7 +5830,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B71" s="9">
         <v>46169.66945298611</v>
@@ -5839,16 +5842,16 @@
         <v>46210.65197810185</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I71" s="9">
         <v>46260</v>
@@ -5866,13 +5869,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q71" s="9">
         <v>46260</v>
@@ -5892,7 +5895,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B72" s="5">
         <v>46169.66945778935</v>
@@ -5902,7 +5905,7 @@
         <v>46209.909264270835</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>25</v>
@@ -5926,7 +5929,7 @@
         <v>26</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>26</v>
@@ -5939,7 +5942,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B73" s="9">
         <v>46169.66946104167</v>
@@ -5951,16 +5954,16 @@
         <v>46244.91622328704</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I73" s="9">
         <v>46262</v>
@@ -5978,13 +5981,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q73" s="9">
         <v>46262</v>
@@ -6004,7 +6007,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B74" s="5">
         <v>46169.669467280095</v>
@@ -6016,16 +6019,16 @@
         <v>46210.65196928241</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I74" s="5">
         <v>46262</v>
@@ -6043,13 +6046,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6059,7 +6062,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B75" s="9">
         <v>46169.66950289352</v>
@@ -6069,16 +6072,16 @@
         <v>46209.90954123843</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I75" s="9">
         <v>46273</v>
@@ -6096,13 +6099,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q75" s="9">
         <v>46273</v>
@@ -6122,7 +6125,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B76" s="5">
         <v>46169.66950758102</v>
@@ -6132,16 +6135,16 @@
         <v>46209.90937868056</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I76" s="5">
         <v>46273</v>
@@ -6159,13 +6162,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6175,7 +6178,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B77" s="9">
         <v>46169.66953380787</v>
@@ -6185,16 +6188,16 @@
         <v>46209.908330833336</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I77" s="9">
         <v>46294</v>
@@ -6212,13 +6215,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q77" s="9">
         <v>46294</v>
@@ -6238,7 +6241,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B78" s="5">
         <v>46169.66953854167</v>
@@ -6248,16 +6251,16 @@
         <v>46197.84256122685</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -6273,13 +6276,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6289,7 +6292,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B79" s="9">
         <v>46169.66960108797</v>
@@ -6299,7 +6302,7 @@
         <v>46209.85402508102</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>25</v>
@@ -6323,7 +6326,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P79" s="10" t="s">
         <v>26</v>
@@ -6338,7 +6341,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B80" s="5">
         <v>46169.66960956018</v>
@@ -6350,16 +6353,16 @@
         <v>46209.844928101855</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I80" s="5">
         <v>46174</v>
@@ -6377,13 +6380,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>133</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q80" s="5">
         <v>46174</v>
@@ -6403,7 +6406,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B81" s="9">
         <v>46169.6696165162</v>
@@ -6415,16 +6418,16 @@
         <v>46209.84471936343</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I81" s="9">
         <v>46288</v>
@@ -6442,13 +6445,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>124</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q81" s="9">
         <v>46288</v>
@@ -6468,7 +6471,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B82" s="5">
         <v>46169.669622939815</v>
@@ -6480,16 +6483,16 @@
         <v>46209.85430440972</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I82" s="5">
         <v>46308</v>
@@ -6507,13 +6510,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>142</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q82" s="5">
         <v>46308</v>
@@ -6533,7 +6536,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B83" s="9">
         <v>46169.66962980324</v>
@@ -6545,16 +6548,16 @@
         <v>46239.59650748843</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I83" s="9">
         <v>46287</v>
@@ -6572,13 +6575,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q83" s="9">
         <v>46287</v>
@@ -6598,7 +6601,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B84" s="5">
         <v>46169.669635185186</v>
@@ -6614,10 +6617,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I84" s="5">
         <v>46220</v>
@@ -6635,13 +6638,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>153</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q84" s="5">
         <v>46220</v>
@@ -6661,7 +6664,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B85" s="9">
         <v>46169.66964790509</v>
@@ -6671,7 +6674,7 @@
         <v>46223.56797070602</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>25</v>
@@ -6695,7 +6698,7 @@
         <v>26</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>26</v>
@@ -6708,7 +6711,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B86" s="5">
         <v>46169.66965109954</v>
@@ -6718,7 +6721,7 @@
         <v>46239.596496921295</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6745,13 +6748,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q86" s="5">
         <v>46294</v>
@@ -6771,7 +6774,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B87" s="9">
         <v>46169.6696568287</v>
@@ -6781,7 +6784,7 @@
         <v>46239.59649744213</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6808,13 +6811,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6824,7 +6827,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B88" s="5">
         <v>46169.669688622685</v>
@@ -6836,7 +6839,7 @@
         <v>46223.568163460644</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6863,13 +6866,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q88" s="5">
         <v>46316</v>
@@ -6889,7 +6892,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B89" s="9">
         <v>46169.66969347223</v>
@@ -6899,7 +6902,7 @@
         <v>46223.83603929398</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6924,13 +6927,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6940,7 +6943,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B90" s="5">
         <v>46169.66972681713</v>
@@ -6952,7 +6955,7 @@
         <v>46223.56815898148</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6979,13 +6982,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q90" s="5">
         <v>46317</v>
@@ -7005,7 +7008,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B91" s="9">
         <v>46169.66973180555</v>
@@ -7015,7 +7018,7 @@
         <v>46223.56782162037</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -7042,13 +7045,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -7058,7 +7061,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B92" s="5">
         <v>46169.66981054399</v>
@@ -7068,7 +7071,7 @@
         <v>46237.54429445602</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7095,13 +7098,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q92" s="5">
         <v>46318</v>
@@ -7121,7 +7124,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B93" s="9">
         <v>46169.66981724537</v>
@@ -7131,7 +7134,7 @@
         <v>46223.56789047454</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7158,13 +7161,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7174,7 +7177,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B94" s="5">
         <v>46169.669861041664</v>
@@ -7184,7 +7187,7 @@
         <v>46223.568144791665</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7211,13 +7214,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q94" s="5">
         <v>46321</v>
@@ -7237,7 +7240,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B95" s="9">
         <v>46169.66986724537</v>
@@ -7247,7 +7250,7 @@
         <v>46223.56796597222</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7274,13 +7277,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7290,7 +7293,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B96" s="5">
         <v>46169.66990296297</v>
@@ -7300,7 +7303,7 @@
         <v>46223.568144212964</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7327,13 +7330,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q96" s="5">
         <v>46323</v>
@@ -7353,7 +7356,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B97" s="9">
         <v>46169.66994555556</v>
@@ -7363,7 +7366,7 @@
         <v>46223.836147291666</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7388,13 +7391,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7404,7 +7407,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B98" s="5">
         <v>46169.669978645834</v>
@@ -7414,7 +7417,7 @@
         <v>46174.82401747685</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>25</v>
@@ -7438,7 +7441,7 @@
         <v>26</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>26</v>
@@ -7451,7 +7454,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B99" s="9">
         <v>46169.66998244213</v>
@@ -7461,16 +7464,16 @@
         <v>46238.48974153935</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I99" s="9">
         <v>46324</v>
@@ -7488,13 +7491,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q99" s="9">
         <v>46324</v>
@@ -7514,7 +7517,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B100" s="5">
         <v>46169.66998994213</v>
@@ -7524,16 +7527,16 @@
         <v>46174.84838837963</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I100" s="6"/>
       <c r="J100" s="5">
@@ -7549,13 +7552,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7565,7 +7568,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B101" s="9">
         <v>46170.63118891204</v>
@@ -7575,16 +7578,16 @@
         <v>46209.90833168982</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="9">
@@ -7600,13 +7603,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7616,7 +7619,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B102" s="5">
         <v>46174.820955891206</v>
@@ -7632,10 +7635,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I102" s="5">
         <v>46324</v>
@@ -7653,13 +7656,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>64</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7669,7 +7672,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B103" s="9">
         <v>46169.670044224535</v>
@@ -7679,7 +7682,7 @@
         <v>46223.56892738426</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7704,13 +7707,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q103" s="9">
         <v>46325</v>
@@ -7730,7 +7733,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B104" s="5">
         <v>46169.670049050925</v>
@@ -7740,7 +7743,7 @@
         <v>46223.568262175926</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7765,13 +7768,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7781,7 +7784,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B105" s="9">
         <v>46170.63213679398</v>
@@ -7791,7 +7794,7 @@
         <v>46223.56826151621</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7816,13 +7819,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7832,7 +7835,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B106" s="5">
         <v>46174.82099290509</v>
@@ -7842,7 +7845,7 @@
         <v>46223.5682608912</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7869,7 +7872,7 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>64</v>
@@ -7885,7 +7888,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B107" s="9">
         <v>46169.67013976852</v>
@@ -7895,16 +7898,16 @@
         <v>46174.84870307871</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I107" s="10"/>
       <c r="J107" s="9">
@@ -7920,13 +7923,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q107" s="9">
         <v>46328</v>
@@ -7946,7 +7949,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B108" s="5">
         <v>46169.670151377315</v>
@@ -7956,16 +7959,16 @@
         <v>46174.848669872685</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I108" s="5">
         <v>46328</v>
@@ -7983,13 +7986,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7999,7 +8002,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B109" s="9">
         <v>46170.63285997685</v>
@@ -8009,16 +8012,16 @@
         <v>46174.848667314815</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I109" s="9">
         <v>46328</v>
@@ -8036,13 +8039,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -8052,7 +8055,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B110" s="5">
         <v>46174.821024143515</v>
@@ -8068,10 +8071,10 @@
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I110" s="5">
         <v>46328</v>
@@ -8089,10 +8092,10 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>64</v>
@@ -8105,7 +8108,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B111" s="9">
         <v>46169.67021965278</v>
@@ -8115,16 +8118,16 @@
         <v>46240.717242997685</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I111" s="9">
         <v>46329</v>
@@ -8142,13 +8145,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q111" s="9">
         <v>46329</v>
@@ -8168,7 +8171,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B112" s="5">
         <v>46169.67022677083</v>
@@ -8178,16 +8181,16 @@
         <v>46174.84878571759</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I112" s="6"/>
       <c r="J112" s="5">
@@ -8203,13 +8206,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8219,7 +8222,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B113" s="9">
         <v>46170.633581828704</v>
@@ -8229,16 +8232,16 @@
         <v>46174.84878314815</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I113" s="10"/>
       <c r="J113" s="9">
@@ -8254,10 +8257,10 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -8270,7 +8273,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B114" s="5">
         <v>46174.821057037036</v>
@@ -8286,10 +8289,10 @@
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I114" s="6"/>
       <c r="J114" s="5">
@@ -8305,7 +8308,7 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>64</v>
@@ -8321,7 +8324,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B115" s="9">
         <v>46169.67031616898</v>
@@ -8331,7 +8334,7 @@
         <v>46174.82401751158</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>25</v>
@@ -8355,7 +8358,7 @@
         <v>26</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P115" s="10" t="s">
         <v>26</v>
@@ -8368,7 +8371,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B116" s="5">
         <v>46169.67031976852</v>
@@ -8378,16 +8381,16 @@
         <v>46174.84885483797</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="I116" s="5">
         <v>46330</v>
@@ -8405,13 +8408,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q116" s="5">
         <v>46330</v>
@@ -8431,7 +8434,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B117" s="9">
         <v>46169.6703253125</v>
@@ -8441,7 +8444,7 @@
         <v>46192.97339644676</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8468,13 +8471,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q117" s="9">
         <v>46330</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -1896,7 +1896,7 @@
         <v>46175.87134493055</v>
       </c>
       <c r="D6" s="5">
-        <v>46213.762757986115</v>
+        <v>46248.9301690162</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -2266,7 +2266,7 @@
         <v>46238.48972837963</v>
       </c>
       <c r="D12" s="5">
-        <v>46238.48974535879</v>
+        <v>46250.15126246528</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -4875,7 +4875,7 @@
         <v>46195.950004328704</v>
       </c>
       <c r="D55" s="9">
-        <v>46197.71564204861</v>
+        <v>46250.346086192134</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>201</v>
@@ -5050,7 +5050,7 @@
         <v>46195.95012040509</v>
       </c>
       <c r="D58" s="5">
-        <v>46240.1885688426</v>
+        <v>46250.34651130787</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>215</v>
@@ -5225,7 +5225,7 @@
         <v>46196.87995266204</v>
       </c>
       <c r="D61" s="9">
-        <v>46241.167933206016</v>
+        <v>46250.34660050926</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>97</v>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46174.84660805555</v>
+        <v>46250.34665685185</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>226</v>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46209.909264270835</v>
+        <v>46250.35988837963</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>253</v>
@@ -5951,7 +5951,7 @@
         <v>46209.90925715277</v>
       </c>
       <c r="D73" s="9">
-        <v>46244.91622328704</v>
+        <v>46250.34668475694</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>256</v>
@@ -6069,7 +6069,7 @@
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46209.90954123843</v>
+        <v>46250.3539153125</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>264</v>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46209.908330833336</v>
+        <v>46250.35603524305</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>269</v>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46239.596496921295</v>
+        <v>46250.36058042824</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>290</v>
@@ -6836,7 +6836,7 @@
         <v>46209.84929427083</v>
       </c>
       <c r="D88" s="5">
-        <v>46223.568163460644</v>
+        <v>46250.36067016204</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>295</v>
@@ -6952,7 +6952,7 @@
         <v>46209.84944726852</v>
       </c>
       <c r="D90" s="5">
-        <v>46223.56815898148</v>
+        <v>46250.36077557871</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>300</v>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46237.54429445602</v>
+        <v>46250.36084331018</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>305</v>
@@ -7184,7 +7184,7 @@
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46223.568144791665</v>
+        <v>46250.360918136575</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>310</v>
@@ -7300,7 +7300,7 @@
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46223.568144212964</v>
+        <v>46250.36095200232</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>314</v>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46238.48974153935</v>
+        <v>46250.36124804398</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>322</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46223.56892738426</v>
+        <v>46250.36143672453</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>332</v>
@@ -7895,7 +7895,7 @@
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46174.84870307871</v>
+        <v>46250.36202353009</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>338</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46240.717242997685</v>
+        <v>46250.362211921296</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>344</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46250.34665685185</v>
+        <v>46250.63425142361</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>226</v>
@@ -6671,7 +6671,7 @@
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46223.56797070602</v>
+        <v>46250.63500270833</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>287</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -5951,7 +5951,7 @@
         <v>46209.90925715277</v>
       </c>
       <c r="D73" s="9">
-        <v>46250.34668475694</v>
+        <v>46251.01852726852</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>256</v>
@@ -6069,7 +6069,7 @@
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46250.3539153125</v>
+        <v>46251.01908697917</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>264</v>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46250.35603524305</v>
+        <v>46251.01951052083</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>269</v>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46250.36124804398</v>
+        <v>46251.02104770833</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>322</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46250.36143672453</v>
+        <v>46251.02178085648</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>332</v>
@@ -7895,7 +7895,7 @@
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46250.36202353009</v>
+        <v>46251.023444618055</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>338</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46250.362211921296</v>
+        <v>46251.02515972222</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>344</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -853,7 +853,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT2 4307 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ </t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1215174141301410</t>
@@ -5514,7 +5514,7 @@
         <v>46210.651376574075</v>
       </c>
       <c r="D66" s="5">
-        <v>46210.651395196764</v>
+        <v>46252.19754037037</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>235</v>
@@ -5558,8 +5558,8 @@
       <c r="R66" s="5">
         <v>46259</v>
       </c>
-      <c r="S66" s="7" t="s">
-        <v>33</v>
+      <c r="S66" s="11" t="s">
+        <v>160</v>
       </c>
       <c r="T66" s="6">
         <v>1</v>
@@ -5644,7 +5644,7 @@
         <v>46210.651382638884</v>
       </c>
       <c r="D68" s="5">
-        <v>46210.65139929398</v>
+        <v>46252.19754055556</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>244</v>
@@ -5688,8 +5688,8 @@
       <c r="R68" s="5">
         <v>46259</v>
       </c>
-      <c r="S68" s="7" t="s">
-        <v>33</v>
+      <c r="S68" s="11" t="s">
+        <v>160</v>
       </c>
       <c r="T68" s="6">
         <v>1</v>
@@ -5774,7 +5774,7 @@
         <v>46210.65139943287</v>
       </c>
       <c r="D70" s="5">
-        <v>46210.65141630787</v>
+        <v>46252.19754061343</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>249</v>
@@ -5818,8 +5818,8 @@
       <c r="R70" s="5">
         <v>46259</v>
       </c>
-      <c r="S70" s="7" t="s">
-        <v>33</v>
+      <c r="S70" s="11" t="s">
+        <v>160</v>
       </c>
       <c r="T70" s="6">
         <v>1</v>
@@ -5951,7 +5951,7 @@
         <v>46209.90925715277</v>
       </c>
       <c r="D73" s="9">
-        <v>46251.01852726852</v>
+        <v>46252.557083900465</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>256</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -853,7 +853,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1215174141301410</t>
@@ -2266,7 +2266,7 @@
         <v>46238.48972837963</v>
       </c>
       <c r="D12" s="5">
-        <v>46250.15126246528</v>
+        <v>46252.61058354167</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2316,8 +2316,8 @@
       <c r="T12" s="6">
         <v>1</v>
       </c>
-      <c r="U12" s="7" t="s">
-        <v>27</v>
+      <c r="U12" s="11" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
@@ -2331,7 +2331,7 @@
         <v>46238.48971166667</v>
       </c>
       <c r="D13" s="9">
-        <v>46238.48971369213</v>
+        <v>46252.610572060184</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>64</v>
@@ -5951,7 +5951,7 @@
         <v>46209.90925715277</v>
       </c>
       <c r="D73" s="9">
-        <v>46252.557083900465</v>
+        <v>46252.6980291088</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>256</v>
@@ -6297,9 +6297,11 @@
       <c r="B79" s="9">
         <v>46169.66960108797</v>
       </c>
-      <c r="C79" s="10"/>
+      <c r="C79" s="9">
+        <v>46252.610585208335</v>
+      </c>
       <c r="D79" s="9">
-        <v>46209.85402508102</v>
+        <v>46252.610598287036</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>232</v>
@@ -6334,9 +6336,11 @@
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
       <c r="S79" s="10"/>
-      <c r="T79" s="10"/>
-      <c r="U79" s="11" t="s">
-        <v>50</v>
+      <c r="T79" s="10">
+        <v>1</v>
+      </c>
+      <c r="U79" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
@@ -6606,9 +6610,11 @@
       <c r="B84" s="5">
         <v>46169.669635185186</v>
       </c>
-      <c r="C84" s="6"/>
+      <c r="C84" s="5">
+        <v>46252.61056563657</v>
+      </c>
       <c r="D84" s="5">
-        <v>46221.186868703706</v>
+        <v>46252.61058555555</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>60</v>
@@ -6656,10 +6662,10 @@
         <v>62</v>
       </c>
       <c r="T84" s="6">
-        <v>0</v>
-      </c>
-      <c r="U84" s="12" t="s">
-        <v>122</v>
+        <v>1</v>
+      </c>
+      <c r="U84" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6671,7 +6677,7 @@
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46250.63500270833</v>
+        <v>46252.61072833333</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>287</v>
@@ -6716,9 +6722,11 @@
       <c r="B86" s="5">
         <v>46169.66965109954</v>
       </c>
-      <c r="C86" s="6"/>
+      <c r="C86" s="5">
+        <v>46252.610662175925</v>
+      </c>
       <c r="D86" s="5">
-        <v>46250.36058042824</v>
+        <v>46252.61067681713</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>290</v>
@@ -6766,7 +6774,7 @@
         <v>33</v>
       </c>
       <c r="T86" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U86" s="7" t="s">
         <v>27</v>
@@ -7066,9 +7074,11 @@
       <c r="B92" s="5">
         <v>46169.66981054399</v>
       </c>
-      <c r="C92" s="6"/>
+      <c r="C92" s="5">
+        <v>46252.610722604164</v>
+      </c>
       <c r="D92" s="5">
-        <v>46250.36084331018</v>
+        <v>46252.61073834491</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>305</v>
@@ -7116,10 +7126,10 @@
         <v>33</v>
       </c>
       <c r="T92" s="6">
-        <v>0</v>
-      </c>
-      <c r="U92" s="11" t="s">
-        <v>50</v>
+        <v>1</v>
+      </c>
+      <c r="U92" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
@@ -7414,7 +7424,7 @@
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46174.82401747685</v>
+        <v>46252.61088775463</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>319</v>
@@ -7459,9 +7469,11 @@
       <c r="B99" s="9">
         <v>46169.66998244213</v>
       </c>
-      <c r="C99" s="10"/>
+      <c r="C99" s="9">
+        <v>46252.61078912037</v>
+      </c>
       <c r="D99" s="9">
-        <v>46251.02104770833</v>
+        <v>46252.61081997685</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>322</v>
@@ -7509,10 +7521,10 @@
         <v>33</v>
       </c>
       <c r="T99" s="10">
-        <v>0</v>
-      </c>
-      <c r="U99" s="12" t="s">
-        <v>122</v>
+        <v>1</v>
+      </c>
+      <c r="U99" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
@@ -7893,9 +7905,11 @@
       <c r="B107" s="9">
         <v>46169.67013976852</v>
       </c>
-      <c r="C107" s="10"/>
+      <c r="C107" s="9">
+        <v>46252.610881747685</v>
+      </c>
       <c r="D107" s="9">
-        <v>46251.023444618055</v>
+        <v>46252.61090652778</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>338</v>
@@ -7941,10 +7955,10 @@
         <v>33</v>
       </c>
       <c r="T107" s="10">
-        <v>0</v>
-      </c>
-      <c r="U107" s="12" t="s">
-        <v>122</v>
+        <v>1</v>
+      </c>
+      <c r="U107" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
@@ -8115,7 +8129,7 @@
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46251.02515972222</v>
+        <v>46252.620752256946</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>344</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -8129,7 +8129,7 @@
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46252.620752256946</v>
+        <v>46253.62502890047</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>344</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -5579,7 +5579,7 @@
         <v>46210.65195509259</v>
       </c>
       <c r="D67" s="9">
-        <v>46210.65197202546</v>
+        <v>46254.20088296296</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>240</v>
@@ -5623,8 +5623,8 @@
       <c r="R67" s="9">
         <v>46261</v>
       </c>
-      <c r="S67" s="7" t="s">
-        <v>33</v>
+      <c r="S67" s="11" t="s">
+        <v>160</v>
       </c>
       <c r="T67" s="10">
         <v>1</v>
@@ -5709,7 +5709,7 @@
         <v>46210.651959571755</v>
       </c>
       <c r="D69" s="9">
-        <v>46210.651975879635</v>
+        <v>46254.20088310185</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>247</v>
@@ -5753,8 +5753,8 @@
       <c r="R69" s="9">
         <v>46261</v>
       </c>
-      <c r="S69" s="7" t="s">
-        <v>33</v>
+      <c r="S69" s="11" t="s">
+        <v>160</v>
       </c>
       <c r="T69" s="10">
         <v>1</v>
@@ -5839,7 +5839,7 @@
         <v>46210.6519625463</v>
       </c>
       <c r="D71" s="9">
-        <v>46210.65197810185</v>
+        <v>46254.20088236111</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>250</v>
@@ -5883,8 +5883,8 @@
       <c r="R71" s="9">
         <v>46261</v>
       </c>
-      <c r="S71" s="7" t="s">
-        <v>33</v>
+      <c r="S71" s="11" t="s">
+        <v>160</v>
       </c>
       <c r="T71" s="10">
         <v>1</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -554,9 +554,6 @@
     <t xml:space="preserve">Generación OC materiales corte Laser ot 4342 -4344,Fabricacion Corte Laser ot 4342 -4344 </t>
   </si>
   <si>
-    <t>Media</t>
-  </si>
-  <si>
     <t>1215174084306570</t>
   </si>
   <si>
@@ -791,6 +788,9 @@
   </si>
   <si>
     <t xml:space="preserve">Bodega:,control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1215174382728414</t>
@@ -4055,7 +4055,7 @@
         <v>46209.82174373843</v>
       </c>
       <c r="D41" s="9">
-        <v>46248.17429667824</v>
+        <v>46256.206877731485</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>156</v>
@@ -4099,8 +4099,8 @@
       <c r="R41" s="9">
         <v>46255</v>
       </c>
-      <c r="S41" s="11" t="s">
-        <v>160</v>
+      <c r="S41" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="T41" s="10">
         <v>1</v>
@@ -4111,7 +4111,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B42" s="5">
         <v>46169.66916377315</v>
@@ -4123,7 +4123,7 @@
         <v>46199.56927892361</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
@@ -4156,7 +4156,7 @@
         <v>96</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4172,7 +4172,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B43" s="9">
         <v>46169.66916960648</v>
@@ -4184,7 +4184,7 @@
         <v>46205.61247092593</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
@@ -4214,10 +4214,10 @@
         <v>156</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4233,7 +4233,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B44" s="5">
         <v>46169.66917503472</v>
@@ -4242,10 +4242,10 @@
         <v>46199.56727092592</v>
       </c>
       <c r="D44" s="5">
-        <v>46248.17429556713</v>
+        <v>46256.206877951394</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
@@ -4275,7 +4275,7 @@
         <v>112</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>26</v>
@@ -4286,8 +4286,8 @@
       <c r="R44" s="5">
         <v>46255</v>
       </c>
-      <c r="S44" s="11" t="s">
-        <v>160</v>
+      <c r="S44" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="T44" s="6">
         <v>1</v>
@@ -4298,7 +4298,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B45" s="9">
         <v>46169.669178888886</v>
@@ -4337,13 +4337,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>100</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4353,7 +4353,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B46" s="5">
         <v>46169.669183680555</v>
@@ -4365,7 +4365,7 @@
         <v>46199.56984034722</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
@@ -4392,13 +4392,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>101</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4408,7 +4408,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B47" s="9">
         <v>46169.66918849537</v>
@@ -4420,16 +4420,16 @@
         <v>46204.863616284725</v>
       </c>
       <c r="E47" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="F47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="10" t="s">
+      <c r="H47" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="I47" s="9">
         <v>46245</v>
@@ -4450,7 +4450,7 @@
         <v>112</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>26</v>
@@ -4473,7 +4473,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B48" s="5">
         <v>46169.66919252315</v>
@@ -4491,10 +4491,10 @@
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I48" s="5">
         <v>46245</v>
@@ -4512,13 +4512,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>106</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4528,7 +4528,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B49" s="9">
         <v>46169.66919734953</v>
@@ -4540,16 +4540,16 @@
         <v>46204.8635487037</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="I49" s="9">
         <v>46254</v>
@@ -4567,13 +4567,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O49" s="10" t="s">
         <v>107</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4583,7 +4583,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
         <v>46169.66920229167</v>
@@ -4595,16 +4595,16 @@
         <v>46210.65313525463</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="H50" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I50" s="5">
         <v>46286</v>
@@ -4622,10 +4622,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4638,7 +4638,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B51" s="9">
         <v>46169.66924202546</v>
@@ -4647,10 +4647,10 @@
         <v>46199.57083833333</v>
       </c>
       <c r="D51" s="9">
-        <v>46248.174295624995</v>
+        <v>46256.20687767361</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
@@ -4680,7 +4680,7 @@
         <v>112</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P51" s="10" t="s">
         <v>26</v>
@@ -4691,8 +4691,8 @@
       <c r="R51" s="9">
         <v>46255</v>
       </c>
-      <c r="S51" s="11" t="s">
-        <v>160</v>
+      <c r="S51" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="T51" s="10">
         <v>1</v>
@@ -4703,7 +4703,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B52" s="5">
         <v>46169.66924635417</v>
@@ -4742,13 +4742,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>103</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4758,7 +4758,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B53" s="9">
         <v>46169.66925091435</v>
@@ -4770,7 +4770,7 @@
         <v>46199.57082731482</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
@@ -4797,13 +4797,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O53" s="10" t="s">
         <v>104</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4813,7 +4813,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B54" s="5">
         <v>46169.669255659726</v>
@@ -4825,7 +4825,7 @@
         <v>46210.52487434028</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>25</v>
@@ -4849,7 +4849,7 @@
         <v>26</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -4866,7 +4866,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B55" s="9">
         <v>46169.66925896991</v>
@@ -4878,16 +4878,16 @@
         <v>46250.346086192134</v>
       </c>
       <c r="E55" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G55" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G55" s="10" t="s">
+      <c r="H55" s="10" t="s">
         <v>202</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>203</v>
       </c>
       <c r="I55" s="9">
         <v>46167</v>
@@ -4899,19 +4899,19 @@
         <v>26</v>
       </c>
       <c r="L55" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="M55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N55" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="O55" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="M55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N55" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="O55" s="10" t="s">
-        <v>205</v>
-      </c>
       <c r="P55" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q55" s="9">
         <v>46167</v>
@@ -4931,7 +4931,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B56" s="5">
         <v>46169.66926408565</v>
@@ -4943,16 +4943,16 @@
         <v>46195.94997940972</v>
       </c>
       <c r="E56" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G56" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="F56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G56" s="6" t="s">
+      <c r="H56" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I56" s="5">
         <v>46167</v>
@@ -4970,13 +4970,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>79</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4986,7 +4986,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B57" s="9">
         <v>46169.66926952546</v>
@@ -4998,16 +4998,16 @@
         <v>46195.94998958333</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I57" s="9">
         <v>46167</v>
@@ -5025,13 +5025,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O57" s="10" t="s">
         <v>79</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -5041,7 +5041,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B58" s="5">
         <v>46169.66929263889</v>
@@ -5053,16 +5053,16 @@
         <v>46250.34651130787</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="I58" s="5">
         <v>46220</v>
@@ -5080,13 +5080,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q58" s="5">
         <v>46220</v>
@@ -5106,7 +5106,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B59" s="9">
         <v>46169.66929775463</v>
@@ -5118,16 +5118,16 @@
         <v>46195.950096458335</v>
       </c>
       <c r="E59" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G59" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="F59" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G59" s="10" t="s">
+      <c r="H59" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I59" s="9">
         <v>46181</v>
@@ -5145,13 +5145,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O59" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="P59" s="10" t="s">
         <v>218</v>
-      </c>
-      <c r="P59" s="10" t="s">
-        <v>219</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5161,7 +5161,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B60" s="5">
         <v>46169.66930358796</v>
@@ -5173,16 +5173,16 @@
         <v>46196.87985491898</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I60" s="5">
         <v>46181</v>
@@ -5200,13 +5200,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5216,7 +5216,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B61" s="9">
         <v>46169.669327048614</v>
@@ -5234,10 +5234,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I61" s="9">
         <v>46240</v>
@@ -5255,13 +5255,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q61" s="9">
         <v>46240</v>
@@ -5281,7 +5281,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B62" s="5">
         <v>46169.6693399537</v>
@@ -5293,16 +5293,16 @@
         <v>46195.95042396991</v>
       </c>
       <c r="E62" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G62" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="F62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G62" s="6" t="s">
+      <c r="H62" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I62" s="5">
         <v>46188</v>
@@ -5323,7 +5323,7 @@
         <v>97</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>97</v>
@@ -5336,7 +5336,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B63" s="9">
         <v>46169.669361203705</v>
@@ -5346,16 +5346,16 @@
         <v>46250.63425142361</v>
       </c>
       <c r="E63" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="F63" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G63" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="F63" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G63" s="10" t="s">
+      <c r="H63" s="10" t="s">
         <v>227</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>228</v>
       </c>
       <c r="I63" s="9">
         <v>46322</v>
@@ -5373,10 +5373,10 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P63" s="10" t="s">
         <v>26</v>
@@ -5399,7 +5399,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B64" s="5">
         <v>46169.66936501158</v>
@@ -5409,16 +5409,16 @@
         <v>46174.846919421296</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>227</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>228</v>
       </c>
       <c r="I64" s="5">
         <v>46290</v>
@@ -5436,13 +5436,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5452,7 +5452,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B65" s="9">
         <v>46169.669418136575</v>
@@ -5464,7 +5464,7 @@
         <v>46210.65198340278</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>25</v>
@@ -5488,7 +5488,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P65" s="10" t="s">
         <v>26</v>
@@ -5505,7 +5505,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B66" s="5">
         <v>46169.66942685185</v>
@@ -5517,16 +5517,16 @@
         <v>46252.19754037037</v>
       </c>
       <c r="E66" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G66" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="F66" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G66" s="6" t="s">
+      <c r="H66" s="6" t="s">
         <v>236</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>237</v>
       </c>
       <c r="I66" s="5">
         <v>46258</v>
@@ -5544,13 +5544,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Q66" s="5">
         <v>46258</v>
@@ -5559,7 +5559,7 @@
         <v>46259</v>
       </c>
       <c r="S66" s="11" t="s">
-        <v>160</v>
+        <v>238</v>
       </c>
       <c r="T66" s="6">
         <v>1</v>
@@ -5588,10 +5588,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I67" s="9">
         <v>46260</v>
@@ -5609,7 +5609,7 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>241</v>
@@ -5624,7 +5624,7 @@
         <v>46261</v>
       </c>
       <c r="S67" s="11" t="s">
-        <v>160</v>
+        <v>238</v>
       </c>
       <c r="T67" s="10">
         <v>1</v>
@@ -5653,10 +5653,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>236</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>237</v>
       </c>
       <c r="I68" s="5">
         <v>46258</v>
@@ -5674,10 +5674,10 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>245</v>
@@ -5689,7 +5689,7 @@
         <v>46259</v>
       </c>
       <c r="S68" s="11" t="s">
-        <v>160</v>
+        <v>238</v>
       </c>
       <c r="T68" s="6">
         <v>1</v>
@@ -5718,10 +5718,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I69" s="9">
         <v>46260</v>
@@ -5739,13 +5739,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O69" s="10" t="s">
         <v>244</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q69" s="9">
         <v>46260</v>
@@ -5754,7 +5754,7 @@
         <v>46261</v>
       </c>
       <c r="S69" s="11" t="s">
-        <v>160</v>
+        <v>238</v>
       </c>
       <c r="T69" s="10">
         <v>1</v>
@@ -5783,10 +5783,10 @@
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>236</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>237</v>
       </c>
       <c r="I70" s="5">
         <v>46258</v>
@@ -5804,10 +5804,10 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>250</v>
@@ -5819,7 +5819,7 @@
         <v>46259</v>
       </c>
       <c r="S70" s="11" t="s">
-        <v>160</v>
+        <v>238</v>
       </c>
       <c r="T70" s="6">
         <v>1</v>
@@ -5848,10 +5848,10 @@
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H71" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I71" s="9">
         <v>46260</v>
@@ -5869,13 +5869,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O71" s="10" t="s">
         <v>249</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q71" s="9">
         <v>46260</v>
@@ -5884,7 +5884,7 @@
         <v>46261</v>
       </c>
       <c r="S71" s="11" t="s">
-        <v>160</v>
+        <v>238</v>
       </c>
       <c r="T71" s="10">
         <v>1</v>
@@ -6019,7 +6019,7 @@
         <v>46210.65196928241</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -6102,7 +6102,7 @@
         <v>253</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P75" s="10" t="s">
         <v>253</v>
@@ -6135,7 +6135,7 @@
         <v>46209.90937868056</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6194,10 +6194,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H77" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I77" s="9">
         <v>46294</v>
@@ -6218,7 +6218,7 @@
         <v>253</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>253</v>
@@ -6251,16 +6251,16 @@
         <v>46197.84256122685</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -6304,7 +6304,7 @@
         <v>46252.610598287036</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>25</v>
@@ -6363,10 +6363,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>236</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>237</v>
       </c>
       <c r="I80" s="5">
         <v>46174</v>
@@ -6384,7 +6384,7 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>133</v>
@@ -6428,10 +6428,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="H81" s="10" t="s">
         <v>236</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>237</v>
       </c>
       <c r="I81" s="9">
         <v>46288</v>
@@ -6449,7 +6449,7 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>124</v>
@@ -6493,10 +6493,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>236</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>237</v>
       </c>
       <c r="I82" s="5">
         <v>46308</v>
@@ -6514,7 +6514,7 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>142</v>
@@ -6558,10 +6558,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="H83" s="10" t="s">
         <v>236</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>237</v>
       </c>
       <c r="I83" s="9">
         <v>46287</v>
@@ -6579,10 +6579,10 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="P83" s="10" t="s">
         <v>283</v>
@@ -6623,10 +6623,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>236</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>237</v>
       </c>
       <c r="I84" s="5">
         <v>46220</v>
@@ -6644,7 +6644,7 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>153</v>
@@ -6792,7 +6792,7 @@
         <v>46239.59649744213</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6877,7 +6877,7 @@
         <v>287</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>287</v>
@@ -6910,7 +6910,7 @@
         <v>46223.83603929398</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6993,7 +6993,7 @@
         <v>287</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>287</v>
@@ -7026,7 +7026,7 @@
         <v>46223.56782162037</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -7111,7 +7111,7 @@
         <v>287</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>287</v>
@@ -7144,7 +7144,7 @@
         <v>46223.56789047454</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7227,7 +7227,7 @@
         <v>287</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>287</v>
@@ -7260,7 +7260,7 @@
         <v>46223.56796597222</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7290,7 +7290,7 @@
         <v>310</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P95" s="10" t="s">
         <v>312</v>
@@ -7343,7 +7343,7 @@
         <v>287</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>315</v>
@@ -7376,7 +7376,7 @@
         <v>46223.836147291666</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7404,7 +7404,7 @@
         <v>314</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P97" s="10" t="s">
         <v>317</v>
@@ -7539,7 +7539,7 @@
         <v>46174.84838837963</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7567,7 +7567,7 @@
         <v>322</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>327</v>
@@ -7590,7 +7590,7 @@
         <v>46209.90833168982</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7621,7 +7621,7 @@
         <v>26</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7722,7 +7722,7 @@
         <v>319</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P103" s="10" t="s">
         <v>319</v>
@@ -7755,7 +7755,7 @@
         <v>46223.568262175926</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7783,7 +7783,7 @@
         <v>332</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P104" s="6" t="s">
         <v>334</v>
@@ -7806,7 +7806,7 @@
         <v>46223.56826151621</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7834,10 +7834,10 @@
         <v>332</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7940,7 +7940,7 @@
         <v>319</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P107" s="10" t="s">
         <v>319</v>
@@ -7973,7 +7973,7 @@
         <v>46174.848669872685</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8003,7 +8003,7 @@
         <v>338</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>340</v>
@@ -8026,7 +8026,7 @@
         <v>46174.848667314815</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -8056,10 +8056,10 @@
         <v>338</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -8162,7 +8162,7 @@
         <v>319</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P111" s="10" t="s">
         <v>345</v>
@@ -8195,7 +8195,7 @@
         <v>46174.84878571759</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8223,7 +8223,7 @@
         <v>344</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>344</v>
@@ -8246,7 +8246,7 @@
         <v>46174.84878314815</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -8274,7 +8274,7 @@
         <v>344</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -5341,9 +5341,11 @@
       <c r="B63" s="9">
         <v>46169.669361203705</v>
       </c>
-      <c r="C63" s="10"/>
+      <c r="C63" s="9">
+        <v>46258.54197802083</v>
+      </c>
       <c r="D63" s="9">
-        <v>46250.63425142361</v>
+        <v>46258.54200784722</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>225</v>
@@ -5391,10 +5393,10 @@
         <v>33</v>
       </c>
       <c r="T63" s="10">
-        <v>0</v>
-      </c>
-      <c r="U63" s="12" t="s">
-        <v>122</v>
+        <v>1</v>
+      </c>
+      <c r="U63" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -853,7 +853,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6</t>
   </si>
   <si>
     <t>1215174141301410</t>
@@ -5953,7 +5953,7 @@
         <v>46209.90925715277</v>
       </c>
       <c r="D73" s="9">
-        <v>46252.6980291088</v>
+        <v>46258.64932118056</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>256</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -790,19 +790,19 @@
     <t xml:space="preserve">Bodega:,control de calidad corte laser </t>
   </si>
   <si>
+    <t>1215174382728414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,Bodega:</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215174382728414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,Bodega:</t>
   </si>
   <si>
     <t>1215174260282365</t>
@@ -5516,7 +5516,7 @@
         <v>46210.651376574075</v>
       </c>
       <c r="D66" s="5">
-        <v>46252.19754037037</v>
+        <v>46260.16864103009</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>234</v>
@@ -5560,8 +5560,8 @@
       <c r="R66" s="5">
         <v>46259</v>
       </c>
-      <c r="S66" s="11" t="s">
-        <v>238</v>
+      <c r="S66" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="T66" s="6">
         <v>1</v>
@@ -5572,7 +5572,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B67" s="9">
         <v>46169.669432361115</v>
@@ -5584,7 +5584,7 @@
         <v>46254.20088296296</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -5614,10 +5614,10 @@
         <v>231</v>
       </c>
       <c r="O67" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="P67" s="10" t="s">
         <v>241</v>
-      </c>
-      <c r="P67" s="10" t="s">
-        <v>242</v>
       </c>
       <c r="Q67" s="9">
         <v>46260</v>
@@ -5626,7 +5626,7 @@
         <v>46261</v>
       </c>
       <c r="S67" s="11" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="T67" s="10">
         <v>1</v>
@@ -5646,7 +5646,7 @@
         <v>46210.651382638884</v>
       </c>
       <c r="D68" s="5">
-        <v>46252.19754055556</v>
+        <v>46260.16864224537</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>244</v>
@@ -5690,8 +5690,8 @@
       <c r="R68" s="5">
         <v>46259</v>
       </c>
-      <c r="S68" s="11" t="s">
-        <v>238</v>
+      <c r="S68" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="T68" s="6">
         <v>1</v>
@@ -5756,7 +5756,7 @@
         <v>46261</v>
       </c>
       <c r="S69" s="11" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="T69" s="10">
         <v>1</v>
@@ -5776,7 +5776,7 @@
         <v>46210.65139943287</v>
       </c>
       <c r="D70" s="5">
-        <v>46252.19754061343</v>
+        <v>46260.168641122684</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>249</v>
@@ -5820,8 +5820,8 @@
       <c r="R70" s="5">
         <v>46259</v>
       </c>
-      <c r="S70" s="11" t="s">
-        <v>238</v>
+      <c r="S70" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="T70" s="6">
         <v>1</v>
@@ -5886,7 +5886,7 @@
         <v>46261</v>
       </c>
       <c r="S71" s="11" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="T71" s="10">
         <v>1</v>
@@ -6392,7 +6392,7 @@
         <v>133</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q80" s="5">
         <v>46174</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -6071,7 +6071,7 @@
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46251.01908697917</v>
+        <v>46260.587916261575</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>264</v>
@@ -6121,8 +6121,8 @@
       <c r="T75" s="10">
         <v>0.1</v>
       </c>
-      <c r="U75" s="11" t="s">
-        <v>50</v>
+      <c r="U75" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46251.01951052083</v>
+        <v>46260.587929270834</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>269</v>
@@ -6237,8 +6237,8 @@
       <c r="T77" s="10">
         <v>0</v>
       </c>
-      <c r="U77" s="12" t="s">
-        <v>122</v>
+      <c r="U77" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46250.360918136575</v>
+        <v>46260.58797681713</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>310</v>
@@ -7246,8 +7246,8 @@
       <c r="T94" s="6">
         <v>0</v>
       </c>
-      <c r="U94" s="12" t="s">
-        <v>122</v>
+      <c r="U94" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -7312,7 +7312,7 @@
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46250.36095200232</v>
+        <v>46260.58799998843</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>314</v>
@@ -7362,8 +7362,8 @@
       <c r="T96" s="6">
         <v>0</v>
       </c>
-      <c r="U96" s="12" t="s">
-        <v>122</v>
+      <c r="U96" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46251.02178085648</v>
+        <v>46260.58802633102</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>332</v>
@@ -7741,8 +7741,8 @@
       <c r="T103" s="10">
         <v>0</v>
       </c>
-      <c r="U103" s="12" t="s">
-        <v>122</v>
+      <c r="U103" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -853,7 +853,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6</t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6</t>
   </si>
   <si>
     <t>1215174141301410</t>
@@ -5953,7 +5953,7 @@
         <v>46209.90925715277</v>
       </c>
       <c r="D73" s="9">
-        <v>46258.64932118056</v>
+        <v>46260.67955340278</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>256</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -853,7 +853,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6</t>
+    <t xml:space="preserve">OT2 4307 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6,OT 4075  -ZVRv 1-16-37/6 ,OT 4413  -ZVRv 1-22-185/6  </t>
   </si>
   <si>
     <t>1215174141301410</t>
@@ -5953,7 +5953,7 @@
         <v>46209.90925715277</v>
       </c>
       <c r="D73" s="9">
-        <v>46260.67955340278</v>
+        <v>46261.60082807871</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>256</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1403" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1403" uniqueCount="357">
   <si>
     <t>50001558 -  GESVIAL</t>
   </si>
@@ -800,9 +800,6 @@
   </si>
   <si>
     <t>OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,Bodega:</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1215174260282365</t>
@@ -5581,7 +5578,7 @@
         <v>46210.65195509259</v>
       </c>
       <c r="D67" s="9">
-        <v>46254.20088296296</v>
+        <v>46262.197503240735</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>239</v>
@@ -5625,8 +5622,8 @@
       <c r="R67" s="9">
         <v>46261</v>
       </c>
-      <c r="S67" s="11" t="s">
-        <v>242</v>
+      <c r="S67" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="T67" s="10">
         <v>1</v>
@@ -5637,7 +5634,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B68" s="5">
         <v>46169.66943836806</v>
@@ -5649,7 +5646,7 @@
         <v>46260.16864224537</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5682,7 +5679,7 @@
         <v>172</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q68" s="5">
         <v>46258</v>
@@ -5702,7 +5699,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B69" s="9">
         <v>46169.669443692124</v>
@@ -5711,10 +5708,10 @@
         <v>46210.651959571755</v>
       </c>
       <c r="D69" s="9">
-        <v>46254.20088310185</v>
+        <v>46262.19750384259</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -5744,7 +5741,7 @@
         <v>231</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P69" s="10" t="s">
         <v>206</v>
@@ -5755,8 +5752,8 @@
       <c r="R69" s="9">
         <v>46261</v>
       </c>
-      <c r="S69" s="11" t="s">
-        <v>242</v>
+      <c r="S69" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="T69" s="10">
         <v>1</v>
@@ -5767,7 +5764,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B70" s="5">
         <v>46169.669448368055</v>
@@ -5779,7 +5776,7 @@
         <v>46260.168641122684</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5812,7 +5809,7 @@
         <v>194</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q70" s="5">
         <v>46258</v>
@@ -5832,7 +5829,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B71" s="9">
         <v>46169.66945298611</v>
@@ -5841,10 +5838,10 @@
         <v>46210.6519625463</v>
       </c>
       <c r="D71" s="9">
-        <v>46254.20088236111</v>
+        <v>46262.19750234953</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
@@ -5874,7 +5871,7 @@
         <v>231</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>206</v>
@@ -5885,8 +5882,8 @@
       <c r="R71" s="9">
         <v>46261</v>
       </c>
-      <c r="S71" s="11" t="s">
-        <v>242</v>
+      <c r="S71" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="T71" s="10">
         <v>1</v>
@@ -5897,7 +5894,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B72" s="5">
         <v>46169.66945778935</v>
@@ -5907,7 +5904,7 @@
         <v>46250.35988837963</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>25</v>
@@ -5931,7 +5928,7 @@
         <v>26</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>26</v>
@@ -5944,7 +5941,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B73" s="9">
         <v>46169.66946104167</v>
@@ -5956,16 +5953,16 @@
         <v>46261.60082807871</v>
       </c>
       <c r="E73" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="F73" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G73" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="F73" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G73" s="10" t="s">
+      <c r="H73" s="10" t="s">
         <v>257</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>258</v>
       </c>
       <c r="I73" s="9">
         <v>46262</v>
@@ -5983,13 +5980,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q73" s="9">
         <v>46262</v>
@@ -6009,7 +6006,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B74" s="5">
         <v>46169.669467280095</v>
@@ -6027,10 +6024,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="I74" s="5">
         <v>46262</v>
@@ -6048,13 +6045,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O74" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="P74" s="6" t="s">
         <v>261</v>
-      </c>
-      <c r="P74" s="6" t="s">
-        <v>262</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6064,7 +6061,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B75" s="9">
         <v>46169.66950289352</v>
@@ -6074,16 +6071,16 @@
         <v>46260.587916261575</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="H75" s="10" t="s">
         <v>257</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>258</v>
       </c>
       <c r="I75" s="9">
         <v>46273</v>
@@ -6101,13 +6098,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O75" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q75" s="9">
         <v>46273</v>
@@ -6127,7 +6124,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B76" s="5">
         <v>46169.66950758102</v>
@@ -6143,10 +6140,10 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="I76" s="5">
         <v>46273</v>
@@ -6164,13 +6161,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O76" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="P76" s="6" t="s">
         <v>266</v>
-      </c>
-      <c r="P76" s="6" t="s">
-        <v>267</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6180,7 +6177,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B77" s="9">
         <v>46169.66953380787</v>
@@ -6190,7 +6187,7 @@
         <v>46260.587929270834</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6217,13 +6214,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O77" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q77" s="9">
         <v>46294</v>
@@ -6243,7 +6240,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B78" s="5">
         <v>46169.66953854167</v>
@@ -6278,13 +6275,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6294,7 +6291,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B79" s="9">
         <v>46169.66960108797</v>
@@ -6330,7 +6327,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P79" s="10" t="s">
         <v>26</v>
@@ -6347,7 +6344,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B80" s="5">
         <v>46169.66960956018</v>
@@ -6359,7 +6356,7 @@
         <v>46209.844928101855</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6412,7 +6409,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B81" s="9">
         <v>46169.6696165162</v>
@@ -6424,7 +6421,7 @@
         <v>46209.84471936343</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6457,7 +6454,7 @@
         <v>124</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q81" s="9">
         <v>46288</v>
@@ -6477,7 +6474,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B82" s="5">
         <v>46169.669622939815</v>
@@ -6489,7 +6486,7 @@
         <v>46209.85430440972</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6522,7 +6519,7 @@
         <v>142</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q82" s="5">
         <v>46308</v>
@@ -6542,7 +6539,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B83" s="9">
         <v>46169.66962980324</v>
@@ -6554,7 +6551,7 @@
         <v>46239.59650748843</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6587,7 +6584,7 @@
         <v>182</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Q83" s="9">
         <v>46287</v>
@@ -6607,7 +6604,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B84" s="5">
         <v>46169.669635185186</v>
@@ -6652,7 +6649,7 @@
         <v>153</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Q84" s="5">
         <v>46220</v>
@@ -6672,7 +6669,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B85" s="9">
         <v>46169.66964790509</v>
@@ -6682,7 +6679,7 @@
         <v>46252.61072833333</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>25</v>
@@ -6706,7 +6703,7 @@
         <v>26</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>26</v>
@@ -6719,7 +6716,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B86" s="5">
         <v>46169.66965109954</v>
@@ -6731,7 +6728,7 @@
         <v>46252.61067681713</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6758,13 +6755,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q86" s="5">
         <v>46294</v>
@@ -6784,7 +6781,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B87" s="9">
         <v>46169.6696568287</v>
@@ -6821,13 +6818,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6837,7 +6834,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B88" s="5">
         <v>46169.669688622685</v>
@@ -6849,7 +6846,7 @@
         <v>46250.36067016204</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6876,13 +6873,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q88" s="5">
         <v>46316</v>
@@ -6902,7 +6899,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B89" s="9">
         <v>46169.66969347223</v>
@@ -6937,13 +6934,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O89" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="P89" s="10" t="s">
         <v>297</v>
-      </c>
-      <c r="P89" s="10" t="s">
-        <v>298</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6953,7 +6950,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B90" s="5">
         <v>46169.66972681713</v>
@@ -6965,7 +6962,7 @@
         <v>46250.36077557871</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6992,13 +6989,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q90" s="5">
         <v>46317</v>
@@ -7018,7 +7015,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B91" s="9">
         <v>46169.66973180555</v>
@@ -7055,13 +7052,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O91" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="P91" s="10" t="s">
         <v>302</v>
-      </c>
-      <c r="P91" s="10" t="s">
-        <v>303</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -7071,7 +7068,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B92" s="5">
         <v>46169.66981054399</v>
@@ -7083,7 +7080,7 @@
         <v>46252.61073834491</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7110,13 +7107,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q92" s="5">
         <v>46318</v>
@@ -7136,7 +7133,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B93" s="9">
         <v>46169.66981724537</v>
@@ -7173,13 +7170,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O93" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="P93" s="10" t="s">
         <v>307</v>
-      </c>
-      <c r="P93" s="10" t="s">
-        <v>308</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7189,7 +7186,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B94" s="5">
         <v>46169.669861041664</v>
@@ -7199,7 +7196,7 @@
         <v>46260.58797681713</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7226,13 +7223,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q94" s="5">
         <v>46321</v>
@@ -7252,7 +7249,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B95" s="9">
         <v>46169.66986724537</v>
@@ -7289,13 +7286,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="O95" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7305,7 +7302,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B96" s="5">
         <v>46169.66990296297</v>
@@ -7315,7 +7312,7 @@
         <v>46260.58799998843</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7342,13 +7339,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q96" s="5">
         <v>46323</v>
@@ -7368,7 +7365,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B97" s="9">
         <v>46169.66994555556</v>
@@ -7403,13 +7400,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="O97" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7419,7 +7416,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B98" s="5">
         <v>46169.669978645834</v>
@@ -7429,7 +7426,7 @@
         <v>46252.61088775463</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>25</v>
@@ -7453,7 +7450,7 @@
         <v>26</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>26</v>
@@ -7466,7 +7463,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B99" s="9">
         <v>46169.66998244213</v>
@@ -7478,16 +7475,16 @@
         <v>46252.61081997685</v>
       </c>
       <c r="E99" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="F99" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G99" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="F99" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G99" s="10" t="s">
+      <c r="H99" s="10" t="s">
         <v>323</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>324</v>
       </c>
       <c r="I99" s="9">
         <v>46324</v>
@@ -7505,13 +7502,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q99" s="9">
         <v>46324</v>
@@ -7531,7 +7528,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B100" s="5">
         <v>46169.66998994213</v>
@@ -7547,10 +7544,10 @@
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="H100" s="6" t="s">
         <v>323</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>324</v>
       </c>
       <c r="I100" s="6"/>
       <c r="J100" s="5">
@@ -7566,13 +7563,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7582,7 +7579,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B101" s="9">
         <v>46170.63118891204</v>
@@ -7598,10 +7595,10 @@
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="H101" s="10" t="s">
         <v>323</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>324</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="9">
@@ -7617,7 +7614,7 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O101" s="10" t="s">
         <v>26</v>
@@ -7633,7 +7630,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B102" s="5">
         <v>46174.820955891206</v>
@@ -7649,10 +7646,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="H102" s="6" t="s">
         <v>323</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>324</v>
       </c>
       <c r="I102" s="5">
         <v>46324</v>
@@ -7670,13 +7667,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>64</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7686,7 +7683,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B103" s="9">
         <v>46169.670044224535</v>
@@ -7696,7 +7693,7 @@
         <v>46260.58802633102</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7721,13 +7718,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O103" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q103" s="9">
         <v>46325</v>
@@ -7747,7 +7744,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B104" s="5">
         <v>46169.670049050925</v>
@@ -7782,13 +7779,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7798,7 +7795,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B105" s="9">
         <v>46170.63213679398</v>
@@ -7833,7 +7830,7 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O105" s="10" t="s">
         <v>211</v>
@@ -7849,7 +7846,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B106" s="5">
         <v>46174.82099290509</v>
@@ -7859,7 +7856,7 @@
         <v>46223.5682608912</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7886,7 +7883,7 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>64</v>
@@ -7902,7 +7899,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B107" s="9">
         <v>46169.67013976852</v>
@@ -7914,16 +7911,16 @@
         <v>46252.61090652778</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="H107" s="10" t="s">
         <v>257</v>
-      </c>
-      <c r="H107" s="10" t="s">
-        <v>258</v>
       </c>
       <c r="I107" s="10"/>
       <c r="J107" s="9">
@@ -7939,13 +7936,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O107" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q107" s="9">
         <v>46328</v>
@@ -7965,7 +7962,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B108" s="5">
         <v>46169.670151377315</v>
@@ -7981,10 +7978,10 @@
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="H108" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="I108" s="5">
         <v>46328</v>
@@ -8002,13 +7999,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8018,7 +8015,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B109" s="9">
         <v>46170.63285997685</v>
@@ -8034,10 +8031,10 @@
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="H109" s="10" t="s">
         <v>257</v>
-      </c>
-      <c r="H109" s="10" t="s">
-        <v>258</v>
       </c>
       <c r="I109" s="9">
         <v>46328</v>
@@ -8055,7 +8052,7 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O109" s="10" t="s">
         <v>211</v>
@@ -8071,7 +8068,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B110" s="5">
         <v>46174.821024143515</v>
@@ -8087,10 +8084,10 @@
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="H110" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="I110" s="5">
         <v>46328</v>
@@ -8108,10 +8105,10 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>64</v>
@@ -8124,7 +8121,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B111" s="9">
         <v>46169.67021965278</v>
@@ -8134,16 +8131,16 @@
         <v>46253.62502890047</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="H111" s="10" t="s">
         <v>257</v>
-      </c>
-      <c r="H111" s="10" t="s">
-        <v>258</v>
       </c>
       <c r="I111" s="9">
         <v>46329</v>
@@ -8161,13 +8158,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O111" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Q111" s="9">
         <v>46329</v>
@@ -8187,7 +8184,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B112" s="5">
         <v>46169.67022677083</v>
@@ -8203,10 +8200,10 @@
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="H112" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="I112" s="6"/>
       <c r="J112" s="5">
@@ -8222,13 +8219,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8238,7 +8235,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B113" s="9">
         <v>46170.633581828704</v>
@@ -8254,10 +8251,10 @@
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="H113" s="10" t="s">
         <v>257</v>
-      </c>
-      <c r="H113" s="10" t="s">
-        <v>258</v>
       </c>
       <c r="I113" s="10"/>
       <c r="J113" s="9">
@@ -8273,7 +8270,7 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="O113" s="10" t="s">
         <v>211</v>
@@ -8289,7 +8286,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B114" s="5">
         <v>46174.821057037036</v>
@@ -8305,10 +8302,10 @@
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="H114" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="H114" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="I114" s="6"/>
       <c r="J114" s="5">
@@ -8324,7 +8321,7 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>64</v>
@@ -8340,7 +8337,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B115" s="9">
         <v>46169.67031616898</v>
@@ -8350,7 +8347,7 @@
         <v>46174.82401751158</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>25</v>
@@ -8374,7 +8371,7 @@
         <v>26</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P115" s="10" t="s">
         <v>26</v>
@@ -8387,7 +8384,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B116" s="5">
         <v>46169.67031976852</v>
@@ -8397,16 +8394,16 @@
         <v>46174.84885483797</v>
       </c>
       <c r="E116" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="F116" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G116" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="F116" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G116" s="6" t="s">
+      <c r="H116" s="6" t="s">
         <v>354</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>355</v>
       </c>
       <c r="I116" s="5">
         <v>46330</v>
@@ -8424,13 +8421,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Q116" s="5">
         <v>46330</v>
@@ -8450,7 +8447,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B117" s="9">
         <v>46169.6703253125</v>
@@ -8460,7 +8457,7 @@
         <v>46192.97339644676</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8487,13 +8484,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Q117" s="9">
         <v>46330</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -2383,7 +2383,7 @@
         <v>46212.79376377315</v>
       </c>
       <c r="D14" s="5">
-        <v>46237.54330734954</v>
+        <v>46263.55528422454</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>66</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -5222,7 +5222,7 @@
         <v>46196.87995266204</v>
       </c>
       <c r="D61" s="9">
-        <v>46250.34660050926</v>
+        <v>46264.11255278935</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>97</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1403" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1403" uniqueCount="358">
   <si>
     <t>50001558 -  GESVIAL</t>
   </si>
@@ -851,6 +851,9 @@
   </si>
   <si>
     <t xml:space="preserve">OT2 4307 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6,OT 4075  -ZVRv 1-16-37/6 ,OT 4413  -ZVRv 1-22-185/6  </t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1215174141301410</t>
@@ -5950,7 +5953,7 @@
         <v>46209.90925715277</v>
       </c>
       <c r="D73" s="9">
-        <v>46261.60082807871</v>
+        <v>46265.171999108796</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>255</v>
@@ -5994,8 +5997,8 @@
       <c r="R73" s="9">
         <v>46272</v>
       </c>
-      <c r="S73" s="7" t="s">
-        <v>33</v>
+      <c r="S73" s="11" t="s">
+        <v>259</v>
       </c>
       <c r="T73" s="10">
         <v>1</v>
@@ -6006,7 +6009,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B74" s="5">
         <v>46169.669467280095</v>
@@ -6048,10 +6051,10 @@
         <v>255</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6061,7 +6064,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B75" s="9">
         <v>46169.66950289352</v>
@@ -6071,7 +6074,7 @@
         <v>46260.587916261575</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -6124,7 +6127,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B76" s="5">
         <v>46169.66950758102</v>
@@ -6161,13 +6164,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6177,7 +6180,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B77" s="9">
         <v>46169.66953380787</v>
@@ -6187,7 +6190,7 @@
         <v>46260.587929270834</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6240,7 +6243,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B78" s="5">
         <v>46169.66953854167</v>
@@ -6275,13 +6278,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6291,7 +6294,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B79" s="9">
         <v>46169.66960108797</v>
@@ -6327,7 +6330,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P79" s="10" t="s">
         <v>26</v>
@@ -6344,7 +6347,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B80" s="5">
         <v>46169.66960956018</v>
@@ -6356,7 +6359,7 @@
         <v>46209.844928101855</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6409,7 +6412,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B81" s="9">
         <v>46169.6696165162</v>
@@ -6421,7 +6424,7 @@
         <v>46209.84471936343</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6454,7 +6457,7 @@
         <v>124</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q81" s="9">
         <v>46288</v>
@@ -6474,7 +6477,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B82" s="5">
         <v>46169.669622939815</v>
@@ -6486,7 +6489,7 @@
         <v>46209.85430440972</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6519,7 +6522,7 @@
         <v>142</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q82" s="5">
         <v>46308</v>
@@ -6539,7 +6542,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B83" s="9">
         <v>46169.66962980324</v>
@@ -6551,7 +6554,7 @@
         <v>46239.59650748843</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6584,7 +6587,7 @@
         <v>182</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q83" s="9">
         <v>46287</v>
@@ -6604,7 +6607,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B84" s="5">
         <v>46169.669635185186</v>
@@ -6649,7 +6652,7 @@
         <v>153</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q84" s="5">
         <v>46220</v>
@@ -6669,7 +6672,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B85" s="9">
         <v>46169.66964790509</v>
@@ -6679,7 +6682,7 @@
         <v>46252.61072833333</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>25</v>
@@ -6703,7 +6706,7 @@
         <v>26</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>26</v>
@@ -6716,7 +6719,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B86" s="5">
         <v>46169.66965109954</v>
@@ -6728,7 +6731,7 @@
         <v>46252.61067681713</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6755,13 +6758,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q86" s="5">
         <v>46294</v>
@@ -6781,7 +6784,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B87" s="9">
         <v>46169.6696568287</v>
@@ -6818,13 +6821,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6834,7 +6837,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B88" s="5">
         <v>46169.669688622685</v>
@@ -6846,7 +6849,7 @@
         <v>46250.36067016204</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6873,13 +6876,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q88" s="5">
         <v>46316</v>
@@ -6899,7 +6902,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B89" s="9">
         <v>46169.66969347223</v>
@@ -6934,13 +6937,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6950,7 +6953,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B90" s="5">
         <v>46169.66972681713</v>
@@ -6962,7 +6965,7 @@
         <v>46250.36077557871</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6989,13 +6992,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q90" s="5">
         <v>46317</v>
@@ -7015,7 +7018,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B91" s="9">
         <v>46169.66973180555</v>
@@ -7052,13 +7055,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -7068,7 +7071,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B92" s="5">
         <v>46169.66981054399</v>
@@ -7080,7 +7083,7 @@
         <v>46252.61073834491</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7107,13 +7110,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q92" s="5">
         <v>46318</v>
@@ -7133,7 +7136,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B93" s="9">
         <v>46169.66981724537</v>
@@ -7170,13 +7173,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7186,7 +7189,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B94" s="5">
         <v>46169.669861041664</v>
@@ -7196,7 +7199,7 @@
         <v>46260.58797681713</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7223,13 +7226,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q94" s="5">
         <v>46321</v>
@@ -7249,7 +7252,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B95" s="9">
         <v>46169.66986724537</v>
@@ -7286,13 +7289,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O95" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7302,7 +7305,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B96" s="5">
         <v>46169.66990296297</v>
@@ -7312,7 +7315,7 @@
         <v>46260.58799998843</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7339,13 +7342,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q96" s="5">
         <v>46323</v>
@@ -7365,7 +7368,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B97" s="9">
         <v>46169.66994555556</v>
@@ -7400,13 +7403,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O97" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7416,7 +7419,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B98" s="5">
         <v>46169.669978645834</v>
@@ -7426,7 +7429,7 @@
         <v>46252.61088775463</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>25</v>
@@ -7450,7 +7453,7 @@
         <v>26</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>26</v>
@@ -7463,7 +7466,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B99" s="9">
         <v>46169.66998244213</v>
@@ -7475,16 +7478,16 @@
         <v>46252.61081997685</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I99" s="9">
         <v>46324</v>
@@ -7502,13 +7505,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q99" s="9">
         <v>46324</v>
@@ -7528,7 +7531,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B100" s="5">
         <v>46169.66998994213</v>
@@ -7544,10 +7547,10 @@
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I100" s="6"/>
       <c r="J100" s="5">
@@ -7563,13 +7566,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7579,7 +7582,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B101" s="9">
         <v>46170.63118891204</v>
@@ -7595,10 +7598,10 @@
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="9">
@@ -7614,7 +7617,7 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O101" s="10" t="s">
         <v>26</v>
@@ -7630,7 +7633,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B102" s="5">
         <v>46174.820955891206</v>
@@ -7646,10 +7649,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I102" s="5">
         <v>46324</v>
@@ -7667,13 +7670,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>64</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7683,7 +7686,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B103" s="9">
         <v>46169.670044224535</v>
@@ -7693,7 +7696,7 @@
         <v>46260.58802633102</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7718,13 +7721,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O103" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q103" s="9">
         <v>46325</v>
@@ -7744,7 +7747,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B104" s="5">
         <v>46169.670049050925</v>
@@ -7779,13 +7782,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7795,7 +7798,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B105" s="9">
         <v>46170.63213679398</v>
@@ -7830,7 +7833,7 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O105" s="10" t="s">
         <v>211</v>
@@ -7846,7 +7849,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B106" s="5">
         <v>46174.82099290509</v>
@@ -7856,7 +7859,7 @@
         <v>46223.5682608912</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7883,7 +7886,7 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>64</v>
@@ -7899,7 +7902,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B107" s="9">
         <v>46169.67013976852</v>
@@ -7911,7 +7914,7 @@
         <v>46252.61090652778</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7936,13 +7939,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O107" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q107" s="9">
         <v>46328</v>
@@ -7962,7 +7965,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B108" s="5">
         <v>46169.670151377315</v>
@@ -7999,13 +8002,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8015,7 +8018,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B109" s="9">
         <v>46170.63285997685</v>
@@ -8052,7 +8055,7 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O109" s="10" t="s">
         <v>211</v>
@@ -8068,7 +8071,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B110" s="5">
         <v>46174.821024143515</v>
@@ -8105,10 +8108,10 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>64</v>
@@ -8121,7 +8124,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B111" s="9">
         <v>46169.67021965278</v>
@@ -8131,7 +8134,7 @@
         <v>46253.62502890047</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -8158,13 +8161,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O111" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q111" s="9">
         <v>46329</v>
@@ -8184,7 +8187,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B112" s="5">
         <v>46169.67022677083</v>
@@ -8219,13 +8222,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8235,7 +8238,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B113" s="9">
         <v>46170.633581828704</v>
@@ -8270,7 +8273,7 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O113" s="10" t="s">
         <v>211</v>
@@ -8286,7 +8289,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B114" s="5">
         <v>46174.821057037036</v>
@@ -8321,7 +8324,7 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>64</v>
@@ -8337,7 +8340,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B115" s="9">
         <v>46169.67031616898</v>
@@ -8347,7 +8350,7 @@
         <v>46174.82401751158</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>25</v>
@@ -8371,7 +8374,7 @@
         <v>26</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P115" s="10" t="s">
         <v>26</v>
@@ -8384,7 +8387,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B116" s="5">
         <v>46169.67031976852</v>
@@ -8394,16 +8397,16 @@
         <v>46174.84885483797</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="I116" s="5">
         <v>46330</v>
@@ -8421,13 +8424,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q116" s="5">
         <v>46330</v>
@@ -8447,7 +8450,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B117" s="9">
         <v>46169.6703253125</v>
@@ -8457,7 +8460,7 @@
         <v>46192.97339644676</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8484,13 +8487,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q117" s="9">
         <v>46330</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -5953,7 +5953,7 @@
         <v>46209.90925715277</v>
       </c>
       <c r="D73" s="9">
-        <v>46265.171999108796</v>
+        <v>46271.708096064816</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>255</v>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46260.587916261575</v>
+        <v>46271.70808619213</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>264</v>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46260.587929270834</v>
+        <v>46271.70811479166</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>269</v>

--- a/data/50001558 - GESVIAL OT4342-4344.xlsx
+++ b/data/50001558 - GESVIAL OT4342-4344.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1403" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1403" uniqueCount="357">
   <si>
     <t>50001558 -  GESVIAL</t>
   </si>
@@ -851,9 +851,6 @@
   </si>
   <si>
     <t xml:space="preserve">OT2 4307 ZVN 1-9-86/2 ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6,OT 4075  -ZVRv 1-16-37/6 ,OT 4413  -ZVRv 1-22-185/6  </t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1215174141301410</t>
@@ -5953,7 +5950,7 @@
         <v>46209.90925715277</v>
       </c>
       <c r="D73" s="9">
-        <v>46271.708096064816</v>
+        <v>46273.14227732639</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>255</v>
@@ -5997,8 +5994,8 @@
       <c r="R73" s="9">
         <v>46272</v>
       </c>
-      <c r="S73" s="11" t="s">
-        <v>259</v>
+      <c r="S73" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="T73" s="10">
         <v>1</v>
@@ -6009,7 +6006,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B74" s="5">
         <v>46169.669467280095</v>
@@ -6051,10 +6048,10 @@
         <v>255</v>
       </c>
       <c r="O74" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="P74" s="6" t="s">
         <v>261</v>
-      </c>
-      <c r="P74" s="6" t="s">
-        <v>262</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6064,7 +6061,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B75" s="9">
         <v>46169.66950289352</v>
@@ -6074,7 +6071,7 @@
         <v>46271.70808619213</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -6127,7 +6124,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B76" s="5">
         <v>46169.66950758102</v>
@@ -6164,13 +6161,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O76" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="P76" s="6" t="s">
         <v>266</v>
-      </c>
-      <c r="P76" s="6" t="s">
-        <v>267</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6180,7 +6177,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B77" s="9">
         <v>46169.66953380787</v>
@@ -6190,7 +6187,7 @@
         <v>46271.70811479166</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6243,7 +6240,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B78" s="5">
         <v>46169.66953854167</v>
@@ -6278,13 +6275,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6294,7 +6291,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B79" s="9">
         <v>46169.66960108797</v>
@@ -6330,7 +6327,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P79" s="10" t="s">
         <v>26</v>
@@ -6347,7 +6344,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B80" s="5">
         <v>46169.66960956018</v>
@@ -6359,7 +6356,7 @@
         <v>46209.844928101855</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6412,7 +6409,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B81" s="9">
         <v>46169.6696165162</v>
@@ -6424,7 +6421,7 @@
         <v>46209.84471936343</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6457,7 +6454,7 @@
         <v>124</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q81" s="9">
         <v>46288</v>
@@ -6477,7 +6474,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B82" s="5">
         <v>46169.669622939815</v>
@@ -6489,7 +6486,7 @@
         <v>46209.85430440972</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6522,7 +6519,7 @@
         <v>142</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q82" s="5">
         <v>46308</v>
@@ -6542,7 +6539,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B83" s="9">
         <v>46169.66962980324</v>
@@ -6554,7 +6551,7 @@
         <v>46239.59650748843</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6587,7 +6584,7 @@
         <v>182</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Q83" s="9">
         <v>46287</v>
@@ -6607,7 +6604,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B84" s="5">
         <v>46169.669635185186</v>
@@ -6652,7 +6649,7 @@
         <v>153</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Q84" s="5">
         <v>46220</v>
@@ -6672,7 +6669,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B85" s="9">
         <v>46169.66964790509</v>
@@ -6682,7 +6679,7 @@
         <v>46252.61072833333</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>25</v>
@@ -6706,7 +6703,7 @@
         <v>26</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>26</v>
@@ -6719,7 +6716,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B86" s="5">
         <v>46169.66965109954</v>
@@ -6731,7 +6728,7 @@
         <v>46252.61067681713</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6758,13 +6755,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q86" s="5">
         <v>46294</v>
@@ -6784,7 +6781,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B87" s="9">
         <v>46169.6696568287</v>
@@ -6821,13 +6818,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6837,7 +6834,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B88" s="5">
         <v>46169.669688622685</v>
@@ -6849,7 +6846,7 @@
         <v>46250.36067016204</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6876,13 +6873,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q88" s="5">
         <v>46316</v>
@@ -6902,7 +6899,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B89" s="9">
         <v>46169.66969347223</v>
@@ -6937,13 +6934,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O89" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="P89" s="10" t="s">
         <v>297</v>
-      </c>
-      <c r="P89" s="10" t="s">
-        <v>298</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6953,7 +6950,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B90" s="5">
         <v>46169.66972681713</v>
@@ -6965,7 +6962,7 @@
         <v>46250.36077557871</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6992,13 +6989,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q90" s="5">
         <v>46317</v>
@@ -7018,7 +7015,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B91" s="9">
         <v>46169.66973180555</v>
@@ -7055,13 +7052,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O91" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="P91" s="10" t="s">
         <v>302</v>
-      </c>
-      <c r="P91" s="10" t="s">
-        <v>303</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -7071,7 +7068,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B92" s="5">
         <v>46169.66981054399</v>
@@ -7083,7 +7080,7 @@
         <v>46252.61073834491</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7110,13 +7107,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q92" s="5">
         <v>46318</v>
@@ -7136,7 +7133,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B93" s="9">
         <v>46169.66981724537</v>
@@ -7173,13 +7170,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O93" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="P93" s="10" t="s">
         <v>307</v>
-      </c>
-      <c r="P93" s="10" t="s">
-        <v>308</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7189,7 +7186,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B94" s="5">
         <v>46169.669861041664</v>
@@ -7199,7 +7196,7 @@
         <v>46260.58797681713</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7226,13 +7223,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q94" s="5">
         <v>46321</v>
@@ -7252,7 +7249,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B95" s="9">
         <v>46169.66986724537</v>
@@ -7289,13 +7286,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="O95" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7305,7 +7302,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B96" s="5">
         <v>46169.66990296297</v>
@@ -7315,7 +7312,7 @@
         <v>46260.58799998843</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7342,13 +7339,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q96" s="5">
         <v>46323</v>
@@ -7368,7 +7365,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B97" s="9">
         <v>46169.66994555556</v>
@@ -7403,13 +7400,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="O97" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7419,7 +7416,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B98" s="5">
         <v>46169.669978645834</v>
@@ -7429,7 +7426,7 @@
         <v>46252.61088775463</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>25</v>
@@ -7453,7 +7450,7 @@
         <v>26</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>26</v>
@@ -7466,7 +7463,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B99" s="9">
         <v>46169.66998244213</v>
@@ -7478,16 +7475,16 @@
         <v>46252.61081997685</v>
       </c>
       <c r="E99" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="F99" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G99" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="F99" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G99" s="10" t="s">
+      <c r="H99" s="10" t="s">
         <v>323</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>324</v>
       </c>
       <c r="I99" s="9">
         <v>46324</v>
@@ -7505,13 +7502,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q99" s="9">
         <v>46324</v>
@@ -7531,7 +7528,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B100" s="5">
         <v>46169.66998994213</v>
@@ -7547,10 +7544,10 @@
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="H100" s="6" t="s">
         <v>323</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>324</v>
       </c>
       <c r="I100" s="6"/>
       <c r="J100" s="5">
@@ -7566,13 +7563,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7582,7 +7579,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B101" s="9">
         <v>46170.63118891204</v>
@@ -7598,10 +7595,10 @@
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="H101" s="10" t="s">
         <v>323</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>324</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="9">
@@ -7617,7 +7614,7 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O101" s="10" t="s">
         <v>26</v>
@@ -7633,7 +7630,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B102" s="5">
         <v>46174.820955891206</v>
@@ -7649,10 +7646,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="H102" s="6" t="s">
         <v>323</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>324</v>
       </c>
       <c r="I102" s="5">
         <v>46324</v>
@@ -7670,13 +7667,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>64</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7686,7 +7683,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B103" s="9">
         <v>46169.670044224535</v>
@@ -7696,7 +7693,7 @@
         <v>46260.58802633102</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7721,13 +7718,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O103" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q103" s="9">
         <v>46325</v>
@@ -7747,7 +7744,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B104" s="5">
         <v>46169.670049050925</v>
@@ -7782,13 +7779,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7798,7 +7795,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B105" s="9">
         <v>46170.63213679398</v>
@@ -7833,7 +7830,7 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O105" s="10" t="s">
         <v>211</v>
@@ -7849,7 +7846,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B106" s="5">
         <v>46174.82099290509</v>
@@ -7859,7 +7856,7 @@
         <v>46223.5682608912</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7886,7 +7883,7 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>64</v>
@@ -7902,7 +7899,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B107" s="9">
         <v>46169.67013976852</v>
@@ -7914,7 +7911,7 @@
         <v>46252.61090652778</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7939,13 +7936,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O107" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q107" s="9">
         <v>46328</v>
@@ -7965,7 +7962,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B108" s="5">
         <v>46169.670151377315</v>
@@ -8002,13 +7999,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8018,7 +8015,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B109" s="9">
         <v>46170.63285997685</v>
@@ -8055,7 +8052,7 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O109" s="10" t="s">
         <v>211</v>
@@ -8071,7 +8068,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B110" s="5">
         <v>46174.821024143515</v>
@@ -8108,10 +8105,10 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>64</v>
@@ -8124,7 +8121,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B111" s="9">
         <v>46169.67021965278</v>
@@ -8134,7 +8131,7 @@
         <v>46253.62502890047</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -8161,13 +8158,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O111" s="10" t="s">
         <v>206</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Q111" s="9">
         <v>46329</v>
@@ -8187,7 +8184,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B112" s="5">
         <v>46169.67022677083</v>
@@ -8222,13 +8219,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8238,7 +8235,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B113" s="9">
         <v>46170.633581828704</v>
@@ -8273,7 +8270,7 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="O113" s="10" t="s">
         <v>211</v>
@@ -8289,7 +8286,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B114" s="5">
         <v>46174.821057037036</v>
@@ -8324,7 +8321,7 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>64</v>
@@ -8340,7 +8337,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B115" s="9">
         <v>46169.67031616898</v>
@@ -8350,7 +8347,7 @@
         <v>46174.82401751158</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>25</v>
@@ -8374,7 +8371,7 @@
         <v>26</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P115" s="10" t="s">
         <v>26</v>
@@ -8387,7 +8384,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B116" s="5">
         <v>46169.67031976852</v>
@@ -8397,16 +8394,16 @@
         <v>46174.84885483797</v>
       </c>
       <c r="E116" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="F116" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G116" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="F116" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G116" s="6" t="s">
+      <c r="H116" s="6" t="s">
         <v>354</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>355</v>
       </c>
       <c r="I116" s="5">
         <v>46330</v>
@@ -8424,13 +8421,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Q116" s="5">
         <v>46330</v>
@@ -8450,7 +8447,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B117" s="9">
         <v>46169.6703253125</v>
@@ -8460,7 +8457,7 @@
         <v>46192.97339644676</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8487,13 +8484,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Q117" s="9">
         <v>46330</v>
